--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G11">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G15">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G65">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G71">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G93">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G96">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G104">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G120">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G157">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G159">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G160">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G164">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O168">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="P168">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27738,10 +27738,10 @@
         <v>0</v>
       </c>
       <c r="AC168">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD168">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="O169">
-        <v>4.62</v>
+        <v>4.26</v>
       </c>
       <c r="P169">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AD169">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="O170">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="P170">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD170">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O171">
-        <v>4.26</v>
+        <v>4.62</v>
       </c>
       <c r="P171">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,10 +28227,10 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD171">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AE171">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G188">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G194">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G196">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G206">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G213">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G215">
@@ -35350,7 +35350,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N215">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G217">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G221">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G231">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G233">
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G242">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G244">
@@ -53741,12 +53741,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G329">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G339">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G340">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU380"/>
+  <dimension ref="A1:AU381"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G11">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Shimizu S-Pulse</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shimizu S-Pulse</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G16">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G45">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G82">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G83">
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G161">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G162">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G164">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G195">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G197">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G206">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G211">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G213">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G217">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G222">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G224">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G225">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G230">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,22 +42484,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,22 +42647,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G261">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O261">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P261">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q261">
         <v>0</v>
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O262">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P262">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G265">
@@ -43620,12 +43620,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G266">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>2026-10-31 13:15:00</t>
+          <t>2026-10-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O267">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P267">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-10-31 13:30:00</t>
+          <t>2026-10-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G269">
@@ -44277,22 +44277,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,22 +44440,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G272">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G275">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G277">
@@ -45576,12 +45576,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G278">
@@ -45619,7 +45619,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N278">
@@ -45727,7 +45727,7 @@
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>2026-10-31 13:45:00</t>
+          <t>2026-10-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G279">
@@ -45782,7 +45782,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G280">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G281">
@@ -46112,13 +46112,13 @@
         </is>
       </c>
       <c r="N281">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O281">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P281">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q281">
         <v>0</v>
@@ -46228,12 +46228,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O282">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P282">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46379,7 +46379,7 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>2026-10-31 14:00:00</t>
+          <t>2026-10-31 13:45:00</t>
         </is>
       </c>
     </row>
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G283">
@@ -46559,7 +46559,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,22 +47048,22 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,22 +47211,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G288">
@@ -47253,13 +47253,13 @@
         </is>
       </c>
       <c r="N288">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O288">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P288">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q288">
         <v>0</v>
@@ -47292,10 +47292,10 @@
         <v>0</v>
       </c>
       <c r="AA288">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB288">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC288">
         <v>0</v>
@@ -47374,7 +47374,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -47384,12 +47384,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47455,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AA289">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB289">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC289">
         <v>0</v>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G290">
@@ -47700,22 +47700,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,7 +48026,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -48036,12 +48036,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G293">
@@ -48068,13 +48068,13 @@
         </is>
       </c>
       <c r="N293">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O293">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P293">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q293">
         <v>0</v>
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O294">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P294">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G295">
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G296">
@@ -48673,12 +48673,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G297">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>2026-10-31 14:15:00</t>
+          <t>2026-10-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G298">
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O298">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P298">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q298">
         <v>0</v>
@@ -48922,10 +48922,10 @@
         <v>0</v>
       </c>
       <c r="AA298">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB298">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC298">
         <v>0</v>
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-31 14:30:00</t>
+          <t>2026-10-31 14:15:00</t>
         </is>
       </c>
     </row>
@@ -49004,7 +49004,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G300">
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G301">
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O304">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P304">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49912,7 +49912,7 @@
         <v>0</v>
       </c>
       <c r="AE304">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF304">
         <v>0</v>
@@ -49977,12 +49977,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50075,7 +50075,7 @@
         <v>0</v>
       </c>
       <c r="AE305">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF305">
         <v>0</v>
@@ -50128,7 +50128,7 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>2026-10-31 14:45:00</t>
+          <t>2026-10-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O306">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P306">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="O307">
-        <v>18.5</v>
+        <v>4.23</v>
       </c>
       <c r="P307">
-        <v>38</v>
+        <v>3.71</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50401,7 +50401,7 @@
         <v>0</v>
       </c>
       <c r="AE307">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF307">
         <v>0</v>
@@ -50466,27 +50466,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O308">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="P308">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50564,7 +50564,7 @@
         <v>0</v>
       </c>
       <c r="AE308">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF308">
         <v>0</v>
@@ -50617,7 +50617,7 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>2026-10-31 15:00:00</t>
+          <t>2026-10-31 14:45:00</t>
         </is>
       </c>
     </row>
@@ -50634,22 +50634,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G309">
@@ -50797,7 +50797,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G310">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G311">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G312">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G313">
@@ -51449,7 +51449,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G314">
@@ -51612,22 +51612,22 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G315">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G317">
@@ -52101,22 +52101,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G318">
@@ -52259,12 +52259,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G319">
@@ -52410,7 +52410,7 @@
       </c>
       <c r="AU319" t="inlineStr">
         <is>
-          <t>2026-10-31 15:15:00</t>
+          <t>2026-10-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G320">
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-10-31 15:30:00</t>
+          <t>2026-10-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -52753,7 +52753,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,13 +52795,13 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O322">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P322">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q322">
         <v>0</v>
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-10-31 15:45:00</t>
+          <t>2026-10-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -53074,27 +53074,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O324">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P324">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53160,10 +53160,10 @@
         <v>0</v>
       </c>
       <c r="AA324">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB324">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC324">
         <v>0</v>
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-10-31 16:00:00</t>
+          <t>2026-10-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -53242,22 +53242,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P325">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53323,10 +53323,10 @@
         <v>0</v>
       </c>
       <c r="AA325">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB325">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC325">
         <v>0</v>
@@ -53405,22 +53405,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G326">
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G327">
@@ -53731,22 +53731,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G328">
@@ -53904,12 +53904,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G329">
@@ -54057,22 +54057,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G330">
@@ -54220,22 +54220,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G331">
@@ -54378,27 +54378,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G332">
@@ -54529,7 +54529,7 @@
       </c>
       <c r="AU332" t="inlineStr">
         <is>
-          <t>2026-10-31 16:15:00</t>
+          <t>2026-10-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -54541,12 +54541,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -54556,12 +54556,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-10-31 16:30:00</t>
+          <t>2026-10-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -54709,7 +54709,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G334">
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O335">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P335">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -54953,10 +54953,10 @@
         <v>0</v>
       </c>
       <c r="AA335">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB335">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC335">
         <v>0</v>
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-10-31 16:45:00</t>
+          <t>2026-10-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="O336">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="P336">
-        <v>2.52</v>
+        <v>3.39</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55116,10 +55116,10 @@
         <v>0</v>
       </c>
       <c r="AA336">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB336">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC336">
         <v>0</v>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.44</v>
+        <v>2.93</v>
       </c>
       <c r="O337">
-        <v>5.24</v>
+        <v>3.62</v>
       </c>
       <c r="P337">
-        <v>7.7</v>
+        <v>2.52</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55279,10 +55279,10 @@
         <v>0</v>
       </c>
       <c r="AA337">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB337">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC337">
         <v>0</v>
@@ -55361,7 +55361,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O338">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P338">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G339">
@@ -55845,12 +55845,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O341">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P341">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q341">
         <v>0</v>
@@ -55931,10 +55931,10 @@
         <v>0</v>
       </c>
       <c r="AA341">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB341">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC341">
         <v>0</v>
@@ -55996,7 +55996,7 @@
       </c>
       <c r="AU341" t="inlineStr">
         <is>
-          <t>2026-10-31 17:00:00</t>
+          <t>2026-10-31 16:45:00</t>
         </is>
       </c>
     </row>
@@ -56013,7 +56013,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O342">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P342">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56094,10 +56094,10 @@
         <v>0</v>
       </c>
       <c r="AA342">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB342">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC342">
         <v>0</v>
@@ -56176,7 +56176,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G343">
@@ -56339,7 +56339,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G344">
@@ -56502,7 +56502,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O345">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P345">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="O346">
-        <v>4.23</v>
+        <v>4.05</v>
       </c>
       <c r="P346">
-        <v>3.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56823,27 +56823,27 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O347">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P347">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -56974,7 +56974,7 @@
       </c>
       <c r="AU347" t="inlineStr">
         <is>
-          <t>2026-10-31 17:30:00</t>
+          <t>2026-10-31 17:00:00</t>
         </is>
       </c>
     </row>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G348">
@@ -57154,22 +57154,22 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G349">
@@ -57312,27 +57312,27 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G350">
@@ -57463,7 +57463,7 @@
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>2026-10-31 18:00:00</t>
+          <t>2026-10-31 17:30:00</t>
         </is>
       </c>
     </row>
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G351">
@@ -57643,7 +57643,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G352">
@@ -57801,12 +57801,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G353">
@@ -57952,7 +57952,7 @@
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>2026-10-31 18:15:00</t>
+          <t>2026-10-31 18:00:00</t>
         </is>
       </c>
     </row>
@@ -57964,12 +57964,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G354">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>2026-10-31 19:30:00</t>
+          <t>2026-10-31 18:15:00</t>
         </is>
       </c>
     </row>
@@ -58127,12 +58127,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G355">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-31 20:00:00</t>
+          <t>2026-10-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -58290,27 +58290,27 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-10-31 21:00:00</t>
+          <t>2026-10-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -58458,7 +58458,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G357">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G360">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G363">
@@ -59599,22 +59599,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G368">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G369">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G370">
@@ -60903,22 +60903,22 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G372">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G373">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G374">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G375">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G376">
@@ -61728,12 +61728,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G377">
@@ -61891,12 +61891,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G378">
@@ -62054,12 +62054,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G379">
@@ -62202,156 +62202,319 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Bor</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="G380">
+        <v>0</v>
+      </c>
+      <c r="H380">
+        <v>0</v>
+      </c>
+      <c r="I380">
+        <v>0</v>
+      </c>
+      <c r="J380">
+        <v>0</v>
+      </c>
+      <c r="K380">
+        <v>0</v>
+      </c>
+      <c r="L380">
+        <v>0</v>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N380">
+        <v>0</v>
+      </c>
+      <c r="O380">
+        <v>0</v>
+      </c>
+      <c r="P380">
+        <v>0</v>
+      </c>
+      <c r="Q380">
+        <v>0</v>
+      </c>
+      <c r="R380">
+        <v>0</v>
+      </c>
+      <c r="S380">
+        <v>0</v>
+      </c>
+      <c r="T380">
+        <v>0</v>
+      </c>
+      <c r="U380">
+        <v>0</v>
+      </c>
+      <c r="V380">
+        <v>0</v>
+      </c>
+      <c r="W380">
+        <v>0</v>
+      </c>
+      <c r="X380">
+        <v>0</v>
+      </c>
+      <c r="Y380">
+        <v>0</v>
+      </c>
+      <c r="Z380">
+        <v>0</v>
+      </c>
+      <c r="AA380">
+        <v>0</v>
+      </c>
+      <c r="AB380">
+        <v>0</v>
+      </c>
+      <c r="AC380">
+        <v>0</v>
+      </c>
+      <c r="AD380">
+        <v>0</v>
+      </c>
+      <c r="AE380">
+        <v>0</v>
+      </c>
+      <c r="AF380">
+        <v>0</v>
+      </c>
+      <c r="AG380">
+        <v>0</v>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ380">
+        <v>0</v>
+      </c>
+      <c r="AK380">
+        <v>0</v>
+      </c>
+      <c r="AL380">
+        <v>0</v>
+      </c>
+      <c r="AM380">
+        <v>-1</v>
+      </c>
+      <c r="AN380">
+        <v>-1</v>
+      </c>
+      <c r="AO380">
+        <v>-1</v>
+      </c>
+      <c r="AP380">
+        <v>-1</v>
+      </c>
+      <c r="AQ380">
+        <v>0</v>
+      </c>
+      <c r="AR380">
+        <v>0</v>
+      </c>
+      <c r="AS380">
+        <v>0</v>
+      </c>
+      <c r="AT380">
+        <v>0</v>
+      </c>
+      <c r="AU380" t="inlineStr">
+        <is>
+          <t>2026-10-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
+      <c r="C381" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D381" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
+      <c r="E381" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
         </is>
       </c>
-      <c r="F380" t="inlineStr">
+      <c r="F381" t="inlineStr">
         <is>
           <t>Chicago Fire</t>
         </is>
       </c>
-      <c r="G380">
-        <v>0</v>
-      </c>
-      <c r="H380">
-        <v>0</v>
-      </c>
-      <c r="I380">
-        <v>0</v>
-      </c>
-      <c r="J380">
-        <v>0</v>
-      </c>
-      <c r="K380">
-        <v>0</v>
-      </c>
-      <c r="L380">
-        <v>0</v>
-      </c>
-      <c r="M380" t="inlineStr">
+      <c r="G381">
+        <v>0</v>
+      </c>
+      <c r="H381">
+        <v>0</v>
+      </c>
+      <c r="I381">
+        <v>0</v>
+      </c>
+      <c r="J381">
+        <v>0</v>
+      </c>
+      <c r="K381">
+        <v>0</v>
+      </c>
+      <c r="L381">
+        <v>0</v>
+      </c>
+      <c r="M381" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N380">
-        <v>0</v>
-      </c>
-      <c r="O380">
-        <v>0</v>
-      </c>
-      <c r="P380">
-        <v>0</v>
-      </c>
-      <c r="Q380">
-        <v>0</v>
-      </c>
-      <c r="R380">
-        <v>0</v>
-      </c>
-      <c r="S380">
-        <v>0</v>
-      </c>
-      <c r="T380">
-        <v>0</v>
-      </c>
-      <c r="U380">
-        <v>0</v>
-      </c>
-      <c r="V380">
-        <v>0</v>
-      </c>
-      <c r="W380">
-        <v>0</v>
-      </c>
-      <c r="X380">
-        <v>0</v>
-      </c>
-      <c r="Y380">
-        <v>0</v>
-      </c>
-      <c r="Z380">
-        <v>0</v>
-      </c>
-      <c r="AA380">
-        <v>0</v>
-      </c>
-      <c r="AB380">
-        <v>0</v>
-      </c>
-      <c r="AC380">
-        <v>0</v>
-      </c>
-      <c r="AD380">
-        <v>0</v>
-      </c>
-      <c r="AE380">
-        <v>0</v>
-      </c>
-      <c r="AF380">
-        <v>0</v>
-      </c>
-      <c r="AG380">
-        <v>0</v>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ380">
-        <v>0</v>
-      </c>
-      <c r="AK380">
-        <v>0</v>
-      </c>
-      <c r="AL380">
-        <v>0</v>
-      </c>
-      <c r="AM380">
-        <v>-1</v>
-      </c>
-      <c r="AN380">
-        <v>-1</v>
-      </c>
-      <c r="AO380">
-        <v>-1</v>
-      </c>
-      <c r="AP380">
-        <v>-1</v>
-      </c>
-      <c r="AQ380">
-        <v>0</v>
-      </c>
-      <c r="AR380">
-        <v>0</v>
-      </c>
-      <c r="AS380">
-        <v>0</v>
-      </c>
-      <c r="AT380">
-        <v>0</v>
-      </c>
-      <c r="AU380" t="inlineStr">
+      <c r="N381">
+        <v>0</v>
+      </c>
+      <c r="O381">
+        <v>0</v>
+      </c>
+      <c r="P381">
+        <v>0</v>
+      </c>
+      <c r="Q381">
+        <v>0</v>
+      </c>
+      <c r="R381">
+        <v>0</v>
+      </c>
+      <c r="S381">
+        <v>0</v>
+      </c>
+      <c r="T381">
+        <v>0</v>
+      </c>
+      <c r="U381">
+        <v>0</v>
+      </c>
+      <c r="V381">
+        <v>0</v>
+      </c>
+      <c r="W381">
+        <v>0</v>
+      </c>
+      <c r="X381">
+        <v>0</v>
+      </c>
+      <c r="Y381">
+        <v>0</v>
+      </c>
+      <c r="Z381">
+        <v>0</v>
+      </c>
+      <c r="AA381">
+        <v>0</v>
+      </c>
+      <c r="AB381">
+        <v>0</v>
+      </c>
+      <c r="AC381">
+        <v>0</v>
+      </c>
+      <c r="AD381">
+        <v>0</v>
+      </c>
+      <c r="AE381">
+        <v>0</v>
+      </c>
+      <c r="AF381">
+        <v>0</v>
+      </c>
+      <c r="AG381">
+        <v>0</v>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ381">
+        <v>0</v>
+      </c>
+      <c r="AK381">
+        <v>0</v>
+      </c>
+      <c r="AL381">
+        <v>0</v>
+      </c>
+      <c r="AM381">
+        <v>-1</v>
+      </c>
+      <c r="AN381">
+        <v>-1</v>
+      </c>
+      <c r="AO381">
+        <v>-1</v>
+      </c>
+      <c r="AP381">
+        <v>-1</v>
+      </c>
+      <c r="AQ381">
+        <v>0</v>
+      </c>
+      <c r="AR381">
+        <v>0</v>
+      </c>
+      <c r="AS381">
+        <v>0</v>
+      </c>
+      <c r="AT381">
+        <v>0</v>
+      </c>
+      <c r="AU381" t="inlineStr">
         <is>
           <t>2026-10-31 22:30:00</t>
         </is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G11">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G34">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Altay</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Altay</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G45">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G71">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G96">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G104">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G120">
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G158">
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G159">
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G187">
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G188">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G197">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G215">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G217">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G222">
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G226">
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G227">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G228">
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G229">
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G230">
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G231">
@@ -39886,12 +39886,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G244">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G28">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G34">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="G42">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G45">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G59">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G73">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC86">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G104">
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G163">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G164">
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="O168">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="P168">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27738,10 +27738,10 @@
         <v>0</v>
       </c>
       <c r="AC168">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD168">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AE168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O169">
-        <v>4.26</v>
+        <v>4.62</v>
       </c>
       <c r="P169">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD169">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="O170">
-        <v>4.07</v>
+        <v>4.21</v>
       </c>
       <c r="P170">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AD170">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="O171">
-        <v>4.62</v>
+        <v>4.26</v>
       </c>
       <c r="P171">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,10 +28227,10 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AD171">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AE171">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G180">
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G181">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G182">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G189">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G190">
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G191">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G192">
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G194">
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G195">
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G197">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G215">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G217">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G318">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G363">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G364">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G368">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G369">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G370">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G372">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G20">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G27">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G45">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11601,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11764,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>6.03</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11927,10 +11927,10 @@
         <v>0</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE71">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O161">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P161">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O162">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P162">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O163">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P163">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O164">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P164">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.81</v>
+        <v>3.04</v>
       </c>
       <c r="O169">
-        <v>4.62</v>
+        <v>4.21</v>
       </c>
       <c r="P169">
-        <v>4.07</v>
+        <v>2.23</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AD169">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>3.04</v>
+        <v>1.91</v>
       </c>
       <c r="O170">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
       <c r="P170">
-        <v>2.23</v>
+        <v>3.9</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD170">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O171">
-        <v>4.26</v>
+        <v>4.62</v>
       </c>
       <c r="P171">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,10 +28227,10 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD171">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AE171">
         <v>0</v>
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O189">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P189">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O192">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G193">
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O194">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P194">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O195">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P195">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O196">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O197">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G214">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O215">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P215">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35393,10 +35393,10 @@
         <v>0</v>
       </c>
       <c r="AA215">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB215">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G216">
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O217">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P217">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35719,16 +35719,16 @@
         <v>0</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC217">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD217">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE217">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G222">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G233">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O237">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P237">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,22 +42647,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -42983,12 +42983,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G262">
@@ -43015,13 +43015,13 @@
         </is>
       </c>
       <c r="N262">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O262">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P262">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O263">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P263">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G264">
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G265">
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G266">
@@ -43783,12 +43783,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G267">
@@ -43934,7 +43934,7 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>2026-10-31 13:15:00</t>
+          <t>2026-10-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O268">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P268">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O269">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P269">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-10-31 13:30:00</t>
+          <t>2026-10-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G270">
@@ -44440,22 +44440,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -44776,12 +44776,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G273">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G274">
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G276">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G278">
@@ -45739,12 +45739,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G279">
@@ -45782,7 +45782,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N279">
@@ -45890,7 +45890,7 @@
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>2026-10-31 13:45:00</t>
+          <t>2026-10-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G280">
@@ -45945,7 +45945,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N280">
@@ -46070,7 +46070,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G281">
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G282">
@@ -46275,13 +46275,13 @@
         </is>
       </c>
       <c r="N282">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O282">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P282">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q282">
         <v>0</v>
@@ -46391,12 +46391,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O283">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P283">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46542,7 +46542,7 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>2026-10-31 14:00:00</t>
+          <t>2026-10-31 13:45:00</t>
         </is>
       </c>
     </row>
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G284">
@@ -46722,7 +46722,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G285">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G286">
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,22 +47211,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G288">
@@ -47374,22 +47374,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O289">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P289">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47455,10 +47455,10 @@
         <v>0</v>
       </c>
       <c r="AA289">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB289">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC289">
         <v>0</v>
@@ -47537,7 +47537,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -47547,12 +47547,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O290">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P290">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47618,10 +47618,10 @@
         <v>0</v>
       </c>
       <c r="AA290">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB290">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC290">
         <v>0</v>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G291">
@@ -47863,22 +47863,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -48199,12 +48199,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G294">
@@ -48231,13 +48231,13 @@
         </is>
       </c>
       <c r="N294">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O294">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P294">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O295">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P295">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G296">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G297">
@@ -48836,12 +48836,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G298">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>2026-10-31 14:15:00</t>
+          <t>2026-10-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O299">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P299">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB299">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-31 14:30:00</t>
+          <t>2026-10-31 14:15:00</t>
         </is>
       </c>
     </row>
@@ -49167,7 +49167,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O300">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P300">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB300">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G301">
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G304">
@@ -49982,7 +49982,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O305">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P305">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50075,7 +50075,7 @@
         <v>0</v>
       </c>
       <c r="AE305">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF305">
         <v>0</v>
@@ -50140,12 +50140,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O306">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P306">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50238,7 +50238,7 @@
         <v>0</v>
       </c>
       <c r="AE306">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF306">
         <v>0</v>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>2026-10-31 14:45:00</t>
+          <t>2026-10-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -50308,7 +50308,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O307">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P307">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="O308">
-        <v>18.5</v>
+        <v>4.23</v>
       </c>
       <c r="P308">
-        <v>38</v>
+        <v>3.71</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50564,7 +50564,7 @@
         <v>0</v>
       </c>
       <c r="AE308">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF308">
         <v>0</v>
@@ -50629,27 +50629,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O309">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="P309">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50727,7 +50727,7 @@
         <v>0</v>
       </c>
       <c r="AE309">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF309">
         <v>0</v>
@@ -50780,7 +50780,7 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>2026-10-31 15:00:00</t>
+          <t>2026-10-31 14:45:00</t>
         </is>
       </c>
     </row>
@@ -50797,22 +50797,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G310">
@@ -50960,7 +50960,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G311">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G312">
@@ -51286,7 +51286,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G313">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G314">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G315">
@@ -51775,22 +51775,22 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G316">
@@ -51948,12 +51948,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G318">
@@ -52264,22 +52264,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G319">
@@ -52422,12 +52422,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G320">
@@ -52573,7 +52573,7 @@
       </c>
       <c r="AU320" t="inlineStr">
         <is>
-          <t>2026-10-31 15:15:00</t>
+          <t>2026-10-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -52748,12 +52748,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G322">
@@ -52899,7 +52899,7 @@
       </c>
       <c r="AU322" t="inlineStr">
         <is>
-          <t>2026-10-31 15:30:00</t>
+          <t>2026-10-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -52916,7 +52916,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="O323">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P323">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53074,12 +53074,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O324">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P324">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53225,7 +53225,7 @@
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>2026-10-31 15:45:00</t>
+          <t>2026-10-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -53237,27 +53237,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O325">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P325">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53323,10 +53323,10 @@
         <v>0</v>
       </c>
       <c r="AA325">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB325">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC325">
         <v>0</v>
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-10-31 16:00:00</t>
+          <t>2026-10-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -53405,22 +53405,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O326">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53486,10 +53486,10 @@
         <v>0</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC326">
         <v>0</v>
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G327">
@@ -53731,22 +53731,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G328">
@@ -53894,22 +53894,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G329">
@@ -54067,12 +54067,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G330">
@@ -54220,22 +54220,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G331">
@@ -54383,22 +54383,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G332">
@@ -54541,27 +54541,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G333">
@@ -54692,7 +54692,7 @@
       </c>
       <c r="AU333" t="inlineStr">
         <is>
-          <t>2026-10-31 16:15:00</t>
+          <t>2026-10-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -54704,12 +54704,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -54719,12 +54719,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G334">
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-10-31 16:30:00</t>
+          <t>2026-10-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -54872,7 +54872,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G335">
@@ -55030,12 +55030,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O336">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="P336">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55116,10 +55116,10 @@
         <v>0</v>
       </c>
       <c r="AA336">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB336">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC336">
         <v>0</v>
@@ -55181,7 +55181,7 @@
       </c>
       <c r="AU336" t="inlineStr">
         <is>
-          <t>2026-10-31 16:45:00</t>
+          <t>2026-10-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="O337">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="P337">
-        <v>2.52</v>
+        <v>3.39</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55279,10 +55279,10 @@
         <v>0</v>
       </c>
       <c r="AA337">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB337">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC337">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.44</v>
+        <v>2.93</v>
       </c>
       <c r="O338">
-        <v>5.24</v>
+        <v>3.62</v>
       </c>
       <c r="P338">
-        <v>7.7</v>
+        <v>2.52</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55442,10 +55442,10 @@
         <v>0</v>
       </c>
       <c r="AA338">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB338">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC338">
         <v>0</v>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O339">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P339">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55687,7 +55687,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G340">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G341">
@@ -56008,12 +56008,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O342">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P342">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56094,10 +56094,10 @@
         <v>0</v>
       </c>
       <c r="AA342">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB342">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC342">
         <v>0</v>
@@ -56159,7 +56159,7 @@
       </c>
       <c r="AU342" t="inlineStr">
         <is>
-          <t>2026-10-31 17:00:00</t>
+          <t>2026-10-31 16:45:00</t>
         </is>
       </c>
     </row>
@@ -56176,7 +56176,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O343">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P343">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56257,10 +56257,10 @@
         <v>0</v>
       </c>
       <c r="AA343">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB343">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC343">
         <v>0</v>
@@ -56339,7 +56339,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G344">
@@ -56502,7 +56502,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G345">
@@ -56665,7 +56665,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G346">
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O346">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P346">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q346">
         <v>0</v>
@@ -56986,27 +56986,27 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O348">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P348">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57137,7 +57137,7 @@
       </c>
       <c r="AU348" t="inlineStr">
         <is>
-          <t>2026-10-31 17:30:00</t>
+          <t>2026-10-31 17:00:00</t>
         </is>
       </c>
     </row>
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G349">
@@ -57317,22 +57317,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G350">
@@ -57475,27 +57475,27 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G351">
@@ -57626,7 +57626,7 @@
       </c>
       <c r="AU351" t="inlineStr">
         <is>
-          <t>2026-10-31 18:00:00</t>
+          <t>2026-10-31 17:30:00</t>
         </is>
       </c>
     </row>
@@ -57806,7 +57806,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G353">
@@ -57964,12 +57964,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G354">
@@ -58115,7 +58115,7 @@
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>2026-10-31 18:15:00</t>
+          <t>2026-10-31 18:00:00</t>
         </is>
       </c>
     </row>
@@ -58127,12 +58127,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G355">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-31 19:30:00</t>
+          <t>2026-10-31 18:15:00</t>
         </is>
       </c>
     </row>
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-10-31 20:00:00</t>
+          <t>2026-10-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -58453,27 +58453,27 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-10-31 21:00:00</t>
+          <t>2026-10-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G358">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G360">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G363">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G368">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G369">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G370">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G372">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G28">
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="O177">
-        <v>3.89</v>
+        <v>3.62</v>
       </c>
       <c r="P177">
-        <v>3.65</v>
+        <v>2.71</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,10 +29199,10 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AB177">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="O178">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="P178">
-        <v>2.71</v>
+        <v>3.65</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AB178">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O181">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P181">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O182">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P182">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O202">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P202">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G233">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O289">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P289">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Q289">
         <v>0</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU381"/>
+  <dimension ref="A1:AU377"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="O81">
         <v>3.54</v>
       </c>
       <c r="P81">
-        <v>4.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O159">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P159">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O166">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P166">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O172">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P172">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O179">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P179">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O180">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P180">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O184">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O185">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB185">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O190">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P190">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB190">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O191">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB191">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O193">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G213">
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G214">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O216">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P216">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O224">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P224">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O225">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P225">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O226">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="P226">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O227">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P227">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O228">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P228">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O229">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P229">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O230">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P230">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O231">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P231">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38001,10 +38001,10 @@
         <v>0</v>
       </c>
       <c r="AA231">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB231">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC231">
         <v>0</v>
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O238">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P238">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB238">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O245">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P245">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB245">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O268">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P268">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O273">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P273">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O285">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P285">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O304">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P304">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O305">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P305">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O314">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P314">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54425,13 +54425,13 @@
         </is>
       </c>
       <c r="N332">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q332">
         <v>0</v>
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O334">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P334">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O336">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P336">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55122,10 +55122,10 @@
         <v>0</v>
       </c>
       <c r="AC336">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD336">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE336">
         <v>0</v>
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O341">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="P341">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q341">
         <v>0</v>
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="O342">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="P342">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O344">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P344">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G360">
@@ -59110,22 +59110,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G361">
@@ -59273,22 +59273,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G362">
@@ -59436,22 +59436,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G363">
@@ -59599,22 +59599,22 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G368">
@@ -60414,22 +60414,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G369">
@@ -60577,22 +60577,22 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G370">
@@ -60740,22 +60740,22 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G371">
@@ -60903,22 +60903,22 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G372">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G373">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G374">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G375">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G376">
@@ -61713,27 +61713,27 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G377">
@@ -61863,658 +61863,6 @@
         <v>0</v>
       </c>
       <c r="AU377" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="G378">
-        <v>0</v>
-      </c>
-      <c r="H378">
-        <v>0</v>
-      </c>
-      <c r="I378">
-        <v>0</v>
-      </c>
-      <c r="J378">
-        <v>0</v>
-      </c>
-      <c r="K378">
-        <v>0</v>
-      </c>
-      <c r="L378">
-        <v>0</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N378">
-        <v>0</v>
-      </c>
-      <c r="O378">
-        <v>0</v>
-      </c>
-      <c r="P378">
-        <v>0</v>
-      </c>
-      <c r="Q378">
-        <v>0</v>
-      </c>
-      <c r="R378">
-        <v>0</v>
-      </c>
-      <c r="S378">
-        <v>0</v>
-      </c>
-      <c r="T378">
-        <v>0</v>
-      </c>
-      <c r="U378">
-        <v>0</v>
-      </c>
-      <c r="V378">
-        <v>0</v>
-      </c>
-      <c r="W378">
-        <v>0</v>
-      </c>
-      <c r="X378">
-        <v>0</v>
-      </c>
-      <c r="Y378">
-        <v>0</v>
-      </c>
-      <c r="Z378">
-        <v>0</v>
-      </c>
-      <c r="AA378">
-        <v>0</v>
-      </c>
-      <c r="AB378">
-        <v>0</v>
-      </c>
-      <c r="AC378">
-        <v>0</v>
-      </c>
-      <c r="AD378">
-        <v>0</v>
-      </c>
-      <c r="AE378">
-        <v>0</v>
-      </c>
-      <c r="AF378">
-        <v>0</v>
-      </c>
-      <c r="AG378">
-        <v>0</v>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ378">
-        <v>0</v>
-      </c>
-      <c r="AK378">
-        <v>0</v>
-      </c>
-      <c r="AL378">
-        <v>0</v>
-      </c>
-      <c r="AM378">
-        <v>-1</v>
-      </c>
-      <c r="AN378">
-        <v>-1</v>
-      </c>
-      <c r="AO378">
-        <v>-1</v>
-      </c>
-      <c r="AP378">
-        <v>-1</v>
-      </c>
-      <c r="AQ378">
-        <v>0</v>
-      </c>
-      <c r="AR378">
-        <v>0</v>
-      </c>
-      <c r="AS378">
-        <v>0</v>
-      </c>
-      <c r="AT378">
-        <v>0</v>
-      </c>
-      <c r="AU378" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G379">
-        <v>0</v>
-      </c>
-      <c r="H379">
-        <v>0</v>
-      </c>
-      <c r="I379">
-        <v>0</v>
-      </c>
-      <c r="J379">
-        <v>0</v>
-      </c>
-      <c r="K379">
-        <v>0</v>
-      </c>
-      <c r="L379">
-        <v>0</v>
-      </c>
-      <c r="M379" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N379">
-        <v>0</v>
-      </c>
-      <c r="O379">
-        <v>0</v>
-      </c>
-      <c r="P379">
-        <v>0</v>
-      </c>
-      <c r="Q379">
-        <v>0</v>
-      </c>
-      <c r="R379">
-        <v>0</v>
-      </c>
-      <c r="S379">
-        <v>0</v>
-      </c>
-      <c r="T379">
-        <v>0</v>
-      </c>
-      <c r="U379">
-        <v>0</v>
-      </c>
-      <c r="V379">
-        <v>0</v>
-      </c>
-      <c r="W379">
-        <v>0</v>
-      </c>
-      <c r="X379">
-        <v>0</v>
-      </c>
-      <c r="Y379">
-        <v>0</v>
-      </c>
-      <c r="Z379">
-        <v>0</v>
-      </c>
-      <c r="AA379">
-        <v>0</v>
-      </c>
-      <c r="AB379">
-        <v>0</v>
-      </c>
-      <c r="AC379">
-        <v>0</v>
-      </c>
-      <c r="AD379">
-        <v>0</v>
-      </c>
-      <c r="AE379">
-        <v>0</v>
-      </c>
-      <c r="AF379">
-        <v>0</v>
-      </c>
-      <c r="AG379">
-        <v>0</v>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ379">
-        <v>0</v>
-      </c>
-      <c r="AK379">
-        <v>0</v>
-      </c>
-      <c r="AL379">
-        <v>0</v>
-      </c>
-      <c r="AM379">
-        <v>-1</v>
-      </c>
-      <c r="AN379">
-        <v>-1</v>
-      </c>
-      <c r="AO379">
-        <v>-1</v>
-      </c>
-      <c r="AP379">
-        <v>-1</v>
-      </c>
-      <c r="AQ379">
-        <v>0</v>
-      </c>
-      <c r="AR379">
-        <v>0</v>
-      </c>
-      <c r="AS379">
-        <v>0</v>
-      </c>
-      <c r="AT379">
-        <v>0</v>
-      </c>
-      <c r="AU379" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G380">
-        <v>0</v>
-      </c>
-      <c r="H380">
-        <v>0</v>
-      </c>
-      <c r="I380">
-        <v>0</v>
-      </c>
-      <c r="J380">
-        <v>0</v>
-      </c>
-      <c r="K380">
-        <v>0</v>
-      </c>
-      <c r="L380">
-        <v>0</v>
-      </c>
-      <c r="M380" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N380">
-        <v>0</v>
-      </c>
-      <c r="O380">
-        <v>0</v>
-      </c>
-      <c r="P380">
-        <v>0</v>
-      </c>
-      <c r="Q380">
-        <v>0</v>
-      </c>
-      <c r="R380">
-        <v>0</v>
-      </c>
-      <c r="S380">
-        <v>0</v>
-      </c>
-      <c r="T380">
-        <v>0</v>
-      </c>
-      <c r="U380">
-        <v>0</v>
-      </c>
-      <c r="V380">
-        <v>0</v>
-      </c>
-      <c r="W380">
-        <v>0</v>
-      </c>
-      <c r="X380">
-        <v>0</v>
-      </c>
-      <c r="Y380">
-        <v>0</v>
-      </c>
-      <c r="Z380">
-        <v>0</v>
-      </c>
-      <c r="AA380">
-        <v>0</v>
-      </c>
-      <c r="AB380">
-        <v>0</v>
-      </c>
-      <c r="AC380">
-        <v>0</v>
-      </c>
-      <c r="AD380">
-        <v>0</v>
-      </c>
-      <c r="AE380">
-        <v>0</v>
-      </c>
-      <c r="AF380">
-        <v>0</v>
-      </c>
-      <c r="AG380">
-        <v>0</v>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ380">
-        <v>0</v>
-      </c>
-      <c r="AK380">
-        <v>0</v>
-      </c>
-      <c r="AL380">
-        <v>0</v>
-      </c>
-      <c r="AM380">
-        <v>-1</v>
-      </c>
-      <c r="AN380">
-        <v>-1</v>
-      </c>
-      <c r="AO380">
-        <v>-1</v>
-      </c>
-      <c r="AP380">
-        <v>-1</v>
-      </c>
-      <c r="AQ380">
-        <v>0</v>
-      </c>
-      <c r="AR380">
-        <v>0</v>
-      </c>
-      <c r="AS380">
-        <v>0</v>
-      </c>
-      <c r="AT380">
-        <v>0</v>
-      </c>
-      <c r="AU380" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="G381">
-        <v>0</v>
-      </c>
-      <c r="H381">
-        <v>0</v>
-      </c>
-      <c r="I381">
-        <v>0</v>
-      </c>
-      <c r="J381">
-        <v>0</v>
-      </c>
-      <c r="K381">
-        <v>0</v>
-      </c>
-      <c r="L381">
-        <v>0</v>
-      </c>
-      <c r="M381" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N381">
-        <v>0</v>
-      </c>
-      <c r="O381">
-        <v>0</v>
-      </c>
-      <c r="P381">
-        <v>0</v>
-      </c>
-      <c r="Q381">
-        <v>0</v>
-      </c>
-      <c r="R381">
-        <v>0</v>
-      </c>
-      <c r="S381">
-        <v>0</v>
-      </c>
-      <c r="T381">
-        <v>0</v>
-      </c>
-      <c r="U381">
-        <v>0</v>
-      </c>
-      <c r="V381">
-        <v>0</v>
-      </c>
-      <c r="W381">
-        <v>0</v>
-      </c>
-      <c r="X381">
-        <v>0</v>
-      </c>
-      <c r="Y381">
-        <v>0</v>
-      </c>
-      <c r="Z381">
-        <v>0</v>
-      </c>
-      <c r="AA381">
-        <v>0</v>
-      </c>
-      <c r="AB381">
-        <v>0</v>
-      </c>
-      <c r="AC381">
-        <v>0</v>
-      </c>
-      <c r="AD381">
-        <v>0</v>
-      </c>
-      <c r="AE381">
-        <v>0</v>
-      </c>
-      <c r="AF381">
-        <v>0</v>
-      </c>
-      <c r="AG381">
-        <v>0</v>
-      </c>
-      <c r="AH381" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI381" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ381">
-        <v>0</v>
-      </c>
-      <c r="AK381">
-        <v>0</v>
-      </c>
-      <c r="AL381">
-        <v>0</v>
-      </c>
-      <c r="AM381">
-        <v>-1</v>
-      </c>
-      <c r="AN381">
-        <v>-1</v>
-      </c>
-      <c r="AO381">
-        <v>-1</v>
-      </c>
-      <c r="AP381">
-        <v>-1</v>
-      </c>
-      <c r="AQ381">
-        <v>0</v>
-      </c>
-      <c r="AR381">
-        <v>0</v>
-      </c>
-      <c r="AS381">
-        <v>0</v>
-      </c>
-      <c r="AT381">
-        <v>0</v>
-      </c>
-      <c r="AU381" t="inlineStr">
         <is>
           <t>2026-10-31 22:30:00</t>
         </is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O170">
-        <v>4.26</v>
+        <v>4.62</v>
       </c>
       <c r="P170">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD170">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="O171">
-        <v>4.62</v>
+        <v>4.26</v>
       </c>
       <c r="P171">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,10 +28227,10 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AD171">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AE171">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.65</v>
+        <v>2.54</v>
       </c>
       <c r="O190">
-        <v>3.84</v>
+        <v>3.34</v>
       </c>
       <c r="P190">
-        <v>4.69</v>
+        <v>2.54</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB190">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="O191">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="P191">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31481,10 +31481,10 @@
         <v>0</v>
       </c>
       <c r="AA191">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB191">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.33</v>
+        <v>3.04</v>
       </c>
       <c r="O192">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P192">
-        <v>2.89</v>
+        <v>2.13</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="O193">
-        <v>3.55</v>
+        <v>3.27</v>
       </c>
       <c r="P193">
-        <v>2.13</v>
+        <v>2.66</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB193">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="O194">
-        <v>3.74</v>
+        <v>4.42</v>
       </c>
       <c r="P194">
-        <v>3.39</v>
+        <v>4.85</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="O195">
-        <v>3.27</v>
+        <v>3.09</v>
       </c>
       <c r="P195">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB195">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="O196">
-        <v>4.42</v>
+        <v>3.74</v>
       </c>
       <c r="P196">
-        <v>4.85</v>
+        <v>3.39</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.68</v>
+        <v>1.65</v>
       </c>
       <c r="O197">
-        <v>3.09</v>
+        <v>3.84</v>
       </c>
       <c r="P197">
-        <v>2.67</v>
+        <v>4.69</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G232">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G233">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G314">
@@ -51491,13 +51491,13 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O314">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P314">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q314">
         <v>0</v>
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O315">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P315">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G368">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G370">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G372">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G373">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G374">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G375">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G376">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G135">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="O170">
-        <v>4.62</v>
+        <v>4.26</v>
       </c>
       <c r="P170">
-        <v>4.07</v>
+        <v>3.9</v>
       </c>
       <c r="Q170">
         <v>0</v>
@@ -28064,10 +28064,10 @@
         <v>0</v>
       </c>
       <c r="AC170">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AD170">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="AE170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,13 +28182,13 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O171">
-        <v>4.26</v>
+        <v>4.62</v>
       </c>
       <c r="P171">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="Q171">
         <v>0</v>
@@ -28227,10 +28227,10 @@
         <v>0</v>
       </c>
       <c r="AC171">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD171">
-        <v>1.63</v>
+        <v>1.98</v>
       </c>
       <c r="AE171">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="O190">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="P190">
-        <v>2.54</v>
+        <v>2.89</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31318,10 +31318,10 @@
         <v>0</v>
       </c>
       <c r="AA190">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB190">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.33</v>
+        <v>3.04</v>
       </c>
       <c r="O191">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P191">
-        <v>2.89</v>
+        <v>2.13</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>3.04</v>
+        <v>2.54</v>
       </c>
       <c r="O192">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="P192">
-        <v>2.13</v>
+        <v>2.54</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB192">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O196">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="P196">
-        <v>3.39</v>
+        <v>4.69</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB196">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="O197">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="P197">
-        <v>4.69</v>
+        <v>3.39</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB197">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G210">
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G211">
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G212">
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G213">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N216">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="O347">
-        <v>4.23</v>
+        <v>4.05</v>
       </c>
       <c r="P347">
-        <v>3.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>3.25</v>
+        <v>1.89</v>
       </c>
       <c r="O348">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="P348">
-        <v>2.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G363">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G367">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G366">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G13">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O136">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P136">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P138">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O312">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P312">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q312">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O313">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P313">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G368">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU377"/>
+  <dimension ref="A1:AU378"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>5.79</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G116">
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-31 10:30:00</t>
+          <t>2026-10-31 10:00:00</t>
         </is>
       </c>
     </row>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G126">
@@ -20963,12 +20963,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="O127">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="P127">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-10-31 10:45:00</t>
+          <t>2026-10-31 10:30:00</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G135">
@@ -22430,12 +22430,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,13 +22477,13 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O136">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P136">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-10-31 11:00:00</t>
+          <t>2026-10-31 10:45:00</t>
         </is>
       </c>
     </row>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="N138">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O138">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P138">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -22924,22 +22924,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,13 +22966,13 @@
         </is>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O139">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P139">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q139">
         <v>0</v>
@@ -23087,22 +23087,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G141">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G143">
@@ -23902,22 +23902,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,13 +23944,13 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O145">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P145">
-        <v>6.06</v>
+        <v>0</v>
       </c>
       <c r="Q145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,13 +24107,13 @@
         </is>
       </c>
       <c r="N146">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O146">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P146">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="Q146">
         <v>0</v>
@@ -24228,7 +24228,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -24238,12 +24238,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G147">
@@ -24391,22 +24391,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Doqarah</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Doqarah</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G149">
@@ -24717,7 +24717,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -24727,12 +24727,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G150">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -24890,12 +24890,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="G151">
@@ -24922,13 +24922,13 @@
         </is>
       </c>
       <c r="N151">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O151">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P151">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -25053,12 +25053,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G152">
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G153">
@@ -25369,7 +25369,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G154">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G155">
@@ -25690,12 +25690,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -25705,12 +25705,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lusail City</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G156">
@@ -25737,13 +25737,13 @@
         </is>
       </c>
       <c r="N156">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O156">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P156">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q156">
         <v>0</v>
@@ -25841,7 +25841,7 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>2026-10-31 11:15:00</t>
+          <t>2026-10-31 11:00:00</t>
         </is>
       </c>
     </row>
@@ -25853,12 +25853,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -25868,12 +25868,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Lusail City</t>
         </is>
       </c>
       <c r="G157">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>2026-10-31 11:30:00</t>
+          <t>2026-10-31 11:15:00</t>
         </is>
       </c>
     </row>
@@ -26031,12 +26031,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G158">
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O158">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P158">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q158">
         <v>0</v>
@@ -26194,12 +26194,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G159">
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="O159">
-        <v>3.56</v>
+        <v>3.88</v>
       </c>
       <c r="P159">
-        <v>2.74</v>
+        <v>4.07</v>
       </c>
       <c r="Q159">
         <v>0</v>
@@ -26347,7 +26347,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G160">
@@ -26389,13 +26389,13 @@
         </is>
       </c>
       <c r="N160">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O160">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P160">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Q160">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O161">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P161">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Q161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="O162">
         <v>3.8</v>
       </c>
       <c r="P162">
-        <v>2.22</v>
+        <v>3.74</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="O163">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P163">
-        <v>4.42</v>
+        <v>2.22</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="O164">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P164">
-        <v>2.4</v>
+        <v>4.42</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27162,7 +27162,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="O165">
-        <v>4.36</v>
+        <v>3.8</v>
       </c>
       <c r="P165">
-        <v>5.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -27335,12 +27335,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G166">
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>9.5</v>
+        <v>1.66</v>
       </c>
       <c r="O166">
-        <v>4.9</v>
+        <v>4.36</v>
       </c>
       <c r="P166">
-        <v>1.29</v>
+        <v>5.48</v>
       </c>
       <c r="Q166">
         <v>0</v>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -27498,12 +27498,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G167">
@@ -27530,13 +27530,13 @@
         </is>
       </c>
       <c r="N167">
-        <v>3.74</v>
+        <v>9.5</v>
       </c>
       <c r="O167">
-        <v>4.36</v>
+        <v>4.9</v>
       </c>
       <c r="P167">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="Q167">
         <v>0</v>
@@ -27575,10 +27575,10 @@
         <v>0</v>
       </c>
       <c r="AC167">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD167">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,13 +27693,13 @@
         </is>
       </c>
       <c r="N168">
-        <v>3.07</v>
+        <v>3.74</v>
       </c>
       <c r="O168">
-        <v>4.07</v>
+        <v>4.36</v>
       </c>
       <c r="P168">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="Q168">
         <v>0</v>
@@ -27738,10 +27738,10 @@
         <v>0</v>
       </c>
       <c r="AC168">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD168">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AE168">
         <v>0</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,13 +27856,13 @@
         </is>
       </c>
       <c r="N169">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="O169">
-        <v>4.21</v>
+        <v>4.07</v>
       </c>
       <c r="P169">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q169">
         <v>0</v>
@@ -27901,10 +27901,10 @@
         <v>0</v>
       </c>
       <c r="AC169">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AD169">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AE169">
         <v>0</v>
@@ -28298,12 +28298,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,13 +28345,13 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.04</v>
+        <v>3.04</v>
       </c>
       <c r="O172">
-        <v>3.32</v>
+        <v>4.21</v>
       </c>
       <c r="P172">
-        <v>3.18</v>
+        <v>2.23</v>
       </c>
       <c r="Q172">
         <v>0</v>
@@ -28390,10 +28390,10 @@
         <v>0</v>
       </c>
       <c r="AC172">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD172">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE172">
         <v>0</v>
@@ -28449,7 +28449,7 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>2026-10-31 11:45:00</t>
+          <t>2026-10-31 11:30:00</t>
         </is>
       </c>
     </row>
@@ -28461,12 +28461,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,13 +28508,13 @@
         </is>
       </c>
       <c r="N173">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O173">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P173">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q173">
         <v>0</v>
@@ -28612,7 +28612,7 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>2026-10-31 11:55:00</t>
+          <t>2026-10-31 11:45:00</t>
         </is>
       </c>
     </row>
@@ -28624,12 +28624,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -28639,12 +28639,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G174">
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="O174">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="P174">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB174">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -28775,7 +28775,7 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>2026-10-31 12:00:00</t>
+          <t>2026-10-31 11:55:00</t>
         </is>
       </c>
     </row>
@@ -28802,12 +28802,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G175">
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O175">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P175">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -28873,10 +28873,10 @@
         <v>0</v>
       </c>
       <c r="AA175">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB175">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC175">
         <v>0</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O176">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P176">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -29036,10 +29036,10 @@
         <v>0</v>
       </c>
       <c r="AA176">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB176">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="O177">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P177">
-        <v>2.71</v>
+        <v>3.14</v>
       </c>
       <c r="Q177">
         <v>0</v>
@@ -29199,7 +29199,7 @@
         <v>0</v>
       </c>
       <c r="AA177">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB177">
         <v>1.95</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="O178">
-        <v>3.89</v>
+        <v>3.62</v>
       </c>
       <c r="P178">
-        <v>3.65</v>
+        <v>2.71</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AB178">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29444,7 +29444,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="O179">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="P179">
-        <v>5.95</v>
+        <v>3.65</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB179">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,13 +29649,13 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="O180">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="P180">
-        <v>5.2</v>
+        <v>5.95</v>
       </c>
       <c r="Q180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,13 +29812,13 @@
         </is>
       </c>
       <c r="N181">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="O181">
-        <v>3.62</v>
+        <v>3.98</v>
       </c>
       <c r="P181">
-        <v>2.88</v>
+        <v>5.2</v>
       </c>
       <c r="Q181">
         <v>0</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O182">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30096,22 +30096,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G183">
@@ -30259,22 +30259,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G184">
@@ -30301,13 +30301,13 @@
         </is>
       </c>
       <c r="N184">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O184">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P184">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q184">
         <v>0</v>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="O185">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="P185">
-        <v>4.25</v>
+        <v>2.53</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30503,10 +30503,10 @@
         <v>0</v>
       </c>
       <c r="AA185">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB185">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC185">
         <v>0</v>
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>3.74</v>
+        <v>1.73</v>
       </c>
       <c r="O186">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="P186">
-        <v>1.91</v>
+        <v>4.25</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O187">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P187">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="O188">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P188">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,13 +31116,13 @@
         </is>
       </c>
       <c r="N189">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O189">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="P189">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="Q189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O190">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P190">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="O191">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P191">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.54</v>
+        <v>3.04</v>
       </c>
       <c r="O192">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="P192">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA192">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB192">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O193">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="P193">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB193">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.54</v>
+        <v>2.56</v>
       </c>
       <c r="O194">
-        <v>4.42</v>
+        <v>3.27</v>
       </c>
       <c r="P194">
-        <v>4.85</v>
+        <v>2.66</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB194">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="O195">
-        <v>3.09</v>
+        <v>4.42</v>
       </c>
       <c r="P195">
-        <v>2.67</v>
+        <v>4.85</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.65</v>
+        <v>2.68</v>
       </c>
       <c r="O196">
-        <v>3.84</v>
+        <v>3.09</v>
       </c>
       <c r="P196">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32296,10 +32296,10 @@
         <v>0</v>
       </c>
       <c r="AA196">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB196">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O197">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="P197">
-        <v>3.39</v>
+        <v>4.69</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB197">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O198">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P198">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G199">
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G200">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G201">
@@ -33193,22 +33193,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G202">
@@ -33235,13 +33235,13 @@
         </is>
       </c>
       <c r="N202">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O202">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P202">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q202">
         <v>0</v>
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O203">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P203">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33529,12 +33529,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G204">
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G206">
@@ -34008,7 +34008,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O208">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P208">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34252,10 +34252,10 @@
         <v>0</v>
       </c>
       <c r="AA208">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB208">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O209">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P209">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34421,10 +34421,10 @@
         <v>0</v>
       </c>
       <c r="AC209">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD209">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O210">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P210">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34578,10 +34578,10 @@
         <v>0</v>
       </c>
       <c r="AA210">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB210">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC210">
         <v>0</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O211">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P211">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34747,10 +34747,10 @@
         <v>0</v>
       </c>
       <c r="AC211">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD211">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE211">
         <v>0</v>
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O212">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P212">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34910,10 +34910,10 @@
         <v>0</v>
       </c>
       <c r="AC212">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD212">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE212">
         <v>0</v>
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O213">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P213">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35067,10 +35067,10 @@
         <v>0</v>
       </c>
       <c r="AA213">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB213">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC213">
         <v>0</v>
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O214">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P214">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35230,10 +35230,10 @@
         <v>0</v>
       </c>
       <c r="AA214">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB214">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC214">
         <v>0</v>
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="O215">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P215">
-        <v>3.98</v>
+        <v>4.71</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35393,10 +35393,10 @@
         <v>0</v>
       </c>
       <c r="AA215">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AB215">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G216">
@@ -35513,17 +35513,17 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N216">
-        <v>3.02</v>
+        <v>1.78</v>
       </c>
       <c r="O216">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P216">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35556,10 +35556,10 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB216">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC216">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G217">
@@ -35676,17 +35676,17 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N217">
-        <v>2.71</v>
+        <v>3.02</v>
       </c>
       <c r="O217">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="P217">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35719,16 +35719,16 @@
         <v>0</v>
       </c>
       <c r="AA217">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB217">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC217">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AD217">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE217">
         <v>0</v>
@@ -35801,22 +35801,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,13 +35843,13 @@
         </is>
       </c>
       <c r="N218">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O218">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P218">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35882,16 +35882,16 @@
         <v>0</v>
       </c>
       <c r="AA218">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB218">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC218">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD218">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE218">
         <v>0</v>
@@ -35974,12 +35974,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G219">
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G221">
@@ -36463,12 +36463,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="G222">
@@ -36616,22 +36616,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G223">
@@ -36779,7 +36779,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -36789,12 +36789,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G224">
@@ -36821,13 +36821,13 @@
         </is>
       </c>
       <c r="N224">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O224">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P224">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q224">
         <v>0</v>
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="O225">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="P225">
-        <v>3.89</v>
+        <v>2.28</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="O226">
-        <v>5.95</v>
+        <v>3.72</v>
       </c>
       <c r="P226">
-        <v>9.75</v>
+        <v>3.89</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="O227">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="P227">
-        <v>2.73</v>
+        <v>9.75</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.74</v>
+        <v>2.36</v>
       </c>
       <c r="O228">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P228">
-        <v>4.28</v>
+        <v>2.73</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O232">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P232">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O233">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P233">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38409,7 +38409,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G234">
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G235">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N235">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G236">
@@ -38773,7 +38773,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,13 +38940,13 @@
         </is>
       </c>
       <c r="N237">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O237">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P237">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q237">
         <v>0</v>
@@ -39056,12 +39056,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>2.48</v>
+        <v>3.54</v>
       </c>
       <c r="O238">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="P238">
-        <v>2.86</v>
+        <v>1.99</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>0</v>
       </c>
       <c r="AA238">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB238">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC238">
         <v>0</v>
@@ -39207,7 +39207,7 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>2026-10-31 12:15:00</t>
+          <t>2026-10-31 12:00:00</t>
         </is>
       </c>
     </row>
@@ -39224,7 +39224,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O239">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P239">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB239">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39382,27 +39382,27 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G240">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>2026-10-31 12:30:00</t>
+          <t>2026-10-31 12:15:00</t>
         </is>
       </c>
     </row>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G241">
@@ -39713,22 +39713,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G242">
@@ -40202,7 +40202,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,13 +40244,13 @@
         </is>
       </c>
       <c r="N245">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O245">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P245">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q245">
         <v>0</v>
@@ -40283,10 +40283,10 @@
         <v>0</v>
       </c>
       <c r="AA245">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB245">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC245">
         <v>0</v>
@@ -40365,22 +40365,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O246">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P246">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB246">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G247">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -40701,12 +40701,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.12</v>
+        <v>2.89</v>
       </c>
       <c r="O251">
-        <v>10.2</v>
+        <v>3.36</v>
       </c>
       <c r="P251">
-        <v>18</v>
+        <v>2.58</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O252">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="P252">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41501,12 +41501,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G253">
@@ -41652,7 +41652,7 @@
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>2026-10-31 13:00:00</t>
+          <t>2026-10-31 12:30:00</t>
         </is>
       </c>
     </row>
@@ -41669,7 +41669,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G254">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G255">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G256">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,22 +42810,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,7 +43136,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -43146,12 +43146,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G263">
@@ -43178,13 +43178,13 @@
         </is>
       </c>
       <c r="N263">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O263">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P263">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O265">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P265">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O266">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P266">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G267">
@@ -43946,12 +43946,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G268">
@@ -43993,13 +43993,13 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O268">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P268">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q268">
         <v>0</v>
@@ -44097,7 +44097,7 @@
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>2026-10-31 13:15:00</t>
+          <t>2026-10-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -44114,7 +44114,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.78</v>
+        <v>2.11</v>
       </c>
       <c r="O269">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="P269">
-        <v>2.53</v>
+        <v>3.27</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44272,12 +44272,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O270">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P270">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44423,7 +44423,7 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>2026-10-31 13:30:00</t>
+          <t>2026-10-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G271">
@@ -44603,22 +44603,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,22 +44766,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G273">
@@ -44808,13 +44808,13 @@
         </is>
       </c>
       <c r="N273">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O273">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P273">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q273">
         <v>0</v>
@@ -44929,7 +44929,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -44939,12 +44939,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G275">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -45265,12 +45265,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G276">
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G277">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G278">
@@ -45744,7 +45744,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G279">
@@ -45902,12 +45902,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G280">
@@ -45945,7 +45945,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N280">
@@ -46053,7 +46053,7 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>2026-10-31 13:45:00</t>
+          <t>2026-10-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G281">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N281">
@@ -46233,7 +46233,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G282">
@@ -46396,7 +46396,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -46406,12 +46406,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="G283">
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O283">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P283">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46554,12 +46554,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -46569,12 +46569,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G284">
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>2.28</v>
+        <v>5.68</v>
       </c>
       <c r="O284">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P284">
-        <v>2.71</v>
+        <v>1.67</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46705,7 +46705,7 @@
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>2026-10-31 14:00:00</t>
+          <t>2026-10-31 13:45:00</t>
         </is>
       </c>
     </row>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="O285">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P285">
-        <v>4.02</v>
+        <v>2.71</v>
       </c>
       <c r="Q285">
         <v>0</v>
@@ -46885,7 +46885,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O286">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P286">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q286">
         <v>0</v>
@@ -47048,7 +47048,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G287">
@@ -47211,7 +47211,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -47221,12 +47221,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G288">
@@ -47374,22 +47374,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="G289">
@@ -47416,13 +47416,13 @@
         </is>
       </c>
       <c r="N289">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O289">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P289">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Q289">
         <v>0</v>
@@ -47537,22 +47537,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G290">
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>7.8</v>
+        <v>1.99</v>
       </c>
       <c r="O290">
-        <v>4.3</v>
+        <v>3.98</v>
       </c>
       <c r="P290">
-        <v>1.41</v>
+        <v>3.42</v>
       </c>
       <c r="Q290">
         <v>0</v>
@@ -47618,10 +47618,10 @@
         <v>0</v>
       </c>
       <c r="AA290">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB290">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC290">
         <v>0</v>
@@ -47700,7 +47700,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -47710,12 +47710,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G291">
@@ -47742,13 +47742,13 @@
         </is>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O291">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P291">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q291">
         <v>0</v>
@@ -47781,10 +47781,10 @@
         <v>0</v>
       </c>
       <c r="AA291">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB291">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC291">
         <v>0</v>
@@ -47863,7 +47863,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -47873,12 +47873,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G292">
@@ -48026,22 +48026,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G293">
@@ -48189,22 +48189,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G294">
@@ -48352,7 +48352,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -48362,12 +48362,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G295">
@@ -48394,13 +48394,13 @@
         </is>
       </c>
       <c r="N295">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O295">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P295">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q295">
         <v>0</v>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -48525,12 +48525,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Arsenal Ceska Lipa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G296">
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q296">
         <v>0</v>
@@ -48678,7 +48678,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -48688,12 +48688,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Arsenal Ceska Lipa</t>
         </is>
       </c>
       <c r="G297">
@@ -48841,7 +48841,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -48851,12 +48851,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G298">
@@ -48999,12 +48999,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G299">
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O299">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P299">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49150,7 +49150,7 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>2026-10-31 14:15:00</t>
+          <t>2026-10-31 14:00:00</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49162,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -49177,12 +49177,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G300">
@@ -49209,13 +49209,13 @@
         </is>
       </c>
       <c r="N300">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="O300">
-        <v>4.05</v>
+        <v>3.87</v>
       </c>
       <c r="P300">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q300">
         <v>0</v>
@@ -49248,10 +49248,10 @@
         <v>0</v>
       </c>
       <c r="AA300">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB300">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC300">
         <v>0</v>
@@ -49313,7 +49313,7 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>2026-10-31 14:30:00</t>
+          <t>2026-10-31 14:15:00</t>
         </is>
       </c>
     </row>
@@ -49330,7 +49330,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -49340,12 +49340,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G301">
@@ -49372,13 +49372,13 @@
         </is>
       </c>
       <c r="N301">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O301">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P301">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q301">
         <v>0</v>
@@ -49411,10 +49411,10 @@
         <v>0</v>
       </c>
       <c r="AA301">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB301">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC301">
         <v>0</v>
@@ -49493,7 +49493,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G302">
@@ -49656,7 +49656,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -49666,12 +49666,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="G303">
@@ -49819,7 +49819,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -49829,12 +49829,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G304">
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O304">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P304">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="Q304">
         <v>0</v>
@@ -49982,7 +49982,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -49992,12 +49992,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G305">
@@ -50024,13 +50024,13 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="O305">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="P305">
-        <v>12</v>
+        <v>4.28</v>
       </c>
       <c r="Q305">
         <v>0</v>
@@ -50145,7 +50145,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -50155,12 +50155,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G306">
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="O306">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="P306">
-        <v>7.85</v>
+        <v>12</v>
       </c>
       <c r="Q306">
         <v>0</v>
@@ -50238,7 +50238,7 @@
         <v>0</v>
       </c>
       <c r="AE306">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF306">
         <v>0</v>
@@ -50303,12 +50303,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -50318,12 +50318,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G307">
@@ -50350,13 +50350,13 @@
         </is>
       </c>
       <c r="N307">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O307">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P307">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q307">
         <v>0</v>
@@ -50401,7 +50401,7 @@
         <v>0</v>
       </c>
       <c r="AE307">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF307">
         <v>0</v>
@@ -50454,7 +50454,7 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>2026-10-31 14:45:00</t>
+          <t>2026-10-31 14:30:00</t>
         </is>
       </c>
     </row>
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -50481,12 +50481,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G308">
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O308">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P308">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Q308">
         <v>0</v>
@@ -50644,12 +50644,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G309">
@@ -50676,13 +50676,13 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="O309">
-        <v>18.5</v>
+        <v>4.23</v>
       </c>
       <c r="P309">
-        <v>38</v>
+        <v>3.71</v>
       </c>
       <c r="Q309">
         <v>0</v>
@@ -50727,7 +50727,7 @@
         <v>0</v>
       </c>
       <c r="AE309">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF309">
         <v>0</v>
@@ -50792,27 +50792,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O310">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="P310">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Q310">
         <v>0</v>
@@ -50890,7 +50890,7 @@
         <v>0</v>
       </c>
       <c r="AE310">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF310">
         <v>0</v>
@@ -50943,7 +50943,7 @@
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>2026-10-31 15:00:00</t>
+          <t>2026-10-31 14:45:00</t>
         </is>
       </c>
     </row>
@@ -50960,22 +50960,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="G311">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -51133,12 +51133,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G312">
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O312">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P312">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q312">
         <v>0</v>
@@ -51296,12 +51296,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G313">
@@ -51328,13 +51328,13 @@
         </is>
       </c>
       <c r="N313">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O313">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P313">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q313">
         <v>0</v>
@@ -51449,7 +51449,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -51459,12 +51459,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G314">
@@ -51622,12 +51622,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="G315">
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>2.34</v>
+        <v>1.49</v>
       </c>
       <c r="O315">
-        <v>3.4</v>
+        <v>4.42</v>
       </c>
       <c r="P315">
-        <v>2.79</v>
+        <v>5.4</v>
       </c>
       <c r="Q315">
         <v>0</v>
@@ -51775,7 +51775,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -51785,12 +51785,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G316">
@@ -51817,13 +51817,13 @@
         </is>
       </c>
       <c r="N316">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O316">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P316">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q316">
         <v>0</v>
@@ -51938,22 +51938,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G317">
@@ -52111,12 +52111,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G318">
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G319">
@@ -52427,22 +52427,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Castellonense</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G320">
@@ -52585,12 +52585,12 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Castellonense</t>
         </is>
       </c>
       <c r="G321">
@@ -52736,7 +52736,7 @@
       </c>
       <c r="AU321" t="inlineStr">
         <is>
-          <t>2026-10-31 15:15:00</t>
+          <t>2026-10-31 15:00:00</t>
         </is>
       </c>
     </row>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G322">
@@ -52911,12 +52911,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,13 +52958,13 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O323">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P323">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="Q323">
         <v>0</v>
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AU323" t="inlineStr">
         <is>
-          <t>2026-10-31 15:30:00</t>
+          <t>2026-10-31 15:15:00</t>
         </is>
       </c>
     </row>
@@ -53079,7 +53079,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,13 +53121,13 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.34</v>
+        <v>2.1</v>
       </c>
       <c r="O324">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="P324">
-        <v>7.55</v>
+        <v>3.47</v>
       </c>
       <c r="Q324">
         <v>0</v>
@@ -53237,12 +53237,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O325">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P325">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53388,7 +53388,7 @@
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>2026-10-31 15:45:00</t>
+          <t>2026-10-31 15:30:00</t>
         </is>
       </c>
     </row>
@@ -53400,27 +53400,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="O326">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P326">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53486,10 +53486,10 @@
         <v>0</v>
       </c>
       <c r="AA326">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB326">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC326">
         <v>0</v>
@@ -53551,7 +53551,7 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>2026-10-31 16:00:00</t>
+          <t>2026-10-31 15:45:00</t>
         </is>
       </c>
     </row>
@@ -53568,22 +53568,22 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,13 +53610,13 @@
         </is>
       </c>
       <c r="N327">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O327">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P327">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Q327">
         <v>0</v>
@@ -53649,10 +53649,10 @@
         <v>0</v>
       </c>
       <c r="AA327">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB327">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC327">
         <v>0</v>
@@ -53731,22 +53731,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G328">
@@ -53894,22 +53894,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="O329">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P329">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54057,22 +54057,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G330">
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O330">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P330">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q330">
         <v>0</v>
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G331">
@@ -54383,22 +54383,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G332">
@@ -54425,13 +54425,13 @@
         </is>
       </c>
       <c r="N332">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O332">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P332">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q332">
         <v>0</v>
@@ -54546,22 +54546,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G333">
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O333">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P333">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54704,27 +54704,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="O334">
-        <v>3.58</v>
+        <v>3.16</v>
       </c>
       <c r="P334">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54790,10 +54790,10 @@
         <v>0</v>
       </c>
       <c r="AA334">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB334">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC334">
         <v>0</v>
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-10-31 16:15:00</t>
+          <t>2026-10-31 16:00:00</t>
         </is>
       </c>
     </row>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O335">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P335">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-10-31 16:30:00</t>
+          <t>2026-10-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -55035,7 +55035,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O336">
-        <v>3.6</v>
+        <v>3.89</v>
       </c>
       <c r="P336">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55122,10 +55122,10 @@
         <v>0</v>
       </c>
       <c r="AC336">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AD336">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AE336">
         <v>0</v>
@@ -55193,12 +55193,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O337">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="P337">
-        <v>3.39</v>
+        <v>2.45</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55279,16 +55279,16 @@
         <v>0</v>
       </c>
       <c r="AA337">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB337">
+        <v>0</v>
+      </c>
+      <c r="AC337">
         <v>2</v>
       </c>
-      <c r="AC337">
-        <v>0</v>
-      </c>
       <c r="AD337">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE337">
         <v>0</v>
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-10-31 16:45:00</t>
+          <t>2026-10-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.93</v>
+        <v>2.2</v>
       </c>
       <c r="O338">
-        <v>3.62</v>
+        <v>3.76</v>
       </c>
       <c r="P338">
-        <v>2.52</v>
+        <v>3.39</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55442,10 +55442,10 @@
         <v>0</v>
       </c>
       <c r="AA338">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB338">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.44</v>
+        <v>2.93</v>
       </c>
       <c r="O339">
-        <v>5.24</v>
+        <v>3.62</v>
       </c>
       <c r="P339">
-        <v>7.7</v>
+        <v>2.52</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55605,10 +55605,10 @@
         <v>0</v>
       </c>
       <c r="AA339">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB339">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC339">
         <v>0</v>
@@ -55687,7 +55687,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O340">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="P340">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55850,7 +55850,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O341">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="P341">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="Q341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>5.57</v>
+        <v>1.67</v>
       </c>
       <c r="O342">
-        <v>4.44</v>
+        <v>4.22</v>
       </c>
       <c r="P342">
-        <v>1.56</v>
+        <v>4.74</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56171,12 +56171,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>2.14</v>
+        <v>5.57</v>
       </c>
       <c r="O343">
-        <v>3.8</v>
+        <v>4.44</v>
       </c>
       <c r="P343">
-        <v>3.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56257,10 +56257,10 @@
         <v>0</v>
       </c>
       <c r="AA343">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB343">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC343">
         <v>0</v>
@@ -56322,7 +56322,7 @@
       </c>
       <c r="AU343" t="inlineStr">
         <is>
-          <t>2026-10-31 17:00:00</t>
+          <t>2026-10-31 16:45:00</t>
         </is>
       </c>
     </row>
@@ -56339,7 +56339,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>2.77</v>
+        <v>2.14</v>
       </c>
       <c r="O344">
-        <v>3.29</v>
+        <v>3.8</v>
       </c>
       <c r="P344">
-        <v>2.66</v>
+        <v>3.52</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56420,10 +56420,10 @@
         <v>0</v>
       </c>
       <c r="AA344">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB344">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC344">
         <v>0</v>
@@ -56502,7 +56502,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="O345">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56665,7 +56665,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G346">
@@ -56828,7 +56828,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O347">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P347">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="O348">
-        <v>4.23</v>
+        <v>4.05</v>
       </c>
       <c r="P348">
-        <v>3.63</v>
+        <v>2.05</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57149,27 +57149,27 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O349">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="P349">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>2026-10-31 17:30:00</t>
+          <t>2026-10-31 17:00:00</t>
         </is>
       </c>
     </row>
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G350">
@@ -57480,22 +57480,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G351">
@@ -57638,27 +57638,27 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O352">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P352">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q352">
         <v>0</v>
@@ -57789,7 +57789,7 @@
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>2026-10-31 18:00:00</t>
+          <t>2026-10-31 17:30:00</t>
         </is>
       </c>
     </row>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G353">
@@ -57969,7 +57969,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G354">
@@ -58127,12 +58127,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G355">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-31 18:15:00</t>
+          <t>2026-10-31 18:00:00</t>
         </is>
       </c>
     </row>
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-10-31 19:30:00</t>
+          <t>2026-10-31 18:15:00</t>
         </is>
       </c>
     </row>
@@ -58453,12 +58453,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-10-31 20:00:00</t>
+          <t>2026-10-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -58616,27 +58616,27 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G358">
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-10-31 21:00:00</t>
+          <t>2026-10-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -58784,7 +58784,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G360">
@@ -59110,22 +59110,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G363">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G364">
@@ -60414,22 +60414,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G369">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G370">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G372">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G373">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G374">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G375">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G376">
@@ -61713,156 +61713,319 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Borac Čačak</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="G377">
+        <v>0</v>
+      </c>
+      <c r="H377">
+        <v>0</v>
+      </c>
+      <c r="I377">
+        <v>0</v>
+      </c>
+      <c r="J377">
+        <v>0</v>
+      </c>
+      <c r="K377">
+        <v>0</v>
+      </c>
+      <c r="L377">
+        <v>0</v>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N377">
+        <v>0</v>
+      </c>
+      <c r="O377">
+        <v>0</v>
+      </c>
+      <c r="P377">
+        <v>0</v>
+      </c>
+      <c r="Q377">
+        <v>0</v>
+      </c>
+      <c r="R377">
+        <v>0</v>
+      </c>
+      <c r="S377">
+        <v>0</v>
+      </c>
+      <c r="T377">
+        <v>0</v>
+      </c>
+      <c r="U377">
+        <v>0</v>
+      </c>
+      <c r="V377">
+        <v>0</v>
+      </c>
+      <c r="W377">
+        <v>0</v>
+      </c>
+      <c r="X377">
+        <v>0</v>
+      </c>
+      <c r="Y377">
+        <v>0</v>
+      </c>
+      <c r="Z377">
+        <v>0</v>
+      </c>
+      <c r="AA377">
+        <v>0</v>
+      </c>
+      <c r="AB377">
+        <v>0</v>
+      </c>
+      <c r="AC377">
+        <v>0</v>
+      </c>
+      <c r="AD377">
+        <v>0</v>
+      </c>
+      <c r="AE377">
+        <v>0</v>
+      </c>
+      <c r="AF377">
+        <v>0</v>
+      </c>
+      <c r="AG377">
+        <v>0</v>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ377">
+        <v>0</v>
+      </c>
+      <c r="AK377">
+        <v>0</v>
+      </c>
+      <c r="AL377">
+        <v>0</v>
+      </c>
+      <c r="AM377">
+        <v>-1</v>
+      </c>
+      <c r="AN377">
+        <v>-1</v>
+      </c>
+      <c r="AO377">
+        <v>-1</v>
+      </c>
+      <c r="AP377">
+        <v>-1</v>
+      </c>
+      <c r="AQ377">
+        <v>0</v>
+      </c>
+      <c r="AR377">
+        <v>0</v>
+      </c>
+      <c r="AS377">
+        <v>0</v>
+      </c>
+      <c r="AT377">
+        <v>0</v>
+      </c>
+      <c r="AU377" t="inlineStr">
+        <is>
+          <t>2026-10-31 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
           <t>22:30</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
+      <c r="C378" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E378" t="inlineStr">
         <is>
           <t>Colorado Rapids</t>
         </is>
       </c>
-      <c r="F377" t="inlineStr">
+      <c r="F378" t="inlineStr">
         <is>
           <t>Chicago Fire</t>
         </is>
       </c>
-      <c r="G377">
-        <v>0</v>
-      </c>
-      <c r="H377">
-        <v>0</v>
-      </c>
-      <c r="I377">
-        <v>0</v>
-      </c>
-      <c r="J377">
-        <v>0</v>
-      </c>
-      <c r="K377">
-        <v>0</v>
-      </c>
-      <c r="L377">
-        <v>0</v>
-      </c>
-      <c r="M377" t="inlineStr">
+      <c r="G378">
+        <v>0</v>
+      </c>
+      <c r="H378">
+        <v>0</v>
+      </c>
+      <c r="I378">
+        <v>0</v>
+      </c>
+      <c r="J378">
+        <v>0</v>
+      </c>
+      <c r="K378">
+        <v>0</v>
+      </c>
+      <c r="L378">
+        <v>0</v>
+      </c>
+      <c r="M378" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N377">
-        <v>0</v>
-      </c>
-      <c r="O377">
-        <v>0</v>
-      </c>
-      <c r="P377">
-        <v>0</v>
-      </c>
-      <c r="Q377">
-        <v>0</v>
-      </c>
-      <c r="R377">
-        <v>0</v>
-      </c>
-      <c r="S377">
-        <v>0</v>
-      </c>
-      <c r="T377">
-        <v>0</v>
-      </c>
-      <c r="U377">
-        <v>0</v>
-      </c>
-      <c r="V377">
-        <v>0</v>
-      </c>
-      <c r="W377">
-        <v>0</v>
-      </c>
-      <c r="X377">
-        <v>0</v>
-      </c>
-      <c r="Y377">
-        <v>0</v>
-      </c>
-      <c r="Z377">
-        <v>0</v>
-      </c>
-      <c r="AA377">
-        <v>0</v>
-      </c>
-      <c r="AB377">
-        <v>0</v>
-      </c>
-      <c r="AC377">
-        <v>0</v>
-      </c>
-      <c r="AD377">
-        <v>0</v>
-      </c>
-      <c r="AE377">
-        <v>0</v>
-      </c>
-      <c r="AF377">
-        <v>0</v>
-      </c>
-      <c r="AG377">
-        <v>0</v>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ377">
-        <v>0</v>
-      </c>
-      <c r="AK377">
-        <v>0</v>
-      </c>
-      <c r="AL377">
-        <v>0</v>
-      </c>
-      <c r="AM377">
-        <v>-1</v>
-      </c>
-      <c r="AN377">
-        <v>-1</v>
-      </c>
-      <c r="AO377">
-        <v>-1</v>
-      </c>
-      <c r="AP377">
-        <v>-1</v>
-      </c>
-      <c r="AQ377">
-        <v>0</v>
-      </c>
-      <c r="AR377">
-        <v>0</v>
-      </c>
-      <c r="AS377">
-        <v>0</v>
-      </c>
-      <c r="AT377">
-        <v>0</v>
-      </c>
-      <c r="AU377" t="inlineStr">
+      <c r="N378">
+        <v>0</v>
+      </c>
+      <c r="O378">
+        <v>0</v>
+      </c>
+      <c r="P378">
+        <v>0</v>
+      </c>
+      <c r="Q378">
+        <v>0</v>
+      </c>
+      <c r="R378">
+        <v>0</v>
+      </c>
+      <c r="S378">
+        <v>0</v>
+      </c>
+      <c r="T378">
+        <v>0</v>
+      </c>
+      <c r="U378">
+        <v>0</v>
+      </c>
+      <c r="V378">
+        <v>0</v>
+      </c>
+      <c r="W378">
+        <v>0</v>
+      </c>
+      <c r="X378">
+        <v>0</v>
+      </c>
+      <c r="Y378">
+        <v>0</v>
+      </c>
+      <c r="Z378">
+        <v>0</v>
+      </c>
+      <c r="AA378">
+        <v>0</v>
+      </c>
+      <c r="AB378">
+        <v>0</v>
+      </c>
+      <c r="AC378">
+        <v>0</v>
+      </c>
+      <c r="AD378">
+        <v>0</v>
+      </c>
+      <c r="AE378">
+        <v>0</v>
+      </c>
+      <c r="AF378">
+        <v>0</v>
+      </c>
+      <c r="AG378">
+        <v>0</v>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ378">
+        <v>0</v>
+      </c>
+      <c r="AK378">
+        <v>0</v>
+      </c>
+      <c r="AL378">
+        <v>0</v>
+      </c>
+      <c r="AM378">
+        <v>-1</v>
+      </c>
+      <c r="AN378">
+        <v>-1</v>
+      </c>
+      <c r="AO378">
+        <v>-1</v>
+      </c>
+      <c r="AP378">
+        <v>-1</v>
+      </c>
+      <c r="AQ378">
+        <v>0</v>
+      </c>
+      <c r="AR378">
+        <v>0</v>
+      </c>
+      <c r="AS378">
+        <v>0</v>
+      </c>
+      <c r="AT378">
+        <v>0</v>
+      </c>
+      <c r="AU378" t="inlineStr">
         <is>
           <t>2026-10-31 22:30:00</t>
         </is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G34">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G104">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G135">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G153">
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G154">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G255">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G256">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G257">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G375">
@@ -61565,12 +61565,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G376">
@@ -61728,12 +61728,12 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G377">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="O19">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="P19">
-        <v>4.36</v>
+        <v>3.95</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="P20">
-        <v>3.95</v>
+        <v>4.36</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G134">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G145">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P234">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="O299">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P299">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q299">
         <v>0</v>
@@ -49085,10 +49085,10 @@
         <v>0</v>
       </c>
       <c r="AA299">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB299">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC299">
         <v>0</v>
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O341">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P341">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q341">
         <v>0</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU378"/>
+  <dimension ref="A1:AU376"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G135">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G145">
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O147">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P147">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q147">
         <v>0</v>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.2</v>
+        <v>2.93</v>
       </c>
       <c r="O338">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="P338">
-        <v>3.39</v>
+        <v>2.52</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55442,10 +55442,10 @@
         <v>0</v>
       </c>
       <c r="AA338">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB338">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.93</v>
+        <v>1.44</v>
       </c>
       <c r="O339">
-        <v>3.62</v>
+        <v>5.24</v>
       </c>
       <c r="P339">
-        <v>2.52</v>
+        <v>7.7</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55605,10 +55605,10 @@
         <v>0</v>
       </c>
       <c r="AA339">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB339">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC339">
         <v>0</v>
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O340">
-        <v>5.24</v>
+        <v>3.76</v>
       </c>
       <c r="P340">
-        <v>7.7</v>
+        <v>3.39</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55768,10 +55768,10 @@
         <v>0</v>
       </c>
       <c r="AA340">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB340">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC340">
         <v>0</v>
@@ -58947,22 +58947,22 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G360">
@@ -59110,22 +59110,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G363">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G367">
@@ -60251,22 +60251,22 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G368">
@@ -60414,22 +60414,22 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G369">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G370">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G372">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G373">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G374">
@@ -61402,12 +61402,12 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G375">
@@ -61550,27 +61550,27 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G376">
@@ -61700,332 +61700,6 @@
         <v>0</v>
       </c>
       <c r="AU376" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E377" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G377">
-        <v>0</v>
-      </c>
-      <c r="H377">
-        <v>0</v>
-      </c>
-      <c r="I377">
-        <v>0</v>
-      </c>
-      <c r="J377">
-        <v>0</v>
-      </c>
-      <c r="K377">
-        <v>0</v>
-      </c>
-      <c r="L377">
-        <v>0</v>
-      </c>
-      <c r="M377" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N377">
-        <v>0</v>
-      </c>
-      <c r="O377">
-        <v>0</v>
-      </c>
-      <c r="P377">
-        <v>0</v>
-      </c>
-      <c r="Q377">
-        <v>0</v>
-      </c>
-      <c r="R377">
-        <v>0</v>
-      </c>
-      <c r="S377">
-        <v>0</v>
-      </c>
-      <c r="T377">
-        <v>0</v>
-      </c>
-      <c r="U377">
-        <v>0</v>
-      </c>
-      <c r="V377">
-        <v>0</v>
-      </c>
-      <c r="W377">
-        <v>0</v>
-      </c>
-      <c r="X377">
-        <v>0</v>
-      </c>
-      <c r="Y377">
-        <v>0</v>
-      </c>
-      <c r="Z377">
-        <v>0</v>
-      </c>
-      <c r="AA377">
-        <v>0</v>
-      </c>
-      <c r="AB377">
-        <v>0</v>
-      </c>
-      <c r="AC377">
-        <v>0</v>
-      </c>
-      <c r="AD377">
-        <v>0</v>
-      </c>
-      <c r="AE377">
-        <v>0</v>
-      </c>
-      <c r="AF377">
-        <v>0</v>
-      </c>
-      <c r="AG377">
-        <v>0</v>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ377">
-        <v>0</v>
-      </c>
-      <c r="AK377">
-        <v>0</v>
-      </c>
-      <c r="AL377">
-        <v>0</v>
-      </c>
-      <c r="AM377">
-        <v>-1</v>
-      </c>
-      <c r="AN377">
-        <v>-1</v>
-      </c>
-      <c r="AO377">
-        <v>-1</v>
-      </c>
-      <c r="AP377">
-        <v>-1</v>
-      </c>
-      <c r="AQ377">
-        <v>0</v>
-      </c>
-      <c r="AR377">
-        <v>0</v>
-      </c>
-      <c r="AS377">
-        <v>0</v>
-      </c>
-      <c r="AT377">
-        <v>0</v>
-      </c>
-      <c r="AU377" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="G378">
-        <v>0</v>
-      </c>
-      <c r="H378">
-        <v>0</v>
-      </c>
-      <c r="I378">
-        <v>0</v>
-      </c>
-      <c r="J378">
-        <v>0</v>
-      </c>
-      <c r="K378">
-        <v>0</v>
-      </c>
-      <c r="L378">
-        <v>0</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N378">
-        <v>0</v>
-      </c>
-      <c r="O378">
-        <v>0</v>
-      </c>
-      <c r="P378">
-        <v>0</v>
-      </c>
-      <c r="Q378">
-        <v>0</v>
-      </c>
-      <c r="R378">
-        <v>0</v>
-      </c>
-      <c r="S378">
-        <v>0</v>
-      </c>
-      <c r="T378">
-        <v>0</v>
-      </c>
-      <c r="U378">
-        <v>0</v>
-      </c>
-      <c r="V378">
-        <v>0</v>
-      </c>
-      <c r="W378">
-        <v>0</v>
-      </c>
-      <c r="X378">
-        <v>0</v>
-      </c>
-      <c r="Y378">
-        <v>0</v>
-      </c>
-      <c r="Z378">
-        <v>0</v>
-      </c>
-      <c r="AA378">
-        <v>0</v>
-      </c>
-      <c r="AB378">
-        <v>0</v>
-      </c>
-      <c r="AC378">
-        <v>0</v>
-      </c>
-      <c r="AD378">
-        <v>0</v>
-      </c>
-      <c r="AE378">
-        <v>0</v>
-      </c>
-      <c r="AF378">
-        <v>0</v>
-      </c>
-      <c r="AG378">
-        <v>0</v>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ378">
-        <v>0</v>
-      </c>
-      <c r="AK378">
-        <v>0</v>
-      </c>
-      <c r="AL378">
-        <v>0</v>
-      </c>
-      <c r="AM378">
-        <v>-1</v>
-      </c>
-      <c r="AN378">
-        <v>-1</v>
-      </c>
-      <c r="AO378">
-        <v>-1</v>
-      </c>
-      <c r="AP378">
-        <v>-1</v>
-      </c>
-      <c r="AQ378">
-        <v>0</v>
-      </c>
-      <c r="AR378">
-        <v>0</v>
-      </c>
-      <c r="AS378">
-        <v>0</v>
-      </c>
-      <c r="AT378">
-        <v>0</v>
-      </c>
-      <c r="AU378" t="inlineStr">
         <is>
           <t>2026-10-31 22:30:00</t>
         </is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G28">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G34">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G65">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="O69">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11601,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="AC69">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD69">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="O70">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P70">
-        <v>2.3</v>
+        <v>6.03</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11764,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="AC70">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AD70">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="O71">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="P71">
-        <v>6.03</v>
+        <v>2.32</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11927,10 +11927,10 @@
         <v>0</v>
       </c>
       <c r="AC71">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD71">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AE71">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G104">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G115">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G117">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G136">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G145">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G45">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G145">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kyzyl-Zhar</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G65">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.56</v>
+        <v>2.33</v>
       </c>
       <c r="O233">
-        <v>4.25</v>
+        <v>3.26</v>
       </c>
       <c r="P233">
-        <v>5.54</v>
+        <v>2.61</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>2.33</v>
+        <v>1.56</v>
       </c>
       <c r="O234">
-        <v>3.26</v>
+        <v>4.25</v>
       </c>
       <c r="P234">
-        <v>2.61</v>
+        <v>5.54</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G363">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G366">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G367">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU376"/>
+  <dimension ref="A1:AU375"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G64">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G65">
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,13 +29975,13 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O182">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P182">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,13 +30138,13 @@
         </is>
       </c>
       <c r="N183">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O183">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q183">
         <v>0</v>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G185">
@@ -30464,13 +30464,13 @@
         </is>
       </c>
       <c r="N185">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O185">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="P185">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q185">
         <v>0</v>
@@ -30585,7 +30585,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -30595,12 +30595,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G186">
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="O186">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="P186">
-        <v>4.25</v>
+        <v>2.53</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB186">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,13 +30790,13 @@
         </is>
       </c>
       <c r="N187">
-        <v>3.74</v>
+        <v>1.73</v>
       </c>
       <c r="O187">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="P187">
-        <v>1.91</v>
+        <v>4.25</v>
       </c>
       <c r="Q187">
         <v>0</v>
@@ -30829,10 +30829,10 @@
         <v>0</v>
       </c>
       <c r="AA187">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB187">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O188">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q188">
         <v>0</v>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O190">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P190">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q190">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,13 +31442,13 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="O191">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="P191">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="Q191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,13 +31605,13 @@
         </is>
       </c>
       <c r="N192">
-        <v>3.04</v>
+        <v>2.33</v>
       </c>
       <c r="O192">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P192">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="Q192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,13 +31768,13 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.54</v>
+        <v>3.04</v>
       </c>
       <c r="O193">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="P193">
-        <v>2.54</v>
+        <v>2.13</v>
       </c>
       <c r="Q193">
         <v>0</v>
@@ -31807,10 +31807,10 @@
         <v>0</v>
       </c>
       <c r="AA193">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB193">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O194">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="P194">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="Q194">
         <v>0</v>
@@ -31970,10 +31970,10 @@
         <v>0</v>
       </c>
       <c r="AA194">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB194">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,13 +32094,13 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.54</v>
+        <v>2.56</v>
       </c>
       <c r="O195">
-        <v>4.42</v>
+        <v>3.27</v>
       </c>
       <c r="P195">
-        <v>4.85</v>
+        <v>2.66</v>
       </c>
       <c r="Q195">
         <v>0</v>
@@ -32133,10 +32133,10 @@
         <v>0</v>
       </c>
       <c r="AA195">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB195">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,13 +32257,13 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="O196">
-        <v>3.09</v>
+        <v>4.42</v>
       </c>
       <c r="P196">
-        <v>2.67</v>
+        <v>4.85</v>
       </c>
       <c r="Q196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.65</v>
+        <v>2.68</v>
       </c>
       <c r="O197">
-        <v>3.84</v>
+        <v>3.09</v>
       </c>
       <c r="P197">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="Q197">
         <v>0</v>
@@ -32459,10 +32459,10 @@
         <v>0</v>
       </c>
       <c r="AA197">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB197">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="O198">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="P198">
-        <v>3.39</v>
+        <v>4.69</v>
       </c>
       <c r="Q198">
         <v>0</v>
@@ -32622,10 +32622,10 @@
         <v>0</v>
       </c>
       <c r="AA198">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB198">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC198">
         <v>0</v>
@@ -32704,7 +32704,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,13 +32746,13 @@
         </is>
       </c>
       <c r="N199">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O199">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q199">
         <v>0</v>
@@ -32867,7 +32867,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G200">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G201">
@@ -33203,12 +33203,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G202">
@@ -33356,22 +33356,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G203">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="O203">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P203">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33519,22 +33519,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G204">
@@ -33561,13 +33561,13 @@
         </is>
       </c>
       <c r="N204">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O204">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P204">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q204">
         <v>0</v>
@@ -33692,12 +33692,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G205">
@@ -33855,12 +33855,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G206">
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G207">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G208">
@@ -34213,13 +34213,13 @@
         </is>
       </c>
       <c r="N208">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O208">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P208">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q208">
         <v>0</v>
@@ -34252,10 +34252,10 @@
         <v>0</v>
       </c>
       <c r="AA208">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB208">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC208">
         <v>0</v>
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G209">
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>1.6</v>
+        <v>2.68</v>
       </c>
       <c r="O209">
-        <v>4.33</v>
+        <v>3.62</v>
       </c>
       <c r="P209">
-        <v>4.69</v>
+        <v>2.35</v>
       </c>
       <c r="Q209">
         <v>0</v>
@@ -34415,16 +34415,16 @@
         <v>0</v>
       </c>
       <c r="AA209">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB209">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC209">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD209">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE209">
         <v>0</v>
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G210">
@@ -34539,13 +34539,13 @@
         </is>
       </c>
       <c r="N210">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="O210">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P210">
-        <v>3.25</v>
+        <v>4.69</v>
       </c>
       <c r="Q210">
         <v>0</v>
@@ -34578,16 +34578,16 @@
         <v>0</v>
       </c>
       <c r="AA210">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB210">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC210">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD210">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE210">
         <v>0</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.22</v>
+        <v>2.14</v>
       </c>
       <c r="O211">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="P211">
-        <v>10.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q211">
         <v>0</v>
@@ -34741,16 +34741,16 @@
         <v>0</v>
       </c>
       <c r="AA211">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB211">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC211">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD211">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,13 +34865,13 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="O212">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="P212">
-        <v>4.74</v>
+        <v>10.5</v>
       </c>
       <c r="Q212">
         <v>0</v>
@@ -34910,10 +34910,10 @@
         <v>0</v>
       </c>
       <c r="AC212">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AD212">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AE212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,13 +35028,13 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="O213">
-        <v>3.74</v>
+        <v>4.3</v>
       </c>
       <c r="P213">
-        <v>4.47</v>
+        <v>4.74</v>
       </c>
       <c r="Q213">
         <v>0</v>
@@ -35067,16 +35067,16 @@
         <v>0</v>
       </c>
       <c r="AA213">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB213">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC213">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD213">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,13 +35191,13 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="O214">
-        <v>4.33</v>
+        <v>3.74</v>
       </c>
       <c r="P214">
-        <v>5.25</v>
+        <v>4.47</v>
       </c>
       <c r="Q214">
         <v>0</v>
@@ -35230,10 +35230,10 @@
         <v>0</v>
       </c>
       <c r="AA214">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AB214">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AC214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,13 +35354,13 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="O215">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="P215">
-        <v>4.71</v>
+        <v>5.25</v>
       </c>
       <c r="Q215">
         <v>0</v>
@@ -35393,10 +35393,10 @@
         <v>0</v>
       </c>
       <c r="AA215">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AB215">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AC215">
         <v>0</v>
@@ -35475,7 +35475,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,13 +35517,13 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="O216">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P216">
-        <v>3.98</v>
+        <v>4.71</v>
       </c>
       <c r="Q216">
         <v>0</v>
@@ -35556,10 +35556,10 @@
         <v>0</v>
       </c>
       <c r="AA216">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AB216">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC216">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G217">
@@ -35676,17 +35676,17 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N217">
-        <v>3.02</v>
+        <v>1.78</v>
       </c>
       <c r="O217">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P217">
-        <v>2.16</v>
+        <v>3.98</v>
       </c>
       <c r="Q217">
         <v>0</v>
@@ -35719,10 +35719,10 @@
         <v>0</v>
       </c>
       <c r="AA217">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB217">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G218">
@@ -35839,17 +35839,17 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N218">
-        <v>2.71</v>
+        <v>3.02</v>
       </c>
       <c r="O218">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="P218">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="Q218">
         <v>0</v>
@@ -35882,16 +35882,16 @@
         <v>0</v>
       </c>
       <c r="AA218">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB218">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC218">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AD218">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE218">
         <v>0</v>
@@ -35964,22 +35964,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G219">
@@ -36006,13 +36006,13 @@
         </is>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O219">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P219">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q219">
         <v>0</v>
@@ -36045,16 +36045,16 @@
         <v>0</v>
       </c>
       <c r="AA219">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB219">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC219">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD219">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE219">
         <v>0</v>
@@ -36137,12 +36137,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Skála</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G220">
@@ -36300,12 +36300,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Skála</t>
         </is>
       </c>
       <c r="G221">
@@ -36779,22 +36779,22 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G224">
@@ -36942,7 +36942,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -36952,12 +36952,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G225">
@@ -36984,13 +36984,13 @@
         </is>
       </c>
       <c r="N225">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O225">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P225">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q225">
         <v>0</v>
@@ -37115,12 +37115,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G226">
@@ -37147,13 +37147,13 @@
         </is>
       </c>
       <c r="N226">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="O226">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="P226">
-        <v>3.89</v>
+        <v>2.28</v>
       </c>
       <c r="Q226">
         <v>0</v>
@@ -37278,12 +37278,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G227">
@@ -37310,13 +37310,13 @@
         </is>
       </c>
       <c r="N227">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="O227">
-        <v>5.95</v>
+        <v>3.72</v>
       </c>
       <c r="P227">
-        <v>9.75</v>
+        <v>3.89</v>
       </c>
       <c r="Q227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,13 +37473,13 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="O228">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="P228">
-        <v>2.73</v>
+        <v>9.75</v>
       </c>
       <c r="Q228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,13 +37636,13 @@
         </is>
       </c>
       <c r="N229">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="O229">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P229">
-        <v>4.52</v>
+        <v>2.73</v>
       </c>
       <c r="Q229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,13 +37799,13 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.51</v>
+        <v>1.7</v>
       </c>
       <c r="O230">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="P230">
-        <v>1.86</v>
+        <v>4.52</v>
       </c>
       <c r="Q230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,13 +37962,13 @@
         </is>
       </c>
       <c r="N231">
-        <v>2.1</v>
+        <v>3.51</v>
       </c>
       <c r="O231">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P231">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q231">
         <v>0</v>
@@ -38001,10 +38001,10 @@
         <v>0</v>
       </c>
       <c r="AA231">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB231">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,13 +38125,13 @@
         </is>
       </c>
       <c r="N232">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="O232">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="P232">
-        <v>4.28</v>
+        <v>3.25</v>
       </c>
       <c r="Q232">
         <v>0</v>
@@ -38164,10 +38164,10 @@
         <v>0</v>
       </c>
       <c r="AA232">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB232">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC232">
         <v>0</v>
@@ -38246,7 +38246,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,13 +38288,13 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.33</v>
+        <v>1.74</v>
       </c>
       <c r="O233">
-        <v>3.26</v>
+        <v>3.82</v>
       </c>
       <c r="P233">
-        <v>2.61</v>
+        <v>4.28</v>
       </c>
       <c r="Q233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,13 +38451,13 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.56</v>
+        <v>2.33</v>
       </c>
       <c r="O234">
-        <v>4.25</v>
+        <v>3.26</v>
       </c>
       <c r="P234">
-        <v>5.54</v>
+        <v>2.61</v>
       </c>
       <c r="Q234">
         <v>0</v>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Llanera</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,13 +38614,13 @@
         </is>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O235">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P235">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="Q235">
         <v>0</v>
@@ -38735,7 +38735,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Llanera</t>
         </is>
       </c>
       <c r="G236">
@@ -38773,7 +38773,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N236">
@@ -38898,7 +38898,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G237">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N237">
@@ -39061,7 +39061,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -39071,12 +39071,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G238">
@@ -39103,13 +39103,13 @@
         </is>
       </c>
       <c r="N238">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O238">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P238">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q238">
         <v>0</v>
@@ -39219,12 +39219,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -39234,12 +39234,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G239">
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.48</v>
+        <v>3.54</v>
       </c>
       <c r="O239">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="P239">
-        <v>2.86</v>
+        <v>1.99</v>
       </c>
       <c r="Q239">
         <v>0</v>
@@ -39305,10 +39305,10 @@
         <v>0</v>
       </c>
       <c r="AA239">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB239">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC239">
         <v>0</v>
@@ -39370,7 +39370,7 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>2026-10-31 12:15:00</t>
+          <t>2026-10-31 12:00:00</t>
         </is>
       </c>
     </row>
@@ -39387,7 +39387,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -39397,12 +39397,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G240">
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O240">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="P240">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q240">
         <v>0</v>
@@ -39468,10 +39468,10 @@
         <v>0</v>
       </c>
       <c r="AA240">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB240">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC240">
         <v>0</v>
@@ -39545,27 +39545,27 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G241">
@@ -39696,7 +39696,7 @@
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>2026-10-31 12:30:00</t>
+          <t>2026-10-31 12:15:00</t>
         </is>
       </c>
     </row>
@@ -39723,12 +39723,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G242">
@@ -39876,22 +39876,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G243">
@@ -40049,12 +40049,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G244">
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G245">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,13 +40407,13 @@
         </is>
       </c>
       <c r="N246">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O246">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="P246">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q246">
         <v>0</v>
@@ -40446,10 +40446,10 @@
         <v>0</v>
       </c>
       <c r="AA246">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB246">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC246">
         <v>0</v>
@@ -40528,22 +40528,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G247">
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O247">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P247">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q247">
         <v>0</v>
@@ -40609,10 +40609,10 @@
         <v>0</v>
       </c>
       <c r="AA247">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB247">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC247">
         <v>0</v>
@@ -40691,22 +40691,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Peña Sport FC</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G248">
@@ -40854,7 +40854,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -40864,12 +40864,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Fortuna Köln</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Peña Sport FC</t>
         </is>
       </c>
       <c r="G249">
@@ -41017,7 +41017,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -41027,12 +41027,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Fortuna Köln</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="G250">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -41190,12 +41190,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G251">
@@ -41222,13 +41222,13 @@
         </is>
       </c>
       <c r="N251">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O251">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P251">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q251">
         <v>0</v>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G252">
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>1.12</v>
+        <v>2.89</v>
       </c>
       <c r="O252">
-        <v>10.2</v>
+        <v>3.36</v>
       </c>
       <c r="P252">
-        <v>18</v>
+        <v>2.58</v>
       </c>
       <c r="Q252">
         <v>0</v>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -41516,12 +41516,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G253">
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="O253">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="P253">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q253">
         <v>0</v>
@@ -41664,12 +41664,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G254">
@@ -41815,7 +41815,7 @@
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>2026-10-31 13:00:00</t>
+          <t>2026-10-31 12:30:00</t>
         </is>
       </c>
     </row>
@@ -41832,7 +41832,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -41842,12 +41842,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G255">
@@ -42005,12 +42005,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G256">
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G257">
@@ -42321,7 +42321,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G258">
@@ -42484,7 +42484,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G259">
@@ -42647,7 +42647,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -42657,12 +42657,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G260">
@@ -42810,7 +42810,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -42820,12 +42820,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G261">
@@ -42973,22 +42973,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G262">
@@ -43136,22 +43136,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G263">
@@ -43299,7 +43299,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -43309,12 +43309,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G264">
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O264">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P264">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43462,7 +43462,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -43472,12 +43472,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="G265">
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O265">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P265">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q265">
         <v>0</v>
@@ -43625,7 +43625,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -43635,12 +43635,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="G266">
@@ -43667,13 +43667,13 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O266">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P266">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q266">
         <v>0</v>
@@ -43788,7 +43788,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -43798,12 +43798,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G267">
@@ -43830,13 +43830,13 @@
         </is>
       </c>
       <c r="N267">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O267">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P267">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q267">
         <v>0</v>
@@ -43951,7 +43951,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -43961,12 +43961,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G268">
@@ -44109,12 +44109,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -44124,12 +44124,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G269">
@@ -44156,13 +44156,13 @@
         </is>
       </c>
       <c r="N269">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O269">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P269">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="Q269">
         <v>0</v>
@@ -44260,7 +44260,7 @@
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>2026-10-31 13:15:00</t>
+          <t>2026-10-31 13:00:00</t>
         </is>
       </c>
     </row>
@@ -44277,7 +44277,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -44287,12 +44287,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G270">
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.78</v>
+        <v>2.11</v>
       </c>
       <c r="O270">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="P270">
-        <v>2.53</v>
+        <v>3.27</v>
       </c>
       <c r="Q270">
         <v>0</v>
@@ -44435,12 +44435,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O271">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P271">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q271">
         <v>0</v>
@@ -44586,7 +44586,7 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>2026-10-31 13:30:00</t>
+          <t>2026-10-31 13:15:00</t>
         </is>
       </c>
     </row>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G272">
@@ -44766,22 +44766,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G273">
@@ -44929,22 +44929,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G274">
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O274">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P274">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45092,7 +45092,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -45102,12 +45102,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G275">
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45418,7 +45418,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G277">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G278">
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G279">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G280">
@@ -46065,12 +46065,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -46080,12 +46080,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="G281">
@@ -46108,7 +46108,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N281">
@@ -46216,7 +46216,7 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>2026-10-31 13:45:00</t>
+          <t>2026-10-31 13:30:00</t>
         </is>
       </c>
     </row>
@@ -46243,12 +46243,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G282">
@@ -46271,7 +46271,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N282">
@@ -53731,22 +53731,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G328">
@@ -53894,22 +53894,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G329">
@@ -53936,13 +53936,13 @@
         </is>
       </c>
       <c r="N329">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="O329">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P329">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q329">
         <v>0</v>
@@ -54057,22 +54057,22 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G330">
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="O330">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="P330">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Q330">
         <v>0</v>
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G331">
@@ -54383,22 +54383,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="G332">
@@ -54425,13 +54425,13 @@
         </is>
       </c>
       <c r="N332">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O332">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P332">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q332">
         <v>0</v>
@@ -54546,22 +54546,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G333">
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="O333">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
       <c r="P333">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54627,10 +54627,10 @@
         <v>0</v>
       </c>
       <c r="AA333">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB333">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC333">
         <v>0</v>
@@ -54704,27 +54704,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G334">
@@ -54751,13 +54751,13 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="O334">
-        <v>3.16</v>
+        <v>3.58</v>
       </c>
       <c r="P334">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="Q334">
         <v>0</v>
@@ -54790,10 +54790,10 @@
         <v>0</v>
       </c>
       <c r="AA334">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB334">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC334">
         <v>0</v>
@@ -54855,7 +54855,7 @@
       </c>
       <c r="AU334" t="inlineStr">
         <is>
-          <t>2026-10-31 16:00:00</t>
+          <t>2026-10-31 16:15:00</t>
         </is>
       </c>
     </row>
@@ -54867,12 +54867,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -54882,12 +54882,12 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G335">
@@ -54914,13 +54914,13 @@
         </is>
       </c>
       <c r="N335">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="O335">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="P335">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -54959,10 +54959,10 @@
         <v>0</v>
       </c>
       <c r="AC335">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD335">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE335">
         <v>0</v>
@@ -55018,7 +55018,7 @@
       </c>
       <c r="AU335" t="inlineStr">
         <is>
-          <t>2026-10-31 16:15:00</t>
+          <t>2026-10-31 16:30:00</t>
         </is>
       </c>
     </row>
@@ -55035,7 +55035,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -55045,12 +55045,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G336">
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O336">
-        <v>3.89</v>
+        <v>3.6</v>
       </c>
       <c r="P336">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="Q336">
         <v>0</v>
@@ -55122,10 +55122,10 @@
         <v>0</v>
       </c>
       <c r="AC336">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AD336">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AE336">
         <v>0</v>
@@ -55193,12 +55193,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -55208,12 +55208,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G337">
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="O337">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P337">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="Q337">
         <v>0</v>
@@ -55279,16 +55279,16 @@
         <v>0</v>
       </c>
       <c r="AA337">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB337">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC337">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD337">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE337">
         <v>0</v>
@@ -55344,7 +55344,7 @@
       </c>
       <c r="AU337" t="inlineStr">
         <is>
-          <t>2026-10-31 16:30:00</t>
+          <t>2026-10-31 16:45:00</t>
         </is>
       </c>
     </row>
@@ -55371,12 +55371,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G338">
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>2.93</v>
+        <v>1.44</v>
       </c>
       <c r="O338">
-        <v>3.62</v>
+        <v>5.24</v>
       </c>
       <c r="P338">
-        <v>2.52</v>
+        <v>7.7</v>
       </c>
       <c r="Q338">
         <v>0</v>
@@ -55442,10 +55442,10 @@
         <v>0</v>
       </c>
       <c r="AA338">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB338">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC338">
         <v>0</v>
@@ -55534,12 +55534,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G339">
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="O339">
-        <v>5.24</v>
+        <v>3.76</v>
       </c>
       <c r="P339">
-        <v>7.7</v>
+        <v>3.39</v>
       </c>
       <c r="Q339">
         <v>0</v>
@@ -55605,10 +55605,10 @@
         <v>0</v>
       </c>
       <c r="AA339">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB339">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC339">
         <v>0</v>
@@ -55687,7 +55687,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -55697,12 +55697,12 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G340">
@@ -55729,13 +55729,13 @@
         </is>
       </c>
       <c r="N340">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="O340">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="P340">
-        <v>3.39</v>
+        <v>2.41</v>
       </c>
       <c r="Q340">
         <v>0</v>
@@ -55768,10 +55768,10 @@
         <v>0</v>
       </c>
       <c r="AA340">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB340">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC340">
         <v>0</v>
@@ -55850,7 +55850,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -55860,12 +55860,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G341">
@@ -55892,13 +55892,13 @@
         </is>
       </c>
       <c r="N341">
-        <v>2.94</v>
+        <v>1.67</v>
       </c>
       <c r="O341">
-        <v>3.85</v>
+        <v>4.22</v>
       </c>
       <c r="P341">
-        <v>2.41</v>
+        <v>4.74</v>
       </c>
       <c r="Q341">
         <v>0</v>
@@ -56023,12 +56023,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G342">
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.67</v>
+        <v>5.57</v>
       </c>
       <c r="O342">
-        <v>4.22</v>
+        <v>4.44</v>
       </c>
       <c r="P342">
-        <v>4.74</v>
+        <v>1.56</v>
       </c>
       <c r="Q342">
         <v>0</v>
@@ -56171,12 +56171,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -56186,12 +56186,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G343">
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>5.57</v>
+        <v>2.14</v>
       </c>
       <c r="O343">
-        <v>4.44</v>
+        <v>3.8</v>
       </c>
       <c r="P343">
-        <v>1.56</v>
+        <v>3.52</v>
       </c>
       <c r="Q343">
         <v>0</v>
@@ -56257,10 +56257,10 @@
         <v>0</v>
       </c>
       <c r="AA343">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB343">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC343">
         <v>0</v>
@@ -56322,7 +56322,7 @@
       </c>
       <c r="AU343" t="inlineStr">
         <is>
-          <t>2026-10-31 16:45:00</t>
+          <t>2026-10-31 17:00:00</t>
         </is>
       </c>
     </row>
@@ -56339,7 +56339,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -56349,12 +56349,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G344">
@@ -56381,13 +56381,13 @@
         </is>
       </c>
       <c r="N344">
-        <v>2.14</v>
+        <v>2.77</v>
       </c>
       <c r="O344">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="P344">
-        <v>3.52</v>
+        <v>2.66</v>
       </c>
       <c r="Q344">
         <v>0</v>
@@ -56420,10 +56420,10 @@
         <v>0</v>
       </c>
       <c r="AA344">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB344">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC344">
         <v>0</v>
@@ -56502,7 +56502,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -56512,12 +56512,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G345">
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="O345">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="P345">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q345">
         <v>0</v>
@@ -56665,7 +56665,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -56675,12 +56675,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G346">
@@ -56828,7 +56828,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -56838,12 +56838,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G347">
@@ -56870,13 +56870,13 @@
         </is>
       </c>
       <c r="N347">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O347">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P347">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q347">
         <v>0</v>
@@ -57001,12 +57001,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G348">
@@ -57033,13 +57033,13 @@
         </is>
       </c>
       <c r="N348">
-        <v>3.25</v>
+        <v>1.89</v>
       </c>
       <c r="O348">
-        <v>4.05</v>
+        <v>4.23</v>
       </c>
       <c r="P348">
-        <v>2.05</v>
+        <v>3.63</v>
       </c>
       <c r="Q348">
         <v>0</v>
@@ -57149,27 +57149,27 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,13 +57196,13 @@
         </is>
       </c>
       <c r="N349">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O349">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="P349">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q349">
         <v>0</v>
@@ -57300,7 +57300,7 @@
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>2026-10-31 17:00:00</t>
+          <t>2026-10-31 17:30:00</t>
         </is>
       </c>
     </row>
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G350">
@@ -57480,22 +57480,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G351">
@@ -57522,13 +57522,13 @@
         </is>
       </c>
       <c r="N351">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O351">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P351">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q351">
         <v>0</v>
@@ -57638,27 +57638,27 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O352">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P352">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Q352">
         <v>0</v>
@@ -57789,7 +57789,7 @@
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>2026-10-31 17:30:00</t>
+          <t>2026-10-31 18:00:00</t>
         </is>
       </c>
     </row>
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G353">
@@ -57969,7 +57969,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G354">
@@ -58127,12 +58127,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G355">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="AU355" t="inlineStr">
         <is>
-          <t>2026-10-31 18:00:00</t>
+          <t>2026-10-31 18:15:00</t>
         </is>
       </c>
     </row>
@@ -58290,12 +58290,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G356">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AU356" t="inlineStr">
         <is>
-          <t>2026-10-31 18:15:00</t>
+          <t>2026-10-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -58453,12 +58453,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G357">
@@ -58604,7 +58604,7 @@
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>2026-10-31 19:30:00</t>
+          <t>2026-10-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -58616,27 +58616,27 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G358">
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AU358" t="inlineStr">
         <is>
-          <t>2026-10-31 20:00:00</t>
+          <t>2026-10-31 21:00:00</t>
         </is>
       </c>
     </row>
@@ -58784,22 +58784,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G359">
@@ -58957,12 +58957,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G360">
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G361">
@@ -59283,12 +59283,12 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G362">
@@ -59446,12 +59446,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G363">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G364">
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G366">
@@ -60088,22 +60088,22 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G367">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G368">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G369">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G370">
@@ -60750,12 +60750,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G371">
@@ -60913,12 +60913,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G372">
@@ -61076,12 +61076,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G373">
@@ -61239,12 +61239,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G374">
@@ -61387,27 +61387,27 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G375">
@@ -61537,169 +61537,6 @@
         <v>0</v>
       </c>
       <c r="AU375" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="G376">
-        <v>0</v>
-      </c>
-      <c r="H376">
-        <v>0</v>
-      </c>
-      <c r="I376">
-        <v>0</v>
-      </c>
-      <c r="J376">
-        <v>0</v>
-      </c>
-      <c r="K376">
-        <v>0</v>
-      </c>
-      <c r="L376">
-        <v>0</v>
-      </c>
-      <c r="M376" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N376">
-        <v>0</v>
-      </c>
-      <c r="O376">
-        <v>0</v>
-      </c>
-      <c r="P376">
-        <v>0</v>
-      </c>
-      <c r="Q376">
-        <v>0</v>
-      </c>
-      <c r="R376">
-        <v>0</v>
-      </c>
-      <c r="S376">
-        <v>0</v>
-      </c>
-      <c r="T376">
-        <v>0</v>
-      </c>
-      <c r="U376">
-        <v>0</v>
-      </c>
-      <c r="V376">
-        <v>0</v>
-      </c>
-      <c r="W376">
-        <v>0</v>
-      </c>
-      <c r="X376">
-        <v>0</v>
-      </c>
-      <c r="Y376">
-        <v>0</v>
-      </c>
-      <c r="Z376">
-        <v>0</v>
-      </c>
-      <c r="AA376">
-        <v>0</v>
-      </c>
-      <c r="AB376">
-        <v>0</v>
-      </c>
-      <c r="AC376">
-        <v>0</v>
-      </c>
-      <c r="AD376">
-        <v>0</v>
-      </c>
-      <c r="AE376">
-        <v>0</v>
-      </c>
-      <c r="AF376">
-        <v>0</v>
-      </c>
-      <c r="AG376">
-        <v>0</v>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ376">
-        <v>0</v>
-      </c>
-      <c r="AK376">
-        <v>0</v>
-      </c>
-      <c r="AL376">
-        <v>0</v>
-      </c>
-      <c r="AM376">
-        <v>-1</v>
-      </c>
-      <c r="AN376">
-        <v>-1</v>
-      </c>
-      <c r="AO376">
-        <v>-1</v>
-      </c>
-      <c r="AP376">
-        <v>-1</v>
-      </c>
-      <c r="AQ376">
-        <v>0</v>
-      </c>
-      <c r="AR376">
-        <v>0</v>
-      </c>
-      <c r="AS376">
-        <v>0</v>
-      </c>
-      <c r="AT376">
-        <v>0</v>
-      </c>
-      <c r="AU376" t="inlineStr">
         <is>
           <t>2026-10-31 22:30:00</t>
         </is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="O6">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="P6">
-        <v>2.03</v>
+        <v>2.97</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="O7">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="P7">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.69</v>
+        <v>1.98</v>
       </c>
       <c r="O8">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="P8">
-        <v>2.33</v>
+        <v>3.49</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.98</v>
+        <v>3.52</v>
       </c>
       <c r="O9">
-        <v>3.18</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>3.49</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.52</v>
+        <v>1.72</v>
       </c>
       <c r="O10">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>4.01</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="O11">
-        <v>3.64</v>
+        <v>3.52</v>
       </c>
       <c r="P11">
-        <v>4.01</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="P19">
-        <v>3.95</v>
+        <v>4.36</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="O20">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="P20">
-        <v>4.36</v>
+        <v>3.95</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="O88">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="P88">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="O89">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="P89">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14855,10 +14855,10 @@
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC89">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G96">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G99">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G135">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G145">
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="O162">
         <v>3.8</v>
       </c>
       <c r="P162">
-        <v>3.74</v>
+        <v>2.22</v>
       </c>
       <c r="Q162">
         <v>0</v>
@@ -26846,12 +26846,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G163">
@@ -26878,13 +26878,13 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.6</v>
+        <v>1.65</v>
       </c>
       <c r="O163">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P163">
-        <v>2.22</v>
+        <v>4.42</v>
       </c>
       <c r="Q163">
         <v>0</v>
@@ -27009,12 +27009,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Voitsberg</t>
         </is>
       </c>
       <c r="G164">
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="O164">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P164">
-        <v>4.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27172,12 +27172,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Voitsberg</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G165">
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.4</v>
+        <v>1.79</v>
       </c>
       <c r="O165">
         <v>3.8</v>
       </c>
       <c r="P165">
-        <v>2.4</v>
+        <v>3.74</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="O178">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="P178">
-        <v>2.71</v>
+        <v>3.65</v>
       </c>
       <c r="Q178">
         <v>0</v>
@@ -29362,10 +29362,10 @@
         <v>0</v>
       </c>
       <c r="AA178">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AB178">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="O179">
-        <v>3.89</v>
+        <v>3.62</v>
       </c>
       <c r="P179">
-        <v>3.65</v>
+        <v>2.71</v>
       </c>
       <c r="Q179">
         <v>0</v>
@@ -29525,10 +29525,10 @@
         <v>0</v>
       </c>
       <c r="AA179">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AB179">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC179">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G365">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G366">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G28">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G117">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G136">

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S15">
         <v>1.36</v>
@@ -2793,10 +2793,10 @@
         <v>3.25</v>
       </c>
       <c r="AA15">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
         <v>3.34</v>
@@ -2808,7 +2808,7 @@
         <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
         <v>1.95</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
         <v>1.48</v>
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.53</v>
+        <v>3.4</v>
       </c>
       <c r="O16">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="P16">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q16">
         <v>4.1</v>
       </c>
       <c r="R16">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
+        <v>1.36</v>
+      </c>
+      <c r="T16">
+        <v>2.8</v>
+      </c>
+      <c r="U16">
+        <v>2.67</v>
+      </c>
+      <c r="V16">
         <v>1.4</v>
       </c>
-      <c r="T16">
-        <v>2.86</v>
-      </c>
-      <c r="U16">
-        <v>3.03</v>
-      </c>
-      <c r="V16">
-        <v>1.36</v>
-      </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z16">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA16">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AC16">
-        <v>3.61</v>
+        <v>3.39</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AK16">
         <v>1.28</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>6.57</v>
+        <v>6.5</v>
       </c>
       <c r="O17">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="P17">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q17">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S17">
         <v>1.3</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
-        <v>4.36</v>
+        <v>4.1</v>
       </c>
       <c r="Q20">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
         <v>1.26</v>
@@ -3626,7 +3626,7 @@
         <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="O21">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
         <v>2.3</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3771,10 +3771,10 @@
         <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AC21">
         <v>2.62</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O30">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q30">
         <v>2.5</v>
@@ -5217,7 +5217,7 @@
         <v>1.25</v>
       </c>
       <c r="T30">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="U30">
         <v>2.21</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="O35">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P35">
-        <v>3.17</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
         <v>2.62</v>
@@ -6177,25 +6177,25 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="O36">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="P36">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S36">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U36">
         <v>2.27</v>
@@ -6231,10 +6231,10 @@
         <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG36">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="O41">
-        <v>4.32</v>
+        <v>5</v>
       </c>
       <c r="P41">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="O42">
-        <v>3.11</v>
+        <v>3.43</v>
       </c>
       <c r="P42">
-        <v>3.91</v>
+        <v>3.43</v>
       </c>
       <c r="Q42">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="R42">
         <v>2.1</v>
@@ -7182,10 +7182,10 @@
         <v>1.36</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
         <v>1.3</v>
@@ -7200,19 +7200,19 @@
         <v>1.75</v>
       </c>
       <c r="AC42">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE42">
         <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7481,58 +7481,58 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="P44">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="Q44">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="S44">
         <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V44">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
         <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z44">
         <v>4.15</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC44">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
         <v>1.45</v>
       </c>
       <c r="AE44">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
         <v>1.59</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7659,10 +7659,10 @@
         <v>2.15</v>
       </c>
       <c r="S45">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T45">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U45">
         <v>2.5</v>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="O46">
-        <v>3.22</v>
+        <v>3.81</v>
       </c>
       <c r="P46">
-        <v>2.87</v>
+        <v>4.31</v>
       </c>
       <c r="Q46">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R46">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S46">
         <v>1.35</v>
       </c>
       <c r="T46">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U46">
         <v>2.75</v>
@@ -7834,13 +7834,13 @@
         <v>1.4</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z46">
         <v>3.3</v>
@@ -7852,19 +7852,19 @@
         <v>1.83</v>
       </c>
       <c r="AC46">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD46">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
         <v>1.07</v>
       </c>
       <c r="AF46">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG46">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>5.33</v>
+        <v>4.72</v>
       </c>
       <c r="O47">
-        <v>3.92</v>
+        <v>4.01</v>
       </c>
       <c r="P47">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q47">
         <v>4.9</v>
@@ -7985,40 +7985,40 @@
         <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U47">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="V47">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA47">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB47">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC47">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD47">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE47">
         <v>1.13</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Hai Phong</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bình Phước</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hai Phong</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bình Phước</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G53">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,80 +11882,80 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.65</v>
+        <v>1.41</v>
       </c>
       <c r="O71">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="P71">
-        <v>2.3</v>
+        <v>6.03</v>
       </c>
       <c r="Q71">
-        <v>3.36</v>
+        <v>1.91</v>
       </c>
       <c r="R71">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="S71">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="T71">
-        <v>3.4</v>
+        <v>4.15</v>
       </c>
       <c r="U71">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="V71">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="W71">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z71">
-        <v>4.67</v>
+        <v>7</v>
       </c>
       <c r="AA71">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB71">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="AC71">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="AD71">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AE71">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AF71">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AG71">
+        <v>2.7</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>1.18</v>
+      </c>
+      <c r="AK71">
         <v>2.45</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>1.27</v>
-      </c>
-      <c r="AK71">
-        <v>1.42</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,80 +12045,80 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="O72">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P72">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q72">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="R72">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="S72">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T72">
-        <v>3.78</v>
+        <v>3.4</v>
       </c>
       <c r="U72">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="V72">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="W72">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>5.5</v>
+        <v>4.67</v>
       </c>
       <c r="AA72">
+        <v>1.57</v>
+      </c>
+      <c r="AB72">
+        <v>2.26</v>
+      </c>
+      <c r="AC72">
+        <v>2.25</v>
+      </c>
+      <c r="AD72">
+        <v>1.57</v>
+      </c>
+      <c r="AE72">
+        <v>1.16</v>
+      </c>
+      <c r="AF72">
+        <v>1.47</v>
+      </c>
+      <c r="AG72">
+        <v>2.45</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>1.27</v>
+      </c>
+      <c r="AK72">
         <v>1.42</v>
-      </c>
-      <c r="AB72">
-        <v>2.49</v>
-      </c>
-      <c r="AC72">
-        <v>2.15</v>
-      </c>
-      <c r="AD72">
-        <v>1.6</v>
-      </c>
-      <c r="AE72">
-        <v>1.25</v>
-      </c>
-      <c r="AF72">
-        <v>1.4</v>
-      </c>
-      <c r="AG72">
-        <v>2.75</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ72">
-        <v>1.6</v>
-      </c>
-      <c r="AK72">
-        <v>1.4</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.41</v>
+        <v>2.66</v>
       </c>
       <c r="O73">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="P73">
-        <v>6.03</v>
+        <v>2.32</v>
       </c>
       <c r="Q73">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="R73">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S73">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="T73">
-        <v>4.15</v>
+        <v>3.78</v>
       </c>
       <c r="U73">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V73">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="W73">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z73">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA73">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AB73">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="AC73">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AD73">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AE73">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AF73">
         <v>1.4</v>
       </c>
       <c r="AG73">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="AK73">
-        <v>2.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="O76">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P76">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q76">
         <v>7.6</v>
@@ -12712,13 +12712,13 @@
         <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T76">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U76">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V76">
         <v>1.34</v>
@@ -12736,10 +12736,10 @@
         <v>2.83</v>
       </c>
       <c r="AA76">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB76">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC76">
         <v>3.84</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="O78">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q78">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S78">
         <v>1.26</v>
@@ -13077,10 +13077,10 @@
         <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG78">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -20684,13 +20684,13 @@
         </is>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O125">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P125">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q125">
         <v>0</v>
@@ -20723,10 +20723,10 @@
         <v>0</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB125">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC125">
         <v>0</v>
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -21010,13 +21010,13 @@
         </is>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O127">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P127">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -21049,10 +21049,10 @@
         <v>0</v>
       </c>
       <c r="AA127">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB127">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC127">
         <v>0</v>
@@ -21173,13 +21173,13 @@
         </is>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O128">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -21212,10 +21212,10 @@
         <v>0</v>
       </c>
       <c r="AA128">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC128">
         <v>0</v>
@@ -21336,13 +21336,13 @@
         </is>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P129">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q129">
         <v>0</v>
@@ -21375,10 +21375,10 @@
         <v>0</v>
       </c>
       <c r="AA129">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB129">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC129">
         <v>0</v>
@@ -26235,55 +26235,55 @@
         <v>0</v>
       </c>
       <c r="Q159">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R159">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S159">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T159">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U159">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V159">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W159">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X159">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z159">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA159">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB159">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC159">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD159">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE159">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF159">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG159">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26296,10 +26296,10 @@
         </is>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK159">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL159">
         <v>0</v>
@@ -26520,12 +26520,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G161">
@@ -26552,80 +26552,80 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.66</v>
+        <v>2.17</v>
       </c>
       <c r="O161">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="P161">
-        <v>4.07</v>
+        <v>2.74</v>
       </c>
       <c r="Q161">
-        <v>2.17</v>
+        <v>2.69</v>
       </c>
       <c r="R161">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="S161">
+        <v>1.24</v>
+      </c>
+      <c r="T161">
+        <v>3.6</v>
+      </c>
+      <c r="U161">
+        <v>2.2</v>
+      </c>
+      <c r="V161">
+        <v>1.57</v>
+      </c>
+      <c r="W161">
+        <v>1.14</v>
+      </c>
+      <c r="X161">
+        <v>1.01</v>
+      </c>
+      <c r="Y161">
+        <v>1.12</v>
+      </c>
+      <c r="Z161">
+        <v>4.98</v>
+      </c>
+      <c r="AA161">
+        <v>1.52</v>
+      </c>
+      <c r="AB161">
+        <v>2.31</v>
+      </c>
+      <c r="AC161">
+        <v>2.34</v>
+      </c>
+      <c r="AD161">
+        <v>1.57</v>
+      </c>
+      <c r="AE161">
+        <v>1.22</v>
+      </c>
+      <c r="AF161">
+        <v>1.46</v>
+      </c>
+      <c r="AG161">
+        <v>2.5</v>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ161">
         <v>1.2</v>
       </c>
-      <c r="T161">
-        <v>4</v>
-      </c>
-      <c r="U161">
-        <v>1.95</v>
-      </c>
-      <c r="V161">
-        <v>1.7</v>
-      </c>
-      <c r="W161">
-        <v>1.18</v>
-      </c>
-      <c r="X161">
-        <v>1.02</v>
-      </c>
-      <c r="Y161">
-        <v>1.07</v>
-      </c>
-      <c r="Z161">
-        <v>5.8</v>
-      </c>
-      <c r="AA161">
-        <v>1.37</v>
-      </c>
-      <c r="AB161">
-        <v>2.66</v>
-      </c>
-      <c r="AC161">
-        <v>1.99</v>
-      </c>
-      <c r="AD161">
-        <v>1.7</v>
-      </c>
-      <c r="AE161">
-        <v>1.26</v>
-      </c>
-      <c r="AF161">
-        <v>1.4</v>
-      </c>
-      <c r="AG161">
-        <v>2.7</v>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ161">
-        <v>1.16</v>
-      </c>
       <c r="AK161">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G162">
@@ -26715,64 +26715,64 @@
         </is>
       </c>
       <c r="N162">
+        <v>1.66</v>
+      </c>
+      <c r="O162">
+        <v>3.88</v>
+      </c>
+      <c r="P162">
+        <v>4.07</v>
+      </c>
+      <c r="Q162">
         <v>2.17</v>
       </c>
-      <c r="O162">
-        <v>3.56</v>
-      </c>
-      <c r="P162">
-        <v>2.74</v>
-      </c>
-      <c r="Q162">
-        <v>2.69</v>
-      </c>
       <c r="R162">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="S162">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T162">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U162">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="V162">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W162">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X162">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Z162">
-        <v>4.98</v>
+        <v>5.8</v>
       </c>
       <c r="AA162">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AB162">
-        <v>2.31</v>
+        <v>2.66</v>
       </c>
       <c r="AC162">
-        <v>2.34</v>
+        <v>1.99</v>
       </c>
       <c r="AD162">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE162">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF162">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG162">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26785,10 +26785,10 @@
         </is>
       </c>
       <c r="AJ162">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK162">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AL162">
         <v>0</v>
@@ -26887,55 +26887,55 @@
         <v>0</v>
       </c>
       <c r="Q163">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R163">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S163">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T163">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U163">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V163">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W163">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X163">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y163">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z163">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="AA163">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB163">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC163">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD163">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE163">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF163">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG163">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH163" t="inlineStr">
         <is>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK163">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="O177">
-        <v>3.7</v>
+        <v>3.89</v>
       </c>
       <c r="P177">
-        <v>3.14</v>
+        <v>3.65</v>
       </c>
       <c r="Q177">
+        <v>2.51</v>
+      </c>
+      <c r="R177">
+        <v>2.28</v>
+      </c>
+      <c r="S177">
+        <v>1.3</v>
+      </c>
+      <c r="T177">
+        <v>3.25</v>
+      </c>
+      <c r="U177">
         <v>2.44</v>
       </c>
-      <c r="R177">
-        <v>2.14</v>
-      </c>
-      <c r="S177">
-        <v>1.4</v>
-      </c>
-      <c r="T177">
-        <v>2.88</v>
-      </c>
-      <c r="U177">
-        <v>2.5</v>
-      </c>
       <c r="V177">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W177">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X177">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z177">
-        <v>3.56</v>
+        <v>4.14</v>
       </c>
       <c r="AA177">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB177">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC177">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="AD177">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE177">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF177">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AK177">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,64 +29323,64 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.07</v>
+        <v>2.79</v>
       </c>
       <c r="O178">
-        <v>3.89</v>
+        <v>3.53</v>
       </c>
       <c r="P178">
-        <v>3.65</v>
+        <v>2.67</v>
       </c>
       <c r="Q178">
-        <v>2.51</v>
+        <v>3.3</v>
       </c>
       <c r="R178">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="S178">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T178">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U178">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="V178">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W178">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X178">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z178">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="AA178">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AB178">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AC178">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="AD178">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AE178">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="AF178">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG178">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK178">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="O179">
-        <v>3.53</v>
+        <v>3.7</v>
       </c>
       <c r="P179">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="Q179">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="R179">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="S179">
         <v>1.4</v>
       </c>
       <c r="T179">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U179">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="V179">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W179">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X179">
         <v>1.03</v>
       </c>
       <c r="Y179">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z179">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="AA179">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AB179">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC179">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD179">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE179">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF179">
         <v>1.67</v>
       </c>
       <c r="AG179">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK179">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -30310,55 +30310,55 @@
         <v>0</v>
       </c>
       <c r="Q184">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S184">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T184">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U184">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V184">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W184">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X184">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y184">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z184">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA184">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB184">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC184">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD184">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE184">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF184">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG184">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,10 +30371,10 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK184">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL184">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
+        <v>2.17</v>
+      </c>
+      <c r="O191">
+        <v>3.18</v>
+      </c>
+      <c r="P191">
+        <v>3.03</v>
+      </c>
+      <c r="Q191">
+        <v>2.78</v>
+      </c>
+      <c r="R191">
+        <v>2.08</v>
+      </c>
+      <c r="S191">
+        <v>1.34</v>
+      </c>
+      <c r="T191">
+        <v>2.8</v>
+      </c>
+      <c r="U191">
+        <v>2.76</v>
+      </c>
+      <c r="V191">
+        <v>1.35</v>
+      </c>
+      <c r="W191">
+        <v>1.05</v>
+      </c>
+      <c r="X191">
+        <v>1.03</v>
+      </c>
+      <c r="Y191">
+        <v>1.25</v>
+      </c>
+      <c r="Z191">
+        <v>3.28</v>
+      </c>
+      <c r="AA191">
+        <v>1.87</v>
+      </c>
+      <c r="AB191">
+        <v>1.8</v>
+      </c>
+      <c r="AC191">
+        <v>3.2</v>
+      </c>
+      <c r="AD191">
+        <v>1.25</v>
+      </c>
+      <c r="AE191">
+        <v>1.05</v>
+      </c>
+      <c r="AF191">
         <v>1.73</v>
       </c>
-      <c r="O191">
-        <v>3.44</v>
-      </c>
-      <c r="P191">
-        <v>4.25</v>
-      </c>
-      <c r="Q191">
-        <v>2.33</v>
-      </c>
-      <c r="R191">
-        <v>2.09</v>
-      </c>
-      <c r="S191">
-        <v>1.36</v>
-      </c>
-      <c r="T191">
-        <v>2.72</v>
-      </c>
-      <c r="U191">
-        <v>2.85</v>
-      </c>
-      <c r="V191">
-        <v>1.33</v>
-      </c>
-      <c r="W191">
-        <v>1.03</v>
-      </c>
-      <c r="X191">
-        <v>1.02</v>
-      </c>
-      <c r="Y191">
-        <v>1.27</v>
-      </c>
-      <c r="Z191">
-        <v>3.14</v>
-      </c>
-      <c r="AA191">
-        <v>1.97</v>
-      </c>
-      <c r="AB191">
-        <v>1.79</v>
-      </c>
-      <c r="AC191">
-        <v>3.42</v>
-      </c>
-      <c r="AD191">
-        <v>1.23</v>
-      </c>
-      <c r="AE191">
-        <v>1.04</v>
-      </c>
-      <c r="AF191">
-        <v>1.84</v>
-      </c>
       <c r="AG191">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK191">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="O192">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="P192">
-        <v>3.03</v>
+        <v>4.25</v>
       </c>
       <c r="Q192">
-        <v>2.78</v>
+        <v>2.33</v>
       </c>
       <c r="R192">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S192">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T192">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="U192">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="V192">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W192">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X192">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y192">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z192">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA192">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AB192">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC192">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD192">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE192">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF192">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AG192">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK192">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="O194">
-        <v>4.42</v>
+        <v>3.84</v>
       </c>
       <c r="P194">
-        <v>4.85</v>
+        <v>4.69</v>
       </c>
       <c r="Q194">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="R194">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S194">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T194">
-        <v>3.56</v>
+        <v>3.14</v>
       </c>
       <c r="U194">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="V194">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="W194">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y194">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="Z194">
-        <v>4.45</v>
+        <v>3.58</v>
       </c>
       <c r="AA194">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="AB194">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="AC194">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AD194">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE194">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF194">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG194">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK194">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="O195">
-        <v>3.84</v>
+        <v>3.35</v>
       </c>
       <c r="P195">
-        <v>4.69</v>
+        <v>2.89</v>
       </c>
       <c r="Q195">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="R195">
+        <v>2.25</v>
+      </c>
+      <c r="S195">
+        <v>1.28</v>
+      </c>
+      <c r="T195">
+        <v>3.22</v>
+      </c>
+      <c r="U195">
         <v>2.3</v>
       </c>
-      <c r="S195">
-        <v>1.3</v>
-      </c>
-      <c r="T195">
-        <v>3.14</v>
-      </c>
-      <c r="U195">
-        <v>2.42</v>
-      </c>
       <c r="V195">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W195">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X195">
         <v>1.02</v>
       </c>
       <c r="Y195">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z195">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA195">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AB195">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AC195">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AD195">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE195">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF195">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG195">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK195">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="O196">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="P196">
-        <v>2.89</v>
+        <v>3.39</v>
       </c>
       <c r="Q196">
-        <v>2.74</v>
+        <v>2.35</v>
       </c>
       <c r="R196">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S196">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T196">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="U196">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V196">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W196">
         <v>1.08</v>
       </c>
       <c r="X196">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
         <v>1.2</v>
       </c>
       <c r="Z196">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA196">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB196">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC196">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AD196">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE196">
         <v>1.13</v>
       </c>
       <c r="AF196">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG196">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK196">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="O197">
-        <v>3.74</v>
+        <v>3.34</v>
       </c>
       <c r="P197">
-        <v>3.39</v>
+        <v>2.54</v>
       </c>
       <c r="Q197">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="R197">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S197">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T197">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="U197">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V197">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W197">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
         <v>1.03</v>
       </c>
       <c r="Y197">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z197">
-        <v>3.84</v>
+        <v>3.34</v>
       </c>
       <c r="AA197">
+        <v>1.93</v>
+      </c>
+      <c r="AB197">
+        <v>1.93</v>
+      </c>
+      <c r="AC197">
+        <v>3.08</v>
+      </c>
+      <c r="AD197">
+        <v>1.28</v>
+      </c>
+      <c r="AE197">
+        <v>1.07</v>
+      </c>
+      <c r="AF197">
         <v>1.67</v>
       </c>
-      <c r="AB197">
-        <v>2.05</v>
-      </c>
-      <c r="AC197">
-        <v>2.7</v>
-      </c>
-      <c r="AD197">
-        <v>1.42</v>
-      </c>
-      <c r="AE197">
-        <v>1.13</v>
-      </c>
-      <c r="AF197">
-        <v>1.6</v>
-      </c>
       <c r="AG197">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK197">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="O198">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="P198">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="Q198">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="R198">
         <v>2.1</v>
       </c>
       <c r="S198">
+        <v>1.39</v>
+      </c>
+      <c r="T198">
+        <v>2.7</v>
+      </c>
+      <c r="U198">
+        <v>2.88</v>
+      </c>
+      <c r="V198">
         <v>1.38</v>
       </c>
-      <c r="T198">
-        <v>2.73</v>
-      </c>
-      <c r="U198">
-        <v>2.67</v>
-      </c>
-      <c r="V198">
-        <v>1.4</v>
-      </c>
       <c r="W198">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X198">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y198">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z198">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA198">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AB198">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AC198">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD198">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE198">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF198">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG198">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK198">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.25</v>
+        <v>2.68</v>
       </c>
       <c r="O199">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="P199">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="Q199">
+        <v>2.76</v>
+      </c>
+      <c r="R199">
+        <v>1.97</v>
+      </c>
+      <c r="S199">
+        <v>1.45</v>
+      </c>
+      <c r="T199">
         <v>2.5</v>
       </c>
-      <c r="R199">
-        <v>2.1</v>
-      </c>
-      <c r="S199">
-        <v>1.39</v>
-      </c>
-      <c r="T199">
-        <v>2.7</v>
-      </c>
       <c r="U199">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V199">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W199">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X199">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y199">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="Z199">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="AA199">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AB199">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC199">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AD199">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE199">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF199">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG199">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK199">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="O200">
-        <v>3.09</v>
+        <v>4.42</v>
       </c>
       <c r="P200">
-        <v>2.67</v>
+        <v>4.85</v>
       </c>
       <c r="Q200">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="R200">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S200">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="T200">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U200">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="V200">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="W200">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X200">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z200">
-        <v>2.77</v>
+        <v>4.45</v>
       </c>
       <c r="AA200">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AB200">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="AC200">
-        <v>3.82</v>
+        <v>2.38</v>
       </c>
       <c r="AD200">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE200">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AF200">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG200">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK200">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -34018,12 +34018,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G207">
@@ -34181,12 +34181,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G208">
@@ -34344,12 +34344,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G209">
@@ -34507,12 +34507,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G210">
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="O233">
-        <v>5.95</v>
+        <v>3.84</v>
       </c>
       <c r="P233">
-        <v>9.75</v>
+        <v>4.52</v>
       </c>
       <c r="Q233">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="R233">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="S233">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T233">
-        <v>3.64</v>
+        <v>3.08</v>
       </c>
       <c r="U233">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V233">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W233">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X233">
         <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z233">
-        <v>6</v>
+        <v>3.84</v>
       </c>
       <c r="AA233">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="AB233">
-        <v>2.49</v>
+        <v>2.11</v>
       </c>
       <c r="AC233">
-        <v>2.09</v>
+        <v>2.79</v>
       </c>
       <c r="AD233">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AE233">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AF233">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG233">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK233">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O234">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P234">
-        <v>4.52</v>
+        <v>3.25</v>
       </c>
       <c r="Q234">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="R234">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S234">
         <v>1.3</v>
       </c>
       <c r="T234">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="U234">
         <v>2.45</v>
       </c>
       <c r="V234">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W234">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X234">
         <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z234">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="AA234">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AB234">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AC234">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="AD234">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE234">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF234">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG234">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK234">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="O235">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="P235">
-        <v>3.25</v>
+        <v>9.75</v>
       </c>
       <c r="Q235">
-        <v>2.29</v>
+        <v>1.65</v>
       </c>
       <c r="R235">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="S235">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T235">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="U235">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V235">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="W235">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X235">
         <v>1.02</v>
       </c>
       <c r="Y235">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z235">
-        <v>3.87</v>
+        <v>6</v>
       </c>
       <c r="AA235">
-        <v>1.81</v>
+        <v>1.42</v>
       </c>
       <c r="AB235">
-        <v>1.99</v>
+        <v>2.49</v>
       </c>
       <c r="AC235">
-        <v>2.97</v>
+        <v>2.09</v>
       </c>
       <c r="AD235">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE235">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AF235">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG235">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK235">
-        <v>2.02</v>
+        <v>3.58</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
+        <v>1.56</v>
+      </c>
+      <c r="O236">
+        <v>4.25</v>
+      </c>
+      <c r="P236">
+        <v>5.54</v>
+      </c>
+      <c r="Q236">
+        <v>2.08</v>
+      </c>
+      <c r="R236">
         <v>2.33</v>
-      </c>
-      <c r="O236">
-        <v>3.26</v>
-      </c>
-      <c r="P236">
-        <v>2.61</v>
-      </c>
-      <c r="Q236">
-        <v>2.88</v>
-      </c>
-      <c r="R236">
-        <v>2.16</v>
       </c>
       <c r="S236">
         <v>1.3</v>
       </c>
       <c r="T236">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U236">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V236">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W236">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X236">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y236">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z236">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="AA236">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AB236">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AC236">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD236">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE236">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF236">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG236">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK236">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38908,12 +38908,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G237">
@@ -38940,64 +38940,64 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.56</v>
+        <v>2.33</v>
       </c>
       <c r="O237">
-        <v>4.25</v>
+        <v>3.26</v>
       </c>
       <c r="P237">
-        <v>5.54</v>
+        <v>2.61</v>
       </c>
       <c r="Q237">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="R237">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="S237">
         <v>1.3</v>
       </c>
       <c r="T237">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U237">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V237">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W237">
+        <v>1.11</v>
+      </c>
+      <c r="X237">
+        <v>1.01</v>
+      </c>
+      <c r="Y237">
+        <v>1.19</v>
+      </c>
+      <c r="Z237">
+        <v>3.75</v>
+      </c>
+      <c r="AA237">
+        <v>1.7</v>
+      </c>
+      <c r="AB237">
+        <v>1.99</v>
+      </c>
+      <c r="AC237">
+        <v>2.66</v>
+      </c>
+      <c r="AD237">
+        <v>1.37</v>
+      </c>
+      <c r="AE237">
         <v>1.12</v>
       </c>
-      <c r="X237">
-        <v>1.03</v>
-      </c>
-      <c r="Y237">
-        <v>1.17</v>
-      </c>
-      <c r="Z237">
-        <v>3.98</v>
-      </c>
-      <c r="AA237">
-        <v>1.63</v>
-      </c>
-      <c r="AB237">
-        <v>2.17</v>
-      </c>
-      <c r="AC237">
-        <v>2.52</v>
-      </c>
-      <c r="AD237">
-        <v>1.41</v>
-      </c>
-      <c r="AE237">
-        <v>1.16</v>
-      </c>
       <c r="AF237">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG237">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK237">
-        <v>2.16</v>
+        <v>1.46</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O274">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P274">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q274">
         <v>0</v>
@@ -45010,10 +45010,10 @@
         <v>0</v>
       </c>
       <c r="AA274">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB274">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC274">
         <v>0</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O275">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P275">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q275">
         <v>0</v>
@@ -45173,10 +45173,10 @@
         <v>0</v>
       </c>
       <c r="AA275">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB275">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC275">
         <v>0</v>
@@ -45754,12 +45754,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G279">
@@ -45786,13 +45786,13 @@
         </is>
       </c>
       <c r="N279">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O279">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P279">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q279">
         <v>0</v>
@@ -45917,12 +45917,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G280">
@@ -45949,13 +45949,13 @@
         </is>
       </c>
       <c r="N280">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O280">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P280">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q280">
         <v>0</v>
@@ -46601,13 +46601,13 @@
         </is>
       </c>
       <c r="N284">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O284">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P284">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q284">
         <v>0</v>
@@ -46640,10 +46640,10 @@
         <v>0</v>
       </c>
       <c r="AA284">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB284">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC284">
         <v>0</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="O320">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P320">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q320">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R320">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S320">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T320">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U320">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="V320">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W320">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X320">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y320">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="Z320">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="AA320">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB320">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC320">
-        <v>4.31</v>
+        <v>3.69</v>
       </c>
       <c r="AD320">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE320">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF320">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="AG320">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AK320">
-        <v>2.5</v>
+        <v>2.03</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,80 +52632,80 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="O321">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P321">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q321">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="R321">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S321">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T321">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U321">
-        <v>2.81</v>
+        <v>3.24</v>
       </c>
       <c r="V321">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="W321">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X321">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y321">
+        <v>1.43</v>
+      </c>
+      <c r="Z321">
+        <v>2.55</v>
+      </c>
+      <c r="AA321">
+        <v>2.33</v>
+      </c>
+      <c r="AB321">
+        <v>1.48</v>
+      </c>
+      <c r="AC321">
+        <v>4.34</v>
+      </c>
+      <c r="AD321">
+        <v>1.13</v>
+      </c>
+      <c r="AE321">
+        <v>1.03</v>
+      </c>
+      <c r="AF321">
+        <v>2.54</v>
+      </c>
+      <c r="AG321">
+        <v>1.43</v>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ321">
         <v>1.29</v>
       </c>
-      <c r="Z321">
-        <v>3.04</v>
-      </c>
-      <c r="AA321">
-        <v>2.3</v>
-      </c>
-      <c r="AB321">
-        <v>1.6</v>
-      </c>
-      <c r="AC321">
-        <v>3.69</v>
-      </c>
-      <c r="AD321">
-        <v>1.24</v>
-      </c>
-      <c r="AE321">
-        <v>1.1</v>
-      </c>
-      <c r="AF321">
-        <v>2</v>
-      </c>
-      <c r="AG321">
-        <v>1.75</v>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ321">
-        <v>1.21</v>
-      </c>
       <c r="AK321">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="O322">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P322">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q322">
-        <v>2.03</v>
+        <v>7</v>
       </c>
       <c r="R322">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S322">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T322">
         <v>2.4</v>
       </c>
       <c r="U322">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="V322">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W322">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X322">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y322">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z322">
         <v>2.55</v>
       </c>
       <c r="AA322">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AB322">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC322">
-        <v>4.34</v>
+        <v>5.2</v>
       </c>
       <c r="AD322">
         <v>1.13</v>
       </c>
       <c r="AE322">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF322">
-        <v>2.54</v>
+        <v>2.45</v>
       </c>
       <c r="AG322">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK322">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,61 +52958,61 @@
         </is>
       </c>
       <c r="N323">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O323">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P323">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q323">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="R323">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S323">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T323">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U323">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="V323">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W323">
+        <v>1.02</v>
+      </c>
+      <c r="X323">
         <v>1.03</v>
       </c>
-      <c r="X323">
-        <v>1.06</v>
-      </c>
       <c r="Y323">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z323">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AA323">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AB323">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC323">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AD323">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE323">
         <v>1.01</v>
       </c>
       <c r="AF323">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AG323">
         <v>1.44</v>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK323">
-        <v>1.05</v>
+        <v>2.45</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,80 +53121,80 @@
         </is>
       </c>
       <c r="N324">
-        <v>8.5</v>
+        <v>1.44</v>
       </c>
       <c r="O324">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="P324">
-        <v>1.32</v>
+        <v>6.75</v>
       </c>
       <c r="Q324">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="R324">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="S324">
+        <v>1.44</v>
+      </c>
+      <c r="T324">
+        <v>2.62</v>
+      </c>
+      <c r="U324">
+        <v>3.1</v>
+      </c>
+      <c r="V324">
         <v>1.33</v>
       </c>
-      <c r="T324">
-        <v>2.95</v>
-      </c>
-      <c r="U324">
-        <v>2.61</v>
-      </c>
-      <c r="V324">
-        <v>1.38</v>
-      </c>
       <c r="W324">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X324">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y324">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="Z324">
-        <v>3.28</v>
+        <v>2.83</v>
       </c>
       <c r="AA324">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="AB324">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AC324">
-        <v>3.08</v>
+        <v>4.31</v>
       </c>
       <c r="AD324">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE324">
+        <v>1.02</v>
+      </c>
+      <c r="AF324">
+        <v>2.32</v>
+      </c>
+      <c r="AG324">
+        <v>1.53</v>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ324">
         <v>1.1</v>
       </c>
-      <c r="AF324">
-        <v>2.2</v>
-      </c>
-      <c r="AG324">
-        <v>1.6</v>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ324">
-        <v>1.12</v>
-      </c>
       <c r="AK324">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,80 +53284,80 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.48</v>
+        <v>8.5</v>
       </c>
       <c r="O325">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="P325">
-        <v>6.75</v>
+        <v>1.32</v>
       </c>
       <c r="Q325">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="R325">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S325">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T325">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="U325">
-        <v>3.24</v>
+        <v>2.61</v>
       </c>
       <c r="V325">
+        <v>1.38</v>
+      </c>
+      <c r="W325">
+        <v>1.07</v>
+      </c>
+      <c r="X325">
+        <v>1.01</v>
+      </c>
+      <c r="Y325">
         <v>1.26</v>
       </c>
-      <c r="W325">
-        <v>1.02</v>
-      </c>
-      <c r="X325">
-        <v>1.03</v>
-      </c>
-      <c r="Y325">
-        <v>1.42</v>
-      </c>
       <c r="Z325">
-        <v>2.49</v>
+        <v>3.28</v>
       </c>
       <c r="AA325">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AB325">
+        <v>1.83</v>
+      </c>
+      <c r="AC325">
+        <v>3.08</v>
+      </c>
+      <c r="AD325">
+        <v>1.28</v>
+      </c>
+      <c r="AE325">
+        <v>1.1</v>
+      </c>
+      <c r="AF325">
+        <v>2.2</v>
+      </c>
+      <c r="AG325">
         <v>1.6</v>
       </c>
-      <c r="AC325">
-        <v>4.7</v>
-      </c>
-      <c r="AD325">
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ325">
         <v>1.12</v>
       </c>
-      <c r="AE325">
-        <v>1.01</v>
-      </c>
-      <c r="AF325">
-        <v>2.57</v>
-      </c>
-      <c r="AG325">
-        <v>1.44</v>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ325">
-        <v>1.18</v>
-      </c>
       <c r="AK325">
-        <v>2.45</v>
+        <v>1.04</v>
       </c>
       <c r="AL325">
         <v>0</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="O2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
         <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S2">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T2">
         <v>3.65</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
         <v>1.85</v>
@@ -970,16 +970,16 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="R4">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
         <v>2.38</v>
@@ -1015,10 +1015,10 @@
         <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O10">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
+        <v>1.35</v>
+      </c>
+      <c r="T10">
+        <v>2.77</v>
+      </c>
+      <c r="U10">
+        <v>2.77</v>
+      </c>
+      <c r="V10">
+        <v>1.37</v>
+      </c>
+      <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.28</v>
+      </c>
+      <c r="Z10">
+        <v>3.05</v>
+      </c>
+      <c r="AA10">
+        <v>1.98</v>
+      </c>
+      <c r="AB10">
+        <v>1.71</v>
+      </c>
+      <c r="AC10">
+        <v>3.42</v>
+      </c>
+      <c r="AD10">
         <v>1.25</v>
       </c>
-      <c r="T10">
-        <v>3.6</v>
-      </c>
-      <c r="U10">
-        <v>2.25</v>
-      </c>
-      <c r="V10">
-        <v>1.57</v>
-      </c>
-      <c r="W10">
-        <v>1.14</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.14</v>
-      </c>
-      <c r="Z10">
-        <v>4.87</v>
-      </c>
-      <c r="AA10">
-        <v>1.6</v>
-      </c>
-      <c r="AB10">
-        <v>2.34</v>
-      </c>
-      <c r="AC10">
-        <v>2.3</v>
-      </c>
-      <c r="AD10">
-        <v>1.49</v>
-      </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AG10">
-        <v>2.47</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P11">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R11">
+        <v>2.4</v>
+      </c>
+      <c r="S11">
+        <v>1.25</v>
+      </c>
+      <c r="T11">
+        <v>3.6</v>
+      </c>
+      <c r="U11">
         <v>2.25</v>
       </c>
-      <c r="S11">
-        <v>1.36</v>
-      </c>
-      <c r="T11">
-        <v>2.8</v>
-      </c>
-      <c r="U11">
-        <v>2.51</v>
-      </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>3.7</v>
+        <v>4.87</v>
       </c>
       <c r="AA11">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="AC11">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
+        <v>3.4</v>
+      </c>
+      <c r="P12">
+        <v>2.05</v>
+      </c>
+      <c r="Q12">
+        <v>3.3</v>
+      </c>
+      <c r="R12">
+        <v>2.25</v>
+      </c>
+      <c r="S12">
+        <v>1.36</v>
+      </c>
+      <c r="T12">
+        <v>2.8</v>
+      </c>
+      <c r="U12">
+        <v>2.51</v>
+      </c>
+      <c r="V12">
+        <v>1.45</v>
+      </c>
+      <c r="W12">
+        <v>1.07</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.7</v>
+      </c>
+      <c r="AA12">
+        <v>1.85</v>
+      </c>
+      <c r="AB12">
+        <v>1.95</v>
+      </c>
+      <c r="AC12">
         <v>3.1</v>
       </c>
-      <c r="P12">
-        <v>2.6</v>
-      </c>
-      <c r="Q12">
-        <v>3.25</v>
-      </c>
-      <c r="R12">
-        <v>2.05</v>
-      </c>
-      <c r="S12">
+      <c r="AD12">
         <v>1.35</v>
       </c>
-      <c r="T12">
-        <v>2.77</v>
-      </c>
-      <c r="U12">
-        <v>2.77</v>
-      </c>
-      <c r="V12">
-        <v>1.37</v>
-      </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.28</v>
-      </c>
-      <c r="Z12">
-        <v>3.05</v>
-      </c>
-      <c r="AA12">
-        <v>1.98</v>
-      </c>
-      <c r="AB12">
-        <v>1.71</v>
-      </c>
-      <c r="AC12">
-        <v>3.42</v>
-      </c>
-      <c r="AD12">
+      <c r="AE12">
+        <v>1.1</v>
+      </c>
+      <c r="AF12">
+        <v>1.65</v>
+      </c>
+      <c r="AG12">
+        <v>2.1</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.23</v>
+      </c>
+      <c r="AK12">
         <v>1.25</v>
-      </c>
-      <c r="AE12">
-        <v>1.04</v>
-      </c>
-      <c r="AF12">
-        <v>1.76</v>
-      </c>
-      <c r="AG12">
-        <v>1.94</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.33</v>
-      </c>
-      <c r="AK12">
-        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="Q19">
         <v>2.62</v>
@@ -3424,7 +3424,7 @@
         <v>1.35</v>
       </c>
       <c r="T19">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U19">
         <v>2.64</v>
@@ -3479,7 +3479,7 @@
         <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -5365,28 +5365,28 @@
         <v>3.1</v>
       </c>
       <c r="O31">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="P31">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q31">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="R31">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="S31">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W31">
         <v>1.1</v>
@@ -5401,7 +5401,7 @@
         <v>3.7</v>
       </c>
       <c r="AA31">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AB31">
         <v>2.02</v>
@@ -5416,10 +5416,10 @@
         <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG31">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>3.75</v>
       </c>
       <c r="R34">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="S34">
         <v>1.22</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK34">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="O35">
         <v>3.35</v>
       </c>
       <c r="P35">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="Q35">
         <v>2.62</v>
@@ -6056,7 +6056,7 @@
         <v>1.79</v>
       </c>
       <c r="AB35">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC35">
         <v>2.88</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
         <v>1.54</v>
@@ -6186,10 +6186,10 @@
         <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="R36">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S36">
         <v>1.29</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AK36">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O37">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q37">
         <v>2.98</v>
@@ -6379,7 +6379,7 @@
         <v>4.8</v>
       </c>
       <c r="AA37">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB37">
         <v>2.38</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="O49">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -8335,10 +8335,10 @@
         <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC49">
         <v>3.6</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O57">
         <v>3.2</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q57">
         <v>2.68</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="O62">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
         <v>3.1</v>
@@ -10436,7 +10436,7 @@
         <v>3.3</v>
       </c>
       <c r="U62">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
         <v>1.5</v>
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>1.53</v>
       </c>
       <c r="O71">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P71">
         <v>4.8</v>
@@ -12087,7 +12087,7 @@
         <v>1.58</v>
       </c>
       <c r="AB72">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AC72">
         <v>2.38</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="O73">
-        <v>3.81</v>
+        <v>3.75</v>
       </c>
       <c r="P73">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q73">
         <v>2.9</v>
@@ -12226,13 +12226,13 @@
         <v>1.22</v>
       </c>
       <c r="T73">
-        <v>3.78</v>
+        <v>3.48</v>
       </c>
       <c r="U73">
         <v>2.15</v>
       </c>
       <c r="V73">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="W73">
         <v>1.18</v>
@@ -12244,19 +12244,19 @@
         <v>1.13</v>
       </c>
       <c r="Z73">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA73">
         <v>1.5</v>
       </c>
       <c r="AB73">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AC73">
         <v>2.28</v>
       </c>
       <c r="AD73">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE73">
         <v>1.22</v>
@@ -12703,7 +12703,7 @@
         <v>3.7</v>
       </c>
       <c r="P76">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q76">
         <v>7.6</v>
@@ -12869,55 +12869,55 @@
         <v>6.65</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="O78">
         <v>3.4</v>
       </c>
       <c r="P78">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q78">
         <v>3</v>
@@ -13050,7 +13050,7 @@
         <v>1.47</v>
       </c>
       <c r="W78">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.03</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13518,7 +13518,7 @@
         <v>3.9</v>
       </c>
       <c r="P81">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="Q81">
         <v>2.26</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>4.69</v>
+        <v>2.72</v>
       </c>
       <c r="Q82">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="R82">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="S82">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U82">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="V82">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="W82">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA82">
-        <v>1.97</v>
+        <v>1.6</v>
       </c>
       <c r="AB82">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="AC82">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="AD82">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AE82">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF82">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AK82">
-        <v>2.07</v>
+        <v>1.53</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.3</v>
+        <v>1.68</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q83">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="R83">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>3.48</v>
+        <v>2.82</v>
       </c>
       <c r="U83">
-        <v>2.29</v>
+        <v>2.74</v>
       </c>
       <c r="V83">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W83">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z83">
-        <v>4.65</v>
+        <v>3.2</v>
       </c>
       <c r="AA83">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="AB83">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AC83">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD83">
-        <v>1.49</v>
+        <v>1.26</v>
       </c>
       <c r="AE83">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>2.49</v>
+        <v>1.83</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.57</v>
+        <v>2.07</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="O86">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P86">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q86">
         <v>3.94</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="O87">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P87">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Q87">
         <v>1.99</v>
@@ -14855,7 +14855,7 @@
         <v>4.75</v>
       </c>
       <c r="AA89">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AB89">
         <v>2.33</v>
@@ -14988,7 +14988,7 @@
         <v>2.38</v>
       </c>
       <c r="Q90">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="R90">
         <v>2.15</v>
@@ -15000,7 +15000,7 @@
         <v>2.96</v>
       </c>
       <c r="U90">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="V90">
         <v>1.44</v>
@@ -15009,28 +15009,28 @@
         <v>1.06</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
         <v>1.27</v>
       </c>
       <c r="Z90">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA90">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB90">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC90">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="AD90">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF90">
         <v>1.63</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK90">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15157,13 +15157,13 @@
         <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T91">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="U91">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V91">
         <v>1.43</v>
@@ -15181,7 +15181,7 @@
         <v>3.63</v>
       </c>
       <c r="AA91">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB91">
         <v>1.84</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AK91">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15314,55 +15314,55 @@
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.64</v>
+        <v>4.2</v>
       </c>
       <c r="R92">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S92">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T92">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U92">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="V92">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W92">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
         <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA92">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB92">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC92">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AD92">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE92">
         <v>1.1</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG92">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O93">
         <v>3.4</v>
@@ -16485,7 +16485,7 @@
         <v>4.35</v>
       </c>
       <c r="AA99">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB99">
         <v>2.14</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,28 +16609,28 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="O100">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P100">
-        <v>2.2</v>
+        <v>4.98</v>
       </c>
       <c r="Q100">
-        <v>3.51</v>
+        <v>2.1</v>
       </c>
       <c r="R100">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S100">
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U100">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V100">
         <v>1.44</v>
@@ -16639,22 +16639,22 @@
         <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y100">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z100">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AA100">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB100">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC100">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="AD100">
         <v>1.38</v>
@@ -16663,10 +16663,10 @@
         <v>1.14</v>
       </c>
       <c r="AF100">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG100">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,28 +16772,28 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.66</v>
+        <v>3.03</v>
       </c>
       <c r="O101">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>4.98</v>
+        <v>2.23</v>
       </c>
       <c r="Q101">
-        <v>2.1</v>
+        <v>3.51</v>
       </c>
       <c r="R101">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S101">
         <v>1.33</v>
       </c>
       <c r="T101">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="U101">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V101">
         <v>1.44</v>
@@ -16802,22 +16802,22 @@
         <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y101">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z101">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AA101">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB101">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC101">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="AD101">
         <v>1.38</v>
@@ -16826,10 +16826,10 @@
         <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG101">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK101">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="O103">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="Q103">
         <v>3.2</v>
@@ -17152,7 +17152,7 @@
         <v>1.19</v>
       </c>
       <c r="AF103">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG103">
         <v>2.5</v>
@@ -18245,10 +18245,10 @@
         <v>4.33</v>
       </c>
       <c r="P110">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q110">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="R110">
         <v>2.31</v>
@@ -18278,16 +18278,16 @@
         <v>5.25</v>
       </c>
       <c r="AA110">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB110">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC110">
         <v>2.31</v>
       </c>
       <c r="AD110">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE110">
         <v>1.2</v>
@@ -18312,7 +18312,7 @@
         <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="G118">
@@ -19745,7 +19745,7 @@
         <v>3.72</v>
       </c>
       <c r="AA119">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB119">
         <v>1.96</v>
@@ -20530,10 +20530,10 @@
         <v>3.9</v>
       </c>
       <c r="Q124">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="R124">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="S124">
         <v>1.41</v>
@@ -20542,10 +20542,10 @@
         <v>2.55</v>
       </c>
       <c r="U124">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="V124">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W124">
         <v>1.03</v>
@@ -20554,31 +20554,31 @@
         <v>1.02</v>
       </c>
       <c r="Y124">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z124">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA124">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB124">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AC124">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="AD124">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE124">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF124">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG124">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -20591,10 +20591,10 @@
         </is>
       </c>
       <c r="AJ124">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK124">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O125">
         <v>3.3</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,64 +20847,64 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="O126">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P126">
+        <v>4.6</v>
+      </c>
+      <c r="Q126">
+        <v>2.25</v>
+      </c>
+      <c r="R126">
         <v>2.05</v>
       </c>
-      <c r="Q126">
-        <v>3.85</v>
-      </c>
-      <c r="R126">
-        <v>2.14</v>
-      </c>
       <c r="S126">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T126">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="U126">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V126">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W126">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y126">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z126">
-        <v>3.72</v>
+        <v>2.97</v>
       </c>
       <c r="AA126">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB126">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC126">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD126">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE126">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG126">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>1.21</v>
       </c>
       <c r="AK126">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="O127">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P127">
-        <v>4.6</v>
+        <v>2.05</v>
       </c>
       <c r="Q127">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="R127">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S127">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T127">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="U127">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V127">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z127">
-        <v>2.97</v>
+        <v>3.72</v>
       </c>
       <c r="AA127">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AB127">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC127">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD127">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE127">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG127">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>1.21</v>
       </c>
       <c r="AK127">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22803,10 +22803,10 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O138">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P138">
         <v>4</v>
@@ -22833,7 +22833,7 @@
         <v>1.11</v>
       </c>
       <c r="X138">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y138">
         <v>1.16</v>
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O139">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P139">
         <v>2.7</v>
       </c>
       <c r="Q139">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="R139">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S139">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T139">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U139">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="V139">
         <v>1.36</v>
       </c>
       <c r="W139">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X139">
         <v>1.01</v>
       </c>
       <c r="Y139">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z139">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA139">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB139">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC139">
-        <v>3.08</v>
+        <v>3.53</v>
       </c>
       <c r="AD139">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE139">
         <v>1.06</v>
       </c>
       <c r="AF139">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG139">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK139">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23135,10 +23135,10 @@
         <v>3.1</v>
       </c>
       <c r="P140">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q140">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R140">
         <v>2.04</v>
@@ -23150,7 +23150,7 @@
         <v>2.75</v>
       </c>
       <c r="U140">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="V140">
         <v>1.33</v>
@@ -23162,7 +23162,7 @@
         <v>1.01</v>
       </c>
       <c r="Y140">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z140">
         <v>3.08</v>
@@ -23455,13 +23455,13 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="O142">
         <v>3.2</v>
       </c>
       <c r="P142">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q142">
         <v>3.02</v>
@@ -23485,7 +23485,7 @@
         <v>1.05</v>
       </c>
       <c r="X142">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y142">
         <v>1.28</v>
@@ -23672,7 +23672,7 @@
         <v>1.08</v>
       </c>
       <c r="AF143">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG143">
         <v>2.11</v>
@@ -23781,7 +23781,7 @@
         </is>
       </c>
       <c r="N144">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O144">
         <v>3.5</v>
@@ -23944,10 +23944,10 @@
         </is>
       </c>
       <c r="N145">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O145">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P145">
         <v>2.2</v>
@@ -24309,7 +24309,7 @@
         <v>5.15</v>
       </c>
       <c r="AA147">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB147">
         <v>2.43</v>
@@ -25257,34 +25257,34 @@
         <v>2.27</v>
       </c>
       <c r="Q153">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R153">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U153">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V153">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W153">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X153">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y153">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z153">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA153">
         <v>1.85</v>
@@ -25293,19 +25293,19 @@
         <v>1.95</v>
       </c>
       <c r="AC153">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD153">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE153">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF153">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG153">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK153">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O159">
         <v>3.4</v>
       </c>
       <c r="P159">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="Q159">
         <v>2.69</v>
@@ -26594,7 +26594,7 @@
         <v>1.67</v>
       </c>
       <c r="AB161">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC161">
         <v>2.65</v>
@@ -26715,7 +26715,7 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="O162">
         <v>3.5</v>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="N163">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O163">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P163">
         <v>2.26</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O164">
         <v>3.6</v>
       </c>
       <c r="P164">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27207,7 +27207,7 @@
         <v>2.5</v>
       </c>
       <c r="O165">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P165">
         <v>2.2</v>
@@ -27243,7 +27243,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AA165">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AB165">
         <v>3.5</v>
@@ -27530,31 +27530,31 @@
         </is>
       </c>
       <c r="N167">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="O167">
         <v>5</v>
       </c>
       <c r="P167">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q167">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="R167">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="S167">
         <v>1.3</v>
       </c>
       <c r="T167">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U167">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V167">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W167">
         <v>1.11</v>
@@ -27563,31 +27563,31 @@
         <v>1.01</v>
       </c>
       <c r="Y167">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z167">
-        <v>4.19</v>
+        <v>4.39</v>
       </c>
       <c r="AA167">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB167">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC167">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="AD167">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE167">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF167">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="AG167">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         </is>
       </c>
       <c r="AJ167">
-        <v>3.86</v>
+        <v>1.1</v>
       </c>
       <c r="AK167">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AL167">
         <v>0</v>
@@ -27661,12 +27661,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G168">
@@ -27693,80 +27693,80 @@
         </is>
       </c>
       <c r="N168">
-        <v>2.72</v>
+        <v>1.93</v>
       </c>
       <c r="O168">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="P168">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q168">
-        <v>3.31</v>
+        <v>2.38</v>
       </c>
       <c r="R168">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="S168">
         <v>1.22</v>
       </c>
       <c r="T168">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="U168">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="V168">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W168">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X168">
         <v>1</v>
       </c>
       <c r="Y168">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z168">
-        <v>5.95</v>
+        <v>5.3</v>
       </c>
       <c r="AA168">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AB168">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AC168">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AD168">
+        <v>1.71</v>
+      </c>
+      <c r="AE168">
+        <v>1.26</v>
+      </c>
+      <c r="AF168">
+        <v>1.44</v>
+      </c>
+      <c r="AG168">
+        <v>2.62</v>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ168">
+        <v>1.24</v>
+      </c>
+      <c r="AK168">
         <v>1.88</v>
-      </c>
-      <c r="AE168">
-        <v>1.36</v>
-      </c>
-      <c r="AF168">
-        <v>1.4</v>
-      </c>
-      <c r="AG168">
-        <v>2.98</v>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ168">
-        <v>1.27</v>
-      </c>
-      <c r="AK168">
-        <v>1.46</v>
       </c>
       <c r="AL168">
         <v>0</v>
@@ -27859,10 +27859,10 @@
         <v>2.96</v>
       </c>
       <c r="O169">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="P169">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Q169">
         <v>3.11</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,16 +28182,16 @@
         </is>
       </c>
       <c r="N171">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="O171">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P171">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="Q171">
-        <v>3.82</v>
+        <v>3.31</v>
       </c>
       <c r="R171">
         <v>2.52</v>
@@ -28200,46 +28200,46 @@
         <v>1.22</v>
       </c>
       <c r="T171">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U171">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V171">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W171">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X171">
         <v>1</v>
       </c>
       <c r="Y171">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z171">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="AA171">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AB171">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="AC171">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AD171">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AE171">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF171">
         <v>1.4</v>
       </c>
       <c r="AG171">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK171">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,31 +28345,31 @@
         </is>
       </c>
       <c r="N172">
+        <v>3.08</v>
+      </c>
+      <c r="O172">
+        <v>3.9</v>
+      </c>
+      <c r="P172">
         <v>1.91</v>
       </c>
-      <c r="O172">
-        <v>4</v>
-      </c>
-      <c r="P172">
-        <v>3.05</v>
-      </c>
       <c r="Q172">
-        <v>2.38</v>
+        <v>3.82</v>
       </c>
       <c r="R172">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="S172">
         <v>1.22</v>
       </c>
       <c r="T172">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="U172">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="V172">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W172">
         <v>1.18</v>
@@ -28381,28 +28381,28 @@
         <v>1.1</v>
       </c>
       <c r="Z172">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AA172">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB172">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AC172">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AD172">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE172">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF172">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG172">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK172">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28671,13 +28671,13 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O174">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="P174">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28997,7 +28997,7 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="O176">
         <v>3.5</v>
@@ -29021,7 +29021,7 @@
         <v>2.6</v>
       </c>
       <c r="V176">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W176">
         <v>1.07</v>
@@ -29163,10 +29163,10 @@
         <v>1.7</v>
       </c>
       <c r="O177">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P177">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="Q177">
         <v>2</v>
@@ -29199,7 +29199,7 @@
         <v>5.72</v>
       </c>
       <c r="AA177">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB177">
         <v>2.75</v>
@@ -29323,13 +29323,13 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="O178">
         <v>3.5</v>
       </c>
       <c r="P178">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="Q178">
         <v>2.44</v>
@@ -29362,10 +29362,10 @@
         <v>3.56</v>
       </c>
       <c r="AA178">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB178">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC178">
         <v>3.06</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="O179">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P179">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q179">
         <v>3.3</v>
@@ -29507,7 +29507,7 @@
         <v>2.9</v>
       </c>
       <c r="U179">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="V179">
         <v>1.4</v>
@@ -29851,7 +29851,7 @@
         <v>4.08</v>
       </c>
       <c r="AA181">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB181">
         <v>2.13</v>
@@ -30017,7 +30017,7 @@
         <v>1.66</v>
       </c>
       <c r="AB182">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC182">
         <v>2.59</v>
@@ -30032,7 +30032,7 @@
         <v>1.67</v>
       </c>
       <c r="AG182">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30147,55 +30147,55 @@
         <v>3.33</v>
       </c>
       <c r="Q183">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R183">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="S183">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T183">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="U183">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V183">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W183">
         <v>1.11</v>
       </c>
       <c r="X183">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z183">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA183">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB183">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AC183">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AD183">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE183">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF183">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AG183">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="O186">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="P186">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="Q186">
         <v>3.96</v>
@@ -30700,7 +30700,7 @@
         <v>1.44</v>
       </c>
       <c r="AK186">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -30758,12 +30758,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G187">
@@ -30790,65 +30790,65 @@
         </is>
       </c>
       <c r="N187">
-        <v>1.99</v>
+        <v>3.7</v>
       </c>
       <c r="O187">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P187">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q187">
-        <v>2.64</v>
+        <v>4.75</v>
       </c>
       <c r="R187">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="S187">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="T187">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="U187">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="V187">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W187">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X187">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y187">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Z187">
-        <v>3.14</v>
+        <v>2.78</v>
       </c>
       <c r="AA187">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB187">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AC187">
-        <v>3.34</v>
+        <v>3.91</v>
       </c>
       <c r="AD187">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE187">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF187">
+        <v>1.93</v>
+      </c>
+      <c r="AG187">
         <v>1.78</v>
       </c>
-      <c r="AG187">
-        <v>1.89</v>
-      </c>
       <c r="AH187" t="inlineStr">
         <is>
           <t>[]</t>
@@ -30860,10 +30860,10 @@
         </is>
       </c>
       <c r="AJ187">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK187">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AL187">
         <v>0</v>
@@ -30921,12 +30921,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G188">
@@ -30953,64 +30953,64 @@
         </is>
       </c>
       <c r="N188">
-        <v>3.7</v>
+        <v>1.21</v>
       </c>
       <c r="O188">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="P188">
-        <v>1.85</v>
+        <v>9</v>
       </c>
       <c r="Q188">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
       <c r="R188">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="S188">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T188">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="U188">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="V188">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="W188">
+        <v>1.13</v>
+      </c>
+      <c r="X188">
         <v>1.02</v>
       </c>
-      <c r="X188">
-        <v>1.03</v>
-      </c>
       <c r="Y188">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="Z188">
-        <v>2.78</v>
+        <v>5.25</v>
       </c>
       <c r="AA188">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="AB188">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AC188">
-        <v>3.91</v>
+        <v>2.17</v>
       </c>
       <c r="AD188">
-        <v>1.19</v>
+        <v>1.59</v>
       </c>
       <c r="AE188">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AF188">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG188">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AH188" t="inlineStr">
         <is>
@@ -31023,10 +31023,10 @@
         </is>
       </c>
       <c r="AJ188">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK188">
-        <v>1.22</v>
+        <v>4.2</v>
       </c>
       <c r="AL188">
         <v>0</v>
@@ -31084,12 +31084,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G189">
@@ -31116,80 +31116,80 @@
         </is>
       </c>
       <c r="N189">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="O189">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="P189">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q189">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="R189">
-        <v>2.8</v>
+        <v>2.09</v>
       </c>
       <c r="S189">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T189">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="U189">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="V189">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="W189">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X189">
         <v>1.02</v>
       </c>
       <c r="Y189">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="Z189">
-        <v>5.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA189">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="AB189">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC189">
-        <v>2.17</v>
+        <v>3.42</v>
       </c>
       <c r="AD189">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="AE189">
+        <v>1.04</v>
+      </c>
+      <c r="AF189">
+        <v>1.84</v>
+      </c>
+      <c r="AG189">
+        <v>1.85</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ189">
         <v>1.21</v>
       </c>
-      <c r="AF189">
-        <v>1.98</v>
-      </c>
-      <c r="AG189">
-        <v>1.72</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ189">
-        <v>1.11</v>
-      </c>
       <c r="AK189">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31247,12 +31247,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="G190">
@@ -31279,25 +31279,25 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="O190">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P190">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q190">
-        <v>2.33</v>
+        <v>2.64</v>
       </c>
       <c r="R190">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="S190">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T190">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="U190">
         <v>2.85</v>
@@ -31306,10 +31306,10 @@
         <v>1.33</v>
       </c>
       <c r="W190">
+        <v>1.08</v>
+      </c>
+      <c r="X190">
         <v>1.03</v>
-      </c>
-      <c r="X190">
-        <v>1.02</v>
       </c>
       <c r="Y190">
         <v>1.27</v>
@@ -31318,25 +31318,25 @@
         <v>3.14</v>
       </c>
       <c r="AA190">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB190">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC190">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD190">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE190">
         <v>1.04</v>
       </c>
       <c r="AF190">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AG190">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK190">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31445,10 +31445,10 @@
         <v>2.9</v>
       </c>
       <c r="O191">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="P191">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q191">
         <v>3.38</v>
@@ -31463,25 +31463,25 @@
         <v>3.65</v>
       </c>
       <c r="U191">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="V191">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W191">
         <v>1.13</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z191">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA191">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB191">
         <v>2.2</v>
@@ -31490,10 +31490,10 @@
         <v>2.33</v>
       </c>
       <c r="AD191">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AE191">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AF191">
         <v>1.47</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK191">
         <v>1.33</v>
@@ -31771,10 +31771,10 @@
         <v>2.6</v>
       </c>
       <c r="O193">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P193">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q193">
         <v>3.08</v>
@@ -31931,13 +31931,13 @@
         </is>
       </c>
       <c r="N194">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O194">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P194">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q194">
         <v>2.6</v>
@@ -31970,10 +31970,10 @@
         <v>3.08</v>
       </c>
       <c r="AA194">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB194">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC194">
         <v>3.42</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="O195">
-        <v>3.5</v>
+        <v>3.16</v>
       </c>
       <c r="P195">
+        <v>3.4</v>
+      </c>
+      <c r="Q195">
+        <v>2.76</v>
+      </c>
+      <c r="R195">
+        <v>2</v>
+      </c>
+      <c r="S195">
+        <v>1.45</v>
+      </c>
+      <c r="T195">
         <v>2.5</v>
       </c>
-      <c r="Q195">
-        <v>3.25</v>
-      </c>
-      <c r="R195">
+      <c r="U195">
+        <v>3</v>
+      </c>
+      <c r="V195">
+        <v>1.33</v>
+      </c>
+      <c r="W195">
+        <v>1.05</v>
+      </c>
+      <c r="X195">
+        <v>1.04</v>
+      </c>
+      <c r="Y195">
+        <v>1.37</v>
+      </c>
+      <c r="Z195">
+        <v>2.79</v>
+      </c>
+      <c r="AA195">
         <v>2.15</v>
       </c>
-      <c r="S195">
-        <v>1.3</v>
-      </c>
-      <c r="T195">
-        <v>2.88</v>
-      </c>
-      <c r="U195">
-        <v>2.6</v>
-      </c>
-      <c r="V195">
-        <v>1.42</v>
-      </c>
-      <c r="W195">
-        <v>1.1</v>
-      </c>
-      <c r="X195">
-        <v>1.01</v>
-      </c>
-      <c r="Y195">
-        <v>1.23</v>
-      </c>
-      <c r="Z195">
-        <v>3.42</v>
-      </c>
-      <c r="AA195">
-        <v>1.82</v>
-      </c>
       <c r="AB195">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AC195">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="AD195">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AE195">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF195">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AG195">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK195">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,80 +32257,80 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="O196">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P196">
         <v>3.4</v>
       </c>
       <c r="Q196">
-        <v>2.76</v>
+        <v>2.28</v>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S196">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="T196">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="U196">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="V196">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X196">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="Z196">
-        <v>2.79</v>
+        <v>3.84</v>
       </c>
       <c r="AA196">
+        <v>1.69</v>
+      </c>
+      <c r="AB196">
+        <v>2.01</v>
+      </c>
+      <c r="AC196">
+        <v>2.7</v>
+      </c>
+      <c r="AD196">
+        <v>1.41</v>
+      </c>
+      <c r="AE196">
+        <v>1.13</v>
+      </c>
+      <c r="AF196">
+        <v>1.62</v>
+      </c>
+      <c r="AG196">
         <v>2.15</v>
       </c>
-      <c r="AB196">
-        <v>1.68</v>
-      </c>
-      <c r="AC196">
-        <v>3.82</v>
-      </c>
-      <c r="AD196">
-        <v>1.25</v>
-      </c>
-      <c r="AE196">
-        <v>1.05</v>
-      </c>
-      <c r="AF196">
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ196">
+        <v>1.16</v>
+      </c>
+      <c r="AK196">
         <v>1.83</v>
-      </c>
-      <c r="AG196">
-        <v>1.85</v>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ196">
-        <v>1.25</v>
-      </c>
-      <c r="AK196">
-        <v>1.65</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="O197">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="P197">
-        <v>3.79</v>
+        <v>2.63</v>
       </c>
       <c r="Q197">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="R197">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S197">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T197">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="U197">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="V197">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W197">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X197">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z197">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="AA197">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB197">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC197">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD197">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE197">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF197">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG197">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK197">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32583,13 +32583,13 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O198">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P198">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q198">
         <v>2.13</v>
@@ -32622,7 +32622,7 @@
         <v>4.45</v>
       </c>
       <c r="AA198">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB198">
         <v>2.24</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="O199">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P199">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q199">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="R199">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S199">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T199">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U199">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V199">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W199">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z199">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AA199">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AB199">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC199">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD199">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE199">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF199">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG199">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK199">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33600,7 +33600,7 @@
         <v>4.35</v>
       </c>
       <c r="AA204">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB204">
         <v>2.22</v>
@@ -34376,13 +34376,13 @@
         </is>
       </c>
       <c r="N209">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O209">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P209">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="Q209">
         <v>2.5</v>
@@ -34418,7 +34418,7 @@
         <v>1.87</v>
       </c>
       <c r="AB209">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC209">
         <v>3.08</v>
@@ -34545,7 +34545,7 @@
         <v>3.62</v>
       </c>
       <c r="P210">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="Q210">
         <v>2.2</v>
@@ -34578,7 +34578,7 @@
         <v>3.42</v>
       </c>
       <c r="AA210">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB210">
         <v>1.98</v>
@@ -34593,7 +34593,7 @@
         <v>1.09</v>
       </c>
       <c r="AF210">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG210">
         <v>2</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.28</v>
+        <v>2.8</v>
       </c>
       <c r="O211">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="P211">
-        <v>8.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q211">
-        <v>1.67</v>
+        <v>2.99</v>
       </c>
       <c r="R211">
-        <v>2.79</v>
+        <v>2.16</v>
       </c>
       <c r="S211">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T211">
-        <v>3.85</v>
+        <v>3.12</v>
       </c>
       <c r="U211">
-        <v>2.03</v>
+        <v>2.47</v>
       </c>
       <c r="V211">
-        <v>1.71</v>
+        <v>1.46</v>
       </c>
       <c r="W211">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y211">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z211">
-        <v>5.5</v>
+        <v>3.92</v>
       </c>
       <c r="AA211">
-        <v>1.36</v>
+        <v>1.72</v>
       </c>
       <c r="AB211">
-        <v>2.69</v>
+        <v>2.08</v>
       </c>
       <c r="AC211">
-        <v>2.01</v>
+        <v>2.84</v>
       </c>
       <c r="AD211">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AE211">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AF211">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AG211">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="AK211">
-        <v>3.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>2.72</v>
+        <v>1.62</v>
       </c>
       <c r="O212">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P212">
-        <v>2.29</v>
+        <v>4.45</v>
       </c>
       <c r="Q212">
-        <v>2.99</v>
+        <v>1.97</v>
       </c>
       <c r="R212">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="S212">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T212">
-        <v>3.12</v>
+        <v>3.74</v>
       </c>
       <c r="U212">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="V212">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="W212">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X212">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="Z212">
-        <v>3.92</v>
+        <v>5.75</v>
       </c>
       <c r="AA212">
-        <v>1.72</v>
+        <v>1.39</v>
       </c>
       <c r="AB212">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AC212">
-        <v>2.84</v>
+        <v>2.12</v>
       </c>
       <c r="AD212">
-        <v>1.43</v>
+        <v>1.67</v>
       </c>
       <c r="AE212">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AF212">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG212">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="AK212">
-        <v>1.42</v>
+        <v>2.18</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,65 +35028,65 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O213">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P213">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="Q213">
         <v>1.97</v>
       </c>
       <c r="R213">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="S213">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T213">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="U213">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="V213">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="W213">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X213">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z213">
-        <v>5.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA213">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AB213">
+        <v>2.3</v>
+      </c>
+      <c r="AC213">
         <v>2.56</v>
       </c>
-      <c r="AC213">
+      <c r="AD213">
+        <v>1.47</v>
+      </c>
+      <c r="AE213">
+        <v>1.19</v>
+      </c>
+      <c r="AF213">
+        <v>1.67</v>
+      </c>
+      <c r="AG213">
         <v>2.1</v>
       </c>
-      <c r="AD213">
-        <v>1.68</v>
-      </c>
-      <c r="AE213">
-        <v>1.26</v>
-      </c>
-      <c r="AF213">
-        <v>1.5</v>
-      </c>
-      <c r="AG213">
-        <v>2.45</v>
-      </c>
       <c r="AH213" t="inlineStr">
         <is>
           <t>[]</t>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK213">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="O214">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P214">
-        <v>5.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q214">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="R214">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S214">
         <v>1.25</v>
       </c>
       <c r="T214">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U214">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V214">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="W214">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X214">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z214">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA214">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AB214">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AC214">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="AD214">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AE214">
         <v>1.19</v>
       </c>
       <c r="AF214">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="AG214">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK214">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="O215">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P215">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q215">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="R215">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S215">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T215">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U215">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="V215">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="W215">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X215">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y215">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z215">
-        <v>5.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA215">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AB215">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AC215">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="AD215">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AE215">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF215">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="AG215">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK215">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.74</v>
+        <v>1.28</v>
       </c>
       <c r="O216">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="P216">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q216">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="R216">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="S216">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T216">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="U216">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="V216">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="W216">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X216">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z216">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AA216">
-        <v>1.89</v>
+        <v>1.36</v>
       </c>
       <c r="AB216">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="AC216">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD216">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE216">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AF216">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG216">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK216">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35849,7 +35849,7 @@
         <v>3.4</v>
       </c>
       <c r="P218">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q218">
         <v>3.28</v>
@@ -36009,10 +36009,10 @@
         <v>1.8</v>
       </c>
       <c r="O219">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P219">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q219">
         <v>2.25</v>
@@ -37156,16 +37156,16 @@
         <v>3.89</v>
       </c>
       <c r="Q226">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R226">
         <v>2.25</v>
       </c>
       <c r="S226">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T226">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="U226">
         <v>2.55</v>
@@ -37174,16 +37174,16 @@
         <v>1.44</v>
       </c>
       <c r="W226">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X226">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y226">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z226">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AA226">
         <v>1.75</v>
@@ -37192,19 +37192,19 @@
         <v>2.03</v>
       </c>
       <c r="AC226">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD226">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE226">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF226">
         <v>1.67</v>
       </c>
       <c r="AG226">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH226" t="inlineStr">
         <is>
@@ -37217,10 +37217,10 @@
         </is>
       </c>
       <c r="AJ226">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK226">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL226">
         <v>0</v>
@@ -37319,55 +37319,55 @@
         <v>4.28</v>
       </c>
       <c r="Q227">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R227">
+        <v>2.38</v>
+      </c>
+      <c r="S227">
+        <v>1.3</v>
+      </c>
+      <c r="T227">
+        <v>3.3</v>
+      </c>
+      <c r="U227">
         <v>2.3</v>
       </c>
-      <c r="S227">
-        <v>1.32</v>
-      </c>
-      <c r="T227">
-        <v>3.02</v>
-      </c>
-      <c r="U227">
-        <v>2.45</v>
-      </c>
       <c r="V227">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W227">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X227">
         <v>1.02</v>
       </c>
       <c r="Y227">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z227">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA227">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB227">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="AC227">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="AD227">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AE227">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF227">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG227">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH227" t="inlineStr">
         <is>
@@ -37380,10 +37380,10 @@
         </is>
       </c>
       <c r="AJ227">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK227">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AL227">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,80 +37473,80 @@
         </is>
       </c>
       <c r="N228">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="O228">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P228">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q228">
-        <v>2.37</v>
+        <v>3.01</v>
       </c>
       <c r="R228">
-        <v>2.21</v>
+        <v>2.45</v>
       </c>
       <c r="S228">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T228">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="U228">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V228">
+        <v>1.57</v>
+      </c>
+      <c r="W228">
+        <v>1.17</v>
+      </c>
+      <c r="X228">
+        <v>1.02</v>
+      </c>
+      <c r="Y228">
+        <v>1.11</v>
+      </c>
+      <c r="Z228">
+        <v>6</v>
+      </c>
+      <c r="AA228">
+        <v>1.57</v>
+      </c>
+      <c r="AB228">
+        <v>2.35</v>
+      </c>
+      <c r="AC228">
+        <v>2.29</v>
+      </c>
+      <c r="AD228">
+        <v>1.59</v>
+      </c>
+      <c r="AE228">
+        <v>1.24</v>
+      </c>
+      <c r="AF228">
+        <v>1.47</v>
+      </c>
+      <c r="AG228">
+        <v>2.6</v>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ228">
+        <v>1.29</v>
+      </c>
+      <c r="AK228">
         <v>1.44</v>
-      </c>
-      <c r="W228">
-        <v>1.07</v>
-      </c>
-      <c r="X228">
-        <v>1</v>
-      </c>
-      <c r="Y228">
-        <v>1.21</v>
-      </c>
-      <c r="Z228">
-        <v>3.83</v>
-      </c>
-      <c r="AA228">
-        <v>1.77</v>
-      </c>
-      <c r="AB228">
-        <v>1.93</v>
-      </c>
-      <c r="AC228">
-        <v>2.83</v>
-      </c>
-      <c r="AD228">
-        <v>1.33</v>
-      </c>
-      <c r="AE228">
-        <v>1.09</v>
-      </c>
-      <c r="AF228">
-        <v>1.68</v>
-      </c>
-      <c r="AG228">
-        <v>2.06</v>
-      </c>
-      <c r="AH228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI228" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ228">
-        <v>1.25</v>
-      </c>
-      <c r="AK228">
-        <v>1.92</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.78</v>
+        <v>3.51</v>
       </c>
       <c r="O229">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P229">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="Q229">
-        <v>3.18</v>
+        <v>3.58</v>
       </c>
       <c r="R229">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S229">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T229">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U229">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="V229">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="W229">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="X229">
         <v>1.02</v>
       </c>
       <c r="Y229">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z229">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA229">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AB229">
-        <v>2.27</v>
+        <v>2.66</v>
       </c>
       <c r="AC229">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="AD229">
-        <v>1.46</v>
+        <v>1.73</v>
       </c>
       <c r="AE229">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AF229">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AG229">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK229">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.51</v>
+        <v>1.7</v>
       </c>
       <c r="O230">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="P230">
-        <v>1.86</v>
+        <v>4.52</v>
       </c>
       <c r="Q230">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="R230">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S230">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T230">
-        <v>3.82</v>
+        <v>3.08</v>
       </c>
       <c r="U230">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="V230">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="W230">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="X230">
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="Z230">
-        <v>5.45</v>
+        <v>3.84</v>
       </c>
       <c r="AA230">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AB230">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="AC230">
-        <v>2.02</v>
+        <v>2.62</v>
       </c>
       <c r="AD230">
-        <v>1.74</v>
+        <v>1.38</v>
       </c>
       <c r="AE230">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AF230">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AG230">
-        <v>2.72</v>
+        <v>2</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK230">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="O231">
-        <v>3.84</v>
+        <v>5.95</v>
       </c>
       <c r="P231">
-        <v>4.52</v>
+        <v>9.75</v>
       </c>
       <c r="Q231">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="R231">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="S231">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T231">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="U231">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="V231">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="W231">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X231">
         <v>1.02</v>
       </c>
       <c r="Y231">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z231">
-        <v>3.84</v>
+        <v>6</v>
       </c>
       <c r="AA231">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AB231">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="AC231">
-        <v>2.62</v>
+        <v>2.09</v>
       </c>
       <c r="AD231">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AE231">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="AF231">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG231">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK231">
-        <v>2.38</v>
+        <v>3.58</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,80 +38125,80 @@
         </is>
       </c>
       <c r="N232">
+        <v>2.36</v>
+      </c>
+      <c r="O232">
+        <v>3.5</v>
+      </c>
+      <c r="P232">
+        <v>2.73</v>
+      </c>
+      <c r="Q232">
+        <v>2.63</v>
+      </c>
+      <c r="R232">
+        <v>2.25</v>
+      </c>
+      <c r="S232">
+        <v>1.29</v>
+      </c>
+      <c r="T232">
+        <v>3.3</v>
+      </c>
+      <c r="U232">
+        <v>2.47</v>
+      </c>
+      <c r="V232">
+        <v>1.51</v>
+      </c>
+      <c r="W232">
+        <v>1.11</v>
+      </c>
+      <c r="X232">
+        <v>1.01</v>
+      </c>
+      <c r="Y232">
+        <v>1.23</v>
+      </c>
+      <c r="Z232">
+        <v>3.6</v>
+      </c>
+      <c r="AA232">
+        <v>1.66</v>
+      </c>
+      <c r="AB232">
+        <v>2.05</v>
+      </c>
+      <c r="AC232">
+        <v>2.7</v>
+      </c>
+      <c r="AD232">
+        <v>1.36</v>
+      </c>
+      <c r="AE232">
+        <v>1.13</v>
+      </c>
+      <c r="AF232">
+        <v>1.58</v>
+      </c>
+      <c r="AG232">
+        <v>2.2</v>
+      </c>
+      <c r="AH232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI232" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ232">
         <v>1.25</v>
       </c>
-      <c r="O232">
-        <v>5.95</v>
-      </c>
-      <c r="P232">
-        <v>9.75</v>
-      </c>
-      <c r="Q232">
+      <c r="AK232">
         <v>1.65</v>
-      </c>
-      <c r="R232">
-        <v>2.72</v>
-      </c>
-      <c r="S232">
-        <v>1.21</v>
-      </c>
-      <c r="T232">
-        <v>3.64</v>
-      </c>
-      <c r="U232">
-        <v>2.09</v>
-      </c>
-      <c r="V232">
-        <v>1.64</v>
-      </c>
-      <c r="W232">
-        <v>1.15</v>
-      </c>
-      <c r="X232">
-        <v>1.02</v>
-      </c>
-      <c r="Y232">
-        <v>1.11</v>
-      </c>
-      <c r="Z232">
-        <v>6</v>
-      </c>
-      <c r="AA232">
-        <v>1.42</v>
-      </c>
-      <c r="AB232">
-        <v>2.7</v>
-      </c>
-      <c r="AC232">
-        <v>2.09</v>
-      </c>
-      <c r="AD232">
-        <v>1.65</v>
-      </c>
-      <c r="AE232">
-        <v>1.27</v>
-      </c>
-      <c r="AF232">
-        <v>1.8</v>
-      </c>
-      <c r="AG232">
-        <v>1.9</v>
-      </c>
-      <c r="AH232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI232" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ232">
-        <v>1.11</v>
-      </c>
-      <c r="AK232">
-        <v>3.58</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="O233">
         <v>3.5</v>
       </c>
       <c r="P233">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="Q233">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="R233">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S233">
         <v>1.3</v>
       </c>
       <c r="T233">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U233">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="V233">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W233">
+        <v>1.07</v>
+      </c>
+      <c r="X233">
+        <v>1</v>
+      </c>
+      <c r="Y233">
+        <v>1.21</v>
+      </c>
+      <c r="Z233">
+        <v>3.83</v>
+      </c>
+      <c r="AA233">
+        <v>1.77</v>
+      </c>
+      <c r="AB233">
+        <v>1.93</v>
+      </c>
+      <c r="AC233">
+        <v>2.83</v>
+      </c>
+      <c r="AD233">
+        <v>1.33</v>
+      </c>
+      <c r="AE233">
         <v>1.09</v>
       </c>
-      <c r="X233">
-        <v>1.02</v>
-      </c>
-      <c r="Y233">
-        <v>1.24</v>
-      </c>
-      <c r="Z233">
-        <v>3.55</v>
-      </c>
-      <c r="AA233">
-        <v>1.7</v>
-      </c>
-      <c r="AB233">
-        <v>1.99</v>
-      </c>
-      <c r="AC233">
-        <v>2.7</v>
-      </c>
-      <c r="AD233">
-        <v>1.36</v>
-      </c>
-      <c r="AE233">
-        <v>1.13</v>
-      </c>
       <c r="AF233">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AG233">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK233">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39142,10 +39142,10 @@
         <v>3.42</v>
       </c>
       <c r="AA238">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB238">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC238">
         <v>3.08</v>
@@ -39266,13 +39266,13 @@
         </is>
       </c>
       <c r="N239">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="O239">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="P239">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q239">
         <v>3.8</v>
@@ -39429,10 +39429,10 @@
         </is>
       </c>
       <c r="N240">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O240">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P240">
         <v>2.7</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O241">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="P241">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q241">
         <v>3</v>
@@ -39631,10 +39631,10 @@
         <v>2.84</v>
       </c>
       <c r="AA241">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB241">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC241">
         <v>3.76</v>
@@ -41086,7 +41086,7 @@
         <v>1.44</v>
       </c>
       <c r="W250">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X250">
         <v>1.02</v>
@@ -41249,7 +41249,7 @@
         <v>1.5</v>
       </c>
       <c r="W251">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X251">
         <v>1.01</v>
@@ -41385,19 +41385,19 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="O252">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="P252">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q252">
         <v>3.58</v>
       </c>
       <c r="R252">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S252">
         <v>1.36</v>
@@ -41548,13 +41548,13 @@
         </is>
       </c>
       <c r="N253">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="O253">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="P253">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Q253">
         <v>1.41</v>
@@ -41587,7 +41587,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AA253">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB253">
         <v>3.7</v>
@@ -41717,7 +41717,7 @@
         <v>3.8</v>
       </c>
       <c r="P254">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q254">
         <v>3.4</v>
@@ -41744,10 +41744,10 @@
         <v>1.02</v>
       </c>
       <c r="Y254">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z254">
-        <v>5.05</v>
+        <v>5.4</v>
       </c>
       <c r="AA254">
         <v>1.43</v>
@@ -41768,7 +41768,7 @@
         <v>1.42</v>
       </c>
       <c r="AG254">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AH254" t="inlineStr">
         <is>
@@ -41877,10 +41877,10 @@
         <v>1.35</v>
       </c>
       <c r="O255">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P255">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="Q255">
         <v>1.69</v>
@@ -42719,19 +42719,19 @@
         <v>1.22</v>
       </c>
       <c r="X260">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y260">
         <v>1.06</v>
       </c>
       <c r="Z260">
-        <v>8.449999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="AA260">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AB260">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="AC260">
         <v>1.79</v>
@@ -43187,55 +43187,55 @@
         <v>3.85</v>
       </c>
       <c r="Q263">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R263">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S263">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T263">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U263">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V263">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W263">
         <v>1.12</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y263">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z263">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="AA263">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB263">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AC263">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AD263">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE263">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF263">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AG263">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>1.22</v>
       </c>
       <c r="AK263">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O265">
         <v>3.4</v>
       </c>
       <c r="P265">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="Q265">
         <v>2.6</v>
@@ -43546,7 +43546,7 @@
         <v>1.66</v>
       </c>
       <c r="AB265">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AC265">
         <v>2.46</v>
@@ -43577,7 +43577,7 @@
         <v>1.25</v>
       </c>
       <c r="AK265">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL265">
         <v>0</v>
@@ -43667,7 +43667,7 @@
         </is>
       </c>
       <c r="N266">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O266">
         <v>3.4</v>
@@ -43694,7 +43694,7 @@
         <v>1.53</v>
       </c>
       <c r="W266">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X266">
         <v>1.01</v>
@@ -44319,13 +44319,13 @@
         </is>
       </c>
       <c r="N270">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O270">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P270">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q270">
         <v>2.58</v>
@@ -44340,7 +44340,7 @@
         <v>3.18</v>
       </c>
       <c r="U270">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V270">
         <v>1.47</v>
@@ -44349,7 +44349,7 @@
         <v>1.07</v>
       </c>
       <c r="X270">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y270">
         <v>1.16</v>
@@ -44358,7 +44358,7 @@
         <v>4.15</v>
       </c>
       <c r="AA270">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB270">
         <v>2.13</v>
@@ -44367,10 +44367,10 @@
         <v>2.59</v>
       </c>
       <c r="AD270">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE270">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF270">
         <v>1.56</v>
@@ -44450,12 +44450,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Grosseto</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G271">
@@ -44482,64 +44482,64 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O271">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P271">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Q271">
-        <v>3.58</v>
+        <v>3.02</v>
       </c>
       <c r="R271">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S271">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T271">
-        <v>3.12</v>
+        <v>2.73</v>
       </c>
       <c r="U271">
-        <v>2.44</v>
+        <v>2.77</v>
       </c>
       <c r="V271">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W271">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X271">
         <v>1.01</v>
       </c>
       <c r="Y271">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z271">
-        <v>3.8</v>
+        <v>3.04</v>
       </c>
       <c r="AA271">
-        <v>1.72</v>
+        <v>1.99</v>
       </c>
       <c r="AB271">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="AC271">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="AD271">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="AE271">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF271">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG271">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AH271" t="inlineStr">
         <is>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK271">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44613,12 +44613,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Grosseto</t>
         </is>
       </c>
       <c r="G272">
@@ -44645,64 +44645,64 @@
         </is>
       </c>
       <c r="N272">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O272">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P272">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="Q272">
-        <v>3.02</v>
+        <v>3.58</v>
       </c>
       <c r="R272">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S272">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T272">
-        <v>2.73</v>
+        <v>3.12</v>
       </c>
       <c r="U272">
-        <v>2.77</v>
+        <v>2.44</v>
       </c>
       <c r="V272">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W272">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X272">
         <v>1.01</v>
       </c>
       <c r="Y272">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z272">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="AA272">
-        <v>1.99</v>
+        <v>1.72</v>
       </c>
       <c r="AB272">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AC272">
-        <v>3.42</v>
+        <v>2.78</v>
       </c>
       <c r="AD272">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE272">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF272">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG272">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AH272" t="inlineStr">
         <is>
@@ -44715,10 +44715,10 @@
         </is>
       </c>
       <c r="AJ272">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK272">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AL272">
         <v>0</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O274">
         <v>3.8</v>
       </c>
       <c r="P274">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="Q274">
         <v>2.14</v>
@@ -45137,13 +45137,13 @@
         <v>2.15</v>
       </c>
       <c r="O275">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P275">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q275">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="R275">
         <v>1.95</v>
@@ -45152,7 +45152,7 @@
         <v>1.5</v>
       </c>
       <c r="T275">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U275">
         <v>3.44</v>
@@ -45173,19 +45173,19 @@
         <v>2.52</v>
       </c>
       <c r="AA275">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AB275">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC275">
-        <v>5.1</v>
+        <v>4.73</v>
       </c>
       <c r="AD275">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE275">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF275">
         <v>2.02</v>
@@ -45204,7 +45204,7 @@
         </is>
       </c>
       <c r="AJ275">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK275">
         <v>1.57</v>
@@ -45297,64 +45297,64 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O276">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="P276">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q276">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R276">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S276">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T276">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U276">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V276">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W276">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X276">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y276">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z276">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA276">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB276">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC276">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD276">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE276">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF276">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG276">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH276" t="inlineStr">
         <is>
@@ -45367,10 +45367,10 @@
         </is>
       </c>
       <c r="AJ276">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK276">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL276">
         <v>0</v>
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="O277">
         <v>3.25</v>
       </c>
       <c r="P277">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="Q277">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R277">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S277">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T277">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U277">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V277">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W277">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X277">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y277">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z277">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA277">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AB277">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC277">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD277">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE277">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF277">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG277">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK277">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45623,13 +45623,13 @@
         </is>
       </c>
       <c r="N278">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O278">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P278">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q278">
         <v>0</v>
@@ -46438,13 +46438,13 @@
         </is>
       </c>
       <c r="N283">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="O283">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="P283">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46732,12 +46732,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G285">
@@ -46764,64 +46764,64 @@
         </is>
       </c>
       <c r="N285">
-        <v>1.8</v>
+        <v>2.56</v>
       </c>
       <c r="O285">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="P285">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q285">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="R285">
         <v>2.41</v>
       </c>
       <c r="S285">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T285">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U285">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="V285">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="W285">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X285">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y285">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z285">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AA285">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AB285">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="AC285">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AD285">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AE285">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF285">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG285">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AH285" t="inlineStr">
         <is>
@@ -46834,10 +46834,10 @@
         </is>
       </c>
       <c r="AJ285">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK285">
-        <v>1.98</v>
+        <v>1.47</v>
       </c>
       <c r="AL285">
         <v>0</v>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="O286">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P286">
-        <v>2.41</v>
+        <v>3.9</v>
       </c>
       <c r="Q286">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="R286">
         <v>2.41</v>
       </c>
       <c r="S286">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T286">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U286">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V286">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="W286">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X286">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y286">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z286">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA286">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AB286">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="AC286">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="AD286">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AE286">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF286">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG286">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK286">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47256,7 +47256,7 @@
         <v>1.85</v>
       </c>
       <c r="O288">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P288">
         <v>3.92</v>
@@ -47579,10 +47579,10 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="O290">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P290">
         <v>3.2</v>
@@ -47748,7 +47748,7 @@
         <v>4.33</v>
       </c>
       <c r="P291">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q291">
         <v>5.22</v>
@@ -47911,19 +47911,19 @@
         <v>6</v>
       </c>
       <c r="P292">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q292">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="R292">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="S292">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="T292">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U292">
         <v>1.85</v>
@@ -47932,7 +47932,7 @@
         <v>1.85</v>
       </c>
       <c r="W292">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X292">
         <v>1.01</v>
@@ -47941,22 +47941,22 @@
         <v>1.03</v>
       </c>
       <c r="Z292">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA292">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB292">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC292">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD292">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AE292">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF292">
         <v>1.62</v>
@@ -47975,10 +47975,10 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK292">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AL292">
         <v>0</v>
@@ -48557,7 +48557,7 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="O296">
         <v>3.1</v>
@@ -48596,10 +48596,10 @@
         <v>3.2</v>
       </c>
       <c r="AA296">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB296">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AC296">
         <v>3.6</v>
@@ -48922,10 +48922,10 @@
         <v>4.7</v>
       </c>
       <c r="AA298">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB298">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC298">
         <v>2.23</v>
@@ -49049,10 +49049,10 @@
         <v>5</v>
       </c>
       <c r="O299">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="P299">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q299">
         <v>5</v>
@@ -49061,10 +49061,10 @@
         <v>2.4</v>
       </c>
       <c r="S299">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T299">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U299">
         <v>2.4</v>
@@ -49375,10 +49375,10 @@
         <v>1.52</v>
       </c>
       <c r="O301">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P301">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="Q301">
         <v>2.04</v>
@@ -49553,7 +49553,7 @@
         <v>1.22</v>
       </c>
       <c r="T302">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U302">
         <v>2.05</v>
@@ -49867,7 +49867,7 @@
         <v>5</v>
       </c>
       <c r="P304">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="Q304">
         <v>1.84</v>
@@ -49897,22 +49897,22 @@
         <v>1.15</v>
       </c>
       <c r="Z304">
-        <v>4.84</v>
+        <v>4.99</v>
       </c>
       <c r="AA304">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB304">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AC304">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AD304">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AE304">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AF304">
         <v>1.7</v>
@@ -49931,7 +49931,7 @@
         </is>
       </c>
       <c r="AJ304">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK304">
         <v>3</v>
@@ -50024,10 +50024,10 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O305">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P305">
         <v>4.5</v>
@@ -50187,13 +50187,13 @@
         </is>
       </c>
       <c r="N306">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O306">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="P306">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q306">
         <v>1.57</v>
@@ -50353,10 +50353,10 @@
         <v>1.25</v>
       </c>
       <c r="O307">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="P307">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q307">
         <v>1.68</v>
@@ -50371,10 +50371,10 @@
         <v>5</v>
       </c>
       <c r="U307">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V307">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="W307">
         <v>1.3</v>
@@ -50383,10 +50383,10 @@
         <v>1</v>
       </c>
       <c r="Y307">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z307">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA307">
         <v>1.2</v>
@@ -50679,7 +50679,7 @@
         <v>2.13</v>
       </c>
       <c r="O309">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P309">
         <v>2.85</v>
@@ -51171,7 +51171,7 @@
         <v>15.5</v>
       </c>
       <c r="P312">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q312">
         <v>1.3</v>
@@ -51328,25 +51328,25 @@
         </is>
       </c>
       <c r="N313">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O313">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="P313">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="Q313">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R313">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="S313">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T313">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="U313">
         <v>3.2</v>
@@ -51355,34 +51355,34 @@
         <v>1.3</v>
       </c>
       <c r="W313">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X313">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y313">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="Z313">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AA313">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AB313">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC313">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD313">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE313">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF313">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG313">
         <v>1.73</v>
@@ -51398,7 +51398,7 @@
         </is>
       </c>
       <c r="AJ313">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK313">
         <v>1.62</v>
@@ -51491,58 +51491,58 @@
         </is>
       </c>
       <c r="N314">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="O314">
         <v>2.75</v>
       </c>
       <c r="P314">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q314">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R314">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S314">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T314">
         <v>2.22</v>
       </c>
       <c r="U314">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="V314">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W314">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X314">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y314">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Z314">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="AA314">
-        <v>2.61</v>
+        <v>2.42</v>
       </c>
       <c r="AB314">
         <v>1.48</v>
       </c>
       <c r="AC314">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD314">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE314">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF314">
         <v>2.05</v>
@@ -51561,10 +51561,10 @@
         </is>
       </c>
       <c r="AJ314">
+        <v>1.36</v>
+      </c>
+      <c r="AK314">
         <v>1.4</v>
-      </c>
-      <c r="AK314">
-        <v>1.36</v>
       </c>
       <c r="AL314">
         <v>0</v>
@@ -51660,7 +51660,7 @@
         <v>3.7</v>
       </c>
       <c r="P315">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q315">
         <v>2.03</v>
@@ -51823,7 +51823,7 @@
         <v>3.25</v>
       </c>
       <c r="P316">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="Q316">
         <v>2.69</v>
@@ -51980,10 +51980,10 @@
         </is>
       </c>
       <c r="N317">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O317">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="P317">
         <v>3.5</v>
@@ -52143,7 +52143,7 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="O318">
         <v>3.5</v>
@@ -52309,7 +52309,7 @@
         <v>2.75</v>
       </c>
       <c r="O319">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P319">
         <v>2.6</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,80 +52469,80 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.4</v>
+        <v>3.58</v>
       </c>
       <c r="O320">
-        <v>3.9</v>
+        <v>2.93</v>
       </c>
       <c r="P320">
-        <v>6.5</v>
+        <v>2.06</v>
       </c>
       <c r="Q320">
-        <v>1.98</v>
+        <v>7</v>
       </c>
       <c r="R320">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="S320">
         <v>1.45</v>
       </c>
       <c r="T320">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="U320">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V320">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W320">
         <v>1.05</v>
       </c>
       <c r="X320">
+        <v>1.06</v>
+      </c>
+      <c r="Y320">
+        <v>1.44</v>
+      </c>
+      <c r="Z320">
+        <v>2.6</v>
+      </c>
+      <c r="AA320">
+        <v>2.36</v>
+      </c>
+      <c r="AB320">
+        <v>1.49</v>
+      </c>
+      <c r="AC320">
+        <v>4.4</v>
+      </c>
+      <c r="AD320">
+        <v>1.16</v>
+      </c>
+      <c r="AE320">
+        <v>1.01</v>
+      </c>
+      <c r="AF320">
+        <v>2.45</v>
+      </c>
+      <c r="AG320">
+        <v>1.44</v>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ320">
+        <v>1.19</v>
+      </c>
+      <c r="AK320">
         <v>1.03</v>
-      </c>
-      <c r="Y320">
-        <v>1.38</v>
-      </c>
-      <c r="Z320">
-        <v>2.87</v>
-      </c>
-      <c r="AA320">
-        <v>2.25</v>
-      </c>
-      <c r="AB320">
-        <v>1.6</v>
-      </c>
-      <c r="AC320">
-        <v>4.22</v>
-      </c>
-      <c r="AD320">
-        <v>1.19</v>
-      </c>
-      <c r="AE320">
-        <v>1.03</v>
-      </c>
-      <c r="AF320">
-        <v>2.38</v>
-      </c>
-      <c r="AG320">
-        <v>1.51</v>
-      </c>
-      <c r="AH320" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI320" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ320">
-        <v>1.16</v>
-      </c>
-      <c r="AK320">
-        <v>2.63</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O321">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P321">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Q321">
-        <v>7</v>
+        <v>2.02</v>
       </c>
       <c r="R321">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S321">
+        <v>1.44</v>
+      </c>
+      <c r="T321">
+        <v>2.45</v>
+      </c>
+      <c r="U321">
+        <v>3.5</v>
+      </c>
+      <c r="V321">
+        <v>1.25</v>
+      </c>
+      <c r="W321">
+        <v>1.04</v>
+      </c>
+      <c r="X321">
+        <v>1.04</v>
+      </c>
+      <c r="Y321">
         <v>1.45</v>
       </c>
-      <c r="T321">
-        <v>2.42</v>
-      </c>
-      <c r="U321">
-        <v>3.3</v>
-      </c>
-      <c r="V321">
-        <v>1.3</v>
-      </c>
-      <c r="W321">
-        <v>1.05</v>
-      </c>
-      <c r="X321">
-        <v>1.06</v>
-      </c>
-      <c r="Y321">
-        <v>1.44</v>
-      </c>
       <c r="Z321">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AA321">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AB321">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AC321">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AD321">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE321">
         <v>1.01</v>
       </c>
       <c r="AF321">
-        <v>2.51</v>
+        <v>2.71</v>
       </c>
       <c r="AG321">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK321">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.44</v>
+        <v>9.5</v>
       </c>
       <c r="O322">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P322">
-        <v>7.25</v>
+        <v>1.25</v>
       </c>
       <c r="Q322">
-        <v>2.02</v>
+        <v>7.52</v>
       </c>
       <c r="R322">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="S322">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T322">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="U322">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="V322">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W322">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X322">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y322">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="Z322">
-        <v>2.41</v>
+        <v>3.34</v>
       </c>
       <c r="AA322">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AB322">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AC322">
-        <v>5</v>
+        <v>2.97</v>
       </c>
       <c r="AD322">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AE322">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF322">
-        <v>2.71</v>
+        <v>2.19</v>
       </c>
       <c r="AG322">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>1.18</v>
       </c>
       <c r="AK322">
-        <v>2.52</v>
+        <v>1.07</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>9.5</v>
+        <v>1.65</v>
       </c>
       <c r="O323">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="P323">
-        <v>1.27</v>
+        <v>4.5</v>
       </c>
       <c r="Q323">
-        <v>8.5</v>
+        <v>2.15</v>
       </c>
       <c r="R323">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="S323">
+        <v>1.37</v>
+      </c>
+      <c r="T323">
+        <v>2.69</v>
+      </c>
+      <c r="U323">
+        <v>2.8</v>
+      </c>
+      <c r="V323">
+        <v>1.36</v>
+      </c>
+      <c r="W323">
+        <v>1.06</v>
+      </c>
+      <c r="X323">
+        <v>1.02</v>
+      </c>
+      <c r="Y323">
         <v>1.31</v>
       </c>
-      <c r="T323">
-        <v>3.06</v>
-      </c>
-      <c r="U323">
-        <v>2.63</v>
-      </c>
-      <c r="V323">
-        <v>1.41</v>
-      </c>
-      <c r="W323">
-        <v>1.11</v>
-      </c>
-      <c r="X323">
-        <v>1.01</v>
-      </c>
-      <c r="Y323">
-        <v>1.23</v>
-      </c>
       <c r="Z323">
+        <v>2.92</v>
+      </c>
+      <c r="AA323">
+        <v>2.02</v>
+      </c>
+      <c r="AB323">
+        <v>1.68</v>
+      </c>
+      <c r="AC323">
         <v>3.5</v>
       </c>
-      <c r="AA323">
-        <v>1.57</v>
-      </c>
-      <c r="AB323">
-        <v>2.35</v>
-      </c>
-      <c r="AC323">
-        <v>2.88</v>
-      </c>
       <c r="AD323">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE323">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF323">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AG323">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK323">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O324">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P324">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q324">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R324">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="S324">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="T324">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="U324">
-        <v>2.8</v>
+        <v>3.52</v>
       </c>
       <c r="V324">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W324">
+        <v>1.04</v>
+      </c>
+      <c r="X324">
         <v>1.06</v>
       </c>
-      <c r="X324">
-        <v>1.02</v>
-      </c>
       <c r="Y324">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="Z324">
-        <v>2.92</v>
+        <v>2.33</v>
       </c>
       <c r="AA324">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AB324">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="AC324">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AD324">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AE324">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF324">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AG324">
-        <v>1.71</v>
+        <v>1.41</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AK324">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="O325">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P325">
         <v>6.5</v>
       </c>
       <c r="Q325">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="R325">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S325">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T325">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="U325">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="V325">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="W325">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X325">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y325">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z325">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="AA325">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB325">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC325">
-        <v>5.3</v>
+        <v>4.22</v>
       </c>
       <c r="AD325">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AE325">
         <v>1.03</v>
       </c>
       <c r="AF325">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG325">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK325">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -54230,12 +54230,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kruger United</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G331">
@@ -54393,12 +54393,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Kruger United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G332">
@@ -54591,10 +54591,10 @@
         <v>2.1</v>
       </c>
       <c r="O333">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P333">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="Q333">
         <v>2.83</v>
@@ -54914,7 +54914,7 @@
         </is>
       </c>
       <c r="N335">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O335">
         <v>3.2</v>
@@ -54956,7 +54956,7 @@
         <v>2.6</v>
       </c>
       <c r="AB335">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC335">
         <v>5.3</v>
@@ -54971,7 +54971,7 @@
         <v>2.3</v>
       </c>
       <c r="AG335">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AH335" t="inlineStr">
         <is>
@@ -55077,13 +55077,13 @@
         </is>
       </c>
       <c r="N336">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="O336">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="P336">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="Q336">
         <v>1.7</v>
@@ -55279,10 +55279,10 @@
         <v>5.25</v>
       </c>
       <c r="AA337">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AB337">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AC337">
         <v>2.03</v>
@@ -55732,7 +55732,7 @@
         <v>3.74</v>
       </c>
       <c r="O340">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P340">
         <v>1.89</v>
@@ -55898,7 +55898,7 @@
         <v>3.1</v>
       </c>
       <c r="P341">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q341">
         <v>2.7</v>
@@ -56707,7 +56707,7 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O346">
         <v>3.5</v>
@@ -56912,7 +56912,7 @@
         <v>1.33</v>
       </c>
       <c r="AB347">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC347">
         <v>1.88</v>
@@ -57057,7 +57057,7 @@
         <v>2.04</v>
       </c>
       <c r="V348">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="W348">
         <v>1.14</v>
@@ -57075,13 +57075,13 @@
         <v>1.4</v>
       </c>
       <c r="AB348">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AC348">
         <v>2.15</v>
       </c>
       <c r="AD348">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE348">
         <v>1.25</v>
@@ -57196,7 +57196,7 @@
         </is>
       </c>
       <c r="N349">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="O349">
         <v>5.15</v>
@@ -57238,7 +57238,7 @@
         <v>1.56</v>
       </c>
       <c r="AB349">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC349">
         <v>2.41</v>
@@ -57365,7 +57365,7 @@
         <v>3.6</v>
       </c>
       <c r="P350">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="Q350">
         <v>2.61</v>
@@ -57374,16 +57374,16 @@
         <v>2.14</v>
       </c>
       <c r="S350">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T350">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="U350">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V350">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W350">
         <v>1.08</v>
@@ -57522,7 +57522,7 @@
         </is>
       </c>
       <c r="N351">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O351">
         <v>3.75</v>
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="O352">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="P352">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="Q352">
         <v>1.91</v>
@@ -57872,7 +57872,7 @@
         <v>2.25</v>
       </c>
       <c r="V353">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W353">
         <v>1.14</v>
@@ -58014,7 +58014,7 @@
         <v>1.96</v>
       </c>
       <c r="O354">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P354">
         <v>3.62</v>
@@ -58056,7 +58056,7 @@
         <v>2.25</v>
       </c>
       <c r="AC354">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AD354">
         <v>1.46</v>
@@ -58081,7 +58081,7 @@
         </is>
       </c>
       <c r="AJ354">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK354">
         <v>1.75</v>
@@ -58180,7 +58180,7 @@
         <v>3.3</v>
       </c>
       <c r="P355">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q355">
         <v>2.34</v>
@@ -58213,10 +58213,10 @@
         <v>2.73</v>
       </c>
       <c r="AA355">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AB355">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC355">
         <v>4.25</v>
@@ -58337,13 +58337,13 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O356">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="P356">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -58500,7 +58500,7 @@
         </is>
       </c>
       <c r="N357">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="O357">
         <v>10</v>
@@ -58548,7 +58548,7 @@
         <v>1.6</v>
       </c>
       <c r="AD357">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="AE357">
         <v>1.61</v>
@@ -58826,19 +58826,19 @@
         </is>
       </c>
       <c r="N359">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O359">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="P359">
         <v>2.2</v>
       </c>
       <c r="Q359">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="R359">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="S359">
         <v>1.22</v>
@@ -58847,10 +58847,10 @@
         <v>4</v>
       </c>
       <c r="U359">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V359">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W359">
         <v>1.17</v>
@@ -58862,19 +58862,19 @@
         <v>1.1</v>
       </c>
       <c r="Z359">
-        <v>5.95</v>
+        <v>5.89</v>
       </c>
       <c r="AA359">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB359">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AC359">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD359">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AE359">
         <v>1.25</v>
@@ -58899,7 +58899,7 @@
         <v>1.71</v>
       </c>
       <c r="AK359">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -58992,10 +58992,10 @@
         <v>1.78</v>
       </c>
       <c r="O360">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="P360">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="Q360">
         <v>2.2</v>
@@ -59478,22 +59478,22 @@
         </is>
       </c>
       <c r="N363">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O363">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="P363">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="Q363">
         <v>1.61</v>
       </c>
       <c r="R363">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="S363">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T363">
         <v>4</v>
@@ -59502,7 +59502,7 @@
         <v>2.03</v>
       </c>
       <c r="V363">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W363">
         <v>1.17</v>
@@ -59514,16 +59514,16 @@
         <v>1.1</v>
       </c>
       <c r="Z363">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="AA363">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB363">
         <v>2.67</v>
       </c>
       <c r="AC363">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD363">
         <v>1.74</v>
@@ -59647,7 +59647,7 @@
         <v>3</v>
       </c>
       <c r="P364">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q364">
         <v>2.38</v>
@@ -59683,7 +59683,7 @@
         <v>2.78</v>
       </c>
       <c r="AB364">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC364">
         <v>5.6</v>
@@ -60456,31 +60456,31 @@
         </is>
       </c>
       <c r="N369">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O369">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P369">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q369">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="R369">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="S369">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T369">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U369">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V369">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W369">
         <v>1.06</v>
@@ -60492,7 +60492,7 @@
         <v>1.3</v>
       </c>
       <c r="Z369">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="AA369">
         <v>1.95</v>
@@ -60785,10 +60785,10 @@
         <v>2.05</v>
       </c>
       <c r="O371">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P371">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q371">
         <v>2.5</v>
@@ -60800,13 +60800,13 @@
         <v>1.36</v>
       </c>
       <c r="T371">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U371">
         <v>2.96</v>
       </c>
       <c r="V371">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W371">
         <v>1.08</v>
@@ -60824,7 +60824,7 @@
         <v>2.07</v>
       </c>
       <c r="AB371">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AC371">
         <v>3.2</v>
@@ -60839,7 +60839,7 @@
         <v>1.8</v>
       </c>
       <c r="AG371">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH371" t="inlineStr">
         <is>
@@ -60852,10 +60852,10 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK371">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL371">
         <v>0</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
         <v>2.9</v>
@@ -982,22 +982,22 @@
         <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>1.18</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AA4">
         <v>1.71</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK4">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>3.1</v>
       </c>
       <c r="P5">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="Q5">
         <v>2.88</v>
@@ -1163,7 +1163,7 @@
         <v>2.9</v>
       </c>
       <c r="AA5">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB5">
         <v>1.61</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q6">
         <v>3.3</v>
@@ -1305,10 +1305,10 @@
         <v>1.36</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="V6">
         <v>1.34</v>
@@ -1492,7 +1492,7 @@
         <v>2.25</v>
       </c>
       <c r="AB7">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC7">
         <v>4.1</v>
@@ -1652,7 +1652,7 @@
         <v>4.4</v>
       </c>
       <c r="AA8">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AB8">
         <v>2.13</v>
@@ -1779,16 +1779,16 @@
         <v>1.83</v>
       </c>
       <c r="O9">
+        <v>3.6</v>
+      </c>
+      <c r="P9">
         <v>3.55</v>
-      </c>
-      <c r="P9">
-        <v>3.5</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
       </c>
       <c r="R9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
         <v>1.28</v>
@@ -1818,7 +1818,7 @@
         <v>1.8</v>
       </c>
       <c r="AB9">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AC9">
         <v>2.9</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,10 +1942,10 @@
         <v>2.57</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q10">
         <v>3.25</v>
@@ -1960,10 +1960,10 @@
         <v>2.77</v>
       </c>
       <c r="U10">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -2138,13 +2138,13 @@
         <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="AA11">
         <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AC11">
         <v>2.3</v>
@@ -2271,7 +2271,7 @@
         <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q12">
         <v>3.3</v>
@@ -2307,7 +2307,7 @@
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
         <v>3.1</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.35</v>
+        <v>4.65</v>
       </c>
       <c r="O14">
         <v>3.75</v>
@@ -2600,10 +2600,10 @@
         <v>1.6</v>
       </c>
       <c r="Q14">
-        <v>4.5</v>
+        <v>5.05</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S14">
         <v>1.3</v>
@@ -2624,31 +2624,31 @@
         <v>1</v>
       </c>
       <c r="Y14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>3.72</v>
+        <v>4</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB14">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AC14">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AD14">
         <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q15">
         <v>3.04</v>
@@ -2793,10 +2793,10 @@
         <v>3.25</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB15">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC15">
         <v>3.34</v>
@@ -2811,7 +2811,7 @@
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P16">
         <v>2.05</v>
@@ -2959,7 +2959,7 @@
         <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC16">
         <v>3.39</v>
@@ -2971,10 +2971,10 @@
         <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="P17">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="Q17">
         <v>6</v>
@@ -3119,10 +3119,10 @@
         <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB17">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AC17">
         <v>2.58</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="O18">
+        <v>3.25</v>
+      </c>
+      <c r="P18">
         <v>3.4</v>
-      </c>
-      <c r="P18">
-        <v>3.35</v>
       </c>
       <c r="Q18">
         <v>2.63</v>
@@ -3261,7 +3261,7 @@
         <v>1.36</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U18">
         <v>2.68</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O20">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="P20">
         <v>4.1</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O21">
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q21">
         <v>2.3</v>
@@ -3771,10 +3771,10 @@
         <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB21">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AC21">
         <v>2.62</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="Q30">
         <v>2.5</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P31">
         <v>2.05</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O32">
         <v>3.1</v>
@@ -5691,13 +5691,13 @@
         <v>2.6</v>
       </c>
       <c r="O33">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
         <v>2.3</v>
       </c>
       <c r="Q33">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
         <v>2.2</v>
@@ -5715,7 +5715,7 @@
         <v>1.55</v>
       </c>
       <c r="W33">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
         <v>1.02</v>
@@ -5724,19 +5724,19 @@
         <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="AA33">
         <v>1.65</v>
       </c>
       <c r="AB33">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AC33">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD33">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE33">
         <v>1.13</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK33">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7825,7 +7825,7 @@
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U46">
         <v>2.6</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>2.91</v>
       </c>
       <c r="R69">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="S69">
         <v>1.3</v>
@@ -12703,7 +12703,7 @@
         <v>3.7</v>
       </c>
       <c r="P76">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q76">
         <v>7.6</v>
@@ -12712,16 +12712,16 @@
         <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U76">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V76">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W76">
         <v>1.07</v>
@@ -12893,7 +12893,7 @@
         <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z77">
         <v>3.58</v>
@@ -12902,7 +12902,7 @@
         <v>1.76</v>
       </c>
       <c r="AB77">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC77">
         <v>2.88</v>
@@ -12911,13 +12911,13 @@
         <v>1.32</v>
       </c>
       <c r="AE77">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
+        <v>1.83</v>
+      </c>
+      <c r="AG77">
         <v>1.84</v>
-      </c>
-      <c r="AG77">
-        <v>1.83</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC117">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -20412,10 +20412,10 @@
         <v>1.11</v>
       </c>
       <c r="AF123">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG123">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="O130">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P130">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="Q130">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="R130">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S130">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T130">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U130">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V130">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X130">
         <v>1</v>
       </c>
       <c r="Y130">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z130">
-        <v>4.24</v>
+        <v>3.34</v>
       </c>
       <c r="AA130">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB130">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC130">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD130">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE130">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF130">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AG130">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK130">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,34 +21662,34 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="O131">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
       <c r="P131">
-        <v>3.89</v>
+        <v>4.7</v>
       </c>
       <c r="Q131">
-        <v>2.4</v>
+        <v>2.08</v>
       </c>
       <c r="R131">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S131">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T131">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="U131">
         <v>2.5</v>
       </c>
       <c r="V131">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W131">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
         <v>1</v>
@@ -21701,25 +21701,25 @@
         <v>3.34</v>
       </c>
       <c r="AA131">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB131">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AC131">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AD131">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE131">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF131">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AG131">
-        <v>1.93</v>
+        <v>1.77</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK131">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="O132">
-        <v>3.82</v>
+        <v>3.35</v>
       </c>
       <c r="P132">
-        <v>5.64</v>
+        <v>3.25</v>
       </c>
       <c r="Q132">
-        <v>2.08</v>
+        <v>2.61</v>
       </c>
       <c r="R132">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S132">
+        <v>1.36</v>
+      </c>
+      <c r="T132">
+        <v>2.75</v>
+      </c>
+      <c r="U132">
+        <v>2.8</v>
+      </c>
+      <c r="V132">
+        <v>1.34</v>
+      </c>
+      <c r="W132">
+        <v>1.07</v>
+      </c>
+      <c r="X132">
+        <v>1.03</v>
+      </c>
+      <c r="Y132">
         <v>1.33</v>
       </c>
-      <c r="T132">
-        <v>2.83</v>
-      </c>
-      <c r="U132">
-        <v>2.5</v>
-      </c>
-      <c r="V132">
-        <v>1.36</v>
-      </c>
-      <c r="W132">
+      <c r="Z132">
+        <v>3.13</v>
+      </c>
+      <c r="AA132">
+        <v>2.07</v>
+      </c>
+      <c r="AB132">
+        <v>1.72</v>
+      </c>
+      <c r="AC132">
+        <v>3.67</v>
+      </c>
+      <c r="AD132">
+        <v>1.26</v>
+      </c>
+      <c r="AE132">
         <v>1.04</v>
       </c>
-      <c r="X132">
-        <v>1</v>
-      </c>
-      <c r="Y132">
-        <v>1.24</v>
-      </c>
-      <c r="Z132">
-        <v>3.34</v>
-      </c>
-      <c r="AA132">
+      <c r="AF132">
         <v>1.85</v>
       </c>
-      <c r="AB132">
-        <v>1.93</v>
-      </c>
-      <c r="AC132">
-        <v>3.11</v>
-      </c>
-      <c r="AD132">
-        <v>1.34</v>
-      </c>
-      <c r="AE132">
-        <v>1.06</v>
-      </c>
-      <c r="AF132">
-        <v>1.89</v>
-      </c>
       <c r="AG132">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK132">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="O133">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P133">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="Q133">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R133">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="S133">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T133">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="U133">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="V133">
         <v>1.34</v>
       </c>
       <c r="W133">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X133">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y133">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z133">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AA133">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="AB133">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC133">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="AD133">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE133">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF133">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG133">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK133">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="O134">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P134">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="Q134">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R134">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S134">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="U134">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="V134">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W134">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X134">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y134">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z134">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AA134">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB134">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC134">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD134">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE134">
         <v>1.06</v>
       </c>
       <c r="AF134">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG134">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK134">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,19 +22314,19 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O135">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P135">
-        <v>4.19</v>
+        <v>3.85</v>
       </c>
       <c r="Q135">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R135">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S135">
         <v>1.36</v>
@@ -22335,43 +22335,43 @@
         <v>2.88</v>
       </c>
       <c r="U135">
-        <v>2.61</v>
+        <v>2.94</v>
       </c>
       <c r="V135">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
         <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z135">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA135">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AB135">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC135">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD135">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE135">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF135">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG135">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK135">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,64 +22477,64 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O136">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="P136">
-        <v>4.01</v>
+        <v>4.45</v>
       </c>
       <c r="Q136">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R136">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S136">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="T136">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="U136">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="V136">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W136">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X136">
         <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z136">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA136">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB136">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC136">
-        <v>3.34</v>
+        <v>3.06</v>
       </c>
       <c r="AD136">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE136">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF136">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG136">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK136">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,64 +22640,64 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="O137">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="P137">
-        <v>5.05</v>
+        <v>2.58</v>
       </c>
       <c r="Q137">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R137">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S137">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U137">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="V137">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W137">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X137">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y137">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="Z137">
-        <v>3.79</v>
+        <v>4.24</v>
       </c>
       <c r="AA137">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AB137">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC137">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="AD137">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE137">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF137">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG137">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AK137">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -25085,7 +25085,7 @@
         </is>
       </c>
       <c r="N152">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O152">
         <v>3.1</v>
@@ -25106,7 +25106,7 @@
         <v>2.62</v>
       </c>
       <c r="U152">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V152">
         <v>1.3</v>
@@ -25260,7 +25260,7 @@
         <v>3.42</v>
       </c>
       <c r="R153">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S153">
         <v>1.3</v>
@@ -25287,10 +25287,10 @@
         <v>3.5</v>
       </c>
       <c r="AA153">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB153">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC153">
         <v>2.97</v>
@@ -26244,7 +26244,7 @@
         <v>1.24</v>
       </c>
       <c r="T159">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U159">
         <v>2.2</v>
@@ -26268,7 +26268,7 @@
         <v>1.52</v>
       </c>
       <c r="AB159">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AC159">
         <v>2.34</v>
@@ -26622,7 +26622,7 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK161">
         <v>1.55</v>
@@ -26715,7 +26715,7 @@
         </is>
       </c>
       <c r="N162">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="O162">
         <v>3.5</v>
@@ -27041,13 +27041,13 @@
         </is>
       </c>
       <c r="N164">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O164">
         <v>3.6</v>
       </c>
       <c r="P164">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="Q164">
         <v>0</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="N165">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O165">
         <v>3.9</v>
@@ -27693,10 +27693,10 @@
         </is>
       </c>
       <c r="N168">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O168">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="P168">
         <v>3.5</v>
@@ -27877,7 +27877,7 @@
         <v>4</v>
       </c>
       <c r="U169">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V169">
         <v>1.67</v>
@@ -28384,10 +28384,10 @@
         <v>5.9</v>
       </c>
       <c r="AA172">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB172">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC172">
         <v>2.09</v>
@@ -28674,10 +28674,10 @@
         <v>2.65</v>
       </c>
       <c r="O174">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="P174">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="Q174">
         <v>0</v>
@@ -28710,10 +28710,10 @@
         <v>0</v>
       </c>
       <c r="AA174">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB174">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC174">
         <v>0</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="O191">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P191">
+        <v>2.5</v>
+      </c>
+      <c r="Q191">
+        <v>3.25</v>
+      </c>
+      <c r="R191">
         <v>2.15</v>
       </c>
-      <c r="Q191">
-        <v>3.38</v>
-      </c>
-      <c r="R191">
-        <v>2.3</v>
-      </c>
       <c r="S191">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T191">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="U191">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="V191">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="W191">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X191">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y191">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z191">
-        <v>4.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA191">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AB191">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC191">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AD191">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="AE191">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AF191">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AG191">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK191">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,64 +31605,64 @@
         </is>
       </c>
       <c r="N192">
+        <v>2.9</v>
+      </c>
+      <c r="O192">
+        <v>3.7</v>
+      </c>
+      <c r="P192">
+        <v>2.15</v>
+      </c>
+      <c r="Q192">
+        <v>3.38</v>
+      </c>
+      <c r="R192">
+        <v>2.3</v>
+      </c>
+      <c r="S192">
+        <v>1.21</v>
+      </c>
+      <c r="T192">
+        <v>3.65</v>
+      </c>
+      <c r="U192">
+        <v>2.39</v>
+      </c>
+      <c r="V192">
+        <v>1.5</v>
+      </c>
+      <c r="W192">
+        <v>1.13</v>
+      </c>
+      <c r="X192">
+        <v>1.03</v>
+      </c>
+      <c r="Y192">
+        <v>1.15</v>
+      </c>
+      <c r="Z192">
+        <v>4.6</v>
+      </c>
+      <c r="AA192">
         <v>1.6</v>
       </c>
-      <c r="O192">
-        <v>3.95</v>
-      </c>
-      <c r="P192">
-        <v>4.4</v>
-      </c>
-      <c r="Q192">
-        <v>2.12</v>
-      </c>
-      <c r="R192">
-        <v>2.42</v>
-      </c>
-      <c r="S192">
-        <v>1.31</v>
-      </c>
-      <c r="T192">
-        <v>2.91</v>
-      </c>
-      <c r="U192">
-        <v>2.59</v>
-      </c>
-      <c r="V192">
+      <c r="AB192">
+        <v>2.2</v>
+      </c>
+      <c r="AC192">
+        <v>2.33</v>
+      </c>
+      <c r="AD192">
+        <v>1.51</v>
+      </c>
+      <c r="AE192">
+        <v>1.19</v>
+      </c>
+      <c r="AF192">
         <v>1.47</v>
       </c>
-      <c r="W192">
-        <v>1.08</v>
-      </c>
-      <c r="X192">
-        <v>1.04</v>
-      </c>
-      <c r="Y192">
-        <v>1.23</v>
-      </c>
-      <c r="Z192">
-        <v>3.96</v>
-      </c>
-      <c r="AA192">
-        <v>1.74</v>
-      </c>
-      <c r="AB192">
-        <v>2.06</v>
-      </c>
-      <c r="AC192">
-        <v>2.82</v>
-      </c>
-      <c r="AD192">
-        <v>1.41</v>
-      </c>
-      <c r="AE192">
-        <v>1.15</v>
-      </c>
-      <c r="AF192">
-        <v>1.74</v>
-      </c>
       <c r="AG192">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK192">
-        <v>2.15</v>
+        <v>1.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O193">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P193">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q193">
-        <v>3.08</v>
+        <v>2.12</v>
       </c>
       <c r="R193">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="S193">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T193">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="U193">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="V193">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W193">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X193">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y193">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z193">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="AA193">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AB193">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC193">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="AD193">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE193">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF193">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AG193">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK193">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="O194">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P194">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q194">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="R194">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S194">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T194">
-        <v>2.7</v>
+        <v>3.19</v>
       </c>
       <c r="U194">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="V194">
+        <v>1.43</v>
+      </c>
+      <c r="W194">
+        <v>1.1</v>
+      </c>
+      <c r="X194">
+        <v>1.02</v>
+      </c>
+      <c r="Y194">
+        <v>1.25</v>
+      </c>
+      <c r="Z194">
+        <v>3.6</v>
+      </c>
+      <c r="AA194">
+        <v>1.78</v>
+      </c>
+      <c r="AB194">
+        <v>2.01</v>
+      </c>
+      <c r="AC194">
+        <v>2.98</v>
+      </c>
+      <c r="AD194">
         <v>1.37</v>
       </c>
-      <c r="W194">
-        <v>1.03</v>
-      </c>
-      <c r="X194">
-        <v>1</v>
-      </c>
-      <c r="Y194">
-        <v>1.28</v>
-      </c>
-      <c r="Z194">
-        <v>3.08</v>
-      </c>
-      <c r="AA194">
-        <v>2.01</v>
-      </c>
-      <c r="AB194">
-        <v>1.74</v>
-      </c>
-      <c r="AC194">
-        <v>3.42</v>
-      </c>
-      <c r="AD194">
-        <v>1.23</v>
-      </c>
       <c r="AE194">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF194">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG194">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK194">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,80 +32094,80 @@
         </is>
       </c>
       <c r="N195">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="O195">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="P195">
         <v>3.4</v>
       </c>
       <c r="Q195">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="R195">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S195">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T195">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U195">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V195">
+        <v>1.37</v>
+      </c>
+      <c r="W195">
+        <v>1.03</v>
+      </c>
+      <c r="X195">
+        <v>1</v>
+      </c>
+      <c r="Y195">
+        <v>1.28</v>
+      </c>
+      <c r="Z195">
+        <v>3.08</v>
+      </c>
+      <c r="AA195">
+        <v>2.01</v>
+      </c>
+      <c r="AB195">
+        <v>1.74</v>
+      </c>
+      <c r="AC195">
+        <v>3.42</v>
+      </c>
+      <c r="AD195">
+        <v>1.23</v>
+      </c>
+      <c r="AE195">
+        <v>1.06</v>
+      </c>
+      <c r="AF195">
+        <v>1.82</v>
+      </c>
+      <c r="AG195">
+        <v>1.88</v>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ195">
         <v>1.33</v>
       </c>
-      <c r="W195">
-        <v>1.05</v>
-      </c>
-      <c r="X195">
-        <v>1.04</v>
-      </c>
-      <c r="Y195">
-        <v>1.37</v>
-      </c>
-      <c r="Z195">
-        <v>2.79</v>
-      </c>
-      <c r="AA195">
-        <v>2.15</v>
-      </c>
-      <c r="AB195">
-        <v>1.68</v>
-      </c>
-      <c r="AC195">
-        <v>3.82</v>
-      </c>
-      <c r="AD195">
-        <v>1.25</v>
-      </c>
-      <c r="AE195">
-        <v>1.05</v>
-      </c>
-      <c r="AF195">
-        <v>1.83</v>
-      </c>
-      <c r="AG195">
-        <v>1.85</v>
-      </c>
-      <c r="AH195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI195" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ195">
-        <v>1.25</v>
-      </c>
       <c r="AK195">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="O196">
-        <v>3.55</v>
+        <v>3.16</v>
       </c>
       <c r="P196">
         <v>3.4</v>
       </c>
       <c r="Q196">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="R196">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S196">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="T196">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="U196">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="V196">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W196">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X196">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y196">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="Z196">
-        <v>3.84</v>
+        <v>2.79</v>
       </c>
       <c r="AA196">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AB196">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AC196">
-        <v>2.7</v>
+        <v>3.82</v>
       </c>
       <c r="AD196">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE196">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF196">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG196">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK196">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="O197">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P197">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q197">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="R197">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S197">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T197">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="U197">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="V197">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="W197">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X197">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y197">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z197">
-        <v>4.33</v>
+        <v>3.84</v>
       </c>
       <c r="AA197">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB197">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="AC197">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD197">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE197">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF197">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG197">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK197">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="O199">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P199">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q199">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="R199">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S199">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T199">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="U199">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="V199">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="W199">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X199">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y199">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z199">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA199">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AB199">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="AC199">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AD199">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE199">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF199">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AG199">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK199">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="O212">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="P212">
-        <v>4.45</v>
+        <v>5.5</v>
       </c>
       <c r="Q212">
         <v>1.97</v>
       </c>
       <c r="R212">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="S212">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T212">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="U212">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="V212">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="W212">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X212">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z212">
-        <v>5.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA212">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="AB212">
+        <v>2.3</v>
+      </c>
+      <c r="AC212">
         <v>2.56</v>
       </c>
-      <c r="AC212">
-        <v>2.12</v>
-      </c>
       <c r="AD212">
+        <v>1.47</v>
+      </c>
+      <c r="AE212">
+        <v>1.19</v>
+      </c>
+      <c r="AF212">
         <v>1.67</v>
       </c>
-      <c r="AE212">
-        <v>1.26</v>
-      </c>
-      <c r="AF212">
-        <v>1.5</v>
-      </c>
       <c r="AG212">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK212">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="O213">
+        <v>3.7</v>
+      </c>
+      <c r="P213">
         <v>4.4</v>
       </c>
-      <c r="P213">
-        <v>5.5</v>
-      </c>
       <c r="Q213">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="R213">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S213">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T213">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U213">
-        <v>2.23</v>
+        <v>2.83</v>
       </c>
       <c r="V213">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="W213">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X213">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y213">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z213">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA213">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AB213">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AC213">
-        <v>2.56</v>
+        <v>2.99</v>
       </c>
       <c r="AD213">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AE213">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF213">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG213">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK213">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
+        <v>1.28</v>
+      </c>
+      <c r="O214">
+        <v>6</v>
+      </c>
+      <c r="P214">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q214">
+        <v>1.62</v>
+      </c>
+      <c r="R214">
+        <v>2.79</v>
+      </c>
+      <c r="S214">
+        <v>1.2</v>
+      </c>
+      <c r="T214">
+        <v>3.85</v>
+      </c>
+      <c r="U214">
+        <v>2.03</v>
+      </c>
+      <c r="V214">
         <v>1.71</v>
       </c>
-      <c r="O214">
-        <v>4</v>
-      </c>
-      <c r="P214">
-        <v>4.2</v>
-      </c>
-      <c r="Q214">
-        <v>2.11</v>
-      </c>
-      <c r="R214">
-        <v>2.34</v>
-      </c>
-      <c r="S214">
-        <v>1.25</v>
-      </c>
-      <c r="T214">
-        <v>3.7</v>
-      </c>
-      <c r="U214">
-        <v>2.2</v>
-      </c>
-      <c r="V214">
-        <v>1.62</v>
-      </c>
       <c r="W214">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X214">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y214">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z214">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA214">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB214">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="AC214">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AD214">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AE214">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF214">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AG214">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AK214">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="O215">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="P215">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="Q215">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R215">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="S215">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T215">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="U215">
-        <v>2.83</v>
+        <v>2.08</v>
       </c>
       <c r="V215">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="W215">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X215">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Z215">
-        <v>3.34</v>
+        <v>5.75</v>
       </c>
       <c r="AA215">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="AB215">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="AC215">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="AD215">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="AE215">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="AF215">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="AG215">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK215">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,80 +35517,80 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="O216">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P216">
-        <v>9.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q216">
+        <v>2.11</v>
+      </c>
+      <c r="R216">
+        <v>2.34</v>
+      </c>
+      <c r="S216">
+        <v>1.25</v>
+      </c>
+      <c r="T216">
+        <v>3.7</v>
+      </c>
+      <c r="U216">
+        <v>2.2</v>
+      </c>
+      <c r="V216">
         <v>1.62</v>
       </c>
-      <c r="R216">
-        <v>2.79</v>
-      </c>
-      <c r="S216">
-        <v>1.2</v>
-      </c>
-      <c r="T216">
-        <v>3.85</v>
-      </c>
-      <c r="U216">
-        <v>2.03</v>
-      </c>
-      <c r="V216">
-        <v>1.71</v>
-      </c>
       <c r="W216">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X216">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z216">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA216">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB216">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AC216">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD216">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AE216">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF216">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AG216">
+        <v>2.4</v>
+      </c>
+      <c r="AH216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ216">
+        <v>1.17</v>
+      </c>
+      <c r="AK216">
         <v>2</v>
-      </c>
-      <c r="AH216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI216" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ216">
-        <v>1.09</v>
-      </c>
-      <c r="AK216">
-        <v>3.5</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,80 +37962,80 @@
         </is>
       </c>
       <c r="N231">
+        <v>2.1</v>
+      </c>
+      <c r="O231">
+        <v>3.5</v>
+      </c>
+      <c r="P231">
+        <v>3.25</v>
+      </c>
+      <c r="Q231">
+        <v>2.37</v>
+      </c>
+      <c r="R231">
+        <v>2.21</v>
+      </c>
+      <c r="S231">
+        <v>1.3</v>
+      </c>
+      <c r="T231">
+        <v>3.14</v>
+      </c>
+      <c r="U231">
+        <v>2.45</v>
+      </c>
+      <c r="V231">
+        <v>1.44</v>
+      </c>
+      <c r="W231">
+        <v>1.07</v>
+      </c>
+      <c r="X231">
+        <v>1</v>
+      </c>
+      <c r="Y231">
+        <v>1.21</v>
+      </c>
+      <c r="Z231">
+        <v>3.83</v>
+      </c>
+      <c r="AA231">
+        <v>1.77</v>
+      </c>
+      <c r="AB231">
+        <v>1.93</v>
+      </c>
+      <c r="AC231">
+        <v>2.83</v>
+      </c>
+      <c r="AD231">
+        <v>1.33</v>
+      </c>
+      <c r="AE231">
+        <v>1.09</v>
+      </c>
+      <c r="AF231">
+        <v>1.68</v>
+      </c>
+      <c r="AG231">
+        <v>2.06</v>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ231">
         <v>1.25</v>
       </c>
-      <c r="O231">
-        <v>5.95</v>
-      </c>
-      <c r="P231">
-        <v>9.75</v>
-      </c>
-      <c r="Q231">
-        <v>1.65</v>
-      </c>
-      <c r="R231">
-        <v>2.72</v>
-      </c>
-      <c r="S231">
-        <v>1.21</v>
-      </c>
-      <c r="T231">
-        <v>3.64</v>
-      </c>
-      <c r="U231">
-        <v>2.16</v>
-      </c>
-      <c r="V231">
-        <v>1.64</v>
-      </c>
-      <c r="W231">
-        <v>1.17</v>
-      </c>
-      <c r="X231">
-        <v>1.02</v>
-      </c>
-      <c r="Y231">
-        <v>1.11</v>
-      </c>
-      <c r="Z231">
-        <v>6</v>
-      </c>
-      <c r="AA231">
-        <v>1.42</v>
-      </c>
-      <c r="AB231">
-        <v>2.7</v>
-      </c>
-      <c r="AC231">
-        <v>2.09</v>
-      </c>
-      <c r="AD231">
-        <v>1.65</v>
-      </c>
-      <c r="AE231">
-        <v>1.27</v>
-      </c>
-      <c r="AF231">
-        <v>1.8</v>
-      </c>
-      <c r="AG231">
-        <v>1.9</v>
-      </c>
-      <c r="AH231" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI231" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ231">
-        <v>1.11</v>
-      </c>
       <c r="AK231">
-        <v>3.58</v>
+        <v>1.92</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="O233">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="P233">
-        <v>3.25</v>
+        <v>9.75</v>
       </c>
       <c r="Q233">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="R233">
-        <v>2.21</v>
+        <v>2.72</v>
       </c>
       <c r="S233">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T233">
-        <v>3.14</v>
+        <v>3.64</v>
       </c>
       <c r="U233">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="V233">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="W233">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="X233">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y233">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="Z233">
-        <v>3.83</v>
+        <v>6</v>
       </c>
       <c r="AA233">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AB233">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="AC233">
-        <v>2.83</v>
+        <v>2.09</v>
       </c>
       <c r="AD233">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE233">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AF233">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AG233">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK233">
-        <v>1.92</v>
+        <v>3.58</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39336,7 +39336,7 @@
         </is>
       </c>
       <c r="AJ239">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AK239">
         <v>1.27</v>
@@ -41551,10 +41551,10 @@
         <v>1.18</v>
       </c>
       <c r="O253">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="P253">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Q253">
         <v>1.41</v>
@@ -41566,7 +41566,7 @@
         <v>1.09</v>
       </c>
       <c r="T253">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="U253">
         <v>1.75</v>
@@ -41587,7 +41587,7 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AA253">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB253">
         <v>3.7</v>
@@ -43993,7 +43993,7 @@
         </is>
       </c>
       <c r="N268">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="O268">
         <v>3.3</v>
@@ -44817,55 +44817,55 @@
         <v>1.38</v>
       </c>
       <c r="Q273">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R273">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S273">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T273">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U273">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V273">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W273">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X273">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y273">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z273">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA273">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB273">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC273">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD273">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE273">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF273">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG273">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH273" t="inlineStr">
         <is>
@@ -44878,10 +44878,10 @@
         </is>
       </c>
       <c r="AJ273">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK273">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL273">
         <v>0</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="O296">
         <v>3.1</v>
       </c>
       <c r="P296">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="Q296">
         <v>3.2</v>
@@ -48593,13 +48593,13 @@
         <v>1.3</v>
       </c>
       <c r="Z296">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA296">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB296">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AC296">
         <v>3.6</v>
@@ -48611,7 +48611,7 @@
         <v>1.06</v>
       </c>
       <c r="AF296">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG296">
         <v>2</v>
@@ -48922,10 +48922,10 @@
         <v>4.7</v>
       </c>
       <c r="AA298">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB298">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC298">
         <v>2.23</v>
@@ -49251,7 +49251,7 @@
         <v>1.66</v>
       </c>
       <c r="AB300">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AC300">
         <v>2.63</v>
@@ -50202,10 +50202,10 @@
         <v>2.75</v>
       </c>
       <c r="S306">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T306">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U306">
         <v>2.15</v>
@@ -50214,7 +50214,7 @@
         <v>1.62</v>
       </c>
       <c r="W306">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X306">
         <v>1.02</v>
@@ -50383,10 +50383,10 @@
         <v>1</v>
       </c>
       <c r="Y307">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z307">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AA307">
         <v>1.2</v>
@@ -50715,7 +50715,7 @@
         <v>7</v>
       </c>
       <c r="AA309">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB309">
         <v>2.98</v>
@@ -50839,7 +50839,7 @@
         </is>
       </c>
       <c r="N310">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="O310">
         <v>12</v>
@@ -50848,7 +50848,7 @@
         <v>15</v>
       </c>
       <c r="Q310">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R310">
         <v>4.25</v>
@@ -50893,10 +50893,10 @@
         <v>2</v>
       </c>
       <c r="AF310">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG310">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK310">
         <v>8.5</v>
@@ -51195,7 +51195,7 @@
         <v>1.36</v>
       </c>
       <c r="X312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y312">
         <v>1.01</v>
@@ -57522,10 +57522,10 @@
         </is>
       </c>
       <c r="N351">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O351">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P351">
         <v>2.1</v>
@@ -57685,13 +57685,13 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O352">
         <v>4.58</v>
       </c>
       <c r="P352">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="Q352">
         <v>1.91</v>
@@ -58847,13 +58847,13 @@
         <v>4</v>
       </c>
       <c r="U359">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="V359">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W359">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X359">
         <v>1</v>
@@ -58989,13 +58989,13 @@
         </is>
       </c>
       <c r="N360">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O360">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P360">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q360">
         <v>2.2</v>
@@ -60130,13 +60130,13 @@
         </is>
       </c>
       <c r="N367">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O367">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="P367">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="Q367">
         <v>2.9</v>
@@ -60187,7 +60187,7 @@
         <v>2.15</v>
       </c>
       <c r="AG367">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH367" t="inlineStr">
         <is>
@@ -60619,13 +60619,13 @@
         </is>
       </c>
       <c r="N370">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O370">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="P370">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="Q370">
         <v>2.6</v>
@@ -60658,7 +60658,7 @@
         <v>3.4</v>
       </c>
       <c r="AA370">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB370">
         <v>1.78</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU373"/>
+  <dimension ref="A1:AU372"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8154,10 +8154,10 @@
         <v>2.9</v>
       </c>
       <c r="U48">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
         <v>1.08</v>
@@ -8338,7 +8338,7 @@
         <v>1.92</v>
       </c>
       <c r="AB49">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC49">
         <v>3.6</v>
@@ -9606,7 +9606,7 @@
         <v>3.2</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>2.68</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK57">
         <v>1.7</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O62">
         <v>3.6</v>
@@ -10430,7 +10430,7 @@
         <v>2.3</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T62">
         <v>3.3</v>
@@ -10442,19 +10442,19 @@
         <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z62">
         <v>4.1</v>
       </c>
       <c r="AA62">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
         <v>2.11</v>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O71">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P71">
         <v>4.8</v>
@@ -11939,7 +11939,7 @@
         <v>1.44</v>
       </c>
       <c r="AG71">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="O73">
         <v>3.75</v>
@@ -12247,7 +12247,7 @@
         <v>5</v>
       </c>
       <c r="AA73">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB73">
         <v>2.39</v>
@@ -13714,13 +13714,13 @@
         <v>4.5</v>
       </c>
       <c r="AA82">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB82">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AC82">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AD82">
         <v>1.44</v>
@@ -13732,7 +13732,7 @@
         <v>1.5</v>
       </c>
       <c r="AG82">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13844,10 +13844,10 @@
         <v>3.6</v>
       </c>
       <c r="P83">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q83">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R83">
         <v>2.1</v>
@@ -13908,7 +13908,7 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
         <v>2.07</v>
@@ -14496,7 +14496,7 @@
         <v>4.33</v>
       </c>
       <c r="P87">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="Q87">
         <v>1.99</v>
@@ -14511,10 +14511,10 @@
         <v>3.8</v>
       </c>
       <c r="U87">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V87">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W87">
         <v>1.15</v>
@@ -14526,19 +14526,19 @@
         <v>1.12</v>
       </c>
       <c r="Z87">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA87">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB87">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="AC87">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AD87">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE87">
         <v>1.2</v>
@@ -14563,7 +14563,7 @@
         <v>1.11</v>
       </c>
       <c r="AK87">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>3.8</v>
       </c>
       <c r="P88">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="Q88">
         <v>2.34</v>
@@ -14668,16 +14668,16 @@
         <v>2.31</v>
       </c>
       <c r="S88">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T88">
         <v>2.88</v>
       </c>
       <c r="U88">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="V88">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W88">
         <v>1.1</v>
@@ -14698,7 +14698,7 @@
         <v>1.93</v>
       </c>
       <c r="AC88">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AD88">
         <v>1.28</v>
@@ -15151,7 +15151,7 @@
         <v>2.66</v>
       </c>
       <c r="Q91">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R91">
         <v>2.1</v>
@@ -15474,7 +15474,7 @@
         <v>3.4</v>
       </c>
       <c r="P93">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Q93">
         <v>2.93</v>
@@ -16485,10 +16485,10 @@
         <v>4.35</v>
       </c>
       <c r="AA99">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB99">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AC99">
         <v>2.45</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,28 +16609,28 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.66</v>
+        <v>3.03</v>
       </c>
       <c r="O100">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
-        <v>4.98</v>
+        <v>2.23</v>
       </c>
       <c r="Q100">
-        <v>2.1</v>
+        <v>3.51</v>
       </c>
       <c r="R100">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S100">
         <v>1.33</v>
       </c>
       <c r="T100">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="U100">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V100">
         <v>1.44</v>
@@ -16639,22 +16639,22 @@
         <v>1.11</v>
       </c>
       <c r="X100">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y100">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z100">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AA100">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB100">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC100">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="AD100">
         <v>1.38</v>
@@ -16663,10 +16663,10 @@
         <v>1.14</v>
       </c>
       <c r="AF100">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG100">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK100">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,28 +16772,28 @@
         </is>
       </c>
       <c r="N101">
-        <v>3.03</v>
+        <v>1.66</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P101">
-        <v>2.23</v>
+        <v>4.98</v>
       </c>
       <c r="Q101">
-        <v>3.51</v>
+        <v>2.1</v>
       </c>
       <c r="R101">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S101">
         <v>1.33</v>
       </c>
       <c r="T101">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U101">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V101">
         <v>1.44</v>
@@ -16802,22 +16802,22 @@
         <v>1.11</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z101">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AA101">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB101">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC101">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="AD101">
         <v>1.38</v>
@@ -16826,10 +16826,10 @@
         <v>1.14</v>
       </c>
       <c r="AF101">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG101">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK101">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16956,13 +16956,13 @@
         <v>4.1</v>
       </c>
       <c r="U102">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V102">
         <v>1.7</v>
       </c>
       <c r="W102">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X102">
         <v>1.02</v>
@@ -17478,7 +17478,7 @@
         <v>1.25</v>
       </c>
       <c r="AF105">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG105">
         <v>2.4</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="O106">
         <v>3.45</v>
       </c>
       <c r="P106">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q106">
         <v>3.02</v>
@@ -18278,10 +18278,10 @@
         <v>5.25</v>
       </c>
       <c r="AA110">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB110">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AC110">
         <v>2.31</v>
@@ -18405,10 +18405,10 @@
         <v>1.83</v>
       </c>
       <c r="O111">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P111">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -18767,7 +18767,7 @@
         <v>5.2</v>
       </c>
       <c r="AA113">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AB113">
         <v>2.49</v>
@@ -20684,7 +20684,7 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O125">
         <v>3.3</v>
@@ -22806,7 +22806,7 @@
         <v>1.67</v>
       </c>
       <c r="O138">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P138">
         <v>4</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="O142">
         <v>3.2</v>
@@ -23503,7 +23503,7 @@
         <v>3.58</v>
       </c>
       <c r="AD142">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE142">
         <v>1.03</v>
@@ -23621,7 +23621,7 @@
         <v>2.3</v>
       </c>
       <c r="O143">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P143">
         <v>2.62</v>
@@ -23781,10 +23781,10 @@
         </is>
       </c>
       <c r="N144">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P144">
         <v>1.73</v>
@@ -23947,7 +23947,7 @@
         <v>2.75</v>
       </c>
       <c r="O145">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P145">
         <v>2.2</v>
@@ -23998,7 +23998,7 @@
         <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG145">
         <v>2.18</v>
@@ -24180,7 +24180,7 @@
         <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24327,7 +24327,7 @@
         <v>1.57</v>
       </c>
       <c r="AG147">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         <v>1.25</v>
       </c>
       <c r="T148">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="U148">
         <v>2.25</v>
@@ -24475,7 +24475,7 @@
         <v>1.55</v>
       </c>
       <c r="AB148">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC148">
         <v>2.3</v>
@@ -24759,19 +24759,19 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O150">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="P150">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q150">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="R150">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S150">
         <v>1.3</v>
@@ -25216,12 +25216,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gyirmót</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G153">
@@ -25248,34 +25248,34 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="O153">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P153">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q153">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="R153">
         <v>2.2</v>
       </c>
       <c r="S153">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T153">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U153">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="V153">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W153">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X153">
         <v>1.01</v>
@@ -25287,25 +25287,25 @@
         <v>3.5</v>
       </c>
       <c r="AA153">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB153">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC153">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD153">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE153">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF153">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG153">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AH153" t="inlineStr">
         <is>
@@ -25318,10 +25318,10 @@
         </is>
       </c>
       <c r="AJ153">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK153">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25379,12 +25379,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Gyirmót</t>
         </is>
       </c>
       <c r="G154">
@@ -25411,34 +25411,34 @@
         </is>
       </c>
       <c r="N154">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O154">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P154">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q154">
-        <v>2.8</v>
+        <v>3.42</v>
       </c>
       <c r="R154">
         <v>2.2</v>
       </c>
       <c r="S154">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T154">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U154">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="V154">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W154">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X154">
         <v>1.01</v>
@@ -25450,25 +25450,25 @@
         <v>3.5</v>
       </c>
       <c r="AA154">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB154">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AC154">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AD154">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE154">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF154">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG154">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK154">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="N175">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="O175">
         <v>3.74</v>
@@ -28846,7 +28846,7 @@
         <v>2.51</v>
       </c>
       <c r="R175">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S175">
         <v>1.3</v>
@@ -29036,10 +29036,10 @@
         <v>3.89</v>
       </c>
       <c r="AA176">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB176">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC176">
         <v>3.14</v>
@@ -29160,13 +29160,13 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O177">
         <v>4.33</v>
       </c>
       <c r="P177">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q177">
         <v>2</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,31 +29323,31 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.11</v>
+        <v>2.68</v>
       </c>
       <c r="O178">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P178">
-        <v>3.56</v>
+        <v>2.3</v>
       </c>
       <c r="Q178">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="R178">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S178">
+        <v>1.36</v>
+      </c>
+      <c r="T178">
+        <v>2.9</v>
+      </c>
+      <c r="U178">
+        <v>2.66</v>
+      </c>
+      <c r="V178">
         <v>1.4</v>
-      </c>
-      <c r="T178">
-        <v>2.88</v>
-      </c>
-      <c r="U178">
-        <v>2.5</v>
-      </c>
-      <c r="V178">
-        <v>1.44</v>
       </c>
       <c r="W178">
         <v>1.07</v>
@@ -29356,31 +29356,31 @@
         <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z178">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="AA178">
         <v>1.92</v>
       </c>
       <c r="AB178">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC178">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="AD178">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE178">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF178">
         <v>1.67</v>
       </c>
       <c r="AG178">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK178">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,31 +29486,31 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.68</v>
+        <v>2.11</v>
       </c>
       <c r="O179">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P179">
-        <v>2.3</v>
+        <v>3.56</v>
       </c>
       <c r="Q179">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="R179">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S179">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T179">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U179">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V179">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W179">
         <v>1.07</v>
@@ -29519,31 +29519,31 @@
         <v>1.03</v>
       </c>
       <c r="Y179">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z179">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="AA179">
         <v>1.92</v>
       </c>
       <c r="AB179">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AC179">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="AD179">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE179">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF179">
         <v>1.67</v>
       </c>
       <c r="AG179">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK179">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,80 +29649,80 @@
         </is>
       </c>
       <c r="N180">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="O180">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P180">
-        <v>2.93</v>
+        <v>4.55</v>
       </c>
       <c r="Q180">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="R180">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S180">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T180">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="U180">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="V180">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="W180">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X180">
         <v>1.02</v>
       </c>
       <c r="Y180">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z180">
-        <v>5.2</v>
+        <v>4.08</v>
       </c>
       <c r="AA180">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AB180">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AC180">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="AD180">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AE180">
+        <v>1.12</v>
+      </c>
+      <c r="AF180">
+        <v>1.75</v>
+      </c>
+      <c r="AG180">
+        <v>2</v>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ180">
         <v>1.2</v>
       </c>
-      <c r="AF180">
-        <v>1.41</v>
-      </c>
-      <c r="AG180">
-        <v>2.6</v>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ180">
-        <v>1.18</v>
-      </c>
       <c r="AK180">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -29780,12 +29780,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G181">
@@ -29812,64 +29812,64 @@
         </is>
       </c>
       <c r="N181">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="O181">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P181">
-        <v>4.55</v>
+        <v>2.93</v>
       </c>
       <c r="Q181">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="R181">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S181">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T181">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="U181">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="V181">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="W181">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X181">
         <v>1.02</v>
       </c>
       <c r="Y181">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z181">
-        <v>4.08</v>
+        <v>5.2</v>
       </c>
       <c r="AA181">
+        <v>1.44</v>
+      </c>
+      <c r="AB181">
+        <v>2.43</v>
+      </c>
+      <c r="AC181">
+        <v>2.27</v>
+      </c>
+      <c r="AD181">
         <v>1.61</v>
       </c>
-      <c r="AB181">
-        <v>2.13</v>
-      </c>
-      <c r="AC181">
-        <v>2.52</v>
-      </c>
-      <c r="AD181">
+      <c r="AE181">
+        <v>1.2</v>
+      </c>
+      <c r="AF181">
         <v>1.41</v>
       </c>
-      <c r="AE181">
-        <v>1.12</v>
-      </c>
-      <c r="AF181">
-        <v>1.75</v>
-      </c>
       <c r="AG181">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="AH181" t="inlineStr">
         <is>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="AJ181">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK181">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AL181">
         <v>0</v>
@@ -30165,7 +30165,7 @@
         <v>1.57</v>
       </c>
       <c r="W183">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X183">
         <v>1.02</v>
@@ -30189,10 +30189,10 @@
         <v>1.43</v>
       </c>
       <c r="AE183">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF183">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AG183">
         <v>2.32</v>
@@ -30802,7 +30802,7 @@
         <v>4.75</v>
       </c>
       <c r="R187">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S187">
         <v>1.44</v>
@@ -30992,10 +30992,10 @@
         <v>5.25</v>
       </c>
       <c r="AA188">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB188">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC188">
         <v>2.17</v>
@@ -31122,13 +31122,13 @@
         <v>3.4</v>
       </c>
       <c r="P189">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Q189">
         <v>2.33</v>
       </c>
       <c r="R189">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S189">
         <v>1.36</v>
@@ -31155,10 +31155,10 @@
         <v>3.14</v>
       </c>
       <c r="AA189">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB189">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AC189">
         <v>3.42</v>
@@ -31285,7 +31285,7 @@
         <v>3.25</v>
       </c>
       <c r="P190">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="Q190">
         <v>2.64</v>
@@ -31410,12 +31410,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G191">
@@ -31442,64 +31442,64 @@
         </is>
       </c>
       <c r="N191">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O191">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P191">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q191">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R191">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S191">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="T191">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="U191">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="V191">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="W191">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X191">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z191">
-        <v>3.42</v>
+        <v>4.6</v>
       </c>
       <c r="AA191">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AB191">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AC191">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="AD191">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="AE191">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AF191">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AG191">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK191">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G192">
@@ -31605,80 +31605,80 @@
         </is>
       </c>
       <c r="N192">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="O192">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P192">
+        <v>4.4</v>
+      </c>
+      <c r="Q192">
+        <v>2.12</v>
+      </c>
+      <c r="R192">
+        <v>2.42</v>
+      </c>
+      <c r="S192">
+        <v>1.31</v>
+      </c>
+      <c r="T192">
+        <v>2.91</v>
+      </c>
+      <c r="U192">
+        <v>2.59</v>
+      </c>
+      <c r="V192">
+        <v>1.47</v>
+      </c>
+      <c r="W192">
+        <v>1.08</v>
+      </c>
+      <c r="X192">
+        <v>1.04</v>
+      </c>
+      <c r="Y192">
+        <v>1.23</v>
+      </c>
+      <c r="Z192">
+        <v>3.96</v>
+      </c>
+      <c r="AA192">
+        <v>1.74</v>
+      </c>
+      <c r="AB192">
+        <v>2.06</v>
+      </c>
+      <c r="AC192">
+        <v>2.82</v>
+      </c>
+      <c r="AD192">
+        <v>1.41</v>
+      </c>
+      <c r="AE192">
+        <v>1.15</v>
+      </c>
+      <c r="AF192">
+        <v>1.74</v>
+      </c>
+      <c r="AG192">
+        <v>1.95</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ192">
+        <v>1.21</v>
+      </c>
+      <c r="AK192">
         <v>2.15</v>
-      </c>
-      <c r="Q192">
-        <v>3.38</v>
-      </c>
-      <c r="R192">
-        <v>2.3</v>
-      </c>
-      <c r="S192">
-        <v>1.21</v>
-      </c>
-      <c r="T192">
-        <v>3.65</v>
-      </c>
-      <c r="U192">
-        <v>2.39</v>
-      </c>
-      <c r="V192">
-        <v>1.5</v>
-      </c>
-      <c r="W192">
-        <v>1.13</v>
-      </c>
-      <c r="X192">
-        <v>1.03</v>
-      </c>
-      <c r="Y192">
-        <v>1.15</v>
-      </c>
-      <c r="Z192">
-        <v>4.6</v>
-      </c>
-      <c r="AA192">
-        <v>1.6</v>
-      </c>
-      <c r="AB192">
-        <v>2.2</v>
-      </c>
-      <c r="AC192">
-        <v>2.33</v>
-      </c>
-      <c r="AD192">
-        <v>1.51</v>
-      </c>
-      <c r="AE192">
-        <v>1.19</v>
-      </c>
-      <c r="AF192">
-        <v>1.47</v>
-      </c>
-      <c r="AG192">
-        <v>2.46</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ192">
-        <v>1.24</v>
-      </c>
-      <c r="AK192">
-        <v>1.33</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O193">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="P193">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q193">
-        <v>2.12</v>
+        <v>3.08</v>
       </c>
       <c r="R193">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="S193">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T193">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="U193">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="V193">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W193">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X193">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y193">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z193">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="AA193">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AB193">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC193">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="AD193">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE193">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF193">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AG193">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK193">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,80 +31931,80 @@
         </is>
       </c>
       <c r="N194">
+        <v>1.96</v>
+      </c>
+      <c r="O194">
+        <v>3.35</v>
+      </c>
+      <c r="P194">
+        <v>3.2</v>
+      </c>
+      <c r="Q194">
         <v>2.6</v>
       </c>
-      <c r="O194">
-        <v>3.5</v>
-      </c>
-      <c r="P194">
-        <v>2.6</v>
-      </c>
-      <c r="Q194">
+      <c r="R194">
+        <v>2.1</v>
+      </c>
+      <c r="S194">
+        <v>1.39</v>
+      </c>
+      <c r="T194">
+        <v>2.7</v>
+      </c>
+      <c r="U194">
+        <v>2.88</v>
+      </c>
+      <c r="V194">
+        <v>1.37</v>
+      </c>
+      <c r="W194">
+        <v>1.03</v>
+      </c>
+      <c r="X194">
+        <v>1</v>
+      </c>
+      <c r="Y194">
+        <v>1.28</v>
+      </c>
+      <c r="Z194">
         <v>3.08</v>
       </c>
-      <c r="R194">
-        <v>2.2</v>
-      </c>
-      <c r="S194">
+      <c r="AA194">
+        <v>2.01</v>
+      </c>
+      <c r="AB194">
+        <v>1.75</v>
+      </c>
+      <c r="AC194">
+        <v>3.42</v>
+      </c>
+      <c r="AD194">
+        <v>1.23</v>
+      </c>
+      <c r="AE194">
+        <v>1.06</v>
+      </c>
+      <c r="AF194">
+        <v>1.82</v>
+      </c>
+      <c r="AG194">
+        <v>1.88</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ194">
         <v>1.33</v>
       </c>
-      <c r="T194">
-        <v>3.19</v>
-      </c>
-      <c r="U194">
-        <v>2.57</v>
-      </c>
-      <c r="V194">
-        <v>1.43</v>
-      </c>
-      <c r="W194">
-        <v>1.1</v>
-      </c>
-      <c r="X194">
-        <v>1.02</v>
-      </c>
-      <c r="Y194">
-        <v>1.25</v>
-      </c>
-      <c r="Z194">
-        <v>3.6</v>
-      </c>
-      <c r="AA194">
-        <v>1.78</v>
-      </c>
-      <c r="AB194">
-        <v>2.01</v>
-      </c>
-      <c r="AC194">
-        <v>2.98</v>
-      </c>
-      <c r="AD194">
-        <v>1.37</v>
-      </c>
-      <c r="AE194">
-        <v>1.13</v>
-      </c>
-      <c r="AF194">
-        <v>1.62</v>
-      </c>
-      <c r="AG194">
-        <v>2.14</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ194">
-        <v>1.44</v>
-      </c>
       <c r="AK194">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="O195">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P195">
         <v>3.4</v>
       </c>
       <c r="Q195">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="R195">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S195">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="T195">
+        <v>2.89</v>
+      </c>
+      <c r="U195">
+        <v>2.43</v>
+      </c>
+      <c r="V195">
+        <v>1.47</v>
+      </c>
+      <c r="W195">
+        <v>1.07</v>
+      </c>
+      <c r="X195">
+        <v>1.03</v>
+      </c>
+      <c r="Y195">
+        <v>1.2</v>
+      </c>
+      <c r="Z195">
+        <v>3.84</v>
+      </c>
+      <c r="AA195">
+        <v>1.69</v>
+      </c>
+      <c r="AB195">
+        <v>2.01</v>
+      </c>
+      <c r="AC195">
         <v>2.7</v>
       </c>
-      <c r="U195">
-        <v>2.88</v>
-      </c>
-      <c r="V195">
-        <v>1.37</v>
-      </c>
-      <c r="W195">
-        <v>1.03</v>
-      </c>
-      <c r="X195">
-        <v>1</v>
-      </c>
-      <c r="Y195">
-        <v>1.28</v>
-      </c>
-      <c r="Z195">
-        <v>3.08</v>
-      </c>
-      <c r="AA195">
-        <v>2.01</v>
-      </c>
-      <c r="AB195">
-        <v>1.74</v>
-      </c>
-      <c r="AC195">
-        <v>3.42</v>
-      </c>
       <c r="AD195">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="AE195">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF195">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AG195">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK195">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,64 +32257,64 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="O196">
-        <v>3.16</v>
+        <v>4.2</v>
       </c>
       <c r="P196">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="Q196">
-        <v>2.76</v>
+        <v>2.13</v>
       </c>
       <c r="R196">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="S196">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T196">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U196">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="V196">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="W196">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X196">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y196">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z196">
-        <v>2.79</v>
+        <v>4.45</v>
       </c>
       <c r="AA196">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AB196">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="AC196">
-        <v>3.82</v>
+        <v>2.38</v>
       </c>
       <c r="AD196">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AE196">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AF196">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG196">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK196">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O197">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P197">
         <v>3.4</v>
       </c>
       <c r="Q197">
-        <v>2.28</v>
+        <v>2.76</v>
       </c>
       <c r="R197">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S197">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="T197">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="U197">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="V197">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="W197">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X197">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y197">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="Z197">
-        <v>3.84</v>
+        <v>2.79</v>
       </c>
       <c r="AA197">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="AB197">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AC197">
-        <v>2.7</v>
+        <v>3.82</v>
       </c>
       <c r="AD197">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AE197">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF197">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AG197">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK197">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,61 +32583,61 @@
         </is>
       </c>
       <c r="N198">
-        <v>1.67</v>
+        <v>2.23</v>
       </c>
       <c r="O198">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P198">
-        <v>4.4</v>
+        <v>2.79</v>
       </c>
       <c r="Q198">
-        <v>2.13</v>
+        <v>2.74</v>
       </c>
       <c r="R198">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S198">
         <v>1.25</v>
       </c>
       <c r="T198">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="U198">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V198">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W198">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X198">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y198">
+        <v>1.18</v>
+      </c>
+      <c r="Z198">
+        <v>4.33</v>
+      </c>
+      <c r="AA198">
+        <v>1.66</v>
+      </c>
+      <c r="AB198">
+        <v>2.12</v>
+      </c>
+      <c r="AC198">
+        <v>2.49</v>
+      </c>
+      <c r="AD198">
+        <v>1.4</v>
+      </c>
+      <c r="AE198">
         <v>1.14</v>
       </c>
-      <c r="Z198">
-        <v>4.45</v>
-      </c>
-      <c r="AA198">
-        <v>1.53</v>
-      </c>
-      <c r="AB198">
-        <v>2.24</v>
-      </c>
-      <c r="AC198">
-        <v>2.38</v>
-      </c>
-      <c r="AD198">
-        <v>1.53</v>
-      </c>
-      <c r="AE198">
-        <v>1.2</v>
-      </c>
       <c r="AF198">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG198">
         <v>2.38</v>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AK198">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="O199">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P199">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Q199">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R199">
         <v>2.25</v>
       </c>
       <c r="S199">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T199">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="U199">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="V199">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W199">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z199">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AA199">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AB199">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="AC199">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AD199">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE199">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF199">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG199">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK199">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -34542,7 +34542,7 @@
         <v>1.73</v>
       </c>
       <c r="O210">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="P210">
         <v>4.5</v>
@@ -34578,7 +34578,7 @@
         <v>3.42</v>
       </c>
       <c r="AA210">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB210">
         <v>1.98</v>
@@ -34702,13 +34702,13 @@
         </is>
       </c>
       <c r="N211">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="O211">
         <v>3.6</v>
       </c>
       <c r="P211">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q211">
         <v>2.99</v>
@@ -34868,10 +34868,10 @@
         <v>1.58</v>
       </c>
       <c r="O212">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P212">
-        <v>5.5</v>
+        <v>4.97</v>
       </c>
       <c r="Q212">
         <v>1.97</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.74</v>
+        <v>1.28</v>
       </c>
       <c r="O213">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="P213">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q213">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="R213">
-        <v>2.2</v>
+        <v>2.79</v>
       </c>
       <c r="S213">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T213">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="U213">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="V213">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="W213">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X213">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y213">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="Z213">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AA213">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AB213">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="AC213">
-        <v>2.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD213">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AE213">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AF213">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG213">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK213">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,80 +35191,80 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.28</v>
+        <v>1.71</v>
       </c>
       <c r="O214">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P214">
-        <v>9.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Q214">
+        <v>2.11</v>
+      </c>
+      <c r="R214">
+        <v>2.34</v>
+      </c>
+      <c r="S214">
+        <v>1.25</v>
+      </c>
+      <c r="T214">
+        <v>3.7</v>
+      </c>
+      <c r="U214">
+        <v>2.2</v>
+      </c>
+      <c r="V214">
         <v>1.62</v>
       </c>
-      <c r="R214">
-        <v>2.79</v>
-      </c>
-      <c r="S214">
-        <v>1.2</v>
-      </c>
-      <c r="T214">
-        <v>3.85</v>
-      </c>
-      <c r="U214">
-        <v>2.03</v>
-      </c>
-      <c r="V214">
-        <v>1.71</v>
-      </c>
       <c r="W214">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X214">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z214">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA214">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AB214">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="AC214">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AD214">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AE214">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AF214">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AG214">
+        <v>2.4</v>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ214">
+        <v>1.17</v>
+      </c>
+      <c r="AK214">
         <v>2</v>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ214">
-        <v>1.09</v>
-      </c>
-      <c r="AK214">
-        <v>3.5</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35393,7 +35393,7 @@
         <v>5.75</v>
       </c>
       <c r="AA215">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB215">
         <v>2.56</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="O216">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P216">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q216">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="R216">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S216">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T216">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U216">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="V216">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="W216">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X216">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y216">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Z216">
-        <v>5.1</v>
+        <v>3.34</v>
       </c>
       <c r="AA216">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AB216">
-        <v>2.42</v>
+        <v>1.93</v>
       </c>
       <c r="AC216">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="AD216">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AE216">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="AF216">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="AG216">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK216">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35843,7 +35843,7 @@
         </is>
       </c>
       <c r="N218">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O218">
         <v>3.4</v>
@@ -35852,10 +35852,10 @@
         <v>2.4</v>
       </c>
       <c r="Q218">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="R218">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S218">
         <v>1.3</v>
@@ -35882,10 +35882,10 @@
         <v>4.1</v>
       </c>
       <c r="AA218">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB218">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC218">
         <v>2.62</v>
@@ -36009,10 +36009,10 @@
         <v>1.8</v>
       </c>
       <c r="O219">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P219">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="Q219">
         <v>2.25</v>
@@ -36048,7 +36048,7 @@
         <v>1.56</v>
       </c>
       <c r="AB219">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC219">
         <v>2.28</v>
@@ -37512,10 +37512,10 @@
         <v>6</v>
       </c>
       <c r="AA228">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB228">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AC228">
         <v>2.29</v>
@@ -37645,7 +37645,7 @@
         <v>1.86</v>
       </c>
       <c r="Q229">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="R229">
         <v>2.5</v>
@@ -37675,7 +37675,7 @@
         <v>5.45</v>
       </c>
       <c r="AA229">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB229">
         <v>2.66</v>
@@ -37838,10 +37838,10 @@
         <v>3.84</v>
       </c>
       <c r="AA230">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB230">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AC230">
         <v>2.62</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="O232">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="P232">
-        <v>2.73</v>
+        <v>9.75</v>
       </c>
       <c r="Q232">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="R232">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="S232">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T232">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="U232">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="V232">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W232">
+        <v>1.17</v>
+      </c>
+      <c r="X232">
+        <v>1.02</v>
+      </c>
+      <c r="Y232">
         <v>1.11</v>
       </c>
-      <c r="X232">
-        <v>1.01</v>
-      </c>
-      <c r="Y232">
-        <v>1.23</v>
-      </c>
       <c r="Z232">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AA232">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AB232">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AC232">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AD232">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AE232">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AF232">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG232">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38195,10 +38195,10 @@
         </is>
       </c>
       <c r="AJ232">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK232">
-        <v>1.65</v>
+        <v>3.58</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,80 +38288,80 @@
         </is>
       </c>
       <c r="N233">
+        <v>2.36</v>
+      </c>
+      <c r="O233">
+        <v>3.5</v>
+      </c>
+      <c r="P233">
+        <v>2.73</v>
+      </c>
+      <c r="Q233">
+        <v>2.63</v>
+      </c>
+      <c r="R233">
+        <v>2.25</v>
+      </c>
+      <c r="S233">
+        <v>1.29</v>
+      </c>
+      <c r="T233">
+        <v>3.3</v>
+      </c>
+      <c r="U233">
+        <v>2.47</v>
+      </c>
+      <c r="V233">
+        <v>1.51</v>
+      </c>
+      <c r="W233">
+        <v>1.11</v>
+      </c>
+      <c r="X233">
+        <v>1.01</v>
+      </c>
+      <c r="Y233">
+        <v>1.23</v>
+      </c>
+      <c r="Z233">
+        <v>3.6</v>
+      </c>
+      <c r="AA233">
+        <v>1.66</v>
+      </c>
+      <c r="AB233">
+        <v>2.05</v>
+      </c>
+      <c r="AC233">
+        <v>2.7</v>
+      </c>
+      <c r="AD233">
+        <v>1.36</v>
+      </c>
+      <c r="AE233">
+        <v>1.13</v>
+      </c>
+      <c r="AF233">
+        <v>1.58</v>
+      </c>
+      <c r="AG233">
+        <v>2.2</v>
+      </c>
+      <c r="AH233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI233" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ233">
         <v>1.25</v>
       </c>
-      <c r="O233">
-        <v>5.95</v>
-      </c>
-      <c r="P233">
-        <v>9.75</v>
-      </c>
-      <c r="Q233">
+      <c r="AK233">
         <v>1.65</v>
-      </c>
-      <c r="R233">
-        <v>2.72</v>
-      </c>
-      <c r="S233">
-        <v>1.21</v>
-      </c>
-      <c r="T233">
-        <v>3.64</v>
-      </c>
-      <c r="U233">
-        <v>2.16</v>
-      </c>
-      <c r="V233">
-        <v>1.64</v>
-      </c>
-      <c r="W233">
-        <v>1.17</v>
-      </c>
-      <c r="X233">
-        <v>1.02</v>
-      </c>
-      <c r="Y233">
-        <v>1.11</v>
-      </c>
-      <c r="Z233">
-        <v>6</v>
-      </c>
-      <c r="AA233">
-        <v>1.42</v>
-      </c>
-      <c r="AB233">
-        <v>2.7</v>
-      </c>
-      <c r="AC233">
-        <v>2.09</v>
-      </c>
-      <c r="AD233">
-        <v>1.65</v>
-      </c>
-      <c r="AE233">
-        <v>1.27</v>
-      </c>
-      <c r="AF233">
-        <v>1.8</v>
-      </c>
-      <c r="AG233">
-        <v>1.9</v>
-      </c>
-      <c r="AH233" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI233" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ233">
-        <v>1.11</v>
-      </c>
-      <c r="AK233">
-        <v>3.58</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -39592,13 +39592,13 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O241">
         <v>3.33</v>
       </c>
       <c r="P241">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q241">
         <v>3</v>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK241">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -40570,13 +40570,13 @@
         </is>
       </c>
       <c r="N247">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="O247">
         <v>3.25</v>
       </c>
       <c r="P247">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q247">
         <v>2.54</v>
@@ -41237,10 +41237,10 @@
         <v>2.37</v>
       </c>
       <c r="S251">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T251">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="U251">
         <v>2.52</v>
@@ -41385,13 +41385,13 @@
         </is>
       </c>
       <c r="N252">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="O252">
         <v>3.3</v>
       </c>
       <c r="P252">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q252">
         <v>3.58</v>
@@ -41403,7 +41403,7 @@
         <v>1.36</v>
       </c>
       <c r="T252">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U252">
         <v>2.8</v>
@@ -41424,7 +41424,7 @@
         <v>3.55</v>
       </c>
       <c r="AA252">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB252">
         <v>1.81</v>
@@ -41874,13 +41874,13 @@
         </is>
       </c>
       <c r="N255">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="O255">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P255">
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="Q255">
         <v>1.69</v>
@@ -41931,7 +41931,7 @@
         <v>1.7</v>
       </c>
       <c r="AG255">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH255" t="inlineStr">
         <is>
@@ -42698,34 +42698,34 @@
         <v>0</v>
       </c>
       <c r="Q260">
-        <v>14.5</v>
+        <v>13.75</v>
       </c>
       <c r="R260">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="S260">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T260">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="U260">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="V260">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W260">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X260">
         <v>1</v>
       </c>
       <c r="Y260">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z260">
-        <v>6.25</v>
+        <v>6.6</v>
       </c>
       <c r="AA260">
         <v>1.3</v>
@@ -42734,19 +42734,19 @@
         <v>3.4</v>
       </c>
       <c r="AC260">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AD260">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AE260">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AF260">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="AG260">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH260" t="inlineStr">
         <is>
@@ -43341,13 +43341,13 @@
         </is>
       </c>
       <c r="N264">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O264">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="P264">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q264">
         <v>0</v>
@@ -43380,10 +43380,10 @@
         <v>0</v>
       </c>
       <c r="AA264">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB264">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC264">
         <v>0</v>
@@ -43513,7 +43513,7 @@
         <v>2.89</v>
       </c>
       <c r="Q265">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R265">
         <v>2.23</v>
@@ -43549,19 +43549,19 @@
         <v>2.24</v>
       </c>
       <c r="AC265">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD265">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE265">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF265">
         <v>1.53</v>
       </c>
       <c r="AG265">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AH265" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>1.25</v>
       </c>
       <c r="T266">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U266">
         <v>2.22</v>
@@ -44322,7 +44322,7 @@
         <v>2.05</v>
       </c>
       <c r="O270">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P270">
         <v>3.3</v>
@@ -44648,10 +44648,10 @@
         <v>2.75</v>
       </c>
       <c r="O272">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P272">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q272">
         <v>3.58</v>
@@ -44971,13 +44971,13 @@
         </is>
       </c>
       <c r="N274">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O274">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P274">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q274">
         <v>2.14</v>
@@ -45185,7 +45185,7 @@
         <v>1.17</v>
       </c>
       <c r="AE275">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF275">
         <v>2.02</v>
@@ -45499,7 +45499,7 @@
         <v>2.97</v>
       </c>
       <c r="AA277">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AB277">
         <v>1.69</v>
@@ -45662,10 +45662,10 @@
         <v>0</v>
       </c>
       <c r="AA278">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB278">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC278">
         <v>0</v>
@@ -46444,7 +46444,7 @@
         <v>3.48</v>
       </c>
       <c r="P283">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q283">
         <v>0</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="O285">
         <v>3.8</v>
       </c>
       <c r="P285">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="Q285">
         <v>2.64</v>
@@ -46785,13 +46785,13 @@
         <v>4.2</v>
       </c>
       <c r="U285">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="V285">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W285">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X285">
         <v>1.01</v>
@@ -46806,7 +46806,7 @@
         <v>1.36</v>
       </c>
       <c r="AB285">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AC285">
         <v>1.93</v>
@@ -46969,7 +46969,7 @@
         <v>1.49</v>
       </c>
       <c r="AB286">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC286">
         <v>2.22</v>
@@ -47259,7 +47259,7 @@
         <v>3.6</v>
       </c>
       <c r="P288">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="Q288">
         <v>2.38</v>
@@ -47292,13 +47292,13 @@
         <v>4.1</v>
       </c>
       <c r="AA288">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB288">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC288">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD288">
         <v>1.4</v>
@@ -47742,7 +47742,7 @@
         </is>
       </c>
       <c r="N291">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="O291">
         <v>4.33</v>
@@ -47781,7 +47781,7 @@
         <v>3.49</v>
       </c>
       <c r="AA291">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB291">
         <v>1.94</v>
@@ -47911,7 +47911,7 @@
         <v>6</v>
       </c>
       <c r="P292">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Q292">
         <v>8</v>
@@ -47941,28 +47941,28 @@
         <v>1.03</v>
       </c>
       <c r="Z292">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA292">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AB292">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC292">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AD292">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AE292">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF292">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG292">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH292" t="inlineStr">
         <is>
@@ -49375,7 +49375,7 @@
         <v>1.52</v>
       </c>
       <c r="O301">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="P301">
         <v>5.75</v>
@@ -49411,10 +49411,10 @@
         <v>4.76</v>
       </c>
       <c r="AA301">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB301">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AC301">
         <v>2.43</v>
@@ -49553,7 +49553,7 @@
         <v>1.22</v>
       </c>
       <c r="T302">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U302">
         <v>2.05</v>
@@ -49577,7 +49577,7 @@
         <v>1.47</v>
       </c>
       <c r="AB302">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC302">
         <v>2.07</v>
@@ -49861,13 +49861,13 @@
         </is>
       </c>
       <c r="N304">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="O304">
         <v>5</v>
       </c>
       <c r="P304">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="Q304">
         <v>1.84</v>
@@ -49918,7 +49918,7 @@
         <v>1.7</v>
       </c>
       <c r="AG304">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH304" t="inlineStr">
         <is>
@@ -49934,7 +49934,7 @@
         <v>1.1</v>
       </c>
       <c r="AK304">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AL304">
         <v>0</v>
@@ -51660,7 +51660,7 @@
         <v>3.7</v>
       </c>
       <c r="P315">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="Q315">
         <v>2.03</v>
@@ -51672,7 +51672,7 @@
         <v>1.33</v>
       </c>
       <c r="T315">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="U315">
         <v>2.6</v>
@@ -51838,7 +51838,7 @@
         <v>3.2</v>
       </c>
       <c r="U316">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V316">
         <v>1.46</v>
@@ -51871,7 +51871,7 @@
         <v>1.1</v>
       </c>
       <c r="AF316">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG316">
         <v>2.15</v>
@@ -52146,7 +52146,7 @@
         <v>1.7</v>
       </c>
       <c r="O318">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P318">
         <v>4.33</v>
@@ -52213,7 +52213,7 @@
         </is>
       </c>
       <c r="AJ318">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK318">
         <v>2</v>
@@ -52309,7 +52309,7 @@
         <v>2.75</v>
       </c>
       <c r="O319">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P319">
         <v>2.6</v>
@@ -52478,10 +52478,10 @@
         <v>2.06</v>
       </c>
       <c r="Q320">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R320">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S320">
         <v>1.45</v>
@@ -52514,7 +52514,7 @@
         <v>1.49</v>
       </c>
       <c r="AC320">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD320">
         <v>1.16</v>
@@ -52523,7 +52523,7 @@
         <v>1.01</v>
       </c>
       <c r="AF320">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AG320">
         <v>1.44</v>
@@ -52638,7 +52638,7 @@
         <v>3.5</v>
       </c>
       <c r="P321">
-        <v>7.25</v>
+        <v>7.75</v>
       </c>
       <c r="Q321">
         <v>2.02</v>
@@ -52674,7 +52674,7 @@
         <v>2.3</v>
       </c>
       <c r="AB321">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="AC321">
         <v>5</v>
@@ -52807,13 +52807,13 @@
         <v>7.52</v>
       </c>
       <c r="R322">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="S322">
         <v>1.33</v>
       </c>
       <c r="T322">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="U322">
         <v>2.73</v>
@@ -52828,7 +52828,7 @@
         <v>1</v>
       </c>
       <c r="Y322">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z322">
         <v>3.34</v>
@@ -52849,10 +52849,10 @@
         <v>1.08</v>
       </c>
       <c r="AF322">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AG322">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.18</v>
+        <v>3</v>
       </c>
       <c r="AK322">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52967,10 +52967,10 @@
         <v>4.5</v>
       </c>
       <c r="Q323">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R323">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="S323">
         <v>1.37</v>
@@ -52997,16 +52997,16 @@
         <v>2.92</v>
       </c>
       <c r="AA323">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AB323">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC323">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD323">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE323">
         <v>1.04</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="O324">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P324">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q324">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="R324">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S324">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T324">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="U324">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="V324">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="W324">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X324">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y324">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z324">
-        <v>2.33</v>
+        <v>2.87</v>
       </c>
       <c r="AA324">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AB324">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AC324">
-        <v>5.3</v>
+        <v>4.22</v>
       </c>
       <c r="AD324">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AE324">
         <v>1.03</v>
       </c>
       <c r="AF324">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AG324">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AK324">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="O325">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P325">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q325">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="R325">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S325">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="T325">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="U325">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="V325">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W325">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X325">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y325">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Z325">
-        <v>2.87</v>
+        <v>2.41</v>
       </c>
       <c r="AA325">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AB325">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AC325">
-        <v>4.22</v>
+        <v>5.03</v>
       </c>
       <c r="AD325">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AE325">
         <v>1.03</v>
       </c>
       <c r="AF325">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
       <c r="AG325">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK325">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O326">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="P326">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="Q326">
         <v>0</v>
@@ -53486,10 +53486,10 @@
         <v>0</v>
       </c>
       <c r="AA326">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB326">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC326">
         <v>0</v>
@@ -54923,7 +54923,7 @@
         <v>4.8</v>
       </c>
       <c r="Q335">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R335">
         <v>2</v>
@@ -54953,7 +54953,7 @@
         <v>2.36</v>
       </c>
       <c r="AA335">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB335">
         <v>1.44</v>
@@ -55080,7 +55080,7 @@
         <v>1.35</v>
       </c>
       <c r="O336">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="P336">
         <v>7.55</v>
@@ -55768,7 +55768,7 @@
         <v>3.9</v>
       </c>
       <c r="AA340">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB340">
         <v>2.04</v>
@@ -55783,7 +55783,7 @@
         <v>1.11</v>
       </c>
       <c r="AF340">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG340">
         <v>2.05</v>
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O346">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P346">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="Q346">
         <v>2.5</v>
@@ -56927,7 +56927,7 @@
         <v>1.3</v>
       </c>
       <c r="AG347">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AH347" t="inlineStr">
         <is>
@@ -57164,12 +57164,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G349">
@@ -57196,64 +57196,64 @@
         </is>
       </c>
       <c r="N349">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="O349">
-        <v>5.15</v>
+        <v>3.6</v>
       </c>
       <c r="P349">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="Q349">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="R349">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="S349">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T349">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U349">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="V349">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="W349">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X349">
         <v>1</v>
       </c>
       <c r="Y349">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="Z349">
-        <v>5.25</v>
+        <v>3.72</v>
       </c>
       <c r="AA349">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AB349">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="AC349">
-        <v>2.41</v>
+        <v>3.09</v>
       </c>
       <c r="AD349">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AE349">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF349">
         <v>1.7</v>
       </c>
       <c r="AG349">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH349" t="inlineStr">
         <is>
@@ -57266,10 +57266,10 @@
         </is>
       </c>
       <c r="AJ349">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK349">
-        <v>3.02</v>
+        <v>1.65</v>
       </c>
       <c r="AL349">
         <v>0</v>
@@ -57317,7 +57317,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -57327,12 +57327,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G350">
@@ -57359,64 +57359,64 @@
         </is>
       </c>
       <c r="N350">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O350">
+        <v>3.7</v>
+      </c>
+      <c r="P350">
+        <v>2.1</v>
+      </c>
+      <c r="Q350">
         <v>3.6</v>
       </c>
-      <c r="P350">
-        <v>3.02</v>
-      </c>
-      <c r="Q350">
-        <v>2.61</v>
-      </c>
       <c r="R350">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S350">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T350">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="U350">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="V350">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="W350">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X350">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y350">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z350">
-        <v>3.72</v>
+        <v>4.51</v>
       </c>
       <c r="AA350">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB350">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC350">
-        <v>3.09</v>
+        <v>2.52</v>
       </c>
       <c r="AD350">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AE350">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF350">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG350">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH350" t="inlineStr">
         <is>
@@ -57429,10 +57429,10 @@
         </is>
       </c>
       <c r="AJ350">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK350">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AL350">
         <v>0</v>
@@ -57480,7 +57480,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -57490,12 +57490,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G351">
@@ -57522,64 +57522,64 @@
         </is>
       </c>
       <c r="N351">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="O351">
-        <v>3.7</v>
+        <v>4.58</v>
       </c>
       <c r="P351">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q351">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="R351">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S351">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T351">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U351">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="V351">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W351">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X351">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y351">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z351">
-        <v>4.51</v>
+        <v>6</v>
       </c>
       <c r="AA351">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB351">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC351">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="AD351">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AE351">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF351">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AG351">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>1.2</v>
       </c>
       <c r="AK351">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AL351">
         <v>0</v>
@@ -57653,12 +57653,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G352">
@@ -57685,80 +57685,80 @@
         </is>
       </c>
       <c r="N352">
-        <v>1.6</v>
+        <v>5.57</v>
       </c>
       <c r="O352">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="P352">
-        <v>4.8</v>
+        <v>1.56</v>
       </c>
       <c r="Q352">
-        <v>1.91</v>
+        <v>5</v>
       </c>
       <c r="R352">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S352">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T352">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U352">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="V352">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W352">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X352">
         <v>1</v>
       </c>
       <c r="Y352">
+        <v>1.15</v>
+      </c>
+      <c r="Z352">
+        <v>4.84</v>
+      </c>
+      <c r="AA352">
+        <v>1.57</v>
+      </c>
+      <c r="AB352">
+        <v>2.4</v>
+      </c>
+      <c r="AC352">
+        <v>2.49</v>
+      </c>
+      <c r="AD352">
+        <v>1.53</v>
+      </c>
+      <c r="AE352">
+        <v>1.19</v>
+      </c>
+      <c r="AF352">
+        <v>1.67</v>
+      </c>
+      <c r="AG352">
+        <v>2.1</v>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ352">
+        <v>2.48</v>
+      </c>
+      <c r="AK352">
         <v>1.1</v>
-      </c>
-      <c r="Z352">
-        <v>6</v>
-      </c>
-      <c r="AA352">
-        <v>1.4</v>
-      </c>
-      <c r="AB352">
-        <v>2.75</v>
-      </c>
-      <c r="AC352">
-        <v>2.01</v>
-      </c>
-      <c r="AD352">
-        <v>1.69</v>
-      </c>
-      <c r="AE352">
-        <v>1.29</v>
-      </c>
-      <c r="AF352">
-        <v>1.48</v>
-      </c>
-      <c r="AG352">
-        <v>2.47</v>
-      </c>
-      <c r="AH352" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI352" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ352">
-        <v>1.2</v>
-      </c>
-      <c r="AK352">
-        <v>2.3</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -57801,12 +57801,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -57816,12 +57816,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G353">
@@ -57848,64 +57848,64 @@
         </is>
       </c>
       <c r="N353">
-        <v>5.57</v>
+        <v>1.96</v>
       </c>
       <c r="O353">
-        <v>4.44</v>
+        <v>3.6</v>
       </c>
       <c r="P353">
-        <v>1.56</v>
+        <v>3.62</v>
       </c>
       <c r="Q353">
-        <v>5</v>
+        <v>2.49</v>
       </c>
       <c r="R353">
+        <v>2.21</v>
+      </c>
+      <c r="S353">
+        <v>1.3</v>
+      </c>
+      <c r="T353">
+        <v>3.3</v>
+      </c>
+      <c r="U353">
         <v>2.5</v>
       </c>
-      <c r="S353">
-        <v>1.25</v>
-      </c>
-      <c r="T353">
-        <v>3.6</v>
-      </c>
-      <c r="U353">
-        <v>2.25</v>
-      </c>
       <c r="V353">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="W353">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X353">
         <v>1</v>
       </c>
       <c r="Y353">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z353">
-        <v>4.84</v>
+        <v>4.25</v>
       </c>
       <c r="AA353">
+        <v>1.75</v>
+      </c>
+      <c r="AB353">
+        <v>2.25</v>
+      </c>
+      <c r="AC353">
+        <v>2.83</v>
+      </c>
+      <c r="AD353">
+        <v>1.45</v>
+      </c>
+      <c r="AE353">
+        <v>1.16</v>
+      </c>
+      <c r="AF353">
         <v>1.57</v>
       </c>
-      <c r="AB353">
-        <v>2.4</v>
-      </c>
-      <c r="AC353">
-        <v>2.49</v>
-      </c>
-      <c r="AD353">
-        <v>1.53</v>
-      </c>
-      <c r="AE353">
-        <v>1.19</v>
-      </c>
-      <c r="AF353">
-        <v>1.67</v>
-      </c>
       <c r="AG353">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -57918,10 +57918,10 @@
         </is>
       </c>
       <c r="AJ353">
-        <v>2.48</v>
+        <v>1.25</v>
       </c>
       <c r="AK353">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AL353">
         <v>0</v>
@@ -57952,7 +57952,7 @@
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>2026-10-31 16:45:00</t>
+          <t>2026-10-31 17:00:00</t>
         </is>
       </c>
     </row>
@@ -57969,22 +57969,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="O354">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P354">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="Q354">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="R354">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="S354">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T354">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="U354">
-        <v>2.5</v>
+        <v>3.24</v>
       </c>
       <c r="V354">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="W354">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="X354">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y354">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="Z354">
+        <v>2.73</v>
+      </c>
+      <c r="AA354">
+        <v>2.28</v>
+      </c>
+      <c r="AB354">
+        <v>1.53</v>
+      </c>
+      <c r="AC354">
         <v>4.25</v>
       </c>
-      <c r="AA354">
-        <v>1.75</v>
-      </c>
-      <c r="AB354">
-        <v>2.25</v>
-      </c>
-      <c r="AC354">
-        <v>2.82</v>
-      </c>
       <c r="AD354">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="AE354">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AF354">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AG354">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>1.25</v>
       </c>
       <c r="AK354">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58132,22 +58132,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,64 +58174,64 @@
         </is>
       </c>
       <c r="N355">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="O355">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="P355">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="Q355">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="R355">
         <v>2</v>
       </c>
       <c r="S355">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T355">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="U355">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V355">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W355">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X355">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y355">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z355">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="AA355">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AB355">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC355">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="AD355">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE355">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF355">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AG355">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AH355" t="inlineStr">
         <is>
@@ -58244,10 +58244,10 @@
         </is>
       </c>
       <c r="AJ355">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK355">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -58295,7 +58295,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -58305,12 +58305,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G356">
@@ -58337,64 +58337,64 @@
         </is>
       </c>
       <c r="N356">
-        <v>2.57</v>
+        <v>1.03</v>
       </c>
       <c r="O356">
-        <v>3.22</v>
+        <v>10</v>
       </c>
       <c r="P356">
-        <v>2.55</v>
+        <v>19</v>
       </c>
       <c r="Q356">
-        <v>3.2</v>
+        <v>1.37</v>
       </c>
       <c r="R356">
+        <v>3.42</v>
+      </c>
+      <c r="S356">
+        <v>1.15</v>
+      </c>
+      <c r="T356">
+        <v>5</v>
+      </c>
+      <c r="U356">
+        <v>1.73</v>
+      </c>
+      <c r="V356">
         <v>2</v>
       </c>
-      <c r="S356">
-        <v>1.4</v>
-      </c>
-      <c r="T356">
-        <v>2.71</v>
-      </c>
-      <c r="U356">
-        <v>3</v>
-      </c>
-      <c r="V356">
-        <v>1.33</v>
-      </c>
       <c r="W356">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="X356">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y356">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="Z356">
-        <v>3.15</v>
+        <v>7.7</v>
       </c>
       <c r="AA356">
-        <v>2.02</v>
+        <v>1.26</v>
       </c>
       <c r="AB356">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="AC356">
-        <v>3.86</v>
+        <v>1.6</v>
       </c>
       <c r="AD356">
-        <v>1.22</v>
+        <v>2.46</v>
       </c>
       <c r="AE356">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
       <c r="AF356">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG356">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AH356" t="inlineStr">
         <is>
@@ -58407,10 +58407,10 @@
         </is>
       </c>
       <c r="AJ356">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AK356">
-        <v>1.43</v>
+        <v>7</v>
       </c>
       <c r="AL356">
         <v>0</v>
@@ -58458,7 +58458,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -58468,12 +58468,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G357">
@@ -58500,64 +58500,64 @@
         </is>
       </c>
       <c r="N357">
-        <v>1.03</v>
+        <v>2.17</v>
       </c>
       <c r="O357">
-        <v>10</v>
+        <v>2.98</v>
       </c>
       <c r="P357">
-        <v>19</v>
+        <v>3.22</v>
       </c>
       <c r="Q357">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="R357">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S357">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="T357">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U357">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="V357">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W357">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X357">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y357">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z357">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AA357">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="AB357">
-        <v>4.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC357">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD357">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AE357">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF357">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG357">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH357" t="inlineStr">
         <is>
@@ -58570,10 +58570,10 @@
         </is>
       </c>
       <c r="AJ357">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK357">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AL357">
         <v>0</v>
@@ -58621,7 +58621,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -58631,12 +58631,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="G358">
@@ -58663,64 +58663,64 @@
         </is>
       </c>
       <c r="N358">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O358">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P358">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q358">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R358">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S358">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T358">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U358">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V358">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W358">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X358">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y358">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z358">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="AA358">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB358">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC358">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD358">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE358">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF358">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG358">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH358" t="inlineStr">
         <is>
@@ -58733,10 +58733,10 @@
         </is>
       </c>
       <c r="AJ358">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AK358">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL358">
         <v>0</v>
@@ -58794,12 +58794,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G359">
@@ -58826,80 +58826,80 @@
         </is>
       </c>
       <c r="N359">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="O359">
-        <v>3.96</v>
+        <v>4.25</v>
       </c>
       <c r="P359">
+        <v>3.7</v>
+      </c>
+      <c r="Q359">
         <v>2.2</v>
       </c>
-      <c r="Q359">
-        <v>3.34</v>
-      </c>
       <c r="R359">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="S359">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T359">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U359">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V359">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="W359">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X359">
         <v>1</v>
       </c>
       <c r="Y359">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z359">
-        <v>5.89</v>
+        <v>6.35</v>
       </c>
       <c r="AA359">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AB359">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AC359">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AD359">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AE359">
+        <v>1.34</v>
+      </c>
+      <c r="AF359">
+        <v>1.36</v>
+      </c>
+      <c r="AG359">
+        <v>2.88</v>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ359">
         <v>1.25</v>
       </c>
-      <c r="AF359">
-        <v>1.4</v>
-      </c>
-      <c r="AG359">
-        <v>2.8</v>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI359" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ359">
-        <v>1.71</v>
-      </c>
       <c r="AK359">
-        <v>1.42</v>
+        <v>2.06</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -58942,27 +58942,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G360">
@@ -58989,64 +58989,64 @@
         </is>
       </c>
       <c r="N360">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O360">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P360">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q360">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R360">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S360">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T360">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U360">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V360">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="W360">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X360">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y360">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z360">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AA360">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB360">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC360">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD360">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE360">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF360">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG360">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>
@@ -59059,10 +59059,10 @@
         </is>
       </c>
       <c r="AJ360">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK360">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AL360">
         <v>0</v>
@@ -59093,7 +59093,7 @@
       </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>2026-10-31 17:00:00</t>
+          <t>2026-10-31 17:30:00</t>
         </is>
       </c>
     </row>
@@ -59120,12 +59120,12 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G361">
@@ -59273,22 +59273,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G362">
@@ -59315,64 +59315,64 @@
         </is>
       </c>
       <c r="N362">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O362">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P362">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q362">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R362">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S362">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T362">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U362">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V362">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W362">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X362">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y362">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z362">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AA362">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB362">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AC362">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD362">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE362">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF362">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG362">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH362" t="inlineStr">
         <is>
@@ -59385,10 +59385,10 @@
         </is>
       </c>
       <c r="AJ362">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK362">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="AL362">
         <v>0</v>
@@ -59431,27 +59431,27 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G363">
@@ -59478,64 +59478,64 @@
         </is>
       </c>
       <c r="N363">
+        <v>1.7</v>
+      </c>
+      <c r="O363">
+        <v>3</v>
+      </c>
+      <c r="P363">
+        <v>5</v>
+      </c>
+      <c r="Q363">
+        <v>2.38</v>
+      </c>
+      <c r="R363">
+        <v>1.91</v>
+      </c>
+      <c r="S363">
+        <v>1.57</v>
+      </c>
+      <c r="T363">
+        <v>2.25</v>
+      </c>
+      <c r="U363">
+        <v>3.8</v>
+      </c>
+      <c r="V363">
         <v>1.22</v>
       </c>
-      <c r="O363">
-        <v>6.1</v>
-      </c>
-      <c r="P363">
-        <v>10.5</v>
-      </c>
-      <c r="Q363">
-        <v>1.61</v>
-      </c>
-      <c r="R363">
-        <v>2.82</v>
-      </c>
-      <c r="S363">
-        <v>1.22</v>
-      </c>
-      <c r="T363">
-        <v>4</v>
-      </c>
-      <c r="U363">
-        <v>2.03</v>
-      </c>
-      <c r="V363">
-        <v>1.67</v>
-      </c>
       <c r="W363">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X363">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="Y363">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="Z363">
-        <v>4.24</v>
+        <v>2.15</v>
       </c>
       <c r="AA363">
-        <v>1.47</v>
+        <v>2.78</v>
       </c>
       <c r="AB363">
-        <v>2.67</v>
+        <v>1.36</v>
       </c>
       <c r="AC363">
-        <v>2.16</v>
+        <v>5.6</v>
       </c>
       <c r="AD363">
-        <v>1.74</v>
+        <v>1.08</v>
       </c>
       <c r="AE363">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AF363">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="AG363">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AH363" t="inlineStr">
         <is>
@@ -59548,10 +59548,10 @@
         </is>
       </c>
       <c r="AJ363">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK363">
-        <v>4.18</v>
+        <v>1.91</v>
       </c>
       <c r="AL363">
         <v>0</v>
@@ -59582,7 +59582,7 @@
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>2026-10-31 17:30:00</t>
+          <t>2026-10-31 18:00:00</t>
         </is>
       </c>
     </row>
@@ -59599,7 +59599,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -59609,12 +59609,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G364">
@@ -59641,64 +59641,64 @@
         </is>
       </c>
       <c r="N364">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O364">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P364">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q364">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="R364">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S364">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="T364">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U364">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V364">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W364">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X364">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y364">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z364">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA364">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AB364">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC364">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD364">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE364">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF364">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG364">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH364" t="inlineStr">
         <is>
@@ -59711,10 +59711,10 @@
         </is>
       </c>
       <c r="AJ364">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK364">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL364">
         <v>0</v>
@@ -59772,12 +59772,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="G365">
@@ -59925,7 +59925,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -59935,12 +59935,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G366">
@@ -59967,64 +59967,64 @@
         </is>
       </c>
       <c r="N366">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O366">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P366">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q366">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R366">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S366">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T366">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U366">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V366">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W366">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X366">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y366">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z366">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA366">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB366">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC366">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD366">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE366">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF366">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG366">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH366" t="inlineStr">
         <is>
@@ -60037,10 +60037,10 @@
         </is>
       </c>
       <c r="AJ366">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK366">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL366">
         <v>0</v>
@@ -60083,12 +60083,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G367">
@@ -60130,64 +60130,64 @@
         </is>
       </c>
       <c r="N367">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O367">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P367">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q367">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R367">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S367">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="T367">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U367">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V367">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W367">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X367">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y367">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z367">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AA367">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB367">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC367">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD367">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE367">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF367">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG367">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH367" t="inlineStr">
         <is>
@@ -60200,10 +60200,10 @@
         </is>
       </c>
       <c r="AJ367">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK367">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL367">
         <v>0</v>
@@ -60234,7 +60234,7 @@
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>2026-10-31 18:00:00</t>
+          <t>2026-10-31 18:15:00</t>
         </is>
       </c>
     </row>
@@ -60246,12 +60246,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -60261,12 +60261,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G368">
@@ -60293,64 +60293,64 @@
         </is>
       </c>
       <c r="N368">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O368">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P368">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q368">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R368">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S368">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T368">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U368">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V368">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W368">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X368">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y368">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z368">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AA368">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB368">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC368">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD368">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE368">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF368">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG368">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH368" t="inlineStr">
         <is>
@@ -60363,10 +60363,10 @@
         </is>
       </c>
       <c r="AJ368">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK368">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL368">
         <v>0</v>
@@ -60397,7 +60397,7 @@
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>2026-10-31 18:15:00</t>
+          <t>2026-10-31 18:30:00</t>
         </is>
       </c>
     </row>
@@ -60409,12 +60409,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G369">
@@ -60456,80 +60456,80 @@
         </is>
       </c>
       <c r="N369">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O369">
         <v>3.25</v>
       </c>
       <c r="P369">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q369">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="R369">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S369">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T369">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="U369">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="V369">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W369">
         <v>1.06</v>
       </c>
       <c r="X369">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y369">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z369">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="AA369">
         <v>1.95</v>
       </c>
       <c r="AB369">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AC369">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD369">
+        <v>1.29</v>
+      </c>
+      <c r="AE369">
+        <v>1.06</v>
+      </c>
+      <c r="AF369">
+        <v>1.75</v>
+      </c>
+      <c r="AG369">
+        <v>1.95</v>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ369">
         <v>1.25</v>
       </c>
-      <c r="AE369">
-        <v>1.05</v>
-      </c>
-      <c r="AF369">
-        <v>1.79</v>
-      </c>
-      <c r="AG369">
-        <v>1.87</v>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ369">
-        <v>1.26</v>
-      </c>
       <c r="AK369">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL369">
         <v>0</v>
@@ -60560,7 +60560,7 @@
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>2026-10-31 18:30:00</t>
+          <t>2026-10-31 19:30:00</t>
         </is>
       </c>
     </row>
@@ -60572,12 +60572,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -60587,12 +60587,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G370">
@@ -60619,81 +60619,81 @@
         </is>
       </c>
       <c r="N370">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O370">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P370">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="Q370">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R370">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S370">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T370">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="U370">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="V370">
         <v>1.4</v>
       </c>
       <c r="W370">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X370">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y370">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z370">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="AA370">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB370">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC370">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD370">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE370">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF370">
+        <v>1.8</v>
+      </c>
+      <c r="AG370">
+        <v>1.91</v>
+      </c>
+      <c r="AH370" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI370" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ370">
+        <v>1.2</v>
+      </c>
+      <c r="AK370">
         <v>1.75</v>
       </c>
-      <c r="AG370">
-        <v>1.95</v>
-      </c>
-      <c r="AH370" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI370" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ370">
-        <v>1.25</v>
-      </c>
-      <c r="AK370">
-        <v>1.7</v>
-      </c>
       <c r="AL370">
         <v>0</v>
       </c>
@@ -60723,7 +60723,7 @@
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>2026-10-31 19:30:00</t>
+          <t>2026-10-31 20:00:00</t>
         </is>
       </c>
     </row>
@@ -60735,27 +60735,27 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G371">
@@ -60782,64 +60782,64 @@
         </is>
       </c>
       <c r="N371">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O371">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P371">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q371">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R371">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S371">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T371">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U371">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V371">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W371">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X371">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y371">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z371">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AA371">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB371">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC371">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD371">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE371">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF371">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG371">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH371" t="inlineStr">
         <is>
@@ -60852,10 +60852,10 @@
         </is>
       </c>
       <c r="AJ371">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK371">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL371">
         <v>0</v>
@@ -60886,7 +60886,7 @@
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>2026-10-31 20:00:00</t>
+          <t>2026-10-31 21:00:00</t>
         </is>
       </c>
     </row>
@@ -60898,27 +60898,27 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G372">
@@ -61048,169 +61048,6 @@
         <v>0</v>
       </c>
       <c r="AU372" t="inlineStr">
-        <is>
-          <t>2026-10-31 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>2026-10-31</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="G373">
-        <v>0</v>
-      </c>
-      <c r="H373">
-        <v>0</v>
-      </c>
-      <c r="I373">
-        <v>0</v>
-      </c>
-      <c r="J373">
-        <v>0</v>
-      </c>
-      <c r="K373">
-        <v>0</v>
-      </c>
-      <c r="L373">
-        <v>0</v>
-      </c>
-      <c r="M373" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N373">
-        <v>0</v>
-      </c>
-      <c r="O373">
-        <v>0</v>
-      </c>
-      <c r="P373">
-        <v>0</v>
-      </c>
-      <c r="Q373">
-        <v>0</v>
-      </c>
-      <c r="R373">
-        <v>0</v>
-      </c>
-      <c r="S373">
-        <v>0</v>
-      </c>
-      <c r="T373">
-        <v>0</v>
-      </c>
-      <c r="U373">
-        <v>0</v>
-      </c>
-      <c r="V373">
-        <v>0</v>
-      </c>
-      <c r="W373">
-        <v>0</v>
-      </c>
-      <c r="X373">
-        <v>0</v>
-      </c>
-      <c r="Y373">
-        <v>0</v>
-      </c>
-      <c r="Z373">
-        <v>0</v>
-      </c>
-      <c r="AA373">
-        <v>0</v>
-      </c>
-      <c r="AB373">
-        <v>0</v>
-      </c>
-      <c r="AC373">
-        <v>0</v>
-      </c>
-      <c r="AD373">
-        <v>0</v>
-      </c>
-      <c r="AE373">
-        <v>0</v>
-      </c>
-      <c r="AF373">
-        <v>0</v>
-      </c>
-      <c r="AG373">
-        <v>0</v>
-      </c>
-      <c r="AH373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI373" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ373">
-        <v>0</v>
-      </c>
-      <c r="AK373">
-        <v>0</v>
-      </c>
-      <c r="AL373">
-        <v>0</v>
-      </c>
-      <c r="AM373">
-        <v>-1</v>
-      </c>
-      <c r="AN373">
-        <v>-1</v>
-      </c>
-      <c r="AO373">
-        <v>-1</v>
-      </c>
-      <c r="AP373">
-        <v>-1</v>
-      </c>
-      <c r="AQ373">
-        <v>0</v>
-      </c>
-      <c r="AR373">
-        <v>0</v>
-      </c>
-      <c r="AS373">
-        <v>0</v>
-      </c>
-      <c r="AT373">
-        <v>0</v>
-      </c>
-      <c r="AU373" t="inlineStr">
         <is>
           <t>2026-10-31 22:30:00</t>
         </is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -807,55 +807,55 @@
         <v>2.55</v>
       </c>
       <c r="Q3">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
         <v>2.7</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AC3">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="AD3">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
         <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O4">
         <v>3.25</v>
@@ -1133,28 +1133,28 @@
         <v>2.91</v>
       </c>
       <c r="Q5">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="R5">
         <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U5">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.36</v>
@@ -1166,7 +1166,7 @@
         <v>2.2</v>
       </c>
       <c r="AB5">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC5">
         <v>4.1</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK5">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,28 +1293,28 @@
         <v>3.1</v>
       </c>
       <c r="P6">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="R6">
         <v>2.1</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
         <v>2.62</v>
       </c>
       <c r="U6">
-        <v>2.71</v>
+        <v>3.03</v>
       </c>
       <c r="V6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.03</v>
@@ -1329,7 +1329,7 @@
         <v>2</v>
       </c>
       <c r="AB6">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
         <v>3.28</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="AK6">
         <v>1.35</v>
@@ -1456,13 +1456,13 @@
         <v>3</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q7">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
         <v>1.4</v>
@@ -1477,10 +1477,10 @@
         <v>1.3</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
         <v>1.36</v>
@@ -1489,22 +1489,22 @@
         <v>2.9</v>
       </c>
       <c r="AA7">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB7">
         <v>1.62</v>
       </c>
       <c r="AC7">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AD7">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE7">
         <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG7">
         <v>1.78</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
         <v>1.85</v>
@@ -1625,13 +1625,13 @@
         <v>3.58</v>
       </c>
       <c r="R8">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
         <v>2.5</v>
@@ -1640,7 +1640,7 @@
         <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.88</v>
       </c>
       <c r="AK8">
         <v>1.2</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="O9">
         <v>3.6</v>
@@ -1785,16 +1785,16 @@
         <v>3.55</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
         <v>2.45</v>
@@ -1803,7 +1803,7 @@
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.03</v>
@@ -1818,16 +1818,16 @@
         <v>1.8</v>
       </c>
       <c r="AB9">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC9">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
         <v>1.62</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,19 +1945,19 @@
         <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="R10">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
         <v>2.8</v>
@@ -1969,25 +1969,25 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z10">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="AA10">
         <v>1.98</v>
       </c>
       <c r="AB10">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>3.42</v>
+        <v>3.57</v>
       </c>
       <c r="AD10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE10">
         <v>1.04</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AC11">
         <v>2.3</v>
@@ -2159,7 +2159,7 @@
         <v>1.47</v>
       </c>
       <c r="AG11">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
         <v>1.38</v>
@@ -2268,49 +2268,49 @@
         <v>3.1</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
         <v>1.45</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC12">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD12">
         <v>1.35</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="AK12">
         <v>1.25</v>
@@ -2431,7 +2431,7 @@
         <v>4.65</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P13">
         <v>1.6</v>
@@ -2440,19 +2440,19 @@
         <v>5.05</v>
       </c>
       <c r="R13">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2461,25 +2461,25 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AC13">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD13">
         <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.75</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
         <v>1.15</v>
@@ -2600,16 +2600,16 @@
         <v>1.93</v>
       </c>
       <c r="Q14">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="R14">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="U14">
         <v>2.63</v>
@@ -2621,7 +2621,7 @@
         <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.29</v>
@@ -2636,13 +2636,13 @@
         <v>1.83</v>
       </c>
       <c r="AC14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD14">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,16 +2757,16 @@
         <v>2.55</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q15">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="R15">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S15">
         <v>1.36</v>
@@ -2775,7 +2775,7 @@
         <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V15">
         <v>1.36</v>
@@ -2796,7 +2796,7 @@
         <v>1.98</v>
       </c>
       <c r="AB15">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
         <v>3.34</v>
@@ -2811,7 +2811,7 @@
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>3.54</v>
       </c>
       <c r="P16">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q16">
         <v>4.1</v>
@@ -2938,7 +2938,7 @@
         <v>2.8</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2959,16 +2959,16 @@
         <v>1.95</v>
       </c>
       <c r="AB16">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AC16">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="AD16">
         <v>1.29</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
         <v>1.8</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,7 +3083,7 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P17">
         <v>1.38</v>
@@ -3119,16 +3119,16 @@
         <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC17">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AD17">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
         <v>1.14</v>
@@ -3137,7 +3137,7 @@
         <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
         <v>1.11</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O18">
         <v>3.25</v>
@@ -3252,19 +3252,19 @@
         <v>3.4</v>
       </c>
       <c r="Q18">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="R18">
         <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
         <v>2.9</v>
       </c>
       <c r="U18">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
         <v>1.37</v>
@@ -3285,7 +3285,7 @@
         <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC18">
         <v>3.08</v>
@@ -3297,7 +3297,7 @@
         <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
         <v>2</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK18">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>1.72</v>
       </c>
       <c r="O20">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="Q20">
         <v>2.1</v>
@@ -3584,7 +3584,7 @@
         <v>2.4</v>
       </c>
       <c r="S20">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
         <v>3.4</v>
@@ -3593,25 +3593,25 @@
         <v>2.32</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>4.6</v>
+        <v>4.68</v>
       </c>
       <c r="AA20">
         <v>1.61</v>
       </c>
       <c r="AB20">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AC20">
         <v>2.36</v>
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="O21">
         <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R21">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="S21">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
         <v>3.25</v>
@@ -3756,7 +3756,7 @@
         <v>2.5</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W21">
         <v>1.11</v>
@@ -3771,16 +3771,16 @@
         <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AC21">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE21">
         <v>1.14</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="O30">
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R30">
         <v>2.31</v>
@@ -5238,10 +5238,10 @@
         <v>4.3</v>
       </c>
       <c r="AA30">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
         <v>2.38</v>
@@ -5250,13 +5250,13 @@
         <v>1.46</v>
       </c>
       <c r="AE30">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF30">
         <v>1.51</v>
       </c>
       <c r="AG30">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O31">
         <v>3.4</v>
       </c>
       <c r="P31">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q31">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="R31">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
         <v>1.3</v>
@@ -5389,7 +5389,7 @@
         <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.01</v>
@@ -5404,7 +5404,7 @@
         <v>1.71</v>
       </c>
       <c r="AB31">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC31">
         <v>2.7</v>
@@ -5540,46 +5540,46 @@
         <v>2.03</v>
       </c>
       <c r="S32">
+        <v>1.36</v>
+      </c>
+      <c r="T32">
+        <v>2.59</v>
+      </c>
+      <c r="U32">
+        <v>2.73</v>
+      </c>
+      <c r="V32">
         <v>1.38</v>
       </c>
-      <c r="T32">
-        <v>2.88</v>
-      </c>
-      <c r="U32">
-        <v>2.8</v>
-      </c>
-      <c r="V32">
-        <v>1.36</v>
-      </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
         <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="AA32">
         <v>2</v>
       </c>
       <c r="AB32">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
         <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
         <v>2</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="P33">
         <v>2.3</v>
@@ -5700,10 +5700,10 @@
         <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
         <v>3.25</v>
@@ -5727,10 +5727,10 @@
         <v>4.4</v>
       </c>
       <c r="AA33">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB33">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC33">
         <v>2.49</v>
@@ -6675,55 +6675,55 @@
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,25 +6838,25 @@
         <v>3.32</v>
       </c>
       <c r="Q40">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="R40">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6868,10 +6868,10 @@
         <v>3.1</v>
       </c>
       <c r="AA40">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB40">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
         <v>3.4</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AK40">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC42">
         <v>3.25</v>
@@ -7656,7 +7656,7 @@
         <v>2.5</v>
       </c>
       <c r="R45">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S45">
         <v>1.3</v>
@@ -7979,7 +7979,7 @@
         <v>4.31</v>
       </c>
       <c r="Q47">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="R47">
         <v>2.17</v>
@@ -7997,7 +7997,7 @@
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
         <v>1.01</v>
@@ -10946,7 +10946,7 @@
         <v>1.99</v>
       </c>
       <c r="AB65">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
         <v>3.42</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="O70">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
         <v>2.42</v>
@@ -11734,7 +11734,7 @@
         <v>2.28</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
         <v>3.2</v>
@@ -11758,7 +11758,7 @@
         <v>3.58</v>
       </c>
       <c r="AA70">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB70">
         <v>2.05</v>
@@ -11770,7 +11770,7 @@
         <v>1.32</v>
       </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF70">
         <v>1.62</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O77">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P77">
         <v>1.44</v>
@@ -12899,10 +12899,10 @@
         <v>2.83</v>
       </c>
       <c r="AA77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB77">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC77">
         <v>3.84</v>
@@ -13047,7 +13047,7 @@
         <v>2.55</v>
       </c>
       <c r="V78">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
         <v>1.11</v>
@@ -13065,7 +13065,7 @@
         <v>1.79</v>
       </c>
       <c r="AB78">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC78">
         <v>2.92</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -14206,7 +14206,7 @@
         <v>1.47</v>
       </c>
       <c r="AB85">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC85">
         <v>2.27</v>
@@ -14360,31 +14360,31 @@
         <v>0</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18272,31 +18272,31 @@
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>3.05</v>
       </c>
       <c r="AA118">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB118">
         <v>1.75</v>
@@ -19715,7 +19715,7 @@
         <v>3.1</v>
       </c>
       <c r="Q119">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="R119">
         <v>1.89</v>
@@ -19763,7 +19763,7 @@
         <v>1.95</v>
       </c>
       <c r="AG119">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>1.08</v>
       </c>
       <c r="X124">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y124">
         <v>1.27</v>
@@ -20569,10 +20569,10 @@
         <v>3.12</v>
       </c>
       <c r="AD124">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE124">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF124">
         <v>1.65</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,64 +21010,64 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="O127">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P127">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="Q127">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="R127">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="S127">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="T127">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="U127">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="V127">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y127">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z127">
-        <v>3.72</v>
+        <v>2.97</v>
       </c>
       <c r="AA127">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AB127">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC127">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AD127">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AE127">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF127">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AG127">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>1.21</v>
       </c>
       <c r="AK127">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G128">
@@ -21173,64 +21173,64 @@
         </is>
       </c>
       <c r="N128">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="O128">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P128">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="Q128">
-        <v>2.25</v>
+        <v>3.85</v>
       </c>
       <c r="R128">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="S128">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="T128">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="U128">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="V128">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W128">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X128">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y128">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z128">
-        <v>2.97</v>
+        <v>3.72</v>
       </c>
       <c r="AA128">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AB128">
-        <v>1.71</v>
+        <v>1.93</v>
       </c>
       <c r="AC128">
-        <v>3.34</v>
+        <v>2.88</v>
       </c>
       <c r="AD128">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE128">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF128">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG128">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>1.21</v>
       </c>
       <c r="AK128">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AL128">
         <v>0</v>
@@ -21345,25 +21345,25 @@
         <v>2.2</v>
       </c>
       <c r="Q129">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="R129">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S129">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T129">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="U129">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="V129">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W129">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X129">
         <v>1.01</v>
@@ -21375,10 +21375,10 @@
         <v>3.04</v>
       </c>
       <c r="AA129">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB129">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC129">
         <v>3.5</v>
@@ -21393,7 +21393,7 @@
         <v>1.77</v>
       </c>
       <c r="AG129">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21406,10 +21406,10 @@
         </is>
       </c>
       <c r="AJ129">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK129">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G132">
@@ -21825,64 +21825,64 @@
         </is>
       </c>
       <c r="N132">
-        <v>2.24</v>
+        <v>1.53</v>
       </c>
       <c r="O132">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P132">
-        <v>2.64</v>
+        <v>4.7</v>
       </c>
       <c r="Q132">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="R132">
         <v>2.18</v>
       </c>
       <c r="S132">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T132">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="U132">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V132">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W132">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X132">
         <v>1</v>
       </c>
       <c r="Y132">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z132">
-        <v>4.24</v>
+        <v>3.34</v>
       </c>
       <c r="AA132">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB132">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AC132">
-        <v>2.7</v>
+        <v>3.11</v>
       </c>
       <c r="AD132">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE132">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF132">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG132">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="AJ132">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK132">
-        <v>1.53</v>
+        <v>2.24</v>
       </c>
       <c r="AL132">
         <v>0</v>
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G133">
@@ -21988,64 +21988,64 @@
         </is>
       </c>
       <c r="N133">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="O133">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="P133">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q133">
-        <v>2.08</v>
+        <v>2.61</v>
       </c>
       <c r="R133">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="S133">
+        <v>1.36</v>
+      </c>
+      <c r="T133">
+        <v>2.75</v>
+      </c>
+      <c r="U133">
+        <v>2.8</v>
+      </c>
+      <c r="V133">
+        <v>1.34</v>
+      </c>
+      <c r="W133">
+        <v>1.07</v>
+      </c>
+      <c r="X133">
+        <v>1.03</v>
+      </c>
+      <c r="Y133">
         <v>1.33</v>
       </c>
-      <c r="T133">
-        <v>2.83</v>
-      </c>
-      <c r="U133">
-        <v>2.5</v>
-      </c>
-      <c r="V133">
-        <v>1.36</v>
-      </c>
-      <c r="W133">
-        <v>1.08</v>
-      </c>
-      <c r="X133">
-        <v>1</v>
-      </c>
-      <c r="Y133">
-        <v>1.24</v>
-      </c>
       <c r="Z133">
-        <v>3.34</v>
+        <v>3.13</v>
       </c>
       <c r="AA133">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="AB133">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="AC133">
-        <v>3.11</v>
+        <v>3.67</v>
       </c>
       <c r="AD133">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE133">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF133">
         <v>1.85</v>
       </c>
       <c r="AG133">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>
@@ -22058,10 +22058,10 @@
         </is>
       </c>
       <c r="AJ133">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK133">
-        <v>2.24</v>
+        <v>1.7</v>
       </c>
       <c r="AL133">
         <v>0</v>
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G134">
@@ -22151,64 +22151,64 @@
         </is>
       </c>
       <c r="N134">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="O134">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P134">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q134">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="R134">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="S134">
         <v>1.36</v>
       </c>
       <c r="T134">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="U134">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V134">
         <v>1.34</v>
       </c>
       <c r="W134">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X134">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y134">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z134">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AA134">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB134">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC134">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="AD134">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE134">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF134">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG134">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
@@ -22221,10 +22221,10 @@
         </is>
       </c>
       <c r="AJ134">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK134">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL134">
         <v>0</v>
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G135">
@@ -22314,55 +22314,55 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="O135">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P135">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="Q135">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="R135">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="S135">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T135">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="U135">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="V135">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W135">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X135">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y135">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z135">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AA135">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB135">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC135">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD135">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE135">
         <v>1.06</v>
@@ -22371,7 +22371,7 @@
         <v>1.75</v>
       </c>
       <c r="AG135">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
@@ -22384,10 +22384,10 @@
         </is>
       </c>
       <c r="AJ135">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK135">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL135">
         <v>0</v>
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G136">
@@ -22477,28 +22477,28 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="O136">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P136">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="Q136">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R136">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="S136">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T136">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="U136">
-        <v>2.61</v>
+        <v>2.94</v>
       </c>
       <c r="V136">
         <v>1.4</v>
@@ -22510,31 +22510,31 @@
         <v>1.01</v>
       </c>
       <c r="Y136">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z136">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="AA136">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB136">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC136">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AD136">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE136">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF136">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG136">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
@@ -22547,10 +22547,10 @@
         </is>
       </c>
       <c r="AJ136">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK136">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL136">
         <v>0</v>
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,65 +22640,65 @@
         </is>
       </c>
       <c r="N137">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="O137">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P137">
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="Q137">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R137">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S137">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T137">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U137">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="V137">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X137">
         <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z137">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA137">
+        <v>1.85</v>
+      </c>
+      <c r="AB137">
+        <v>1.87</v>
+      </c>
+      <c r="AC137">
+        <v>3.06</v>
+      </c>
+      <c r="AD137">
+        <v>1.35</v>
+      </c>
+      <c r="AE137">
+        <v>1.07</v>
+      </c>
+      <c r="AF137">
+        <v>1.73</v>
+      </c>
+      <c r="AG137">
         <v>1.95</v>
       </c>
-      <c r="AB137">
-        <v>1.75</v>
-      </c>
-      <c r="AC137">
-        <v>3.34</v>
-      </c>
-      <c r="AD137">
-        <v>1.29</v>
-      </c>
-      <c r="AE137">
-        <v>1.05</v>
-      </c>
-      <c r="AF137">
-        <v>1.83</v>
-      </c>
-      <c r="AG137">
-        <v>1.85</v>
-      </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22710,10 +22710,10 @@
         </is>
       </c>
       <c r="AJ137">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK137">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="O138">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P138">
-        <v>4.45</v>
+        <v>2.64</v>
       </c>
       <c r="Q138">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="R138">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S138">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T138">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U138">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="V138">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W138">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X138">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y138">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z138">
-        <v>3.5</v>
+        <v>4.24</v>
       </c>
       <c r="AA138">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB138">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="AC138">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="AD138">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE138">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF138">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG138">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AK138">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -24759,13 +24759,13 @@
         </is>
       </c>
       <c r="N150">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O150">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P150">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q150">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="N154">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="O154">
         <v>3.1</v>
       </c>
       <c r="P154">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q154">
         <v>2.53</v>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK154">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25583,25 +25583,25 @@
         <v>0</v>
       </c>
       <c r="Q155">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R155">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S155">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T155">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U155">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="V155">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W155">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X155">
         <v>1.01</v>
@@ -25644,10 +25644,10 @@
         </is>
       </c>
       <c r="AJ155">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK155">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL155">
         <v>0</v>
@@ -25746,25 +25746,25 @@
         <v>2.27</v>
       </c>
       <c r="Q156">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R156">
         <v>2.2</v>
       </c>
       <c r="S156">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T156">
         <v>3</v>
       </c>
       <c r="U156">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="V156">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W156">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X156">
         <v>1.01</v>
@@ -25776,7 +25776,7 @@
         <v>3.5</v>
       </c>
       <c r="AA156">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB156">
         <v>1.95</v>
@@ -25794,7 +25794,7 @@
         <v>1.63</v>
       </c>
       <c r="AG156">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH156" t="inlineStr">
         <is>
@@ -25807,7 +25807,7 @@
         </is>
       </c>
       <c r="AJ156">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK156">
         <v>1.35</v>
@@ -26063,19 +26063,19 @@
         </is>
       </c>
       <c r="N158">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="O158">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="P158">
         <v>4.4</v>
       </c>
       <c r="Q158">
+        <v>2.3</v>
+      </c>
+      <c r="R158">
         <v>2.2</v>
-      </c>
-      <c r="R158">
-        <v>2.3</v>
       </c>
       <c r="S158">
         <v>1.33</v>
@@ -26090,10 +26090,10 @@
         <v>1.44</v>
       </c>
       <c r="W158">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X158">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y158">
         <v>1.27</v>
@@ -26102,7 +26102,7 @@
         <v>3.61</v>
       </c>
       <c r="AA158">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB158">
         <v>1.9</v>
@@ -26111,7 +26111,7 @@
         <v>3.1</v>
       </c>
       <c r="AD158">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE158">
         <v>1.09</v>
@@ -26133,10 +26133,10 @@
         </is>
       </c>
       <c r="AJ158">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK158">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL158">
         <v>0</v>
@@ -26259,31 +26259,31 @@
         <v>1.02</v>
       </c>
       <c r="Y159">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z159">
-        <v>4.15</v>
+        <v>4.39</v>
       </c>
       <c r="AA159">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB159">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC159">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="AD159">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE159">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF159">
         <v>1.53</v>
       </c>
       <c r="AG159">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="AH159" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>2.3</v>
       </c>
       <c r="S160">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T160">
         <v>3.4</v>
@@ -26416,7 +26416,7 @@
         <v>1.53</v>
       </c>
       <c r="W160">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X160">
         <v>1.03</v>
@@ -26434,13 +26434,13 @@
         <v>2.25</v>
       </c>
       <c r="AC160">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AD160">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE160">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AF160">
         <v>1.51</v>
@@ -26459,10 +26459,10 @@
         </is>
       </c>
       <c r="AJ160">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK160">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL160">
         <v>0</v>
@@ -26561,7 +26561,7 @@
         <v>2.7</v>
       </c>
       <c r="Q161">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R161">
         <v>2.32</v>
@@ -26594,7 +26594,7 @@
         <v>1.57</v>
       </c>
       <c r="AB161">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AC161">
         <v>2.34</v>
@@ -26609,7 +26609,7 @@
         <v>1.44</v>
       </c>
       <c r="AG161">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH161" t="inlineStr">
         <is>
@@ -26733,7 +26733,7 @@
         <v>1.22</v>
       </c>
       <c r="T162">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U162">
         <v>2.01</v>
@@ -27856,16 +27856,16 @@
         </is>
       </c>
       <c r="N169">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="O169">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="P169">
         <v>1.22</v>
       </c>
       <c r="Q169">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R169">
         <v>2.55</v>
@@ -27895,10 +27895,10 @@
         <v>4.39</v>
       </c>
       <c r="AA169">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB169">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC169">
         <v>2.62</v>
@@ -28019,13 +28019,13 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="O170">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="P170">
-        <v>3.56</v>
+        <v>3.05</v>
       </c>
       <c r="Q170">
         <v>2.52</v>
@@ -28037,7 +28037,7 @@
         <v>1.22</v>
       </c>
       <c r="T170">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="U170">
         <v>2.28</v>
@@ -28052,25 +28052,25 @@
         <v>1</v>
       </c>
       <c r="Y170">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z170">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA170">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AB170">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="AC170">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AD170">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE170">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF170">
         <v>1.44</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK170">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28182,7 +28182,7 @@
         </is>
       </c>
       <c r="N171">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O171">
         <v>3.92</v>
@@ -28224,16 +28224,16 @@
         <v>1.44</v>
       </c>
       <c r="AB171">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AC171">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AD171">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE171">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF171">
         <v>1.44</v>
@@ -28348,13 +28348,13 @@
         <v>1.81</v>
       </c>
       <c r="O172">
-        <v>4.15</v>
+        <v>4.55</v>
       </c>
       <c r="P172">
         <v>3.76</v>
       </c>
       <c r="Q172">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R172">
         <v>2.53</v>
@@ -28378,10 +28378,10 @@
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z172">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AA172">
         <v>1.3</v>
@@ -28390,13 +28390,13 @@
         <v>3.24</v>
       </c>
       <c r="AC172">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AD172">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AE172">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AF172">
         <v>1.29</v>
@@ -28511,10 +28511,10 @@
         <v>2.72</v>
       </c>
       <c r="O173">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P173">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q173">
         <v>3.31</v>
@@ -28541,16 +28541,16 @@
         <v>1</v>
       </c>
       <c r="Y173">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z173">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA173">
         <v>1.38</v>
       </c>
       <c r="AB173">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AC173">
         <v>2.02</v>
@@ -28559,7 +28559,7 @@
         <v>1.84</v>
       </c>
       <c r="AE173">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF173">
         <v>1.35</v>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK173">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,10 +28671,10 @@
         </is>
       </c>
       <c r="N174">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O174">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P174">
         <v>1.88</v>
@@ -28707,13 +28707,13 @@
         <v>1.1</v>
       </c>
       <c r="Z174">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA174">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AB174">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AC174">
         <v>2.19</v>
@@ -28722,7 +28722,7 @@
         <v>1.7</v>
       </c>
       <c r="AE174">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF174">
         <v>1.4</v>
@@ -28997,13 +28997,13 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="O176">
         <v>3.35</v>
       </c>
       <c r="P176">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="Q176">
         <v>0</v>
@@ -31116,25 +31116,25 @@
         </is>
       </c>
       <c r="N189">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="O189">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P189">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q189">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="R189">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S189">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T189">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U189">
         <v>3</v>
@@ -31143,7 +31143,7 @@
         <v>1.35</v>
       </c>
       <c r="W189">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X189">
         <v>1.03</v>
@@ -31186,10 +31186,10 @@
         </is>
       </c>
       <c r="AJ189">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK189">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AL189">
         <v>0</v>
@@ -31288,10 +31288,10 @@
         <v>9</v>
       </c>
       <c r="Q190">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R190">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="S190">
         <v>1.22</v>
@@ -31303,7 +31303,7 @@
         <v>2.1</v>
       </c>
       <c r="V190">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W190">
         <v>1.14</v>
@@ -31312,10 +31312,10 @@
         <v>1.02</v>
       </c>
       <c r="Y190">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z190">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AA190">
         <v>1.5</v>
@@ -31330,13 +31330,13 @@
         <v>1.59</v>
       </c>
       <c r="AE190">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AF190">
         <v>1.98</v>
       </c>
       <c r="AG190">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH190" t="inlineStr">
         <is>
@@ -31349,10 +31349,10 @@
         </is>
       </c>
       <c r="AJ190">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK190">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AL190">
         <v>0</v>
@@ -31451,55 +31451,55 @@
         <v>4</v>
       </c>
       <c r="Q191">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R191">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S191">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T191">
         <v>2.72</v>
       </c>
       <c r="U191">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="V191">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="W191">
         <v>1.03</v>
       </c>
       <c r="X191">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z191">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AA191">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB191">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC191">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD191">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE191">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF191">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG191">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH191" t="inlineStr">
         <is>
@@ -31512,10 +31512,10 @@
         </is>
       </c>
       <c r="AJ191">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK191">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AL191">
         <v>0</v>
@@ -31605,19 +31605,19 @@
         </is>
       </c>
       <c r="N192">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O192">
         <v>3.25</v>
       </c>
       <c r="P192">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q192">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="R192">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S192">
         <v>1.37</v>
@@ -31644,10 +31644,10 @@
         <v>3.14</v>
       </c>
       <c r="AA192">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB192">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AC192">
         <v>3.34</v>
@@ -31675,10 +31675,10 @@
         </is>
       </c>
       <c r="AJ192">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK192">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL192">
         <v>0</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,64 +32420,64 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O197">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P197">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="Q197">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="R197">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="S197">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T197">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="U197">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="V197">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W197">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X197">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y197">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="Z197">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="AA197">
+        <v>2.14</v>
+      </c>
+      <c r="AB197">
+        <v>1.68</v>
+      </c>
+      <c r="AC197">
+        <v>3.82</v>
+      </c>
+      <c r="AD197">
+        <v>1.22</v>
+      </c>
+      <c r="AE197">
+        <v>1.02</v>
+      </c>
+      <c r="AF197">
         <v>1.83</v>
       </c>
-      <c r="AB197">
-        <v>1.93</v>
-      </c>
-      <c r="AC197">
-        <v>2.88</v>
-      </c>
-      <c r="AD197">
-        <v>1.32</v>
-      </c>
-      <c r="AE197">
-        <v>1.08</v>
-      </c>
-      <c r="AF197">
-        <v>1.64</v>
-      </c>
       <c r="AG197">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AH197" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK197">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,34 +32583,34 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="O198">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P198">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q198">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="R198">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S198">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T198">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U198">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="V198">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W198">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X198">
         <v>1.03</v>
@@ -32619,28 +32619,28 @@
         <v>1.2</v>
       </c>
       <c r="Z198">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA198">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AB198">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AC198">
         <v>2.7</v>
       </c>
       <c r="AD198">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE198">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF198">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG198">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK198">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,64 +32746,64 @@
         </is>
       </c>
       <c r="N199">
+        <v>1.7</v>
+      </c>
+      <c r="O199">
+        <v>4.05</v>
+      </c>
+      <c r="P199">
+        <v>4.5</v>
+      </c>
+      <c r="Q199">
         <v>2.15</v>
       </c>
-      <c r="O199">
-        <v>3.4</v>
-      </c>
-      <c r="P199">
-        <v>3.4</v>
-      </c>
-      <c r="Q199">
-        <v>2.76</v>
-      </c>
       <c r="R199">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="S199">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="T199">
-        <v>2.5</v>
+        <v>3.56</v>
       </c>
       <c r="U199">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="V199">
-        <v>1.32</v>
+        <v>1.55</v>
       </c>
       <c r="W199">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X199">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z199">
-        <v>2.79</v>
+        <v>4.45</v>
       </c>
       <c r="AA199">
-        <v>2.14</v>
+        <v>1.52</v>
       </c>
       <c r="AB199">
-        <v>1.68</v>
+        <v>2.24</v>
       </c>
       <c r="AC199">
-        <v>3.82</v>
+        <v>2.38</v>
       </c>
       <c r="AD199">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AE199">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AF199">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG199">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK199">
-        <v>1.65</v>
+        <v>2.11</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32877,12 +32877,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G200">
@@ -32909,64 +32909,64 @@
         </is>
       </c>
       <c r="N200">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O200">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P200">
-        <v>3.9</v>
+        <v>2.49</v>
       </c>
       <c r="Q200">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R200">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S200">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T200">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="U200">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="V200">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="W200">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X200">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y200">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z200">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="AA200">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AB200">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AC200">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD200">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AE200">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF200">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG200">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH200" t="inlineStr">
         <is>
@@ -32979,10 +32979,10 @@
         </is>
       </c>
       <c r="AJ200">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK200">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AL200">
         <v>0</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="O201">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P201">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q201">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="R201">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="S201">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T201">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="U201">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V201">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="W201">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X201">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y201">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z201">
-        <v>4.45</v>
+        <v>4.1</v>
       </c>
       <c r="AA201">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AB201">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="AC201">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD201">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE201">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF201">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG201">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK201">
-        <v>2.11</v>
+        <v>1.45</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33896,10 +33896,10 @@
         <v>1.86</v>
       </c>
       <c r="Q206">
-        <v>4.41</v>
+        <v>4.2</v>
       </c>
       <c r="R206">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S206">
         <v>1.29</v>
@@ -33926,7 +33926,7 @@
         <v>4.35</v>
       </c>
       <c r="AA206">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB206">
         <v>2.15</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="O216">
+        <v>3.85</v>
+      </c>
+      <c r="P216">
+        <v>3.8</v>
+      </c>
+      <c r="Q216">
+        <v>2.11</v>
+      </c>
+      <c r="R216">
+        <v>2.5</v>
+      </c>
+      <c r="S216">
+        <v>1.25</v>
+      </c>
+      <c r="T216">
         <v>3.7</v>
       </c>
-      <c r="P216">
-        <v>4.46</v>
-      </c>
-      <c r="Q216">
-        <v>2.3</v>
-      </c>
-      <c r="R216">
-        <v>2.11</v>
-      </c>
-      <c r="S216">
-        <v>1.35</v>
-      </c>
-      <c r="T216">
-        <v>3</v>
-      </c>
       <c r="U216">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="V216">
+        <v>1.62</v>
+      </c>
+      <c r="W216">
+        <v>1.15</v>
+      </c>
+      <c r="X216">
+        <v>1.02</v>
+      </c>
+      <c r="Y216">
+        <v>1.1</v>
+      </c>
+      <c r="Z216">
+        <v>5.1</v>
+      </c>
+      <c r="AA216">
         <v>1.44</v>
       </c>
-      <c r="W216">
-        <v>1.06</v>
-      </c>
-      <c r="X216">
-        <v>1.03</v>
-      </c>
-      <c r="Y216">
-        <v>1.24</v>
-      </c>
-      <c r="Z216">
-        <v>3.34</v>
-      </c>
-      <c r="AA216">
-        <v>1.89</v>
-      </c>
       <c r="AB216">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="AC216">
-        <v>2.99</v>
+        <v>2.25</v>
       </c>
       <c r="AD216">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AE216">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AF216">
-        <v>1.82</v>
+        <v>1.49</v>
       </c>
       <c r="AG216">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK216">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,64 +35680,64 @@
         </is>
       </c>
       <c r="N217">
+        <v>1.28</v>
+      </c>
+      <c r="O217">
+        <v>6</v>
+      </c>
+      <c r="P217">
+        <v>8.6</v>
+      </c>
+      <c r="Q217">
+        <v>1.62</v>
+      </c>
+      <c r="R217">
+        <v>2.75</v>
+      </c>
+      <c r="S217">
+        <v>1.2</v>
+      </c>
+      <c r="T217">
+        <v>3.85</v>
+      </c>
+      <c r="U217">
+        <v>2.03</v>
+      </c>
+      <c r="V217">
         <v>1.71</v>
       </c>
-      <c r="O217">
-        <v>3.85</v>
-      </c>
-      <c r="P217">
-        <v>3.8</v>
-      </c>
-      <c r="Q217">
-        <v>2.11</v>
-      </c>
-      <c r="R217">
-        <v>2.5</v>
-      </c>
-      <c r="S217">
-        <v>1.25</v>
-      </c>
-      <c r="T217">
-        <v>3.7</v>
-      </c>
-      <c r="U217">
-        <v>2.2</v>
-      </c>
-      <c r="V217">
-        <v>1.62</v>
-      </c>
       <c r="W217">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X217">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y217">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z217">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA217">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB217">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="AC217">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AD217">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AE217">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF217">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AG217">
-        <v>2.4</v>
+        <v>2.01</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK217">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,80 +35843,80 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="O218">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="P218">
-        <v>8.6</v>
+        <v>4.46</v>
       </c>
       <c r="Q218">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="R218">
-        <v>2.75</v>
+        <v>2.11</v>
       </c>
       <c r="S218">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T218">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="U218">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="V218">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="W218">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X218">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y218">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z218">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA218">
-        <v>1.36</v>
+        <v>1.89</v>
       </c>
       <c r="AB218">
-        <v>2.69</v>
+        <v>1.9</v>
       </c>
       <c r="AC218">
+        <v>2.99</v>
+      </c>
+      <c r="AD218">
+        <v>1.32</v>
+      </c>
+      <c r="AE218">
+        <v>1.07</v>
+      </c>
+      <c r="AF218">
+        <v>1.82</v>
+      </c>
+      <c r="AG218">
+        <v>1.88</v>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ218">
+        <v>1.21</v>
+      </c>
+      <c r="AK218">
         <v>2.01</v>
-      </c>
-      <c r="AD218">
-        <v>1.75</v>
-      </c>
-      <c r="AE218">
-        <v>1.28</v>
-      </c>
-      <c r="AF218">
-        <v>1.72</v>
-      </c>
-      <c r="AG218">
-        <v>2.01</v>
-      </c>
-      <c r="AH218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI218" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ218">
-        <v>1.08</v>
-      </c>
-      <c r="AK218">
-        <v>3.5</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36169,16 +36169,16 @@
         </is>
       </c>
       <c r="N220">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="O220">
         <v>3.4</v>
       </c>
       <c r="P220">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q220">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R220">
         <v>2.3</v>
@@ -36187,7 +36187,7 @@
         <v>1.3</v>
       </c>
       <c r="T220">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U220">
         <v>2.45</v>
@@ -36196,7 +36196,7 @@
         <v>1.47</v>
       </c>
       <c r="W220">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X220">
         <v>1.02</v>
@@ -36211,10 +36211,10 @@
         <v>1.66</v>
       </c>
       <c r="AB220">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC220">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD220">
         <v>1.38</v>
@@ -36223,10 +36223,10 @@
         <v>1.11</v>
       </c>
       <c r="AF220">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG220">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH220" t="inlineStr">
         <is>
@@ -36239,10 +36239,10 @@
         </is>
       </c>
       <c r="AJ220">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK220">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL220">
         <v>0</v>
@@ -36335,16 +36335,16 @@
         <v>1.8</v>
       </c>
       <c r="O221">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P221">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q221">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R221">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S221">
         <v>1.25</v>
@@ -36389,7 +36389,7 @@
         <v>1.53</v>
       </c>
       <c r="AG221">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH221" t="inlineStr">
         <is>
@@ -36402,10 +36402,10 @@
         </is>
       </c>
       <c r="AJ221">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK221">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>1.74</v>
+        <v>2.78</v>
       </c>
       <c r="O228">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="P228">
-        <v>4.28</v>
+        <v>2.28</v>
       </c>
       <c r="Q228">
-        <v>2.15</v>
+        <v>3.01</v>
       </c>
       <c r="R228">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S228">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T228">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="U228">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V228">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="W228">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X228">
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z228">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AA228">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AB228">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="AC228">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="AD228">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE228">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AF228">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG228">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK228">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,64 +37636,64 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.78</v>
+        <v>3.51</v>
       </c>
       <c r="O229">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P229">
-        <v>2.28</v>
+        <v>1.86</v>
       </c>
       <c r="Q229">
-        <v>3.01</v>
+        <v>3.56</v>
       </c>
       <c r="R229">
         <v>2.45</v>
       </c>
       <c r="S229">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T229">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="U229">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V229">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="W229">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X229">
         <v>1.02</v>
       </c>
       <c r="Y229">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z229">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="AA229">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AB229">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AC229">
-        <v>2.29</v>
+        <v>2.02</v>
       </c>
       <c r="AD229">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AE229">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AF229">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AG229">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH229" t="inlineStr">
         <is>
@@ -37706,10 +37706,10 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK229">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -37767,12 +37767,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G230">
@@ -37799,64 +37799,64 @@
         </is>
       </c>
       <c r="N230">
-        <v>3.51</v>
+        <v>1.7</v>
       </c>
       <c r="O230">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="P230">
-        <v>1.86</v>
+        <v>4.52</v>
       </c>
       <c r="Q230">
-        <v>3.56</v>
+        <v>2</v>
       </c>
       <c r="R230">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S230">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="T230">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="U230">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="V230">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="W230">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X230">
         <v>1.02</v>
       </c>
       <c r="Y230">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z230">
-        <v>5.45</v>
+        <v>4</v>
       </c>
       <c r="AA230">
+        <v>1.63</v>
+      </c>
+      <c r="AB230">
+        <v>2.21</v>
+      </c>
+      <c r="AC230">
+        <v>2.5</v>
+      </c>
+      <c r="AD230">
         <v>1.41</v>
       </c>
-      <c r="AB230">
-        <v>2.62</v>
-      </c>
-      <c r="AC230">
-        <v>2.02</v>
-      </c>
-      <c r="AD230">
-        <v>1.74</v>
-      </c>
       <c r="AE230">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF230">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AG230">
-        <v>2.88</v>
+        <v>2</v>
       </c>
       <c r="AH230" t="inlineStr">
         <is>
@@ -37869,10 +37869,10 @@
         </is>
       </c>
       <c r="AJ230">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK230">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL230">
         <v>0</v>
@@ -37930,12 +37930,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G231">
@@ -37962,64 +37962,64 @@
         </is>
       </c>
       <c r="N231">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O231">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="P231">
-        <v>4.52</v>
+        <v>3.25</v>
       </c>
       <c r="Q231">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="R231">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S231">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T231">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="U231">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="V231">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W231">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X231">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y231">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z231">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="AA231">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AB231">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="AC231">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AD231">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AE231">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF231">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG231">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH231" t="inlineStr">
         <is>
@@ -38032,10 +38032,10 @@
         </is>
       </c>
       <c r="AJ231">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK231">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AL231">
         <v>0</v>
@@ -38093,12 +38093,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G232">
@@ -38125,64 +38125,64 @@
         </is>
       </c>
       <c r="N232">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="O232">
         <v>3.5</v>
       </c>
       <c r="P232">
-        <v>3.25</v>
+        <v>2.73</v>
       </c>
       <c r="Q232">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="R232">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S232">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T232">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U232">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V232">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W232">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X232">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y232">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z232">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AA232">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB232">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC232">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD232">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE232">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF232">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AG232">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AH232" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>1.25</v>
       </c>
       <c r="AK232">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AL232">
         <v>0</v>
@@ -38256,12 +38256,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G233">
@@ -38288,64 +38288,64 @@
         </is>
       </c>
       <c r="N233">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="O233">
-        <v>3.5</v>
+        <v>5.95</v>
       </c>
       <c r="P233">
-        <v>2.73</v>
+        <v>9.75</v>
       </c>
       <c r="Q233">
-        <v>2.63</v>
+        <v>1.65</v>
       </c>
       <c r="R233">
-        <v>2.25</v>
+        <v>2.72</v>
       </c>
       <c r="S233">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="T233">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U233">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="V233">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="W233">
+        <v>1.15</v>
+      </c>
+      <c r="X233">
+        <v>1.02</v>
+      </c>
+      <c r="Y233">
         <v>1.11</v>
       </c>
-      <c r="X233">
-        <v>1.01</v>
-      </c>
-      <c r="Y233">
-        <v>1.23</v>
-      </c>
       <c r="Z233">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AA233">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AB233">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="AC233">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AD233">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AE233">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF233">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AG233">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH233" t="inlineStr">
         <is>
@@ -38358,10 +38358,10 @@
         </is>
       </c>
       <c r="AJ233">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK233">
-        <v>1.68</v>
+        <v>3.58</v>
       </c>
       <c r="AL233">
         <v>0</v>
@@ -38419,12 +38419,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G234">
@@ -38451,64 +38451,64 @@
         </is>
       </c>
       <c r="N234">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="O234">
-        <v>5.95</v>
+        <v>3.82</v>
       </c>
       <c r="P234">
-        <v>9.75</v>
+        <v>4.28</v>
       </c>
       <c r="Q234">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="R234">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="S234">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="T234">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="U234">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="V234">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="W234">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X234">
         <v>1.02</v>
       </c>
       <c r="Y234">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z234">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AA234">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="AB234">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AC234">
-        <v>2.08</v>
+        <v>2.51</v>
       </c>
       <c r="AD234">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE234">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AF234">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG234">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AH234" t="inlineStr">
         <is>
@@ -38521,10 +38521,10 @@
         </is>
       </c>
       <c r="AJ234">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AK234">
-        <v>3.58</v>
+        <v>2.03</v>
       </c>
       <c r="AL234">
         <v>0</v>
@@ -38979,10 +38979,10 @@
         <v>4.25</v>
       </c>
       <c r="AA237">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB237">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC237">
         <v>2.52</v>
@@ -39432,13 +39432,13 @@
         <v>3.18</v>
       </c>
       <c r="O240">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="P240">
         <v>1.95</v>
       </c>
       <c r="Q240">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="R240">
         <v>2.3</v>
@@ -39468,13 +39468,13 @@
         <v>4.4</v>
       </c>
       <c r="AA240">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB240">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC240">
-        <v>2.52</v>
+        <v>2.63</v>
       </c>
       <c r="AD240">
         <v>1.44</v>
@@ -39502,7 +39502,7 @@
         <v>1.22</v>
       </c>
       <c r="AK240">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AL240">
         <v>0</v>
@@ -40896,13 +40896,13 @@
         </is>
       </c>
       <c r="N249">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O249">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P249">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q249">
         <v>0</v>
@@ -41750,10 +41750,10 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AA254">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB254">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AC254">
         <v>1.7</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O261">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="P261">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Q261">
         <v>14.75</v>
@@ -42867,19 +42867,19 @@
         <v>2.89</v>
       </c>
       <c r="S261">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T261">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="U261">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V261">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W261">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X261">
         <v>1</v>
@@ -42888,7 +42888,7 @@
         <v>1.06</v>
       </c>
       <c r="Z261">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="AA261">
         <v>1.3</v>
@@ -42897,19 +42897,19 @@
         <v>3.4</v>
       </c>
       <c r="AC261">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AD261">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AE261">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AF261">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="AG261">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>1.03</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AK261">
         <v>0</v>
@@ -44165,22 +44165,22 @@
         <v>2.89</v>
       </c>
       <c r="Q269">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="R269">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S269">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T269">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U269">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="V269">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W269">
         <v>1.08</v>
@@ -44195,10 +44195,10 @@
         <v>3.42</v>
       </c>
       <c r="AA269">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB269">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC269">
         <v>2.92</v>
@@ -44213,7 +44213,7 @@
         <v>1.64</v>
       </c>
       <c r="AG269">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH269" t="inlineStr">
         <is>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK269">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44328,55 +44328,55 @@
         <v>2.13</v>
       </c>
       <c r="Q270">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R270">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S270">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T270">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U270">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V270">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W270">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X270">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y270">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z270">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA270">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB270">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC270">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AD270">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AE270">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF270">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG270">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44389,10 +44389,10 @@
         </is>
       </c>
       <c r="AJ270">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK270">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -46133,10 +46133,10 @@
         <v>4</v>
       </c>
       <c r="U281">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V281">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="W281">
         <v>1.17</v>
@@ -46151,10 +46151,10 @@
         <v>6.2</v>
       </c>
       <c r="AA281">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB281">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC281">
         <v>1.87</v>
@@ -46163,10 +46163,10 @@
         <v>1.8</v>
       </c>
       <c r="AE281">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF281">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG281">
         <v>3</v>
@@ -46185,7 +46185,7 @@
         <v>1.2</v>
       </c>
       <c r="AK281">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL281">
         <v>0</v>
@@ -46284,16 +46284,16 @@
         <v>2.59</v>
       </c>
       <c r="Q282">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="R282">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S282">
         <v>1.36</v>
       </c>
       <c r="T282">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="U282">
         <v>2.72</v>
@@ -46302,7 +46302,7 @@
         <v>1.36</v>
       </c>
       <c r="W282">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X282">
         <v>1.01</v>
@@ -46314,10 +46314,10 @@
         <v>3.08</v>
       </c>
       <c r="AA282">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB282">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC282">
         <v>3.34</v>
@@ -46332,7 +46332,7 @@
         <v>1.72</v>
       </c>
       <c r="AG282">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AH282" t="inlineStr">
         <is>
@@ -46345,10 +46345,10 @@
         </is>
       </c>
       <c r="AJ282">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK282">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL282">
         <v>0</v>
@@ -47253,58 +47253,58 @@
         </is>
       </c>
       <c r="N288">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="O288">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P288">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="Q288">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R288">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S288">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T288">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U288">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V288">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W288">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X288">
         <v>0</v>
       </c>
       <c r="Y288">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z288">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AA288">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB288">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC288">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD288">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE288">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF288">
         <v>0</v>
@@ -47323,10 +47323,10 @@
         </is>
       </c>
       <c r="AJ288">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK288">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL288">
         <v>0</v>
@@ -47742,34 +47742,34 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O291">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P291">
         <v>3.2</v>
       </c>
       <c r="Q291">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R291">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S291">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T291">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U291">
         <v>2.05</v>
       </c>
       <c r="V291">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W291">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X291">
         <v>1</v>
@@ -47790,16 +47790,16 @@
         <v>2.14</v>
       </c>
       <c r="AD291">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AE291">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF291">
         <v>1.4</v>
       </c>
       <c r="AG291">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH291" t="inlineStr">
         <is>
@@ -48566,55 +48566,55 @@
         <v>0</v>
       </c>
       <c r="Q296">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R296">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T296">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U296">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V296">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W296">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X296">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y296">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z296">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA296">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB296">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC296">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD296">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE296">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG296">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK296">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48735,10 +48735,10 @@
         <v>2.02</v>
       </c>
       <c r="S297">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T297">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U297">
         <v>2.88</v>
@@ -48762,10 +48762,10 @@
         <v>2.02</v>
       </c>
       <c r="AB297">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC297">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="AD297">
         <v>1.25</v>
@@ -48790,7 +48790,7 @@
         </is>
       </c>
       <c r="AJ297">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK297">
         <v>1.42</v>
@@ -48892,28 +48892,28 @@
         <v>2.79</v>
       </c>
       <c r="Q298">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R298">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S298">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T298">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="U298">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V298">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W298">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X298">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y298">
         <v>1.15</v>
@@ -48922,10 +48922,10 @@
         <v>4.25</v>
       </c>
       <c r="AA298">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AB298">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AC298">
         <v>2.46</v>
@@ -48940,7 +48940,7 @@
         <v>1.5</v>
       </c>
       <c r="AG298">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AH298" t="inlineStr">
         <is>
@@ -48953,10 +48953,10 @@
         </is>
       </c>
       <c r="AJ298">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK298">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL298">
         <v>0</v>
@@ -49212,7 +49212,7 @@
         <v>5</v>
       </c>
       <c r="O300">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="P300">
         <v>1.6</v>
@@ -49372,7 +49372,7 @@
         </is>
       </c>
       <c r="N301">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O301">
         <v>3.9</v>
@@ -50350,10 +50350,10 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O307">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="P307">
         <v>9</v>
@@ -50389,10 +50389,10 @@
         <v>4.93</v>
       </c>
       <c r="AA307">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB307">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC307">
         <v>2.29</v>
@@ -50513,13 +50513,13 @@
         </is>
       </c>
       <c r="N308">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O308">
         <v>5.5</v>
       </c>
       <c r="P308">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="Q308">
         <v>1.68</v>
@@ -50863,7 +50863,7 @@
         <v>1.9</v>
       </c>
       <c r="V310">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="W310">
         <v>1.22</v>
@@ -50878,13 +50878,13 @@
         <v>7</v>
       </c>
       <c r="AA310">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB310">
         <v>2.98</v>
       </c>
       <c r="AC310">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AD310">
         <v>1.89</v>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK310">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51337,10 +51337,10 @@
         <v>26</v>
       </c>
       <c r="Q313">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="R313">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="S313">
         <v>1.08</v>
@@ -51370,7 +51370,7 @@
         <v>1.2</v>
       </c>
       <c r="AB313">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AC313">
         <v>1.45</v>
@@ -51382,7 +51382,7 @@
         <v>1.69</v>
       </c>
       <c r="AF313">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AG313">
         <v>1.67</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>1.4</v>
+        <v>7</v>
       </c>
       <c r="O322">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P322">
-        <v>7.75</v>
+        <v>1.35</v>
       </c>
       <c r="Q322">
-        <v>1.95</v>
+        <v>8.5</v>
       </c>
       <c r="R322">
+        <v>2.38</v>
+      </c>
+      <c r="S322">
+        <v>1.33</v>
+      </c>
+      <c r="T322">
+        <v>2.96</v>
+      </c>
+      <c r="U322">
+        <v>2.73</v>
+      </c>
+      <c r="V322">
+        <v>1.38</v>
+      </c>
+      <c r="W322">
+        <v>1.08</v>
+      </c>
+      <c r="X322">
+        <v>1</v>
+      </c>
+      <c r="Y322">
+        <v>1.26</v>
+      </c>
+      <c r="Z322">
+        <v>3.34</v>
+      </c>
+      <c r="AA322">
+        <v>1.7</v>
+      </c>
+      <c r="AB322">
         <v>2.1</v>
       </c>
-      <c r="S322">
-        <v>1.44</v>
-      </c>
-      <c r="T322">
-        <v>2.45</v>
-      </c>
-      <c r="U322">
-        <v>3.5</v>
-      </c>
-      <c r="V322">
-        <v>1.29</v>
-      </c>
-      <c r="W322">
-        <v>1.05</v>
-      </c>
-      <c r="X322">
-        <v>1.03</v>
-      </c>
-      <c r="Y322">
-        <v>1.42</v>
-      </c>
-      <c r="Z322">
-        <v>2.49</v>
-      </c>
-      <c r="AA322">
-        <v>2.3</v>
-      </c>
-      <c r="AB322">
-        <v>1.6</v>
-      </c>
       <c r="AC322">
-        <v>4.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD322">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AE322">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF322">
-        <v>2.84</v>
+        <v>2.19</v>
       </c>
       <c r="AG322">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK322">
-        <v>2.78</v>
+        <v>1.07</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O323">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P323">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="Q323">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R323">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S323">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T323">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U323">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V323">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W323">
         <v>1.05</v>
       </c>
       <c r="X323">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Y323">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z323">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AA323">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB323">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AC323">
-        <v>4.95</v>
+        <v>4.75</v>
       </c>
       <c r="AD323">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE323">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF323">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="AG323">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK323">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,64 +53121,64 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="O324">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P324">
-        <v>4.6</v>
+        <v>7.25</v>
       </c>
       <c r="Q324">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="R324">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="S324">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="T324">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U324">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="V324">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W324">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X324">
+        <v>1.03</v>
+      </c>
+      <c r="Y324">
+        <v>1.4</v>
+      </c>
+      <c r="Z324">
+        <v>2.79</v>
+      </c>
+      <c r="AA324">
+        <v>2.25</v>
+      </c>
+      <c r="AB324">
+        <v>1.58</v>
+      </c>
+      <c r="AC324">
+        <v>4.36</v>
+      </c>
+      <c r="AD324">
+        <v>1.18</v>
+      </c>
+      <c r="AE324">
         <v>1.02</v>
       </c>
-      <c r="Y324">
-        <v>1.31</v>
-      </c>
-      <c r="Z324">
-        <v>2.92</v>
-      </c>
-      <c r="AA324">
-        <v>2.05</v>
-      </c>
-      <c r="AB324">
-        <v>1.67</v>
-      </c>
-      <c r="AC324">
-        <v>3.6</v>
-      </c>
-      <c r="AD324">
-        <v>1.23</v>
-      </c>
-      <c r="AE324">
-        <v>1.04</v>
-      </c>
       <c r="AF324">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AG324">
-        <v>1.71</v>
+        <v>1.52</v>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
@@ -53191,10 +53191,10 @@
         </is>
       </c>
       <c r="AJ324">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK324">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="O325">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P325">
-        <v>7.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q325">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="R325">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="S325">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T325">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="U325">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="V325">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W325">
+        <v>1.06</v>
+      </c>
+      <c r="X325">
+        <v>1.02</v>
+      </c>
+      <c r="Y325">
+        <v>1.31</v>
+      </c>
+      <c r="Z325">
+        <v>2.92</v>
+      </c>
+      <c r="AA325">
+        <v>2.05</v>
+      </c>
+      <c r="AB325">
+        <v>1.67</v>
+      </c>
+      <c r="AC325">
+        <v>3.6</v>
+      </c>
+      <c r="AD325">
+        <v>1.23</v>
+      </c>
+      <c r="AE325">
         <v>1.04</v>
       </c>
-      <c r="X325">
-        <v>1.03</v>
-      </c>
-      <c r="Y325">
-        <v>1.4</v>
-      </c>
-      <c r="Z325">
-        <v>2.79</v>
-      </c>
-      <c r="AA325">
-        <v>2.25</v>
-      </c>
-      <c r="AB325">
-        <v>1.58</v>
-      </c>
-      <c r="AC325">
-        <v>4.36</v>
-      </c>
-      <c r="AD325">
-        <v>1.18</v>
-      </c>
-      <c r="AE325">
-        <v>1.02</v>
-      </c>
       <c r="AF325">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AG325">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK325">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53415,12 +53415,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G326">
@@ -53447,80 +53447,80 @@
         </is>
       </c>
       <c r="N326">
+        <v>1.49</v>
+      </c>
+      <c r="O326">
+        <v>3.6</v>
+      </c>
+      <c r="P326">
         <v>7</v>
       </c>
-      <c r="O326">
-        <v>4.33</v>
-      </c>
-      <c r="P326">
-        <v>1.35</v>
-      </c>
       <c r="Q326">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="R326">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="S326">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="T326">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="U326">
-        <v>2.73</v>
+        <v>3.35</v>
       </c>
       <c r="V326">
+        <v>1.24</v>
+      </c>
+      <c r="W326">
+        <v>1.05</v>
+      </c>
+      <c r="X326">
+        <v>1.11</v>
+      </c>
+      <c r="Y326">
+        <v>1.48</v>
+      </c>
+      <c r="Z326">
+        <v>2.41</v>
+      </c>
+      <c r="AA326">
+        <v>2.4</v>
+      </c>
+      <c r="AB326">
+        <v>1.42</v>
+      </c>
+      <c r="AC326">
+        <v>4.95</v>
+      </c>
+      <c r="AD326">
+        <v>1.11</v>
+      </c>
+      <c r="AE326">
+        <v>1.03</v>
+      </c>
+      <c r="AF326">
+        <v>2.71</v>
+      </c>
+      <c r="AG326">
         <v>1.38</v>
       </c>
-      <c r="W326">
-        <v>1.08</v>
-      </c>
-      <c r="X326">
-        <v>1</v>
-      </c>
-      <c r="Y326">
-        <v>1.26</v>
-      </c>
-      <c r="Z326">
-        <v>3.34</v>
-      </c>
-      <c r="AA326">
-        <v>1.7</v>
-      </c>
-      <c r="AB326">
-        <v>2.1</v>
-      </c>
-      <c r="AC326">
-        <v>2.97</v>
-      </c>
-      <c r="AD326">
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ326">
         <v>1.3</v>
       </c>
-      <c r="AE326">
-        <v>1.08</v>
-      </c>
-      <c r="AF326">
-        <v>2.19</v>
-      </c>
-      <c r="AG326">
-        <v>1.59</v>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI326" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ326">
-        <v>1.18</v>
-      </c>
       <c r="AK326">
-        <v>1.07</v>
+        <v>2.45</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -57685,7 +57685,7 @@
         </is>
       </c>
       <c r="N352">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O352">
         <v>3.7</v>
@@ -57718,7 +57718,7 @@
         <v>1.01</v>
       </c>
       <c r="Y352">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z352">
         <v>4.51</v>
@@ -57742,7 +57742,7 @@
         <v>1.57</v>
       </c>
       <c r="AG352">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH352" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         </is>
       </c>
       <c r="AJ352">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="AK352">
         <v>1.29</v>
@@ -57848,7 +57848,7 @@
         </is>
       </c>
       <c r="N353">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="O353">
         <v>4.4</v>
@@ -57860,7 +57860,7 @@
         <v>1.9</v>
       </c>
       <c r="R353">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="S353">
         <v>1.22</v>
@@ -57887,7 +57887,7 @@
         <v>6</v>
       </c>
       <c r="AA353">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB353">
         <v>2.7</v>
@@ -57902,10 +57902,10 @@
         <v>1.3</v>
       </c>
       <c r="AF353">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG353">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH353" t="inlineStr">
         <is>
@@ -58011,16 +58011,16 @@
         </is>
       </c>
       <c r="N354">
-        <v>5.57</v>
+        <v>5.75</v>
       </c>
       <c r="O354">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="P354">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="Q354">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R354">
         <v>2.5</v>
@@ -58050,22 +58050,22 @@
         <v>4.84</v>
       </c>
       <c r="AA354">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB354">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="AC354">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="AD354">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE354">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF354">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG354">
         <v>2.1</v>
@@ -58871,7 +58871,7 @@
         <v>2.72</v>
       </c>
       <c r="AC359">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AD359">
         <v>1.74</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="AJ359">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AK359">
         <v>1.34</v>
@@ -58992,16 +58992,16 @@
         <v>1.78</v>
       </c>
       <c r="O360">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P360">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="Q360">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="R360">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="S360">
         <v>1.14</v>
@@ -59028,25 +59028,25 @@
         <v>6.35</v>
       </c>
       <c r="AA360">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB360">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AC360">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AD360">
         <v>1.84</v>
       </c>
       <c r="AE360">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF360">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG360">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AH360" t="inlineStr">
         <is>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="P9">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R9">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U9">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>3.05</v>
+        <v>4.45</v>
       </c>
       <c r="AA9">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>2.29</v>
       </c>
       <c r="AC9">
-        <v>3.42</v>
+        <v>2.3</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AG9">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AK9">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="O10">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>2.63</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R10">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
+        <v>1.43</v>
+      </c>
+      <c r="T10">
+        <v>2.8</v>
+      </c>
+      <c r="U10">
+        <v>2.77</v>
+      </c>
+      <c r="V10">
+        <v>1.37</v>
+      </c>
+      <c r="W10">
+        <v>1.05</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.32</v>
+      </c>
+      <c r="Z10">
+        <v>3.05</v>
+      </c>
+      <c r="AA10">
+        <v>2.08</v>
+      </c>
+      <c r="AB10">
+        <v>1.75</v>
+      </c>
+      <c r="AC10">
+        <v>3.42</v>
+      </c>
+      <c r="AD10">
         <v>1.25</v>
       </c>
-      <c r="T10">
-        <v>3.6</v>
-      </c>
-      <c r="U10">
-        <v>2.25</v>
-      </c>
-      <c r="V10">
-        <v>1.57</v>
-      </c>
-      <c r="W10">
-        <v>1.14</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.14</v>
-      </c>
-      <c r="Z10">
-        <v>4.45</v>
-      </c>
-      <c r="AA10">
-        <v>1.53</v>
-      </c>
-      <c r="AB10">
-        <v>2.29</v>
-      </c>
-      <c r="AC10">
-        <v>2.3</v>
-      </c>
-      <c r="AD10">
-        <v>1.49</v>
-      </c>
       <c r="AE10">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AG10">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AK10">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>2.34</v>
       </c>
       <c r="Q11">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R11">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="S11">
+        <v>1.36</v>
+      </c>
+      <c r="T11">
+        <v>2.6</v>
+      </c>
+      <c r="U11">
+        <v>2.73</v>
+      </c>
+      <c r="V11">
+        <v>1.36</v>
+      </c>
+      <c r="W11">
+        <v>1.08</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
         <v>1.3</v>
       </c>
-      <c r="T11">
+      <c r="Z11">
         <v>3.3</v>
       </c>
-      <c r="U11">
-        <v>2.4</v>
-      </c>
-      <c r="V11">
-        <v>1.5</v>
-      </c>
-      <c r="W11">
-        <v>1.12</v>
-      </c>
-      <c r="X11">
-        <v>1.02</v>
-      </c>
-      <c r="Y11">
-        <v>1.18</v>
-      </c>
-      <c r="Z11">
-        <v>4.4</v>
-      </c>
       <c r="AA11">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AB11">
-        <v>2.13</v>
+        <v>1.77</v>
       </c>
       <c r="AC11">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="AD11">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AK11">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="O12">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="Q12">
+        <v>3.52</v>
+      </c>
+      <c r="R12">
+        <v>2.24</v>
+      </c>
+      <c r="S12">
+        <v>1.3</v>
+      </c>
+      <c r="T12">
         <v>3.3</v>
       </c>
-      <c r="R12">
-        <v>2.06</v>
-      </c>
-      <c r="S12">
-        <v>1.36</v>
-      </c>
-      <c r="T12">
-        <v>2.6</v>
-      </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>1.64</v>
       </c>
       <c r="AB12">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="AC12">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="AD12">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -7816,22 +7816,22 @@
         <v>2.38</v>
       </c>
       <c r="Q46">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R46">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T46">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U46">
         <v>2.5</v>
       </c>
       <c r="V46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
         <v>1.11</v>
@@ -7846,7 +7846,7 @@
         <v>3.6</v>
       </c>
       <c r="AA46">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AB46">
         <v>1.93</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,10 +8142,10 @@
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>2.97</v>
+        <v>3.31</v>
       </c>
       <c r="R48">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="S48">
         <v>1.36</v>
@@ -8206,7 +8206,7 @@
         <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="O49">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P49">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -8468,55 +8468,55 @@
         <v>1.87</v>
       </c>
       <c r="Q50">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="R50">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T50">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="U50">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
         <v>1</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z50">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AA50">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC50">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AD50">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="AK50">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P57">
         <v>3.3</v>
@@ -9639,10 +9639,10 @@
         <v>2.88</v>
       </c>
       <c r="AA57">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB57">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC57">
         <v>3.84</v>
@@ -9929,10 +9929,10 @@
         <v>3.05</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P59">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10418,7 +10418,7 @@
         <v>2.11</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P62">
         <v>2.68</v>
@@ -10469,10 +10469,10 @@
         <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG62">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
         <v>1.73</v>
@@ -10617,7 +10617,7 @@
         <v>3.52</v>
       </c>
       <c r="AA63">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB63">
         <v>1.86</v>
@@ -10946,7 +10946,7 @@
         <v>1.99</v>
       </c>
       <c r="AB65">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
         <v>3.42</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
         <v>2.62</v>
@@ -11740,16 +11740,16 @@
         <v>3.2</v>
       </c>
       <c r="U70">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
         <v>1.1</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.21</v>
@@ -11761,7 +11761,7 @@
         <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC70">
         <v>2.88</v>
@@ -11792,7 +11792,7 @@
         <v>1.4</v>
       </c>
       <c r="AK70">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="O72">
         <v>3.54</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O73">
         <v>4.5</v>
@@ -12217,7 +12217,7 @@
         <v>4.87</v>
       </c>
       <c r="Q73">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R73">
         <v>2.63</v>
@@ -12247,7 +12247,7 @@
         <v>5.75</v>
       </c>
       <c r="AA73">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB73">
         <v>2.9</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="O74">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P74">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q74">
         <v>3.01</v>
@@ -12410,7 +12410,7 @@
         <v>5</v>
       </c>
       <c r="AA74">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB74">
         <v>2.35</v>
@@ -12866,7 +12866,7 @@
         <v>4.1</v>
       </c>
       <c r="P77">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q77">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>2.45</v>
       </c>
       <c r="V78">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
         <v>1.11</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AK78">
         <v>2.6</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="O81">
         <v>3.26</v>
@@ -13714,13 +13714,13 @@
         <v>4.9</v>
       </c>
       <c r="AA82">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC82">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AD82">
         <v>1.65</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK82">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P83">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="Q83">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="R83">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S83">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U83">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
       <c r="V83">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z83">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="AA83">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AB83">
-        <v>2.23</v>
+        <v>1.79</v>
       </c>
       <c r="AC83">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD83">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AE83">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AF83">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="O84">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q84">
-        <v>2.13</v>
+        <v>2.57</v>
       </c>
       <c r="R84">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="S84">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="T84">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="U84">
-        <v>2.64</v>
+        <v>2.21</v>
       </c>
       <c r="V84">
+        <v>1.57</v>
+      </c>
+      <c r="W84">
+        <v>1.13</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.14</v>
+      </c>
+      <c r="Z84">
+        <v>4.75</v>
+      </c>
+      <c r="AA84">
+        <v>1.56</v>
+      </c>
+      <c r="AB84">
+        <v>2.23</v>
+      </c>
+      <c r="AC84">
+        <v>2.33</v>
+      </c>
+      <c r="AD84">
+        <v>1.44</v>
+      </c>
+      <c r="AE84">
+        <v>1.21</v>
+      </c>
+      <c r="AF84">
+        <v>1.53</v>
+      </c>
+      <c r="AG84">
+        <v>2.5</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.4</v>
       </c>
-      <c r="W84">
-        <v>1.06</v>
-      </c>
-      <c r="X84">
-        <v>1.03</v>
-      </c>
-      <c r="Y84">
-        <v>1.29</v>
-      </c>
-      <c r="Z84">
-        <v>3.3</v>
-      </c>
-      <c r="AA84">
-        <v>1.91</v>
-      </c>
-      <c r="AB84">
-        <v>1.79</v>
-      </c>
-      <c r="AC84">
-        <v>3.3</v>
-      </c>
-      <c r="AD84">
-        <v>1.26</v>
-      </c>
-      <c r="AE84">
-        <v>1.06</v>
-      </c>
-      <c r="AF84">
-        <v>1.85</v>
-      </c>
-      <c r="AG84">
-        <v>1.83</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.21</v>
-      </c>
       <c r="AK84">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK87">
         <v>2.37</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="O88">
         <v>3.8</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P89">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q89">
         <v>3.75</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O94">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q94">
         <v>2.93</v>
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="N100">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O100">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P100">
         <v>2</v>
@@ -16624,7 +16624,7 @@
         <v>2.22</v>
       </c>
       <c r="S100">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T100">
         <v>3.5</v>
@@ -16648,10 +16648,10 @@
         <v>4.1</v>
       </c>
       <c r="AA100">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB100">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC100">
         <v>2.56</v>
@@ -16663,7 +16663,7 @@
         <v>1.14</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG100">
         <v>2.3</v>
@@ -16935,7 +16935,7 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O102">
         <v>3.6</v>
@@ -16977,7 +16977,7 @@
         <v>1.57</v>
       </c>
       <c r="AB102">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="AC102">
         <v>2.24</v>
@@ -16992,7 +16992,7 @@
         <v>1.44</v>
       </c>
       <c r="AG102">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P103">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="Q103">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="R103">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T103">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V103">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="W103">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z103">
-        <v>5.05</v>
+        <v>5.79</v>
       </c>
       <c r="AA103">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AB103">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AC103">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AD103">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AE103">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AF103">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG103">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,80 +17261,80 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="O104">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P104">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="Q104">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="R104">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="S104">
+        <v>1.18</v>
+      </c>
+      <c r="T104">
+        <v>4.5</v>
+      </c>
+      <c r="U104">
+        <v>2</v>
+      </c>
+      <c r="V104">
+        <v>1.82</v>
+      </c>
+      <c r="W104">
+        <v>1.15</v>
+      </c>
+      <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
+        <v>1.05</v>
+      </c>
+      <c r="Z104">
+        <v>4</v>
+      </c>
+      <c r="AA104">
+        <v>1.25</v>
+      </c>
+      <c r="AB104">
+        <v>2.5</v>
+      </c>
+      <c r="AC104">
+        <v>1.67</v>
+      </c>
+      <c r="AD104">
+        <v>1.88</v>
+      </c>
+      <c r="AE104">
+        <v>1.25</v>
+      </c>
+      <c r="AF104">
+        <v>1.33</v>
+      </c>
+      <c r="AG104">
+        <v>3</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ104">
         <v>1.2</v>
       </c>
-      <c r="T104">
-        <v>4</v>
-      </c>
-      <c r="U104">
-        <v>2.05</v>
-      </c>
-      <c r="V104">
-        <v>1.7</v>
-      </c>
-      <c r="W104">
-        <v>1.2</v>
-      </c>
-      <c r="X104">
-        <v>1.02</v>
-      </c>
-      <c r="Y104">
-        <v>1.12</v>
-      </c>
-      <c r="Z104">
-        <v>5.79</v>
-      </c>
-      <c r="AA104">
+      <c r="AK104">
         <v>1.44</v>
-      </c>
-      <c r="AB104">
-        <v>2.88</v>
-      </c>
-      <c r="AC104">
-        <v>2.02</v>
-      </c>
-      <c r="AD104">
-        <v>1.68</v>
-      </c>
-      <c r="AE104">
-        <v>1.3</v>
-      </c>
-      <c r="AF104">
-        <v>1.4</v>
-      </c>
-      <c r="AG104">
-        <v>2.62</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ104">
-        <v>1.25</v>
-      </c>
-      <c r="AK104">
-        <v>1.21</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17427,7 +17427,7 @@
         <v>1.47</v>
       </c>
       <c r="O105">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="P105">
         <v>5.25</v>
@@ -17445,10 +17445,10 @@
         <v>4</v>
       </c>
       <c r="U105">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="V105">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W105">
         <v>1.13</v>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="O106">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P106">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q106">
         <v>3</v>
       </c>
       <c r="R106">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="S106">
+        <v>1.22</v>
+      </c>
+      <c r="T106">
+        <v>3.9</v>
+      </c>
+      <c r="U106">
+        <v>2.1</v>
+      </c>
+      <c r="V106">
+        <v>1.58</v>
+      </c>
+      <c r="W106">
         <v>1.18</v>
       </c>
-      <c r="T106">
-        <v>4.5</v>
-      </c>
-      <c r="U106">
-        <v>1.95</v>
-      </c>
-      <c r="V106">
-        <v>1.82</v>
-      </c>
-      <c r="W106">
+      <c r="X106">
+        <v>1.02</v>
+      </c>
+      <c r="Y106">
+        <v>1.1</v>
+      </c>
+      <c r="Z106">
+        <v>5.05</v>
+      </c>
+      <c r="AA106">
+        <v>1.46</v>
+      </c>
+      <c r="AB106">
+        <v>2.4</v>
+      </c>
+      <c r="AC106">
+        <v>1.94</v>
+      </c>
+      <c r="AD106">
+        <v>1.46</v>
+      </c>
+      <c r="AE106">
         <v>1.15</v>
-      </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.05</v>
-      </c>
-      <c r="Z106">
-        <v>4</v>
-      </c>
-      <c r="AA106">
-        <v>1.25</v>
-      </c>
-      <c r="AB106">
-        <v>2.5</v>
-      </c>
-      <c r="AC106">
-        <v>1.67</v>
-      </c>
-      <c r="AD106">
-        <v>1.66</v>
-      </c>
-      <c r="AE106">
-        <v>1.25</v>
       </c>
       <c r="AF106">
         <v>1.33</v>
       </c>
       <c r="AG106">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK106">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="O110">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="P110">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q110">
         <v>5</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O111">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="P111">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -18441,10 +18441,10 @@
         <v>3.42</v>
       </c>
       <c r="AA111">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB111">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC111">
         <v>3.2</v>
@@ -18571,7 +18571,7 @@
         <v>4.2</v>
       </c>
       <c r="P112">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q112">
         <v>1.95</v>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O113">
         <v>5.25</v>
@@ -18764,28 +18764,28 @@
         <v>1.11</v>
       </c>
       <c r="Z113">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA113">
         <v>1.42</v>
       </c>
       <c r="AB113">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC113">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AD113">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE113">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF113">
         <v>1.73</v>
       </c>
       <c r="AG113">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>1.07</v>
       </c>
       <c r="AK113">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19706,7 +19706,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O119">
         <v>3.6</v>
@@ -19748,7 +19748,7 @@
         <v>1.72</v>
       </c>
       <c r="AB119">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC119">
         <v>2.74</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>7.6</v>
+        <v>8.15</v>
       </c>
       <c r="O120">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P120">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19899,7 +19899,7 @@
         <v>0</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -20364,7 +20364,7 @@
         <v>3.57</v>
       </c>
       <c r="P123">
-        <v>2.83</v>
+        <v>2.89</v>
       </c>
       <c r="Q123">
         <v>2.8</v>
@@ -20376,7 +20376,7 @@
         <v>1.3</v>
       </c>
       <c r="T123">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U123">
         <v>2.6</v>
@@ -20397,7 +20397,7 @@
         <v>3.55</v>
       </c>
       <c r="AA123">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB123">
         <v>1.91</v>
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G125">
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>3.25</v>
+        <v>1.65</v>
       </c>
       <c r="O125">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P125">
-        <v>1.95</v>
+        <v>4.6</v>
       </c>
       <c r="Q125">
-        <v>4.28</v>
+        <v>2.23</v>
       </c>
       <c r="R125">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S125">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T125">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="U125">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V125">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W125">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X125">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y125">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z125">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AA125">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB125">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC125">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="AD125">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE125">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF125">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG125">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK125">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,80 +20847,80 @@
         </is>
       </c>
       <c r="N126">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="O126">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P126">
-        <v>4.6</v>
+        <v>1.98</v>
       </c>
       <c r="Q126">
-        <v>2.23</v>
+        <v>3.6</v>
       </c>
       <c r="R126">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S126">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="T126">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="U126">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V126">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W126">
         <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y126">
+        <v>1.22</v>
+      </c>
+      <c r="Z126">
+        <v>3.5</v>
+      </c>
+      <c r="AA126">
+        <v>1.82</v>
+      </c>
+      <c r="AB126">
+        <v>1.85</v>
+      </c>
+      <c r="AC126">
+        <v>3.05</v>
+      </c>
+      <c r="AD126">
+        <v>1.28</v>
+      </c>
+      <c r="AE126">
+        <v>1.07</v>
+      </c>
+      <c r="AF126">
+        <v>1.66</v>
+      </c>
+      <c r="AG126">
+        <v>2.01</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <v>1.61</v>
+      </c>
+      <c r="AK126">
         <v>1.3</v>
-      </c>
-      <c r="Z126">
-        <v>2.97</v>
-      </c>
-      <c r="AA126">
-        <v>2.05</v>
-      </c>
-      <c r="AB126">
-        <v>1.75</v>
-      </c>
-      <c r="AC126">
-        <v>3.34</v>
-      </c>
-      <c r="AD126">
-        <v>1.24</v>
-      </c>
-      <c r="AE126">
-        <v>1.05</v>
-      </c>
-      <c r="AF126">
-        <v>1.91</v>
-      </c>
-      <c r="AG126">
-        <v>1.74</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>1.21</v>
-      </c>
-      <c r="AK126">
-        <v>1.97</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G127">
@@ -21010,25 +21010,25 @@
         </is>
       </c>
       <c r="N127">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O127">
         <v>3.3</v>
       </c>
       <c r="P127">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q127">
-        <v>3.6</v>
+        <v>4.28</v>
       </c>
       <c r="R127">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S127">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T127">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="U127">
         <v>2.75</v>
@@ -21037,37 +21037,37 @@
         <v>1.4</v>
       </c>
       <c r="W127">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X127">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y127">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z127">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA127">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB127">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC127">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD127">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE127">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF127">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG127">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,10 +21080,10 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="AK127">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL127">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O138">
         <v>3.6</v>
@@ -22966,7 +22966,7 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O139">
         <v>3.1</v>
@@ -23132,7 +23132,7 @@
         <v>2.25</v>
       </c>
       <c r="O140">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P140">
         <v>3.13</v>
@@ -23141,7 +23141,7 @@
         <v>2.67</v>
       </c>
       <c r="R140">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S140">
         <v>1.36</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="N142">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O142">
         <v>3.2</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,64 +23618,64 @@
         </is>
       </c>
       <c r="N143">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O143">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P143">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q143">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="R143">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="S143">
+        <v>1.33</v>
+      </c>
+      <c r="T143">
+        <v>2.97</v>
+      </c>
+      <c r="U143">
+        <v>2.59</v>
+      </c>
+      <c r="V143">
+        <v>1.42</v>
+      </c>
+      <c r="W143">
+        <v>1.07</v>
+      </c>
+      <c r="X143">
+        <v>1.01</v>
+      </c>
+      <c r="Y143">
+        <v>1.22</v>
+      </c>
+      <c r="Z143">
+        <v>3.5</v>
+      </c>
+      <c r="AA143">
+        <v>1.83</v>
+      </c>
+      <c r="AB143">
+        <v>1.87</v>
+      </c>
+      <c r="AC143">
+        <v>3.04</v>
+      </c>
+      <c r="AD143">
         <v>1.29</v>
       </c>
-      <c r="T143">
-        <v>3.3</v>
-      </c>
-      <c r="U143">
-        <v>2.5</v>
-      </c>
-      <c r="V143">
-        <v>1.44</v>
-      </c>
-      <c r="W143">
-        <v>1.11</v>
-      </c>
-      <c r="X143">
-        <v>1.02</v>
-      </c>
-      <c r="Y143">
-        <v>1.23</v>
-      </c>
-      <c r="Z143">
-        <v>3.92</v>
-      </c>
-      <c r="AA143">
-        <v>1.73</v>
-      </c>
-      <c r="AB143">
-        <v>2.07</v>
-      </c>
-      <c r="AC143">
-        <v>2.59</v>
-      </c>
-      <c r="AD143">
-        <v>1.4</v>
-      </c>
       <c r="AE143">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF143">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG143">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH143" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>1.14</v>
+        <v>1.87</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,64 +23781,64 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="O144">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P144">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q144">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R144">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S144">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T144">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="U144">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V144">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X144">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y144">
         <v>1.25</v>
       </c>
       <c r="Z144">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA144">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB144">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC144">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AD144">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE144">
         <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG144">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH144" t="inlineStr">
         <is>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK144">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G145">
@@ -23944,64 +23944,64 @@
         </is>
       </c>
       <c r="N145">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O145">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P145">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q145">
-        <v>2.42</v>
+        <v>3.14</v>
       </c>
       <c r="R145">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S145">
+        <v>1.31</v>
+      </c>
+      <c r="T145">
+        <v>3.1</v>
+      </c>
+      <c r="U145">
+        <v>2.73</v>
+      </c>
+      <c r="V145">
+        <v>1.47</v>
+      </c>
+      <c r="W145">
+        <v>1.08</v>
+      </c>
+      <c r="X145">
+        <v>1</v>
+      </c>
+      <c r="Y145">
+        <v>1.25</v>
+      </c>
+      <c r="Z145">
+        <v>3.6</v>
+      </c>
+      <c r="AA145">
+        <v>1.87</v>
+      </c>
+      <c r="AB145">
+        <v>1.9</v>
+      </c>
+      <c r="AC145">
+        <v>3.1</v>
+      </c>
+      <c r="AD145">
         <v>1.33</v>
       </c>
-      <c r="T145">
-        <v>2.97</v>
-      </c>
-      <c r="U145">
-        <v>2.59</v>
-      </c>
-      <c r="V145">
-        <v>1.42</v>
-      </c>
-      <c r="W145">
-        <v>1.07</v>
-      </c>
-      <c r="X145">
-        <v>1.01</v>
-      </c>
-      <c r="Y145">
-        <v>1.22</v>
-      </c>
-      <c r="Z145">
-        <v>3.5</v>
-      </c>
-      <c r="AA145">
-        <v>1.83</v>
-      </c>
-      <c r="AB145">
-        <v>1.87</v>
-      </c>
-      <c r="AC145">
-        <v>3.04</v>
-      </c>
-      <c r="AD145">
-        <v>1.29</v>
-      </c>
       <c r="AE145">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF145">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG145">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AH145" t="inlineStr">
         <is>
@@ -24014,10 +24014,10 @@
         </is>
       </c>
       <c r="AJ145">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK145">
-        <v>1.87</v>
+        <v>1.32</v>
       </c>
       <c r="AL145">
         <v>0</v>
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G146">
@@ -24107,25 +24107,25 @@
         </is>
       </c>
       <c r="N146">
+        <v>4.1</v>
+      </c>
+      <c r="O146">
+        <v>3.5</v>
+      </c>
+      <c r="P146">
+        <v>1.73</v>
+      </c>
+      <c r="Q146">
+        <v>4.5</v>
+      </c>
+      <c r="R146">
         <v>2.3</v>
       </c>
-      <c r="O146">
-        <v>3.4</v>
-      </c>
-      <c r="P146">
-        <v>2.62</v>
-      </c>
-      <c r="Q146">
-        <v>2.88</v>
-      </c>
-      <c r="R146">
-        <v>2.1</v>
-      </c>
       <c r="S146">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T146">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="U146">
         <v>2.5</v>
@@ -24134,37 +24134,37 @@
         <v>1.44</v>
       </c>
       <c r="W146">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X146">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y146">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z146">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AA146">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AB146">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC146">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="AD146">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE146">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF146">
         <v>1.65</v>
       </c>
       <c r="AG146">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
@@ -24177,10 +24177,10 @@
         </is>
       </c>
       <c r="AJ146">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK146">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AL146">
         <v>0</v>
@@ -24276,13 +24276,13 @@
         <v>3.5</v>
       </c>
       <c r="P147">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q147">
-        <v>2.81</v>
+        <v>2.58</v>
       </c>
       <c r="R147">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S147">
         <v>1.25</v>
@@ -24343,7 +24343,7 @@
         <v>1.25</v>
       </c>
       <c r="AK147">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AL147">
         <v>0</v>
@@ -24436,10 +24436,10 @@
         <v>1.32</v>
       </c>
       <c r="O148">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P148">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q148">
         <v>1.9</v>
@@ -24762,10 +24762,10 @@
         <v>1.3</v>
       </c>
       <c r="O150">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="P150">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="Q150">
         <v>1.73</v>
@@ -24928,7 +24928,7 @@
         <v>3.98</v>
       </c>
       <c r="P151">
-        <v>4.35</v>
+        <v>4.71</v>
       </c>
       <c r="Q151">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         </is>
       </c>
       <c r="N152">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O152">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P152">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q152">
         <v>0</v>
@@ -25287,7 +25287,7 @@
         <v>2.75</v>
       </c>
       <c r="AA153">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB153">
         <v>1.61</v>
@@ -25453,7 +25453,7 @@
         <v>1.75</v>
       </c>
       <c r="AB154">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC154">
         <v>2.83</v>
@@ -25613,10 +25613,10 @@
         <v>3.5</v>
       </c>
       <c r="AA155">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB155">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC155">
         <v>2.97</v>
@@ -25900,13 +25900,13 @@
         </is>
       </c>
       <c r="N157">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="O157">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="P157">
-        <v>4.62</v>
+        <v>4.4</v>
       </c>
       <c r="Q157">
         <v>2.3</v>
@@ -25927,7 +25927,7 @@
         <v>1.48</v>
       </c>
       <c r="W157">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X157">
         <v>1</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O158">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P158">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q158">
         <v>3.93</v>
@@ -26265,7 +26265,7 @@
         <v>4.2</v>
       </c>
       <c r="AA159">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB159">
         <v>2.25</v>
@@ -26413,7 +26413,7 @@
         <v>2.2</v>
       </c>
       <c r="V160">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W160">
         <v>1.15</v>
@@ -26428,7 +26428,7 @@
         <v>4.65</v>
       </c>
       <c r="AA160">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB160">
         <v>2.45</v>
@@ -26772,7 +26772,7 @@
         <v>1.55</v>
       </c>
       <c r="AG162">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>3.55</v>
       </c>
       <c r="P163">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q163">
         <v>2.25</v>
@@ -27065,7 +27065,7 @@
         <v>1.99</v>
       </c>
       <c r="V164">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="W164">
         <v>1.2</v>
@@ -27204,13 +27204,13 @@
         </is>
       </c>
       <c r="N165">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="O165">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P165">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,13 +27367,13 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O166">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P166">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -27856,7 +27856,7 @@
         </is>
       </c>
       <c r="N169">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O169">
         <v>3.8</v>
@@ -27901,10 +27901,10 @@
         <v>2.66</v>
       </c>
       <c r="AC169">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AD169">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE169">
         <v>1.29</v>
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="N170">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="O170">
         <v>3.8</v>
@@ -28031,7 +28031,7 @@
         <v>3.08</v>
       </c>
       <c r="R170">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S170">
         <v>1.22</v>
@@ -28040,10 +28040,10 @@
         <v>4</v>
       </c>
       <c r="U170">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="V170">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="W170">
         <v>1.18</v>
@@ -28064,10 +28064,10 @@
         <v>2.63</v>
       </c>
       <c r="AC170">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD170">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE170">
         <v>1.25</v>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AK170">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.67</v>
+        <v>2.71</v>
       </c>
       <c r="O171">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P171">
-        <v>3.76</v>
+        <v>2.2</v>
       </c>
       <c r="Q171">
-        <v>2.22</v>
+        <v>3.31</v>
       </c>
       <c r="R171">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="S171">
         <v>1.18</v>
       </c>
       <c r="T171">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U171">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="V171">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="W171">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="X171">
         <v>1</v>
       </c>
       <c r="Y171">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z171">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA171">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AB171">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="AC171">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AD171">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AE171">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AF171">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AG171">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK171">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,34 +28345,34 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="O172">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P172">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q172">
         <v>3.31</v>
       </c>
       <c r="R172">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="S172">
+        <v>1.22</v>
+      </c>
+      <c r="T172">
+        <v>3.9</v>
+      </c>
+      <c r="U172">
+        <v>2.16</v>
+      </c>
+      <c r="V172">
+        <v>1.72</v>
+      </c>
+      <c r="W172">
         <v>1.18</v>
-      </c>
-      <c r="T172">
-        <v>4.5</v>
-      </c>
-      <c r="U172">
-        <v>2.05</v>
-      </c>
-      <c r="V172">
-        <v>1.81</v>
-      </c>
-      <c r="W172">
-        <v>1.22</v>
       </c>
       <c r="X172">
         <v>1</v>
@@ -28384,25 +28384,25 @@
         <v>6.5</v>
       </c>
       <c r="AA172">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB172">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AC172">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="AD172">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AE172">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF172">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AG172">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK172">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="O173">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="P173">
-        <v>1.88</v>
+        <v>3.76</v>
       </c>
       <c r="Q173">
-        <v>3.31</v>
+        <v>2.22</v>
       </c>
       <c r="R173">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="S173">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T173">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="U173">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="V173">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="W173">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X173">
         <v>1</v>
       </c>
       <c r="Y173">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z173">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA173">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AB173">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="AC173">
-        <v>2.19</v>
+        <v>1.75</v>
       </c>
       <c r="AD173">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AE173">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF173">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AG173">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK173">
-        <v>1.29</v>
+        <v>1.95</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28671,10 +28671,10 @@
         </is>
       </c>
       <c r="N174">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O174">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P174">
         <v>3.2</v>
@@ -28834,13 +28834,13 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O175">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="P175">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q175">
         <v>0</v>
@@ -29003,7 +29003,7 @@
         <v>3.5</v>
       </c>
       <c r="P176">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q176">
         <v>2.87</v>
@@ -29024,7 +29024,7 @@
         <v>1.48</v>
       </c>
       <c r="W176">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X176">
         <v>1.02</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,64 +29160,64 @@
         </is>
       </c>
       <c r="N177">
-        <v>1.65</v>
+        <v>2.99</v>
       </c>
       <c r="O177">
-        <v>4.46</v>
+        <v>3.35</v>
       </c>
       <c r="P177">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="Q177">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="R177">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S177">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="T177">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="U177">
-        <v>2.17</v>
+        <v>2.66</v>
       </c>
       <c r="V177">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="W177">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
+        <v>1.29</v>
+      </c>
+      <c r="Z177">
+        <v>3.42</v>
+      </c>
+      <c r="AA177">
+        <v>1.86</v>
+      </c>
+      <c r="AB177">
+        <v>1.81</v>
+      </c>
+      <c r="AC177">
+        <v>3.08</v>
+      </c>
+      <c r="AD177">
+        <v>1.31</v>
+      </c>
+      <c r="AE177">
         <v>1.08</v>
       </c>
-      <c r="Z177">
-        <v>6.13</v>
-      </c>
-      <c r="AA177">
-        <v>1.4</v>
-      </c>
-      <c r="AB177">
-        <v>2.8</v>
-      </c>
-      <c r="AC177">
-        <v>2.09</v>
-      </c>
-      <c r="AD177">
-        <v>1.77</v>
-      </c>
-      <c r="AE177">
-        <v>1.32</v>
-      </c>
       <c r="AF177">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG177">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29230,10 +29230,10 @@
         </is>
       </c>
       <c r="AJ177">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AK177">
-        <v>2.27</v>
+        <v>1.42</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,31 +29323,31 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="O178">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P178">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q178">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="R178">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S178">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T178">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="U178">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="V178">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W178">
         <v>1.07</v>
@@ -29356,31 +29356,31 @@
         <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z178">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="AA178">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB178">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AC178">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="AD178">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AE178">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF178">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG178">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29393,10 +29393,10 @@
         </is>
       </c>
       <c r="AJ178">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AK178">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29454,12 +29454,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G179">
@@ -29486,64 +29486,64 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="O179">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="P179">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q179">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="R179">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="S179">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T179">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="U179">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="V179">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="W179">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X179">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y179">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z179">
-        <v>4.14</v>
+        <v>6.13</v>
       </c>
       <c r="AA179">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="AB179">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="AC179">
-        <v>2.89</v>
+        <v>2.12</v>
       </c>
       <c r="AD179">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AE179">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AF179">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG179">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AH179" t="inlineStr">
         <is>
@@ -29556,10 +29556,10 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK179">
-        <v>1.81</v>
+        <v>2.27</v>
       </c>
       <c r="AL179">
         <v>0</v>
@@ -29617,12 +29617,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G180">
@@ -29649,25 +29649,25 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O180">
+        <v>3.74</v>
+      </c>
+      <c r="P180">
         <v>3.4</v>
       </c>
-      <c r="P180">
-        <v>2.95</v>
-      </c>
       <c r="Q180">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="R180">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S180">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T180">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U180">
         <v>2.5</v>
@@ -29676,37 +29676,37 @@
         <v>1.44</v>
       </c>
       <c r="W180">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X180">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y180">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z180">
-        <v>3.56</v>
+        <v>4.14</v>
       </c>
       <c r="AA180">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AB180">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC180">
-        <v>3.13</v>
+        <v>2.89</v>
       </c>
       <c r="AD180">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE180">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF180">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG180">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH180" t="inlineStr">
         <is>
@@ -29719,10 +29719,10 @@
         </is>
       </c>
       <c r="AJ180">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK180">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AL180">
         <v>0</v>
@@ -30269,12 +30269,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G184">
@@ -30304,61 +30304,61 @@
         <v>1.98</v>
       </c>
       <c r="O184">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P184">
-        <v>2.99</v>
+        <v>2.93</v>
       </c>
       <c r="Q184">
+        <v>2.62</v>
+      </c>
+      <c r="R184">
         <v>2.5</v>
       </c>
-      <c r="R184">
-        <v>2.38</v>
-      </c>
       <c r="S184">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T184">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U184">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V184">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W184">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X184">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y184">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z184">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA184">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AB184">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC184">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="AD184">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AE184">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF184">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AG184">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         </is>
       </c>
       <c r="AJ184">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK184">
         <v>1.67</v>
@@ -30432,12 +30432,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G185">
@@ -30467,61 +30467,61 @@
         <v>1.98</v>
       </c>
       <c r="O185">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P185">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="Q185">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R185">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S185">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T185">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U185">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V185">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W185">
+        <v>1.11</v>
+      </c>
+      <c r="X185">
+        <v>1.03</v>
+      </c>
+      <c r="Y185">
         <v>1.15</v>
       </c>
-      <c r="X185">
-        <v>1.02</v>
-      </c>
-      <c r="Y185">
-        <v>1.1</v>
-      </c>
       <c r="Z185">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA185">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AB185">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC185">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AD185">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AE185">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF185">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG185">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH185" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         </is>
       </c>
       <c r="AJ185">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK185">
         <v>1.67</v>
@@ -31122,7 +31122,7 @@
         <v>3.25</v>
       </c>
       <c r="P189">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="Q189">
         <v>2.47</v>
@@ -31442,7 +31442,7 @@
         </is>
       </c>
       <c r="N191">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="O191">
         <v>3.2</v>
@@ -31608,13 +31608,13 @@
         <v>1.14</v>
       </c>
       <c r="O192">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="P192">
-        <v>12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q192">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="R192">
         <v>2.73</v>
@@ -32097,7 +32097,7 @@
         <v>2.87</v>
       </c>
       <c r="O195">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="P195">
         <v>2.35</v>
@@ -32260,7 +32260,7 @@
         <v>2</v>
       </c>
       <c r="O196">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P196">
         <v>3.6</v>
@@ -32388,12 +32388,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G197">
@@ -32420,65 +32420,65 @@
         </is>
       </c>
       <c r="N197">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="O197">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P197">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q197">
-        <v>2.28</v>
+        <v>2.99</v>
       </c>
       <c r="R197">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S197">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T197">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="U197">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V197">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W197">
+        <v>1.1</v>
+      </c>
+      <c r="X197">
+        <v>1.02</v>
+      </c>
+      <c r="Y197">
+        <v>1.25</v>
+      </c>
+      <c r="Z197">
+        <v>3.6</v>
+      </c>
+      <c r="AA197">
+        <v>1.83</v>
+      </c>
+      <c r="AB197">
+        <v>2</v>
+      </c>
+      <c r="AC197">
+        <v>3</v>
+      </c>
+      <c r="AD197">
+        <v>1.33</v>
+      </c>
+      <c r="AE197">
         <v>1.08</v>
       </c>
-      <c r="X197">
-        <v>1.03</v>
-      </c>
-      <c r="Y197">
-        <v>1.18</v>
-      </c>
-      <c r="Z197">
-        <v>3.84</v>
-      </c>
-      <c r="AA197">
-        <v>1.73</v>
-      </c>
-      <c r="AB197">
+      <c r="AF197">
+        <v>1.67</v>
+      </c>
+      <c r="AG197">
         <v>2.1</v>
       </c>
-      <c r="AC197">
-        <v>2.7</v>
-      </c>
-      <c r="AD197">
-        <v>1.41</v>
-      </c>
-      <c r="AE197">
-        <v>1.13</v>
-      </c>
-      <c r="AF197">
-        <v>1.62</v>
-      </c>
-      <c r="AG197">
-        <v>2.15</v>
-      </c>
       <c r="AH197" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32490,10 +32490,10 @@
         </is>
       </c>
       <c r="AJ197">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK197">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="AL197">
         <v>0</v>
@@ -32551,12 +32551,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G198">
@@ -32583,64 +32583,64 @@
         </is>
       </c>
       <c r="N198">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="O198">
         <v>3.25</v>
       </c>
       <c r="P198">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="Q198">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="R198">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="S198">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="T198">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="U198">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="V198">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W198">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X198">
+        <v>1.04</v>
+      </c>
+      <c r="Y198">
+        <v>1.37</v>
+      </c>
+      <c r="Z198">
+        <v>2.79</v>
+      </c>
+      <c r="AA198">
+        <v>2.1</v>
+      </c>
+      <c r="AB198">
+        <v>1.73</v>
+      </c>
+      <c r="AC198">
+        <v>3.82</v>
+      </c>
+      <c r="AD198">
+        <v>1.22</v>
+      </c>
+      <c r="AE198">
         <v>1.02</v>
       </c>
-      <c r="Y198">
-        <v>1.25</v>
-      </c>
-      <c r="Z198">
-        <v>3.6</v>
-      </c>
-      <c r="AA198">
+      <c r="AF198">
         <v>1.83</v>
       </c>
-      <c r="AB198">
-        <v>2</v>
-      </c>
-      <c r="AC198">
-        <v>3</v>
-      </c>
-      <c r="AD198">
-        <v>1.33</v>
-      </c>
-      <c r="AE198">
-        <v>1.08</v>
-      </c>
-      <c r="AF198">
-        <v>1.67</v>
-      </c>
       <c r="AG198">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH198" t="inlineStr">
         <is>
@@ -32653,10 +32653,10 @@
         </is>
       </c>
       <c r="AJ198">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK198">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AL198">
         <v>0</v>
@@ -32714,12 +32714,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G199">
@@ -32746,80 +32746,80 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="O199">
-        <v>3.16</v>
+        <v>3.7</v>
       </c>
       <c r="P199">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="Q199">
-        <v>2.76</v>
+        <v>2.14</v>
       </c>
       <c r="R199">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="S199">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T199">
-        <v>2.51</v>
+        <v>3.6</v>
       </c>
       <c r="U199">
-        <v>3</v>
+        <v>2.19</v>
       </c>
       <c r="V199">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W199">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X199">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y199">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z199">
-        <v>2.79</v>
+        <v>4.45</v>
       </c>
       <c r="AA199">
+        <v>1.57</v>
+      </c>
+      <c r="AB199">
+        <v>2.38</v>
+      </c>
+      <c r="AC199">
+        <v>2.52</v>
+      </c>
+      <c r="AD199">
+        <v>1.51</v>
+      </c>
+      <c r="AE199">
+        <v>1.19</v>
+      </c>
+      <c r="AF199">
+        <v>1.53</v>
+      </c>
+      <c r="AG199">
+        <v>2.3</v>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ199">
+        <v>1.14</v>
+      </c>
+      <c r="AK199">
         <v>2.1</v>
-      </c>
-      <c r="AB199">
-        <v>1.73</v>
-      </c>
-      <c r="AC199">
-        <v>3.82</v>
-      </c>
-      <c r="AD199">
-        <v>1.22</v>
-      </c>
-      <c r="AE199">
-        <v>1.02</v>
-      </c>
-      <c r="AF199">
-        <v>1.83</v>
-      </c>
-      <c r="AG199">
-        <v>1.85</v>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ199">
-        <v>1.35</v>
-      </c>
-      <c r="AK199">
-        <v>1.65</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -32909,7 +32909,7 @@
         </is>
       </c>
       <c r="N200">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O200">
         <v>3.4</v>
@@ -33040,12 +33040,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G201">
@@ -33072,64 +33072,64 @@
         </is>
       </c>
       <c r="N201">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="O201">
-        <v>4.05</v>
+        <v>3.75</v>
       </c>
       <c r="P201">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q201">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="R201">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S201">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="T201">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="U201">
-        <v>2.19</v>
+        <v>2.41</v>
       </c>
       <c r="V201">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W201">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X201">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y201">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z201">
-        <v>4.45</v>
+        <v>3.84</v>
       </c>
       <c r="AA201">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB201">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AC201">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD201">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AE201">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF201">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG201">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH201" t="inlineStr">
         <is>
@@ -33142,10 +33142,10 @@
         </is>
       </c>
       <c r="AJ201">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK201">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="AL201">
         <v>0</v>
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="N203">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O203">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P203">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q203">
         <v>0</v>
@@ -33763,7 +33763,7 @@
         <v>2.74</v>
       </c>
       <c r="AA205">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB205">
         <v>1.62</v>
@@ -33890,7 +33890,7 @@
         <v>3.35</v>
       </c>
       <c r="O206">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P206">
         <v>1.86</v>
@@ -34705,7 +34705,7 @@
         <v>2.03</v>
       </c>
       <c r="O211">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P211">
         <v>3.44</v>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK211">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34865,7 +34865,7 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="O212">
         <v>3.8</v>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK212">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35028,19 +35028,19 @@
         </is>
       </c>
       <c r="N213">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="O213">
         <v>3.5</v>
       </c>
       <c r="P213">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="Q213">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R213">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="S213">
         <v>1.35</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="O214">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="P214">
-        <v>9.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q214">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="R214">
-        <v>2.79</v>
+        <v>2.2</v>
       </c>
       <c r="S214">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T214">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="U214">
-        <v>2.09</v>
+        <v>2.75</v>
       </c>
       <c r="V214">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W214">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X214">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y214">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Z214">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA214">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="AB214">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC214">
-        <v>2.11</v>
+        <v>2.99</v>
       </c>
       <c r="AD214">
-        <v>1.72</v>
+        <v>1.32</v>
       </c>
       <c r="AE214">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AF214">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG214">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AK214">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="O215">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P215">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Q215">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R215">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="S215">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T215">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U215">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="V215">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W215">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X215">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z215">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="AA215">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="AB215">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AC215">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
       <c r="AD215">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="AE215">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF215">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG215">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK215">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="O216">
-        <v>3.93</v>
+        <v>5.75</v>
       </c>
       <c r="P216">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="Q216">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="R216">
-        <v>2.42</v>
+        <v>2.79</v>
       </c>
       <c r="S216">
         <v>1.2</v>
       </c>
       <c r="T216">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="U216">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="V216">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W216">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X216">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y216">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z216">
         <v>5.5</v>
       </c>
       <c r="AA216">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB216">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AC216">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AD216">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AE216">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF216">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AG216">
-        <v>2.45</v>
+        <v>2.01</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AK216">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35648,12 +35648,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G217">
@@ -35680,31 +35680,31 @@
         </is>
       </c>
       <c r="N217">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="O217">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P217">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q217">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="R217">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="S217">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T217">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U217">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V217">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W217">
         <v>1.15</v>
@@ -35713,31 +35713,31 @@
         <v>1.02</v>
       </c>
       <c r="Y217">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z217">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA217">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AB217">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="AC217">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AD217">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE217">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF217">
         <v>1.5</v>
       </c>
       <c r="AG217">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
@@ -35750,10 +35750,10 @@
         </is>
       </c>
       <c r="AJ217">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK217">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -35811,12 +35811,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G218">
@@ -35843,64 +35843,64 @@
         </is>
       </c>
       <c r="N218">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="O218">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P218">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
       <c r="Q218">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="R218">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="S218">
         <v>1.25</v>
       </c>
       <c r="T218">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U218">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V218">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W218">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X218">
         <v>1.02</v>
       </c>
       <c r="Y218">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z218">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA218">
         <v>1.57</v>
       </c>
       <c r="AB218">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AC218">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AD218">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AE218">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF218">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG218">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH218" t="inlineStr">
         <is>
@@ -35913,10 +35913,10 @@
         </is>
       </c>
       <c r="AJ218">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK218">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AL218">
         <v>0</v>
@@ -36208,7 +36208,7 @@
         <v>3.96</v>
       </c>
       <c r="AA220">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB220">
         <v>2.02</v>
@@ -36338,7 +36338,7 @@
         <v>3.8</v>
       </c>
       <c r="P221">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q221">
         <v>2.28</v>
@@ -37706,7 +37706,7 @@
         </is>
       </c>
       <c r="AJ229">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AK229">
         <v>2.31</v>
@@ -38164,10 +38164,10 @@
         <v>3.7</v>
       </c>
       <c r="AA232">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AB232">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC232">
         <v>2.51</v>
@@ -38582,12 +38582,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Francs Borains</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G235">
@@ -38614,64 +38614,64 @@
         </is>
       </c>
       <c r="N235">
-        <v>1.57</v>
+        <v>2.32</v>
       </c>
       <c r="O235">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P235">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q235">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="R235">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="S235">
         <v>1.3</v>
       </c>
       <c r="T235">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U235">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V235">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W235">
+        <v>1.11</v>
+      </c>
+      <c r="X235">
+        <v>1.01</v>
+      </c>
+      <c r="Y235">
+        <v>1.19</v>
+      </c>
+      <c r="Z235">
+        <v>3.75</v>
+      </c>
+      <c r="AA235">
+        <v>1.7</v>
+      </c>
+      <c r="AB235">
+        <v>1.99</v>
+      </c>
+      <c r="AC235">
+        <v>2.66</v>
+      </c>
+      <c r="AD235">
+        <v>1.37</v>
+      </c>
+      <c r="AE235">
         <v>1.12</v>
       </c>
-      <c r="X235">
-        <v>1.02</v>
-      </c>
-      <c r="Y235">
-        <v>1.17</v>
-      </c>
-      <c r="Z235">
-        <v>3.98</v>
-      </c>
-      <c r="AA235">
-        <v>1.67</v>
-      </c>
-      <c r="AB235">
-        <v>2.15</v>
-      </c>
-      <c r="AC235">
-        <v>2.52</v>
-      </c>
-      <c r="AD235">
-        <v>1.41</v>
-      </c>
-      <c r="AE235">
-        <v>1.16</v>
-      </c>
       <c r="AF235">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG235">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH235" t="inlineStr">
         <is>
@@ -38684,10 +38684,10 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK235">
-        <v>2.2</v>
+        <v>1.46</v>
       </c>
       <c r="AL235">
         <v>0</v>
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Francs Borains</t>
         </is>
       </c>
       <c r="G236">
@@ -38777,64 +38777,64 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.32</v>
+        <v>1.57</v>
       </c>
       <c r="O236">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P236">
-        <v>2.61</v>
+        <v>4.5</v>
       </c>
       <c r="Q236">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="R236">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S236">
         <v>1.3</v>
       </c>
       <c r="T236">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U236">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V236">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="W236">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X236">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y236">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z236">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="AA236">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB236">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="AC236">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="AD236">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE236">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF236">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG236">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH236" t="inlineStr">
         <is>
@@ -38847,10 +38847,10 @@
         </is>
       </c>
       <c r="AJ236">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK236">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="AL236">
         <v>0</v>
@@ -38982,7 +38982,7 @@
         <v>1.65</v>
       </c>
       <c r="AB237">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC237">
         <v>2.52</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>3.18</v>
+        <v>3.72</v>
       </c>
       <c r="O240">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="P240">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -39447,16 +39447,16 @@
         <v>1.29</v>
       </c>
       <c r="T240">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U240">
         <v>2.44</v>
       </c>
       <c r="V240">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W240">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X240">
         <v>1</v>
@@ -39483,7 +39483,7 @@
         <v>1.17</v>
       </c>
       <c r="AF240">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG240">
         <v>2.25</v>
@@ -39604,7 +39604,7 @@
         <v>2.7</v>
       </c>
       <c r="R241">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S241">
         <v>1.3</v>
@@ -39761,7 +39761,7 @@
         <v>3.3</v>
       </c>
       <c r="P242">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q242">
         <v>2.77</v>
@@ -39770,7 +39770,7 @@
         <v>2.05</v>
       </c>
       <c r="S242">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T242">
         <v>2.55</v>
@@ -39794,10 +39794,10 @@
         <v>3.1</v>
       </c>
       <c r="AA242">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB242">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC242">
         <v>3.8</v>
@@ -40736,10 +40736,10 @@
         <v>2.02</v>
       </c>
       <c r="O248">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P248">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q248">
         <v>2.54</v>
@@ -41101,7 +41101,7 @@
         <v>1.94</v>
       </c>
       <c r="AB250">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC250">
         <v>3.34</v>
@@ -41222,7 +41222,7 @@
         </is>
       </c>
       <c r="N251">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O251">
         <v>3.4</v>
@@ -41237,7 +41237,7 @@
         <v>2.12</v>
       </c>
       <c r="S251">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T251">
         <v>3.25</v>
@@ -41246,7 +41246,7 @@
         <v>2.45</v>
       </c>
       <c r="V251">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W251">
         <v>1.05</v>
@@ -41557,7 +41557,7 @@
         <v>2.45</v>
       </c>
       <c r="Q253">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="R253">
         <v>2.21</v>
@@ -41711,13 +41711,13 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O254">
         <v>8</v>
       </c>
       <c r="P254">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q254">
         <v>1.43</v>
@@ -41735,7 +41735,7 @@
         <v>1.75</v>
       </c>
       <c r="V254">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="W254">
         <v>1.25</v>
@@ -41756,10 +41756,10 @@
         <v>3.8</v>
       </c>
       <c r="AC254">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AD254">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AE254">
         <v>1.47</v>
@@ -42043,7 +42043,7 @@
         <v>5.25</v>
       </c>
       <c r="P256">
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="Q256">
         <v>1.69</v>
@@ -42064,7 +42064,7 @@
         <v>1.66</v>
       </c>
       <c r="W256">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X256">
         <v>1</v>
@@ -42168,12 +42168,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G257">
@@ -42331,12 +42331,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G258">
@@ -42494,12 +42494,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="G259">
@@ -42867,13 +42867,13 @@
         <v>2.88</v>
       </c>
       <c r="S261">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="T261">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="U261">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="V261">
         <v>1.82</v>
@@ -42891,10 +42891,10 @@
         <v>6.5</v>
       </c>
       <c r="AA261">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AB261">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC261">
         <v>1.76</v>
@@ -42906,7 +42906,7 @@
         <v>1.51</v>
       </c>
       <c r="AF261">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AG261">
         <v>1.56</v>
@@ -43018,10 +43018,10 @@
         <v>2.75</v>
       </c>
       <c r="O262">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P262">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q262">
         <v>3.55</v>
@@ -43187,55 +43187,55 @@
         <v>0</v>
       </c>
       <c r="Q263">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R263">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S263">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T263">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U263">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V263">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W263">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X263">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y263">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z263">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA263">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB263">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC263">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD263">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE263">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF263">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG263">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH263" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="AJ263">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK263">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL263">
         <v>0</v>
@@ -43673,7 +43673,7 @@
         <v>3.4</v>
       </c>
       <c r="P266">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="Q266">
         <v>2.67</v>
@@ -43685,7 +43685,7 @@
         <v>1.29</v>
       </c>
       <c r="T266">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U266">
         <v>2.4</v>
@@ -43830,7 +43830,7 @@
         </is>
       </c>
       <c r="N267">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="O267">
         <v>3.4</v>
@@ -44011,7 +44011,7 @@
         <v>1.4</v>
       </c>
       <c r="T268">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U268">
         <v>2.92</v>
@@ -44047,7 +44047,7 @@
         <v>1.03</v>
       </c>
       <c r="AF268">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AG268">
         <v>1.91</v>
@@ -44226,10 +44226,10 @@
         </is>
       </c>
       <c r="AJ269">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK269">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL269">
         <v>0</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O271">
         <v>3.5</v>
       </c>
       <c r="P271">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="Q271">
         <v>2.43</v>
@@ -44518,7 +44518,7 @@
         <v>1.23</v>
       </c>
       <c r="Z271">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="AA271">
         <v>1.75</v>
@@ -44552,7 +44552,7 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK271">
         <v>1.56</v>
@@ -44651,7 +44651,7 @@
         <v>3.2</v>
       </c>
       <c r="P272">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q272">
         <v>3.52</v>
@@ -44687,7 +44687,7 @@
         <v>1.79</v>
       </c>
       <c r="AB272">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC272">
         <v>2.97</v>
@@ -45134,10 +45134,10 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="O275">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P275">
         <v>4</v>
@@ -45207,7 +45207,7 @@
         <v>1.16</v>
       </c>
       <c r="AK275">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AL275">
         <v>0</v>
@@ -45428,12 +45428,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Barletta</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G277">
@@ -45460,64 +45460,64 @@
         </is>
       </c>
       <c r="N277">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="O277">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P277">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="Q277">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="R277">
-        <v>1.94</v>
+        <v>2.03</v>
       </c>
       <c r="S277">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T277">
-        <v>2.55</v>
+        <v>2.73</v>
       </c>
       <c r="U277">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="V277">
+        <v>1.35</v>
+      </c>
+      <c r="W277">
+        <v>1.05</v>
+      </c>
+      <c r="X277">
+        <v>1.01</v>
+      </c>
+      <c r="Y277">
         <v>1.3</v>
       </c>
-      <c r="W277">
+      <c r="Z277">
+        <v>2.97</v>
+      </c>
+      <c r="AA277">
+        <v>2.01</v>
+      </c>
+      <c r="AB277">
+        <v>1.69</v>
+      </c>
+      <c r="AC277">
+        <v>3.5</v>
+      </c>
+      <c r="AD277">
+        <v>1.22</v>
+      </c>
+      <c r="AE277">
         <v>1.04</v>
       </c>
-      <c r="X277">
-        <v>1.03</v>
-      </c>
-      <c r="Y277">
-        <v>1.36</v>
-      </c>
-      <c r="Z277">
-        <v>2.7</v>
-      </c>
-      <c r="AA277">
-        <v>2.25</v>
-      </c>
-      <c r="AB277">
-        <v>1.61</v>
-      </c>
-      <c r="AC277">
-        <v>4</v>
-      </c>
-      <c r="AD277">
-        <v>1.17</v>
-      </c>
-      <c r="AE277">
-        <v>1.02</v>
-      </c>
       <c r="AF277">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AG277">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AH277" t="inlineStr">
         <is>
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="AJ277">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK277">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AL277">
         <v>0</v>
@@ -45591,12 +45591,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Barletta</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G278">
@@ -45623,64 +45623,64 @@
         </is>
       </c>
       <c r="N278">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="O278">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P278">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="Q278">
+        <v>3.08</v>
+      </c>
+      <c r="R278">
+        <v>1.94</v>
+      </c>
+      <c r="S278">
+        <v>1.41</v>
+      </c>
+      <c r="T278">
         <v>2.55</v>
       </c>
-      <c r="R278">
-        <v>2.03</v>
-      </c>
-      <c r="S278">
+      <c r="U278">
+        <v>3</v>
+      </c>
+      <c r="V278">
+        <v>1.3</v>
+      </c>
+      <c r="W278">
+        <v>1.04</v>
+      </c>
+      <c r="X278">
+        <v>1.03</v>
+      </c>
+      <c r="Y278">
         <v>1.36</v>
       </c>
-      <c r="T278">
-        <v>2.73</v>
-      </c>
-      <c r="U278">
-        <v>2.77</v>
-      </c>
-      <c r="V278">
-        <v>1.35</v>
-      </c>
-      <c r="W278">
-        <v>1.05</v>
-      </c>
-      <c r="X278">
-        <v>1.01</v>
-      </c>
-      <c r="Y278">
-        <v>1.3</v>
-      </c>
       <c r="Z278">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AA278">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="AB278">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AC278">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD278">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE278">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF278">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AG278">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AH278" t="inlineStr">
         <is>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="AJ278">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK278">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="AL278">
         <v>0</v>
@@ -46314,7 +46314,7 @@
         <v>3.08</v>
       </c>
       <c r="AA282">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB282">
         <v>1.74</v>
@@ -46643,7 +46643,7 @@
         <v>1.47</v>
       </c>
       <c r="AB284">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC284">
         <v>2.2</v>
@@ -46764,13 +46764,13 @@
         </is>
       </c>
       <c r="N285">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O285">
         <v>4.15</v>
       </c>
       <c r="P285">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q285">
         <v>4.65</v>
@@ -46927,13 +46927,13 @@
         </is>
       </c>
       <c r="N286">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="O286">
         <v>3.8</v>
       </c>
       <c r="P286">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q286">
         <v>3</v>
@@ -46966,10 +46966,10 @@
         <v>7</v>
       </c>
       <c r="AA286">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB286">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="AC286">
         <v>2</v>
@@ -47090,13 +47090,13 @@
         </is>
       </c>
       <c r="N287">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="O287">
         <v>3.7</v>
       </c>
       <c r="P287">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q287">
         <v>2.17</v>
@@ -47253,7 +47253,7 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O288">
         <v>3.5</v>
@@ -47419,7 +47419,7 @@
         <v>1.85</v>
       </c>
       <c r="O289">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P289">
         <v>3.92</v>
@@ -47470,7 +47470,7 @@
         <v>1.13</v>
       </c>
       <c r="AF289">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG289">
         <v>2.1</v>
@@ -47742,7 +47742,7 @@
         </is>
       </c>
       <c r="N291">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="O291">
         <v>3.94</v>
@@ -47781,10 +47781,10 @@
         <v>5.6</v>
       </c>
       <c r="AA291">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB291">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC291">
         <v>2.06</v>
@@ -47908,10 +47908,10 @@
         <v>6</v>
       </c>
       <c r="O292">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P292">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q292">
         <v>5.22</v>
@@ -47975,7 +47975,7 @@
         </is>
       </c>
       <c r="AJ292">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK292">
         <v>1.04</v>
@@ -48252,10 +48252,10 @@
         <v>4.2</v>
       </c>
       <c r="U294">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="V294">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W294">
         <v>1.2</v>
@@ -48557,64 +48557,64 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O296">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="P296">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="Q296">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R296">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S296">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T296">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="U296">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V296">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W296">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X296">
         <v>0</v>
       </c>
       <c r="Y296">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z296">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA296">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB296">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC296">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD296">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE296">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF296">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG296">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH296" t="inlineStr">
         <is>
@@ -48627,10 +48627,10 @@
         </is>
       </c>
       <c r="AJ296">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK296">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL296">
         <v>0</v>
@@ -48883,13 +48883,13 @@
         </is>
       </c>
       <c r="N298">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O298">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P298">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q298">
         <v>2.89</v>
@@ -49375,10 +49375,10 @@
         <v>5.5</v>
       </c>
       <c r="O301">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="P301">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q301">
         <v>5</v>
@@ -49399,7 +49399,7 @@
         <v>1.53</v>
       </c>
       <c r="W301">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X301">
         <v>1.01</v>
@@ -49411,10 +49411,10 @@
         <v>4.3</v>
       </c>
       <c r="AA301">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB301">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC301">
         <v>2.55</v>
@@ -49429,7 +49429,7 @@
         <v>1.7</v>
       </c>
       <c r="AG301">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH301" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         </is>
       </c>
       <c r="AJ301">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="AK301">
         <v>1.11</v>
@@ -49574,7 +49574,7 @@
         <v>4.2</v>
       </c>
       <c r="AA302">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB302">
         <v>2.05</v>
@@ -49701,10 +49701,10 @@
         <v>1.54</v>
       </c>
       <c r="O303">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="P303">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q303">
         <v>2.03</v>
@@ -49722,7 +49722,7 @@
         <v>2.38</v>
       </c>
       <c r="V303">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W303">
         <v>1.13</v>
@@ -49737,10 +49737,10 @@
         <v>5</v>
       </c>
       <c r="AA303">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB303">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AC303">
         <v>2.43</v>
@@ -49879,7 +49879,7 @@
         <v>1.22</v>
       </c>
       <c r="T304">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U304">
         <v>2</v>
@@ -49903,7 +49903,7 @@
         <v>1.5</v>
       </c>
       <c r="AB304">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC304">
         <v>2.11</v>
@@ -50193,7 +50193,7 @@
         <v>5</v>
       </c>
       <c r="P306">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Q306">
         <v>1.84</v>
@@ -50205,7 +50205,7 @@
         <v>1.25</v>
       </c>
       <c r="T306">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U306">
         <v>2.2</v>
@@ -50350,7 +50350,7 @@
         </is>
       </c>
       <c r="N307">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O307">
         <v>3.9</v>
@@ -50519,7 +50519,7 @@
         <v>6.25</v>
       </c>
       <c r="P308">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q308">
         <v>1.67</v>
@@ -50682,7 +50682,7 @@
         <v>5.5</v>
       </c>
       <c r="P309">
-        <v>6.75</v>
+        <v>6.8</v>
       </c>
       <c r="Q309">
         <v>1.68</v>
@@ -51002,16 +51002,16 @@
         </is>
       </c>
       <c r="N311">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="O311">
         <v>4</v>
       </c>
       <c r="P311">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="Q311">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="R311">
         <v>2.52</v>
@@ -51023,13 +51023,13 @@
         <v>4.4</v>
       </c>
       <c r="U311">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V311">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="W311">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X311">
         <v>1</v>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK311">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51165,13 +51165,13 @@
         </is>
       </c>
       <c r="N312">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="O312">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P312">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q312">
         <v>1.29</v>
@@ -51238,7 +51238,7 @@
         <v>1.01</v>
       </c>
       <c r="AK312">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AL312">
         <v>0</v>
@@ -51494,10 +51494,10 @@
         <v>1.01</v>
       </c>
       <c r="O314">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P314">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q314">
         <v>1.3</v>
@@ -51530,7 +51530,7 @@
         <v>11</v>
       </c>
       <c r="AA314">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AB314">
         <v>5</v>
@@ -51548,7 +51548,7 @@
         <v>1.8</v>
       </c>
       <c r="AG314">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>3.7</v>
       </c>
       <c r="P318">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="Q318">
         <v>2.03</v>
@@ -52306,7 +52306,7 @@
         </is>
       </c>
       <c r="N319">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O319">
         <v>2.7</v>
@@ -52632,13 +52632,13 @@
         </is>
       </c>
       <c r="N321">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="O321">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P321">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="O322">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P322">
-        <v>1.31</v>
+        <v>7</v>
       </c>
       <c r="Q322">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="R322">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S322">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T322">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="U322">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="V322">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W322">
         <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y322">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z322">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AA322">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB322">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AC322">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AD322">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE322">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF322">
         <v>2.88</v>
       </c>
       <c r="AG322">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>3.04</v>
+        <v>1.25</v>
       </c>
       <c r="AK322">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52926,12 +52926,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G323">
@@ -52958,64 +52958,64 @@
         </is>
       </c>
       <c r="N323">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="O323">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P323">
-        <v>7.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q323">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="R323">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="S323">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T323">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U323">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="V323">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W323">
         <v>1.06</v>
       </c>
       <c r="X323">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y323">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z323">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="AA323">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AB323">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AC323">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
       <c r="AD323">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE323">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF323">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG323">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
@@ -53028,10 +53028,10 @@
         </is>
       </c>
       <c r="AJ323">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AK323">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AL323">
         <v>0</v>
@@ -53089,12 +53089,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G324">
@@ -53121,80 +53121,80 @@
         </is>
       </c>
       <c r="N324">
+        <v>8.1</v>
+      </c>
+      <c r="O324">
+        <v>4.3</v>
+      </c>
+      <c r="P324">
+        <v>1.31</v>
+      </c>
+      <c r="Q324">
+        <v>10</v>
+      </c>
+      <c r="R324">
+        <v>2.2</v>
+      </c>
+      <c r="S324">
         <v>1.42</v>
       </c>
-      <c r="O324">
-        <v>4</v>
-      </c>
-      <c r="P324">
-        <v>7</v>
-      </c>
-      <c r="Q324">
-        <v>2</v>
-      </c>
-      <c r="R324">
-        <v>2.1</v>
-      </c>
-      <c r="S324">
-        <v>1.44</v>
-      </c>
       <c r="T324">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="U324">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="V324">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W324">
         <v>1.05</v>
       </c>
       <c r="X324">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y324">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z324">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AA324">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB324">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC324">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AD324">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE324">
+        <v>1.06</v>
+      </c>
+      <c r="AF324">
+        <v>2.88</v>
+      </c>
+      <c r="AG324">
+        <v>1.34</v>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ324">
+        <v>3.04</v>
+      </c>
+      <c r="AK324">
         <v>1.02</v>
-      </c>
-      <c r="AF324">
-        <v>2.7</v>
-      </c>
-      <c r="AG324">
-        <v>1.4</v>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ324">
-        <v>1.25</v>
-      </c>
-      <c r="AK324">
-        <v>2.7</v>
       </c>
       <c r="AL324">
         <v>0</v>
@@ -53252,12 +53252,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G325">
@@ -53284,64 +53284,64 @@
         </is>
       </c>
       <c r="N325">
-        <v>1.64</v>
+        <v>7</v>
       </c>
       <c r="O325">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P325">
-        <v>4.6</v>
+        <v>1.37</v>
       </c>
       <c r="Q325">
-        <v>2.17</v>
+        <v>8.5</v>
       </c>
       <c r="R325">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="S325">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T325">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U325">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="V325">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W325">
+        <v>1.08</v>
+      </c>
+      <c r="X325">
+        <v>1.01</v>
+      </c>
+      <c r="Y325">
+        <v>1.27</v>
+      </c>
+      <c r="Z325">
+        <v>3.2</v>
+      </c>
+      <c r="AA325">
+        <v>1.9</v>
+      </c>
+      <c r="AB325">
+        <v>1.78</v>
+      </c>
+      <c r="AC325">
+        <v>3.1</v>
+      </c>
+      <c r="AD325">
+        <v>1.27</v>
+      </c>
+      <c r="AE325">
         <v>1.06</v>
       </c>
-      <c r="X325">
-        <v>1.02</v>
-      </c>
-      <c r="Y325">
-        <v>1.31</v>
-      </c>
-      <c r="Z325">
-        <v>2.92</v>
-      </c>
-      <c r="AA325">
-        <v>2.05</v>
-      </c>
-      <c r="AB325">
-        <v>1.68</v>
-      </c>
-      <c r="AC325">
-        <v>3.5</v>
-      </c>
-      <c r="AD325">
-        <v>1.23</v>
-      </c>
-      <c r="AE325">
-        <v>1.04</v>
-      </c>
       <c r="AF325">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AG325">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
@@ -53354,10 +53354,10 @@
         </is>
       </c>
       <c r="AJ325">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK325">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL325">
         <v>0</v>
@@ -53453,13 +53453,13 @@
         <v>3.5</v>
       </c>
       <c r="P326">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q326">
         <v>2.05</v>
       </c>
       <c r="R326">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S326">
         <v>1.55</v>
@@ -53477,22 +53477,22 @@
         <v>1.04</v>
       </c>
       <c r="X326">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y326">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Z326">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AA326">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AB326">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AC326">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AD326">
         <v>1.09</v>
@@ -53501,10 +53501,10 @@
         <v>1.03</v>
       </c>
       <c r="AF326">
-        <v>2.79</v>
+        <v>2.62</v>
       </c>
       <c r="AG326">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK326">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53578,12 +53578,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G327">
@@ -53610,64 +53610,64 @@
         </is>
       </c>
       <c r="N327">
-        <v>7</v>
+        <v>1.43</v>
       </c>
       <c r="O327">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P327">
-        <v>1.37</v>
+        <v>7.25</v>
       </c>
       <c r="Q327">
-        <v>8.5</v>
+        <v>2.02</v>
       </c>
       <c r="R327">
-        <v>2.38</v>
+        <v>2.09</v>
       </c>
       <c r="S327">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T327">
-        <v>2.89</v>
+        <v>2.56</v>
       </c>
       <c r="U327">
+        <v>3.1</v>
+      </c>
+      <c r="V327">
+        <v>1.33</v>
+      </c>
+      <c r="W327">
+        <v>1.06</v>
+      </c>
+      <c r="X327">
+        <v>1.03</v>
+      </c>
+      <c r="Y327">
+        <v>1.4</v>
+      </c>
+      <c r="Z327">
         <v>2.79</v>
       </c>
-      <c r="V327">
-        <v>1.4</v>
-      </c>
-      <c r="W327">
-        <v>1.08</v>
-      </c>
-      <c r="X327">
-        <v>1.01</v>
-      </c>
-      <c r="Y327">
-        <v>1.27</v>
-      </c>
-      <c r="Z327">
-        <v>3.2</v>
-      </c>
       <c r="AA327">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AB327">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AC327">
-        <v>3.1</v>
+        <v>4.36</v>
       </c>
       <c r="AD327">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE327">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF327">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="AG327">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
@@ -53680,10 +53680,10 @@
         </is>
       </c>
       <c r="AJ327">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK327">
-        <v>1.07</v>
+        <v>2.63</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53773,80 +53773,80 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O328">
-        <v>4</v>
+        <v>4.51</v>
       </c>
       <c r="P328">
         <v>4.8</v>
       </c>
       <c r="Q328">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="R328">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S328">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T328">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U328">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V328">
+        <v>1.57</v>
+      </c>
+      <c r="W328">
+        <v>1.14</v>
+      </c>
+      <c r="X328">
+        <v>0</v>
+      </c>
+      <c r="Y328">
+        <v>1.15</v>
+      </c>
+      <c r="Z328">
+        <v>4.8</v>
+      </c>
+      <c r="AA328">
         <v>1.56</v>
       </c>
-      <c r="W328">
-        <v>0</v>
-      </c>
-      <c r="X328">
-        <v>0</v>
-      </c>
-      <c r="Y328">
-        <v>1.18</v>
-      </c>
-      <c r="Z328">
-        <v>4.66</v>
-      </c>
-      <c r="AA328">
-        <v>0</v>
-      </c>
       <c r="AB328">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC328">
+        <v>2.38</v>
+      </c>
+      <c r="AD328">
+        <v>1.46</v>
+      </c>
+      <c r="AE328">
+        <v>1.16</v>
+      </c>
+      <c r="AF328">
+        <v>1.67</v>
+      </c>
+      <c r="AG328">
+        <v>2.1</v>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ328">
+        <v>1.14</v>
+      </c>
+      <c r="AK328">
         <v>2.45</v>
-      </c>
-      <c r="AD328">
-        <v>1.54</v>
-      </c>
-      <c r="AE328">
-        <v>1.21</v>
-      </c>
-      <c r="AF328">
-        <v>0</v>
-      </c>
-      <c r="AG328">
-        <v>0</v>
-      </c>
-      <c r="AH328" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI328" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ328">
-        <v>0</v>
-      </c>
-      <c r="AK328">
-        <v>0</v>
       </c>
       <c r="AL328">
         <v>0</v>
@@ -53936,64 +53936,64 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="O329">
-        <v>4.76</v>
+        <v>4.95</v>
       </c>
       <c r="P329">
-        <v>5.67</v>
+        <v>5.94</v>
       </c>
       <c r="Q329">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R329">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="S329">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T329">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U329">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V329">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W329">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X329">
         <v>0</v>
       </c>
       <c r="Y329">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z329">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="AA329">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB329">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC329">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD329">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE329">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF329">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG329">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK329">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54099,64 +54099,64 @@
         </is>
       </c>
       <c r="N330">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="O330">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="P330">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q330">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R330">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S330">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T330">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U330">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V330">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="W330">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X330">
         <v>0</v>
       </c>
       <c r="Y330">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z330">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA330">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB330">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AC330">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD330">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE330">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF330">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG330">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54169,10 +54169,10 @@
         </is>
       </c>
       <c r="AJ330">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK330">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54751,28 +54751,28 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O334">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="P334">
-        <v>3.31</v>
+        <v>3.46</v>
       </c>
       <c r="Q334">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="R334">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S334">
         <v>1.46</v>
       </c>
       <c r="T334">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="U334">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="V334">
         <v>1.32</v>
@@ -54790,10 +54790,10 @@
         <v>2.97</v>
       </c>
       <c r="AA334">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AB334">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC334">
         <v>3.58</v>
@@ -54824,7 +54824,7 @@
         <v>1.33</v>
       </c>
       <c r="AK334">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL334">
         <v>0</v>
@@ -54920,7 +54920,7 @@
         <v>3.2</v>
       </c>
       <c r="P335">
-        <v>4.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q335">
         <v>0</v>
@@ -55083,7 +55083,7 @@
         <v>3.25</v>
       </c>
       <c r="P336">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q336">
         <v>2.3</v>
@@ -55122,7 +55122,7 @@
         <v>1.44</v>
       </c>
       <c r="AC336">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AD336">
         <v>1.13</v>
@@ -55134,7 +55134,7 @@
         <v>2.3</v>
       </c>
       <c r="AG336">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AH336" t="inlineStr">
         <is>
@@ -55240,16 +55240,16 @@
         </is>
       </c>
       <c r="N337">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O337">
         <v>4.8</v>
       </c>
       <c r="P337">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="Q337">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R337">
         <v>2.8</v>
@@ -55310,7 +55310,7 @@
         </is>
       </c>
       <c r="AJ337">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK337">
         <v>2.86</v>
@@ -55403,13 +55403,13 @@
         </is>
       </c>
       <c r="N338">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O338">
         <v>3.7</v>
       </c>
       <c r="P338">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Q338">
         <v>2.46</v>
@@ -55473,7 +55473,7 @@
         </is>
       </c>
       <c r="AJ338">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK338">
         <v>1.64</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O339">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P339">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="Q339">
         <v>2.8</v>
@@ -55636,7 +55636,7 @@
         </is>
       </c>
       <c r="AJ339">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK339">
         <v>1.55</v>
@@ -55768,7 +55768,7 @@
         <v>6.45</v>
       </c>
       <c r="AA340">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB340">
         <v>3.1</v>
@@ -55895,7 +55895,7 @@
         <v>3.5</v>
       </c>
       <c r="O341">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="P341">
         <v>1.88</v>
@@ -55931,7 +55931,7 @@
         <v>4.1</v>
       </c>
       <c r="AA341">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB341">
         <v>2.1</v>
@@ -56055,7 +56055,7 @@
         </is>
       </c>
       <c r="N342">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O342">
         <v>3.1</v>
@@ -56233,7 +56233,7 @@
         <v>1.95</v>
       </c>
       <c r="S343">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T343">
         <v>2.45</v>
@@ -56381,64 +56381,64 @@
         </is>
       </c>
       <c r="N344">
-        <v>3.32</v>
+        <v>3.56</v>
       </c>
       <c r="O344">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="P344">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q344">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R344">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S344">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T344">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U344">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V344">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W344">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X344">
         <v>0</v>
       </c>
       <c r="Y344">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z344">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AA344">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB344">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AC344">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD344">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE344">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF344">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG344">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH344" t="inlineStr">
         <is>
@@ -56451,10 +56451,10 @@
         </is>
       </c>
       <c r="AJ344">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK344">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL344">
         <v>0</v>
@@ -56544,64 +56544,64 @@
         </is>
       </c>
       <c r="N345">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O345">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="P345">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q345">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R345">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S345">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T345">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U345">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V345">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W345">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X345">
         <v>0</v>
       </c>
       <c r="Y345">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z345">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="AA345">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB345">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC345">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD345">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE345">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF345">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG345">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH345" t="inlineStr">
         <is>
@@ -56614,10 +56614,10 @@
         </is>
       </c>
       <c r="AJ345">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK345">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL345">
         <v>0</v>
@@ -57075,7 +57075,7 @@
         <v>1.58</v>
       </c>
       <c r="AB348">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AC348">
         <v>2.35</v>
@@ -57199,16 +57199,16 @@
         <v>2.61</v>
       </c>
       <c r="O349">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P349">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q349">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="R349">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="S349">
         <v>1.18</v>
@@ -57362,13 +57362,13 @@
         <v>2.65</v>
       </c>
       <c r="O350">
-        <v>3.9</v>
+        <v>3.83</v>
       </c>
       <c r="P350">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q350">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="R350">
         <v>2.4</v>
@@ -57429,10 +57429,10 @@
         </is>
       </c>
       <c r="AJ350">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK350">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL350">
         <v>0</v>
@@ -57691,13 +57691,13 @@
         <v>3.5</v>
       </c>
       <c r="P352">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="Q352">
         <v>2.61</v>
       </c>
       <c r="R352">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S352">
         <v>1.33</v>
@@ -57724,10 +57724,10 @@
         <v>3.8</v>
       </c>
       <c r="AA352">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB352">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC352">
         <v>3.1</v>
@@ -57755,10 +57755,10 @@
         </is>
       </c>
       <c r="AJ352">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK352">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL352">
         <v>0</v>
@@ -57851,7 +57851,7 @@
         <v>3.4</v>
       </c>
       <c r="O353">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="P353">
         <v>2</v>
@@ -57918,7 +57918,7 @@
         </is>
       </c>
       <c r="AJ353">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AK353">
         <v>1.29</v>
@@ -58023,7 +58023,7 @@
         <v>1.9</v>
       </c>
       <c r="R354">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S354">
         <v>1.22</v>
@@ -58174,13 +58174,13 @@
         </is>
       </c>
       <c r="N355">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="O355">
-        <v>4.35</v>
+        <v>4.58</v>
       </c>
       <c r="P355">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q355">
         <v>5.45</v>
@@ -58247,7 +58247,7 @@
         <v>2.5</v>
       </c>
       <c r="AK355">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -58337,10 +58337,10 @@
         </is>
       </c>
       <c r="N356">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O356">
-        <v>3.75</v>
+        <v>3.53</v>
       </c>
       <c r="P356">
         <v>3.6</v>
@@ -58364,7 +58364,7 @@
         <v>1.51</v>
       </c>
       <c r="W356">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X356">
         <v>1.01</v>
@@ -58376,7 +58376,7 @@
         <v>4.2</v>
       </c>
       <c r="AA356">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB356">
         <v>2.2</v>
@@ -58527,7 +58527,7 @@
         <v>1.26</v>
       </c>
       <c r="W357">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X357">
         <v>1.04</v>
@@ -58663,13 +58663,13 @@
         </is>
       </c>
       <c r="N358">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O358">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="P358">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q358">
         <v>3.35</v>
@@ -58826,13 +58826,13 @@
         </is>
       </c>
       <c r="N359">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="O359">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P359">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q359">
         <v>1.3</v>
@@ -58899,7 +58899,7 @@
         <v>1.05</v>
       </c>
       <c r="AK359">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -58992,13 +58992,13 @@
         <v>2.66</v>
       </c>
       <c r="O360">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="P360">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q360">
-        <v>3.07</v>
+        <v>3.24</v>
       </c>
       <c r="R360">
         <v>2.43</v>
@@ -59013,7 +59013,7 @@
         <v>2.05</v>
       </c>
       <c r="V360">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W360">
         <v>1.18</v>
@@ -59028,7 +59028,7 @@
         <v>5.89</v>
       </c>
       <c r="AA360">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB360">
         <v>2.88</v>
@@ -59062,7 +59062,7 @@
         <v>1.6</v>
       </c>
       <c r="AK360">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL360">
         <v>0</v>
@@ -59152,16 +59152,16 @@
         </is>
       </c>
       <c r="N361">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O361">
         <v>4.2</v>
       </c>
       <c r="P361">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q361">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="R361">
         <v>2.54</v>
@@ -59641,10 +59641,10 @@
         </is>
       </c>
       <c r="N364">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="O364">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="P364">
         <v>13</v>
@@ -59653,13 +59653,13 @@
         <v>1.62</v>
       </c>
       <c r="R364">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="S364">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T364">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U364">
         <v>2.18</v>
@@ -59674,19 +59674,19 @@
         <v>1</v>
       </c>
       <c r="Y364">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z364">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="AA364">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AB364">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AC364">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AD364">
         <v>1.46</v>
@@ -59804,13 +59804,13 @@
         </is>
       </c>
       <c r="N365">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O365">
         <v>3</v>
       </c>
       <c r="P365">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q365">
         <v>2.4</v>
@@ -59846,7 +59846,7 @@
         <v>3.1</v>
       </c>
       <c r="AB365">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC365">
         <v>5.6</v>
@@ -59967,64 +59967,64 @@
         </is>
       </c>
       <c r="N366">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O366">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P366">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="Q366">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="R366">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S366">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T366">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U366">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V366">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W366">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X366">
         <v>0</v>
       </c>
       <c r="Y366">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z366">
-        <v>0</v>
+        <v>5.93</v>
       </c>
       <c r="AA366">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB366">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AC366">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD366">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE366">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF366">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG366">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH366" t="inlineStr">
         <is>
@@ -60037,10 +60037,10 @@
         </is>
       </c>
       <c r="AJ366">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK366">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL366">
         <v>0</v>
@@ -60130,64 +60130,64 @@
         </is>
       </c>
       <c r="N367">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O367">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P367">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q367">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R367">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S367">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T367">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U367">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V367">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W367">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X367">
         <v>0</v>
       </c>
       <c r="Y367">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z367">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="AA367">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB367">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC367">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD367">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE367">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF367">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG367">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH367" t="inlineStr">
         <is>
@@ -60200,10 +60200,10 @@
         </is>
       </c>
       <c r="AJ367">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK367">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL367">
         <v>0</v>
@@ -60456,13 +60456,13 @@
         </is>
       </c>
       <c r="N369">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O369">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="P369">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q369">
         <v>2.49</v>
@@ -60471,7 +60471,7 @@
         <v>2.33</v>
       </c>
       <c r="S369">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T369">
         <v>3.9</v>
@@ -60640,10 +60640,10 @@
         <v>2.88</v>
       </c>
       <c r="U370">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V370">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W370">
         <v>1.06</v>
@@ -60673,7 +60673,7 @@
         <v>1.05</v>
       </c>
       <c r="AF370">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG370">
         <v>1.85</v>
@@ -60960,7 +60960,7 @@
         <v>2.15</v>
       </c>
       <c r="S372">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T372">
         <v>2.88</v>
@@ -60984,7 +60984,7 @@
         <v>3.15</v>
       </c>
       <c r="AA372">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AB372">
         <v>1.79</v>
@@ -61108,64 +61108,64 @@
         </is>
       </c>
       <c r="N373">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O373">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P373">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q373">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R373">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S373">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T373">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U373">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V373">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W373">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X373">
         <v>0</v>
       </c>
       <c r="Y373">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z373">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AA373">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB373">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC373">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD373">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE373">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF373">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG373">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH373" t="inlineStr">
         <is>
@@ -61178,10 +61178,10 @@
         </is>
       </c>
       <c r="AJ373">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK373">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL373">
         <v>0</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,65 +1124,65 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
+        <v>1.85</v>
+      </c>
+      <c r="Q5">
+        <v>3.52</v>
+      </c>
+      <c r="R5">
+        <v>2.24</v>
+      </c>
+      <c r="S5">
+        <v>1.3</v>
+      </c>
+      <c r="T5">
+        <v>3.3</v>
+      </c>
+      <c r="U5">
+        <v>2.4</v>
+      </c>
+      <c r="V5">
+        <v>1.5</v>
+      </c>
+      <c r="W5">
+        <v>1.12</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.18</v>
+      </c>
+      <c r="Z5">
+        <v>4.4</v>
+      </c>
+      <c r="AA5">
+        <v>1.64</v>
+      </c>
+      <c r="AB5">
+        <v>2.13</v>
+      </c>
+      <c r="AC5">
+        <v>2.63</v>
+      </c>
+      <c r="AD5">
+        <v>1.44</v>
+      </c>
+      <c r="AE5">
+        <v>1.14</v>
+      </c>
+      <c r="AF5">
+        <v>1.57</v>
+      </c>
+      <c r="AG5">
         <v>2.25</v>
       </c>
-      <c r="Q5">
-        <v>3.3</v>
-      </c>
-      <c r="R5">
-        <v>2.04</v>
-      </c>
-      <c r="S5">
-        <v>1.36</v>
-      </c>
-      <c r="T5">
-        <v>2.59</v>
-      </c>
-      <c r="U5">
-        <v>2.8</v>
-      </c>
-      <c r="V5">
-        <v>1.36</v>
-      </c>
-      <c r="W5">
-        <v>1.08</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>1.3</v>
-      </c>
-      <c r="Z5">
-        <v>3.3</v>
-      </c>
-      <c r="AA5">
-        <v>1.92</v>
-      </c>
-      <c r="AB5">
-        <v>1.8</v>
-      </c>
-      <c r="AC5">
-        <v>3.5</v>
-      </c>
-      <c r="AD5">
-        <v>1.29</v>
-      </c>
-      <c r="AE5">
-        <v>1.1</v>
-      </c>
-      <c r="AF5">
-        <v>1.75</v>
-      </c>
-      <c r="AG5">
-        <v>1.95</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AK5">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
+        <v>3.1</v>
+      </c>
+      <c r="P6">
+        <v>2.25</v>
+      </c>
+      <c r="Q6">
+        <v>3.3</v>
+      </c>
+      <c r="R6">
+        <v>2.04</v>
+      </c>
+      <c r="S6">
+        <v>1.36</v>
+      </c>
+      <c r="T6">
+        <v>2.59</v>
+      </c>
+      <c r="U6">
+        <v>2.8</v>
+      </c>
+      <c r="V6">
+        <v>1.36</v>
+      </c>
+      <c r="W6">
+        <v>1.08</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.3</v>
+      </c>
+      <c r="Z6">
+        <v>3.3</v>
+      </c>
+      <c r="AA6">
+        <v>1.92</v>
+      </c>
+      <c r="AB6">
+        <v>1.8</v>
+      </c>
+      <c r="AC6">
         <v>3.5</v>
       </c>
-      <c r="P6">
-        <v>1.85</v>
-      </c>
-      <c r="Q6">
-        <v>3.52</v>
-      </c>
-      <c r="R6">
-        <v>2.24</v>
-      </c>
-      <c r="S6">
-        <v>1.3</v>
-      </c>
-      <c r="T6">
-        <v>3.3</v>
-      </c>
-      <c r="U6">
-        <v>2.4</v>
-      </c>
-      <c r="V6">
-        <v>1.5</v>
-      </c>
-      <c r="W6">
-        <v>1.12</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.18</v>
-      </c>
-      <c r="Z6">
-        <v>4.4</v>
-      </c>
-      <c r="AA6">
-        <v>1.64</v>
-      </c>
-      <c r="AB6">
-        <v>2.13</v>
-      </c>
-      <c r="AC6">
-        <v>2.63</v>
-      </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="O16">
-        <v>3.58</v>
+        <v>4.64</v>
       </c>
       <c r="P16">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="Q16">
-        <v>3.82</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AB16">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AC16">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.84</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="O17">
-        <v>4.64</v>
+        <v>3.58</v>
       </c>
       <c r="P17">
-        <v>1.46</v>
+        <v>1.98</v>
       </c>
       <c r="Q17">
-        <v>6</v>
+        <v>3.82</v>
       </c>
       <c r="R17">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="S17">
+        <v>1.39</v>
+      </c>
+      <c r="T17">
+        <v>2.68</v>
+      </c>
+      <c r="U17">
+        <v>2.67</v>
+      </c>
+      <c r="V17">
+        <v>1.4</v>
+      </c>
+      <c r="W17">
+        <v>1.08</v>
+      </c>
+      <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
         <v>1.3</v>
       </c>
-      <c r="T17">
-        <v>3.25</v>
-      </c>
-      <c r="U17">
-        <v>2.29</v>
-      </c>
-      <c r="V17">
-        <v>1.5</v>
-      </c>
-      <c r="W17">
-        <v>1.11</v>
-      </c>
-      <c r="X17">
-        <v>1</v>
-      </c>
-      <c r="Y17">
-        <v>1.15</v>
-      </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AC17">
-        <v>2.49</v>
+        <v>3.4</v>
       </c>
       <c r="AD17">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.84</v>
       </c>
       <c r="AK17">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G22">
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
+        <v>1.85</v>
+      </c>
+      <c r="R22">
+        <v>2.4</v>
+      </c>
+      <c r="S22">
+        <v>1.26</v>
+      </c>
+      <c r="T22">
+        <v>3.24</v>
+      </c>
+      <c r="U22">
+        <v>2.38</v>
+      </c>
+      <c r="V22">
+        <v>1.53</v>
+      </c>
+      <c r="W22">
+        <v>1.13</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.2</v>
+      </c>
+      <c r="Z22">
         <v>4.5</v>
       </c>
-      <c r="R22">
-        <v>2.25</v>
-      </c>
-      <c r="S22">
-        <v>1.34</v>
-      </c>
-      <c r="T22">
-        <v>2.95</v>
-      </c>
-      <c r="U22">
-        <v>2.48</v>
-      </c>
-      <c r="V22">
+      <c r="AA22">
+        <v>1.61</v>
+      </c>
+      <c r="AB22">
+        <v>2.13</v>
+      </c>
+      <c r="AC22">
+        <v>2.49</v>
+      </c>
+      <c r="AD22">
         <v>1.42</v>
       </c>
-      <c r="W22">
-        <v>1.08</v>
-      </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.22</v>
-      </c>
-      <c r="Z22">
-        <v>4.1</v>
-      </c>
-      <c r="AA22">
-        <v>1.83</v>
-      </c>
-      <c r="AB22">
-        <v>1.89</v>
-      </c>
-      <c r="AC22">
-        <v>3.1</v>
-      </c>
-      <c r="AD22">
-        <v>1.36</v>
-      </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>1.18</v>
+        <v>2.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P23">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="R23">
         <v>2.15</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="U23">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA23">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AB23">
         <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q24">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
+        <v>1.4</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.25</v>
+      </c>
+      <c r="Z24">
+        <v>3.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.87</v>
+      </c>
+      <c r="AB24">
+        <v>1.85</v>
+      </c>
+      <c r="AC24">
+        <v>3.1</v>
+      </c>
+      <c r="AD24">
+        <v>1.36</v>
+      </c>
+      <c r="AE24">
+        <v>1.1</v>
+      </c>
+      <c r="AF24">
         <v>1.63</v>
       </c>
-      <c r="W24">
-        <v>1.15</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.13</v>
-      </c>
-      <c r="Z24">
-        <v>6</v>
-      </c>
-      <c r="AA24">
-        <v>1.45</v>
-      </c>
-      <c r="AB24">
-        <v>2.54</v>
-      </c>
-      <c r="AC24">
-        <v>2.18</v>
-      </c>
-      <c r="AD24">
-        <v>1.62</v>
-      </c>
-      <c r="AE24">
-        <v>1.29</v>
-      </c>
-      <c r="AF24">
-        <v>1.53</v>
-      </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G25">
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
+        <v>1.08</v>
+      </c>
+      <c r="X25">
+        <v>1.04</v>
+      </c>
+      <c r="Y25">
+        <v>1.22</v>
+      </c>
+      <c r="Z25">
+        <v>4.1</v>
+      </c>
+      <c r="AA25">
+        <v>1.83</v>
+      </c>
+      <c r="AB25">
+        <v>1.89</v>
+      </c>
+      <c r="AC25">
+        <v>3.1</v>
+      </c>
+      <c r="AD25">
+        <v>1.36</v>
+      </c>
+      <c r="AE25">
         <v>1.13</v>
       </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.2</v>
-      </c>
-      <c r="Z25">
-        <v>4.5</v>
-      </c>
-      <c r="AA25">
-        <v>1.61</v>
-      </c>
-      <c r="AB25">
-        <v>2.13</v>
-      </c>
-      <c r="AC25">
-        <v>2.49</v>
-      </c>
-      <c r="AD25">
-        <v>1.42</v>
-      </c>
-      <c r="AE25">
-        <v>1.14</v>
-      </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK25">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="P26">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="Q26">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="R26">
+        <v>2.5</v>
+      </c>
+      <c r="S26">
+        <v>1.22</v>
+      </c>
+      <c r="T26">
+        <v>3.7</v>
+      </c>
+      <c r="U26">
         <v>2.15</v>
       </c>
-      <c r="S26">
-        <v>1.36</v>
-      </c>
-      <c r="T26">
-        <v>2.83</v>
-      </c>
-      <c r="U26">
-        <v>2.7</v>
-      </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z26">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AB26">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AC26">
-        <v>3.08</v>
+        <v>2.18</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AF26">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>5.48</v>
+        <v>5.83</v>
       </c>
       <c r="O40">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q40">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="R40">
         <v>2.2</v>
@@ -6856,7 +6856,7 @@
         <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.05</v>
@@ -6868,10 +6868,10 @@
         <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC40">
         <v>3.5</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK40">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7807,25 +7807,25 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.91</v>
+        <v>3.22</v>
       </c>
       <c r="O46">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="P46">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="Q46">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
         <v>2.5</v>
@@ -7834,7 +7834,7 @@
         <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
         <v>1.02</v>
@@ -7843,28 +7843,28 @@
         <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="AA46">
         <v>1.67</v>
       </c>
       <c r="AB46">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AC46">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AD46">
         <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
+        <v>1.22</v>
+      </c>
+      <c r="AK46">
         <v>1.25</v>
-      </c>
-      <c r="AK46">
-        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -10955,7 +10955,7 @@
         <v>1.23</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
         <v>1.76</v>
@@ -13032,10 +13032,10 @@
         <v>6.65</v>
       </c>
       <c r="Q78">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="R78">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S78">
         <v>1.31</v>
@@ -13050,7 +13050,7 @@
         <v>1.43</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X78">
         <v>1</v>
@@ -19054,7 +19054,7 @@
         </is>
       </c>
       <c r="N115">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="O115">
         <v>3.4</v>
@@ -19063,7 +19063,7 @@
         <v>1.48</v>
       </c>
       <c r="Q115">
-        <v>7.95</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R115">
         <v>1.97</v>
@@ -19081,10 +19081,10 @@
         <v>1.22</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y115">
         <v>1.48</v>
@@ -19099,19 +19099,19 @@
         <v>1.4</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE115">
         <v>0</v>
       </c>
       <c r="AF115">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AG115">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -20358,10 +20358,10 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="O123">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="P123">
         <v>2.9</v>
@@ -21499,7 +21499,7 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="O130">
         <v>3.45</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="O131">
         <v>3.4</v>
       </c>
       <c r="P131">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q131">
         <v>2.96</v>
@@ -21825,10 +21825,10 @@
         </is>
       </c>
       <c r="N132">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O132">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P132">
         <v>3.75</v>
@@ -22154,10 +22154,10 @@
         <v>1.95</v>
       </c>
       <c r="O134">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P134">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q134">
         <v>2.63</v>
@@ -22205,7 +22205,7 @@
         <v>1.04</v>
       </c>
       <c r="AF134">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG134">
         <v>1.8</v>
@@ -22314,13 +22314,13 @@
         </is>
       </c>
       <c r="N135">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="O135">
         <v>3.4</v>
       </c>
       <c r="P135">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q135">
         <v>2.5</v>
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O136">
         <v>3.3</v>
@@ -22643,16 +22643,16 @@
         <v>1.65</v>
       </c>
       <c r="O137">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P137">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q137">
         <v>2.2</v>
       </c>
       <c r="R137">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="S137">
         <v>1.3</v>
@@ -22661,31 +22661,31 @@
         <v>3</v>
       </c>
       <c r="U137">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="V137">
         <v>1.44</v>
       </c>
       <c r="W137">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X137">
         <v>1.01</v>
       </c>
       <c r="Y137">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z137">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA137">
         <v>1.85</v>
       </c>
       <c r="AB137">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC137">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD137">
         <v>1.3</v>
@@ -22713,7 +22713,7 @@
         <v>1.18</v>
       </c>
       <c r="AK137">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,61 +23618,61 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.87</v>
+        <v>4.1</v>
       </c>
       <c r="O143">
+        <v>3.6</v>
+      </c>
+      <c r="P143">
+        <v>1.73</v>
+      </c>
+      <c r="Q143">
+        <v>4</v>
+      </c>
+      <c r="R143">
+        <v>2.18</v>
+      </c>
+      <c r="S143">
+        <v>1.29</v>
+      </c>
+      <c r="T143">
         <v>3.3</v>
       </c>
-      <c r="P143">
-        <v>2.2</v>
-      </c>
-      <c r="Q143">
-        <v>3.14</v>
-      </c>
-      <c r="R143">
-        <v>2.06</v>
-      </c>
-      <c r="S143">
-        <v>1.31</v>
-      </c>
-      <c r="T143">
-        <v>3.1</v>
-      </c>
       <c r="U143">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V143">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W143">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X143">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y143">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z143">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA143">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB143">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC143">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD143">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE143">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF143">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG143">
         <v>2.1</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK143">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,61 +23781,61 @@
         </is>
       </c>
       <c r="N144">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="O144">
+        <v>3.3</v>
+      </c>
+      <c r="P144">
+        <v>2.2</v>
+      </c>
+      <c r="Q144">
+        <v>3.14</v>
+      </c>
+      <c r="R144">
+        <v>2.06</v>
+      </c>
+      <c r="S144">
+        <v>1.31</v>
+      </c>
+      <c r="T144">
+        <v>3.1</v>
+      </c>
+      <c r="U144">
+        <v>2.73</v>
+      </c>
+      <c r="V144">
+        <v>1.47</v>
+      </c>
+      <c r="W144">
+        <v>1.1</v>
+      </c>
+      <c r="X144">
+        <v>1.04</v>
+      </c>
+      <c r="Y144">
+        <v>1.25</v>
+      </c>
+      <c r="Z144">
         <v>3.6</v>
       </c>
-      <c r="P144">
-        <v>1.73</v>
-      </c>
-      <c r="Q144">
-        <v>4</v>
-      </c>
-      <c r="R144">
-        <v>2.18</v>
-      </c>
-      <c r="S144">
-        <v>1.29</v>
-      </c>
-      <c r="T144">
-        <v>3.3</v>
-      </c>
-      <c r="U144">
-        <v>2.5</v>
-      </c>
-      <c r="V144">
-        <v>1.44</v>
-      </c>
-      <c r="W144">
-        <v>1.08</v>
-      </c>
-      <c r="X144">
-        <v>1.03</v>
-      </c>
-      <c r="Y144">
-        <v>1.22</v>
-      </c>
-      <c r="Z144">
-        <v>4.2</v>
-      </c>
       <c r="AA144">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB144">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC144">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD144">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE144">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF144">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG144">
         <v>2.1</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK144">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -25248,10 +25248,10 @@
         </is>
       </c>
       <c r="N153">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O153">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P153">
         <v>3.25</v>
@@ -25278,7 +25278,7 @@
         <v>1.03</v>
       </c>
       <c r="X153">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y153">
         <v>1.4</v>
@@ -25287,19 +25287,19 @@
         <v>2.75</v>
       </c>
       <c r="AA153">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AB153">
         <v>1.61</v>
       </c>
       <c r="AC153">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD153">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE153">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF153">
         <v>1.93</v>
@@ -25321,7 +25321,7 @@
         <v>1.29</v>
       </c>
       <c r="AK153">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -25924,7 +25924,7 @@
         <v>2.5</v>
       </c>
       <c r="V157">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W157">
         <v>1.11</v>
@@ -26063,13 +26063,13 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O158">
         <v>3.5</v>
       </c>
       <c r="P158">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q158">
         <v>3.6</v>
@@ -26552,61 +26552,61 @@
         </is>
       </c>
       <c r="N161">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O161">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P161">
         <v>3.35</v>
       </c>
       <c r="Q161">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R161">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S161">
+        <v>1.2</v>
+      </c>
+      <c r="T161">
+        <v>4.4</v>
+      </c>
+      <c r="U161">
+        <v>1.94</v>
+      </c>
+      <c r="V161">
+        <v>1.7</v>
+      </c>
+      <c r="W161">
         <v>1.22</v>
       </c>
-      <c r="T161">
-        <v>3.9</v>
-      </c>
-      <c r="U161">
-        <v>2.1</v>
-      </c>
-      <c r="V161">
-        <v>1.67</v>
-      </c>
-      <c r="W161">
-        <v>1.18</v>
-      </c>
       <c r="X161">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y161">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z161">
-        <v>5.45</v>
+        <v>7</v>
       </c>
       <c r="AA161">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AB161">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="AC161">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AD161">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AE161">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AF161">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AG161">
         <v>2.7</v>
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="AJ161">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK161">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AL161">
         <v>0</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O162">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P162">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q162">
         <v>2.67</v>
@@ -26917,7 +26917,7 @@
         <v>4.52</v>
       </c>
       <c r="AA163">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB163">
         <v>2.25</v>
@@ -27065,7 +27065,7 @@
         <v>1.99</v>
       </c>
       <c r="V164">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="W164">
         <v>1.2</v>
@@ -27111,7 +27111,7 @@
         </is>
       </c>
       <c r="AJ164">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AK164">
         <v>1.38</v>
@@ -27210,7 +27210,7 @@
         <v>3.68</v>
       </c>
       <c r="P165">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="Q165">
         <v>0</v>
@@ -27367,7 +27367,7 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O166">
         <v>3.9</v>
@@ -27693,28 +27693,28 @@
         </is>
       </c>
       <c r="N168">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="O168">
         <v>5.5</v>
       </c>
       <c r="P168">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Q168">
         <v>9.9</v>
       </c>
       <c r="R168">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S168">
         <v>1.3</v>
       </c>
       <c r="T168">
-        <v>3.26</v>
+        <v>3.14</v>
       </c>
       <c r="U168">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V168">
         <v>1.5</v>
@@ -27723,19 +27723,19 @@
         <v>1.11</v>
       </c>
       <c r="X168">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y168">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z168">
         <v>4.19</v>
       </c>
       <c r="AA168">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB168">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AC168">
         <v>2.68</v>
@@ -27744,7 +27744,7 @@
         <v>1.43</v>
       </c>
       <c r="AE168">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF168">
         <v>2.15</v>
@@ -27763,7 +27763,7 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>3.86</v>
+        <v>1.15</v>
       </c>
       <c r="AK168">
         <v>1.04</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="O169">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P169">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q169">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="R169">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="S169">
+        <v>1.18</v>
+      </c>
+      <c r="T169">
+        <v>4.5</v>
+      </c>
+      <c r="U169">
+        <v>2.08</v>
+      </c>
+      <c r="V169">
+        <v>1.75</v>
+      </c>
+      <c r="W169">
         <v>1.22</v>
-      </c>
-      <c r="T169">
-        <v>4</v>
-      </c>
-      <c r="U169">
-        <v>2.17</v>
-      </c>
-      <c r="V169">
-        <v>1.71</v>
-      </c>
-      <c r="W169">
-        <v>1.18</v>
       </c>
       <c r="X169">
         <v>1</v>
       </c>
       <c r="Y169">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z169">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA169">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB169">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AC169">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AD169">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AE169">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF169">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AG169">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AK169">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>1.82</v>
+        <v>3</v>
       </c>
       <c r="O170">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P170">
-        <v>3.76</v>
+        <v>2.17</v>
       </c>
       <c r="Q170">
-        <v>2.22</v>
+        <v>3.08</v>
       </c>
       <c r="R170">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="S170">
+        <v>1.22</v>
+      </c>
+      <c r="T170">
+        <v>4</v>
+      </c>
+      <c r="U170">
+        <v>2.17</v>
+      </c>
+      <c r="V170">
+        <v>1.71</v>
+      </c>
+      <c r="W170">
         <v>1.18</v>
-      </c>
-      <c r="T170">
-        <v>4.8</v>
-      </c>
-      <c r="U170">
-        <v>1.85</v>
-      </c>
-      <c r="V170">
-        <v>1.91</v>
-      </c>
-      <c r="W170">
-        <v>1.29</v>
       </c>
       <c r="X170">
         <v>1</v>
       </c>
       <c r="Y170">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z170">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA170">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AB170">
-        <v>3.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC170">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="AD170">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AE170">
+        <v>1.25</v>
+      </c>
+      <c r="AF170">
         <v>1.44</v>
       </c>
-      <c r="AF170">
-        <v>1.29</v>
-      </c>
       <c r="AG170">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AK170">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="O171">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P171">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="Q171">
-        <v>2.52</v>
+        <v>2.22</v>
       </c>
       <c r="R171">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S171">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="T171">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="U171">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="V171">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="W171">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="X171">
         <v>1</v>
       </c>
       <c r="Y171">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z171">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA171">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="AB171">
-        <v>2.53</v>
+        <v>3.52</v>
       </c>
       <c r="AC171">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="AD171">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AE171">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AF171">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG171">
-        <v>2.58</v>
+        <v>3.1</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK171">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>2.71</v>
+        <v>1.95</v>
       </c>
       <c r="O172">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P172">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q172">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="R172">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S172">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="T172">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U172">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V172">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W172">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X172">
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z172">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA172">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AB172">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="AC172">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="AD172">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="AE172">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF172">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AG172">
-        <v>2.98</v>
+        <v>2.58</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>1.27</v>
       </c>
       <c r="AK172">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="N175">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O175">
         <v>3.05</v>
@@ -28965,12 +28965,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G176">
@@ -28997,64 +28997,64 @@
         </is>
       </c>
       <c r="N176">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="O176">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P176">
-        <v>2.95</v>
+        <v>4.5</v>
       </c>
       <c r="Q176">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="R176">
+        <v>2.41</v>
+      </c>
+      <c r="S176">
+        <v>1.2</v>
+      </c>
+      <c r="T176">
+        <v>4.33</v>
+      </c>
+      <c r="U176">
         <v>2.14</v>
       </c>
-      <c r="S176">
+      <c r="V176">
+        <v>1.73</v>
+      </c>
+      <c r="W176">
+        <v>1.2</v>
+      </c>
+      <c r="X176">
+        <v>1</v>
+      </c>
+      <c r="Y176">
+        <v>1.08</v>
+      </c>
+      <c r="Z176">
+        <v>7</v>
+      </c>
+      <c r="AA176">
         <v>1.4</v>
       </c>
-      <c r="T176">
-        <v>2.88</v>
-      </c>
-      <c r="U176">
-        <v>2.5</v>
-      </c>
-      <c r="V176">
+      <c r="AB176">
+        <v>3</v>
+      </c>
+      <c r="AC176">
+        <v>2.12</v>
+      </c>
+      <c r="AD176">
+        <v>1.82</v>
+      </c>
+      <c r="AE176">
+        <v>1.32</v>
+      </c>
+      <c r="AF176">
         <v>1.44</v>
       </c>
-      <c r="W176">
-        <v>1.07</v>
-      </c>
-      <c r="X176">
-        <v>1.03</v>
-      </c>
-      <c r="Y176">
-        <v>1.25</v>
-      </c>
-      <c r="Z176">
-        <v>3.7</v>
-      </c>
-      <c r="AA176">
-        <v>1.87</v>
-      </c>
-      <c r="AB176">
-        <v>1.9</v>
-      </c>
-      <c r="AC176">
-        <v>3.21</v>
-      </c>
-      <c r="AD176">
-        <v>1.33</v>
-      </c>
-      <c r="AE176">
-        <v>1.09</v>
-      </c>
-      <c r="AF176">
-        <v>1.67</v>
-      </c>
       <c r="AG176">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AH176" t="inlineStr">
         <is>
@@ -29067,10 +29067,10 @@
         </is>
       </c>
       <c r="AJ176">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK176">
-        <v>1.67</v>
+        <v>2.19</v>
       </c>
       <c r="AL176">
         <v>0</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,25 +29160,25 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O177">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P177">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q177">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="R177">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T177">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U177">
         <v>2.5</v>
@@ -29187,37 +29187,37 @@
         <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z177">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA177">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AB177">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AC177">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="AD177">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE177">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF177">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG177">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,80 +29323,80 @@
         </is>
       </c>
       <c r="N178">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="O178">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="P178">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q178">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="R178">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="S178">
+        <v>1.3</v>
+      </c>
+      <c r="T178">
+        <v>3.25</v>
+      </c>
+      <c r="U178">
+        <v>2.5</v>
+      </c>
+      <c r="V178">
+        <v>1.44</v>
+      </c>
+      <c r="W178">
+        <v>1.11</v>
+      </c>
+      <c r="X178">
+        <v>1.01</v>
+      </c>
+      <c r="Y178">
         <v>1.2</v>
       </c>
-      <c r="T178">
-        <v>4.33</v>
-      </c>
-      <c r="U178">
-        <v>2.14</v>
-      </c>
-      <c r="V178">
+      <c r="Z178">
+        <v>4.2</v>
+      </c>
+      <c r="AA178">
+        <v>1.72</v>
+      </c>
+      <c r="AB178">
+        <v>2.16</v>
+      </c>
+      <c r="AC178">
+        <v>2.9</v>
+      </c>
+      <c r="AD178">
+        <v>1.44</v>
+      </c>
+      <c r="AE178">
+        <v>1.16</v>
+      </c>
+      <c r="AF178">
+        <v>1.57</v>
+      </c>
+      <c r="AG178">
+        <v>2.25</v>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ178">
+        <v>1.25</v>
+      </c>
+      <c r="AK178">
         <v>1.73</v>
-      </c>
-      <c r="W178">
-        <v>1.2</v>
-      </c>
-      <c r="X178">
-        <v>1</v>
-      </c>
-      <c r="Y178">
-        <v>1.08</v>
-      </c>
-      <c r="Z178">
-        <v>7</v>
-      </c>
-      <c r="AA178">
-        <v>1.4</v>
-      </c>
-      <c r="AB178">
-        <v>3</v>
-      </c>
-      <c r="AC178">
-        <v>2.12</v>
-      </c>
-      <c r="AD178">
-        <v>1.82</v>
-      </c>
-      <c r="AE178">
-        <v>1.32</v>
-      </c>
-      <c r="AF178">
-        <v>1.44</v>
-      </c>
-      <c r="AG178">
-        <v>2.7</v>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ178">
-        <v>1.17</v>
-      </c>
-      <c r="AK178">
-        <v>2.19</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,64 +31768,64 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="O193">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P193">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q193">
-        <v>2.14</v>
+        <v>2.61</v>
       </c>
       <c r="R193">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="S193">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T193">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="U193">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="V193">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W193">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X193">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y193">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z193">
-        <v>4.45</v>
+        <v>2.79</v>
       </c>
       <c r="AA193">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB193">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC193">
-        <v>2.52</v>
+        <v>3.82</v>
       </c>
       <c r="AD193">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AE193">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF193">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AG193">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AK193">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,80 +31931,80 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="O194">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P194">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q194">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="R194">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="S194">
+        <v>1.3</v>
+      </c>
+      <c r="T194">
+        <v>3.3</v>
+      </c>
+      <c r="U194">
+        <v>2.3</v>
+      </c>
+      <c r="V194">
+        <v>1.47</v>
+      </c>
+      <c r="W194">
+        <v>1.12</v>
+      </c>
+      <c r="X194">
+        <v>1.03</v>
+      </c>
+      <c r="Y194">
+        <v>1.2</v>
+      </c>
+      <c r="Z194">
+        <v>4.1</v>
+      </c>
+      <c r="AA194">
+        <v>1.73</v>
+      </c>
+      <c r="AB194">
+        <v>2.1</v>
+      </c>
+      <c r="AC194">
+        <v>2.7</v>
+      </c>
+      <c r="AD194">
+        <v>1.36</v>
+      </c>
+      <c r="AE194">
+        <v>1.13</v>
+      </c>
+      <c r="AF194">
+        <v>1.55</v>
+      </c>
+      <c r="AG194">
+        <v>2.25</v>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ194">
+        <v>1.22</v>
+      </c>
+      <c r="AK194">
         <v>1.45</v>
-      </c>
-      <c r="T194">
-        <v>2.51</v>
-      </c>
-      <c r="U194">
-        <v>3.2</v>
-      </c>
-      <c r="V194">
-        <v>1.3</v>
-      </c>
-      <c r="W194">
-        <v>1.05</v>
-      </c>
-      <c r="X194">
-        <v>1.04</v>
-      </c>
-      <c r="Y194">
-        <v>1.37</v>
-      </c>
-      <c r="Z194">
-        <v>2.79</v>
-      </c>
-      <c r="AA194">
-        <v>2.15</v>
-      </c>
-      <c r="AB194">
-        <v>1.67</v>
-      </c>
-      <c r="AC194">
-        <v>3.82</v>
-      </c>
-      <c r="AD194">
-        <v>1.22</v>
-      </c>
-      <c r="AE194">
-        <v>1.07</v>
-      </c>
-      <c r="AF194">
-        <v>1.83</v>
-      </c>
-      <c r="AG194">
-        <v>1.85</v>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ194">
-        <v>1.35</v>
-      </c>
-      <c r="AK194">
-        <v>1.65</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,65 +32094,65 @@
         </is>
       </c>
       <c r="N195">
+        <v>1.7</v>
+      </c>
+      <c r="O195">
+        <v>4</v>
+      </c>
+      <c r="P195">
+        <v>4.5</v>
+      </c>
+      <c r="Q195">
+        <v>2.14</v>
+      </c>
+      <c r="R195">
+        <v>2.5</v>
+      </c>
+      <c r="S195">
+        <v>1.25</v>
+      </c>
+      <c r="T195">
+        <v>3.6</v>
+      </c>
+      <c r="U195">
+        <v>2.19</v>
+      </c>
+      <c r="V195">
+        <v>1.55</v>
+      </c>
+      <c r="W195">
+        <v>1.13</v>
+      </c>
+      <c r="X195">
+        <v>1.01</v>
+      </c>
+      <c r="Y195">
+        <v>1.14</v>
+      </c>
+      <c r="Z195">
+        <v>4.45</v>
+      </c>
+      <c r="AA195">
+        <v>1.57</v>
+      </c>
+      <c r="AB195">
+        <v>2.38</v>
+      </c>
+      <c r="AC195">
+        <v>2.52</v>
+      </c>
+      <c r="AD195">
+        <v>1.51</v>
+      </c>
+      <c r="AE195">
+        <v>1.19</v>
+      </c>
+      <c r="AF195">
+        <v>1.53</v>
+      </c>
+      <c r="AG195">
         <v>2.3</v>
       </c>
-      <c r="O195">
-        <v>3.4</v>
-      </c>
-      <c r="P195">
-        <v>2.69</v>
-      </c>
-      <c r="Q195">
-        <v>2.74</v>
-      </c>
-      <c r="R195">
-        <v>2.18</v>
-      </c>
-      <c r="S195">
-        <v>1.3</v>
-      </c>
-      <c r="T195">
-        <v>3.3</v>
-      </c>
-      <c r="U195">
-        <v>2.3</v>
-      </c>
-      <c r="V195">
-        <v>1.47</v>
-      </c>
-      <c r="W195">
-        <v>1.12</v>
-      </c>
-      <c r="X195">
-        <v>1.03</v>
-      </c>
-      <c r="Y195">
-        <v>1.2</v>
-      </c>
-      <c r="Z195">
-        <v>4.1</v>
-      </c>
-      <c r="AA195">
-        <v>1.73</v>
-      </c>
-      <c r="AB195">
-        <v>2.1</v>
-      </c>
-      <c r="AC195">
-        <v>2.7</v>
-      </c>
-      <c r="AD195">
-        <v>1.36</v>
-      </c>
-      <c r="AE195">
-        <v>1.13</v>
-      </c>
-      <c r="AF195">
-        <v>1.55</v>
-      </c>
-      <c r="AG195">
-        <v>2.25</v>
-      </c>
       <c r="AH195" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK195">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -33893,7 +33893,7 @@
         <v>3.5</v>
       </c>
       <c r="P206">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q206">
         <v>3.6</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O211">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P211">
-        <v>4.1</v>
+        <v>4.79</v>
       </c>
       <c r="Q211">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="R211">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="S211">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T211">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="U211">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="V211">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W211">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X211">
         <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z211">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA211">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB211">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AC211">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="AD211">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AE211">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF211">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG211">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK211">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="O212">
         <v>4</v>
       </c>
       <c r="P212">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
       <c r="Q212">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R212">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S212">
         <v>1.25</v>
       </c>
       <c r="T212">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U212">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V212">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W212">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X212">
         <v>1.02</v>
       </c>
       <c r="Y212">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z212">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA212">
+        <v>1.57</v>
+      </c>
+      <c r="AB212">
+        <v>2.42</v>
+      </c>
+      <c r="AC212">
+        <v>2.25</v>
+      </c>
+      <c r="AD212">
         <v>1.6</v>
       </c>
-      <c r="AB212">
-        <v>2.3</v>
-      </c>
-      <c r="AC212">
-        <v>2.63</v>
-      </c>
-      <c r="AD212">
-        <v>1.47</v>
-      </c>
       <c r="AE212">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF212">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG212">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK212">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,31 +35191,31 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="O214">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P214">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q214">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="R214">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="S214">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T214">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="U214">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V214">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="W214">
         <v>1.15</v>
@@ -35224,31 +35224,31 @@
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z214">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA214">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB214">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC214">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AD214">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE214">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF214">
         <v>1.5</v>
       </c>
       <c r="AG214">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>1.17</v>
       </c>
       <c r="AK214">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,31 +35354,31 @@
         </is>
       </c>
       <c r="N215">
-        <v>1.78</v>
+        <v>2.87</v>
       </c>
       <c r="O215">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P215">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q215">
-        <v>2.23</v>
+        <v>3.02</v>
       </c>
       <c r="R215">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="S215">
         <v>1.35</v>
       </c>
       <c r="T215">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U215">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="V215">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W215">
         <v>1.07</v>
@@ -35387,31 +35387,31 @@
         <v>1.02</v>
       </c>
       <c r="Y215">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z215">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="AA215">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AB215">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AC215">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="AD215">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE215">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF215">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AG215">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="AK215">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,31 +35517,31 @@
         </is>
       </c>
       <c r="N216">
-        <v>2.87</v>
+        <v>1.78</v>
       </c>
       <c r="O216">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P216">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q216">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="R216">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S216">
         <v>1.35</v>
       </c>
       <c r="T216">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U216">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="V216">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W216">
         <v>1.07</v>
@@ -35550,31 +35550,31 @@
         <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z216">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="AA216">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AB216">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC216">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="AD216">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE216">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF216">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AG216">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="AK216">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -36332,16 +36332,16 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O221">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P221">
-        <v>2.67</v>
+        <v>2.81</v>
       </c>
       <c r="Q221">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R221">
         <v>2.25</v>
@@ -36368,10 +36368,10 @@
         <v>1.17</v>
       </c>
       <c r="Z221">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="AA221">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AB221">
         <v>2</v>
@@ -36380,10 +36380,10 @@
         <v>2.8</v>
       </c>
       <c r="AD221">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE221">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF221">
         <v>1.56</v>
@@ -36405,7 +36405,7 @@
         <v>1.3</v>
       </c>
       <c r="AK221">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL221">
         <v>0</v>
@@ -37441,12 +37441,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G228">
@@ -37473,64 +37473,64 @@
         </is>
       </c>
       <c r="N228">
-        <v>3.51</v>
+        <v>2.36</v>
       </c>
       <c r="O228">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="P228">
-        <v>1.86</v>
+        <v>2.73</v>
       </c>
       <c r="Q228">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="R228">
-        <v>2.45</v>
+        <v>2.24</v>
       </c>
       <c r="S228">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T228">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="U228">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="V228">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="W228">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X228">
         <v>1.02</v>
       </c>
       <c r="Y228">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z228">
-        <v>5.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA228">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AB228">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AC228">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="AD228">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="AE228">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AF228">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AG228">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="AH228" t="inlineStr">
         <is>
@@ -37543,10 +37543,10 @@
         </is>
       </c>
       <c r="AJ228">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK228">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37604,12 +37604,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G229">
@@ -37636,80 +37636,80 @@
         </is>
       </c>
       <c r="N229">
-        <v>2.36</v>
+        <v>3.51</v>
       </c>
       <c r="O229">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P229">
-        <v>2.73</v>
+        <v>1.86</v>
       </c>
       <c r="Q229">
-        <v>2.57</v>
+        <v>3.1</v>
       </c>
       <c r="R229">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="S229">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T229">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="U229">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="V229">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="W229">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X229">
         <v>1.02</v>
       </c>
       <c r="Y229">
+        <v>1.08</v>
+      </c>
+      <c r="Z229">
+        <v>5.45</v>
+      </c>
+      <c r="AA229">
+        <v>1.41</v>
+      </c>
+      <c r="AB229">
+        <v>2.62</v>
+      </c>
+      <c r="AC229">
+        <v>2.02</v>
+      </c>
+      <c r="AD229">
+        <v>1.74</v>
+      </c>
+      <c r="AE229">
+        <v>1.31</v>
+      </c>
+      <c r="AF229">
+        <v>1.36</v>
+      </c>
+      <c r="AG229">
+        <v>2.8</v>
+      </c>
+      <c r="AH229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI229" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ229">
         <v>1.22</v>
       </c>
-      <c r="Z229">
-        <v>3.7</v>
-      </c>
-      <c r="AA229">
-        <v>1.66</v>
-      </c>
-      <c r="AB229">
-        <v>2.15</v>
-      </c>
-      <c r="AC229">
-        <v>2.59</v>
-      </c>
-      <c r="AD229">
-        <v>1.45</v>
-      </c>
-      <c r="AE229">
-        <v>1.18</v>
-      </c>
-      <c r="AF229">
-        <v>1.56</v>
-      </c>
-      <c r="AG229">
-        <v>2.24</v>
-      </c>
-      <c r="AH229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI229" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ229">
+      <c r="AK229">
         <v>1.3</v>
-      </c>
-      <c r="AK229">
-        <v>1.58</v>
       </c>
       <c r="AL229">
         <v>0</v>
@@ -38940,19 +38940,19 @@
         </is>
       </c>
       <c r="N237">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="O237">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P237">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q237">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="R237">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S237">
         <v>1.33</v>
@@ -38961,7 +38961,7 @@
         <v>2.9</v>
       </c>
       <c r="U237">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V237">
         <v>1.44</v>
@@ -38979,25 +38979,25 @@
         <v>3.58</v>
       </c>
       <c r="AA237">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AB237">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AC237">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AD237">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE237">
         <v>1.09</v>
       </c>
       <c r="AF237">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG237">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH237" t="inlineStr">
         <is>
@@ -39010,10 +39010,10 @@
         </is>
       </c>
       <c r="AJ237">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK237">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AL237">
         <v>0</v>
@@ -39266,10 +39266,10 @@
         </is>
       </c>
       <c r="N239">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O239">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P239">
         <v>2.62</v>
@@ -41717,7 +41717,7 @@
         <v>8</v>
       </c>
       <c r="P254">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q254">
         <v>1.43</v>
@@ -43030,13 +43030,13 @@
         <v>2.03</v>
       </c>
       <c r="S262">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T262">
         <v>2.86</v>
       </c>
       <c r="U262">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="V262">
         <v>1.44</v>
@@ -44319,19 +44319,19 @@
         </is>
       </c>
       <c r="N270">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O270">
         <v>3.6</v>
       </c>
       <c r="P270">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q270">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="R270">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S270">
         <v>1.16</v>
@@ -44340,10 +44340,10 @@
         <v>4.6</v>
       </c>
       <c r="U270">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V270">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W270">
         <v>1.23</v>
@@ -44358,25 +44358,25 @@
         <v>6.6</v>
       </c>
       <c r="AA270">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AB270">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AC270">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD270">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE270">
         <v>1.31</v>
       </c>
       <c r="AF270">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AG270">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="AH270" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>1.19</v>
       </c>
       <c r="AK270">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AL270">
         <v>0</v>
@@ -46305,7 +46305,7 @@
         <v>1.07</v>
       </c>
       <c r="X282">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y282">
         <v>1.28</v>
@@ -46314,19 +46314,19 @@
         <v>3.08</v>
       </c>
       <c r="AA282">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB282">
         <v>1.74</v>
       </c>
       <c r="AC282">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AD282">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE282">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF282">
         <v>1.72</v>
@@ -47757,10 +47757,10 @@
         <v>2.39</v>
       </c>
       <c r="S291">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T291">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U291">
         <v>2.05</v>
@@ -47787,7 +47787,7 @@
         <v>2.63</v>
       </c>
       <c r="AC291">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AD291">
         <v>1.66</v>
@@ -48557,13 +48557,13 @@
         </is>
       </c>
       <c r="N296">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O296">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P296">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q296">
         <v>2.4</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="O297">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P297">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="Q297">
         <v>2.89</v>
@@ -48916,22 +48916,22 @@
         <v>1.02</v>
       </c>
       <c r="Y298">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z298">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="AA298">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB298">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC298">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="AD298">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE298">
         <v>1.12</v>
@@ -49049,7 +49049,7 @@
         <v>1.25</v>
       </c>
       <c r="O299">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="P299">
         <v>7.9</v>
@@ -49061,7 +49061,7 @@
         <v>2.57</v>
       </c>
       <c r="S299">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T299">
         <v>3.6</v>
@@ -49079,7 +49079,7 @@
         <v>1.02</v>
       </c>
       <c r="Y299">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z299">
         <v>4.55</v>
@@ -49100,10 +49100,10 @@
         <v>1.2</v>
       </c>
       <c r="AF299">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG299">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH299" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>5.5</v>
       </c>
       <c r="O300">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="P300">
         <v>1.53</v>
@@ -49378,7 +49378,7 @@
         <v>3.9</v>
       </c>
       <c r="P301">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q301">
         <v>2.08</v>
@@ -49402,28 +49402,28 @@
         <v>1.13</v>
       </c>
       <c r="X301">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y301">
         <v>1.2</v>
       </c>
       <c r="Z301">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA301">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB301">
         <v>2.05</v>
       </c>
       <c r="AC301">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD301">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE301">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF301">
         <v>1.62</v>
@@ -50359,7 +50359,7 @@
         <v>10</v>
       </c>
       <c r="Q307">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="R307">
         <v>2.62</v>
@@ -50380,28 +50380,28 @@
         <v>1.15</v>
       </c>
       <c r="X307">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y307">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z307">
-        <v>4.93</v>
+        <v>5</v>
       </c>
       <c r="AA307">
         <v>1.53</v>
       </c>
       <c r="AB307">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC307">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AD307">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE307">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF307">
         <v>2</v>
@@ -50537,7 +50537,7 @@
         <v>1.76</v>
       </c>
       <c r="V308">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="W308">
         <v>1.3</v>
@@ -50586,7 +50586,7 @@
         <v>1.1</v>
       </c>
       <c r="AK308">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AL308">
         <v>0</v>
@@ -50839,13 +50839,13 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="O310">
         <v>4</v>
       </c>
       <c r="P310">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="Q310">
         <v>2.5</v>
@@ -51005,10 +51005,10 @@
         <v>1.09</v>
       </c>
       <c r="O311">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="P311">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="Q311">
         <v>1.24</v>
@@ -51029,7 +51029,7 @@
         <v>2.5</v>
       </c>
       <c r="W311">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="X311">
         <v>1</v>
@@ -51044,7 +51044,7 @@
         <v>1.11</v>
       </c>
       <c r="AB311">
-        <v>6.5</v>
+        <v>6.58</v>
       </c>
       <c r="AC311">
         <v>1.26</v>
@@ -51053,7 +51053,7 @@
         <v>3.2</v>
       </c>
       <c r="AE311">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AF311">
         <v>1.65</v>
@@ -51075,7 +51075,7 @@
         <v>1.01</v>
       </c>
       <c r="AK311">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G319">
@@ -52306,64 +52306,64 @@
         </is>
       </c>
       <c r="N319">
-        <v>7.5</v>
+        <v>1.61</v>
       </c>
       <c r="O319">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P319">
-        <v>1.38</v>
+        <v>4.6</v>
       </c>
       <c r="Q319">
-        <v>7.51</v>
+        <v>2.17</v>
       </c>
       <c r="R319">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="S319">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="T319">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U319">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="V319">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W319">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X319">
         <v>1.02</v>
       </c>
       <c r="Y319">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z319">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA319">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB319">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC319">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AD319">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE319">
         <v>1.04</v>
       </c>
       <c r="AF319">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="AG319">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
@@ -52376,10 +52376,10 @@
         </is>
       </c>
       <c r="AJ319">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK319">
-        <v>1.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,80 +52632,80 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.61</v>
+        <v>9.9</v>
       </c>
       <c r="O321">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P321">
-        <v>4.6</v>
+        <v>1.33</v>
       </c>
       <c r="Q321">
-        <v>2.17</v>
+        <v>10</v>
       </c>
       <c r="R321">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S321">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T321">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="U321">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="V321">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W321">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X321">
+        <v>1.07</v>
+      </c>
+      <c r="Y321">
+        <v>1.44</v>
+      </c>
+      <c r="Z321">
+        <v>2.7</v>
+      </c>
+      <c r="AA321">
+        <v>2.35</v>
+      </c>
+      <c r="AB321">
+        <v>1.51</v>
+      </c>
+      <c r="AC321">
+        <v>4.5</v>
+      </c>
+      <c r="AD321">
+        <v>1.16</v>
+      </c>
+      <c r="AE321">
+        <v>1.05</v>
+      </c>
+      <c r="AF321">
+        <v>2.88</v>
+      </c>
+      <c r="AG321">
+        <v>1.3</v>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ321">
+        <v>3.1</v>
+      </c>
+      <c r="AK321">
         <v>1.02</v>
-      </c>
-      <c r="Y321">
-        <v>1.31</v>
-      </c>
-      <c r="Z321">
-        <v>2.92</v>
-      </c>
-      <c r="AA321">
-        <v>2.15</v>
-      </c>
-      <c r="AB321">
-        <v>1.68</v>
-      </c>
-      <c r="AC321">
-        <v>3.5</v>
-      </c>
-      <c r="AD321">
-        <v>1.23</v>
-      </c>
-      <c r="AE321">
-        <v>1.04</v>
-      </c>
-      <c r="AF321">
-        <v>2</v>
-      </c>
-      <c r="AG321">
-        <v>1.71</v>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ321">
-        <v>1.29</v>
-      </c>
-      <c r="AK321">
-        <v>2.1</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,64 +52795,64 @@
         </is>
       </c>
       <c r="N322">
-        <v>9.9</v>
+        <v>7.5</v>
       </c>
       <c r="O322">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P322">
+        <v>1.38</v>
+      </c>
+      <c r="Q322">
+        <v>7.51</v>
+      </c>
+      <c r="R322">
+        <v>2.28</v>
+      </c>
+      <c r="S322">
+        <v>1.38</v>
+      </c>
+      <c r="T322">
+        <v>2.75</v>
+      </c>
+      <c r="U322">
+        <v>2.96</v>
+      </c>
+      <c r="V322">
         <v>1.33</v>
       </c>
-      <c r="Q322">
-        <v>10</v>
-      </c>
-      <c r="R322">
-        <v>2.2</v>
-      </c>
-      <c r="S322">
-        <v>1.45</v>
-      </c>
-      <c r="T322">
-        <v>2.51</v>
-      </c>
-      <c r="U322">
-        <v>3.1</v>
-      </c>
-      <c r="V322">
-        <v>1.29</v>
-      </c>
       <c r="W322">
+        <v>1.07</v>
+      </c>
+      <c r="X322">
+        <v>1.02</v>
+      </c>
+      <c r="Y322">
+        <v>1.3</v>
+      </c>
+      <c r="Z322">
+        <v>2.97</v>
+      </c>
+      <c r="AA322">
+        <v>2.1</v>
+      </c>
+      <c r="AB322">
+        <v>1.69</v>
+      </c>
+      <c r="AC322">
+        <v>3.38</v>
+      </c>
+      <c r="AD322">
+        <v>1.22</v>
+      </c>
+      <c r="AE322">
         <v>1.04</v>
       </c>
-      <c r="X322">
-        <v>1.07</v>
-      </c>
-      <c r="Y322">
-        <v>1.44</v>
-      </c>
-      <c r="Z322">
-        <v>2.7</v>
-      </c>
-      <c r="AA322">
-        <v>2.35</v>
-      </c>
-      <c r="AB322">
-        <v>1.51</v>
-      </c>
-      <c r="AC322">
-        <v>4.5</v>
-      </c>
-      <c r="AD322">
-        <v>1.16</v>
-      </c>
-      <c r="AE322">
-        <v>1.05</v>
-      </c>
       <c r="AF322">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="AG322">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
@@ -52865,10 +52865,10 @@
         </is>
       </c>
       <c r="AJ322">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="AK322">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -57848,13 +57848,13 @@
         </is>
       </c>
       <c r="N353">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O353">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P353">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q353">
         <v>3.75</v>
@@ -58011,7 +58011,7 @@
         </is>
       </c>
       <c r="N354">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="O354">
         <v>4.5</v>
@@ -58244,7 +58244,7 @@
         </is>
       </c>
       <c r="AJ355">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK355">
         <v>2.3</v>
@@ -59025,25 +59025,25 @@
         <v>1.1</v>
       </c>
       <c r="Z360">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA360">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB360">
         <v>2.88</v>
       </c>
       <c r="AC360">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD360">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE360">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF360">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG360">
         <v>2.7</v>
@@ -59152,13 +59152,13 @@
         </is>
       </c>
       <c r="N361">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O361">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="P361">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Q361">
         <v>2.09</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>3.1</v>
+      </c>
+      <c r="O5">
         <v>3.4</v>
       </c>
-      <c r="O5">
+      <c r="P5">
+        <v>2.05</v>
+      </c>
+      <c r="Q5">
         <v>3.5</v>
       </c>
-      <c r="P5">
-        <v>1.85</v>
-      </c>
-      <c r="Q5">
-        <v>3.52</v>
-      </c>
       <c r="R5">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA5">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AB5">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AD5">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="S7">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
+        <v>1.5</v>
+      </c>
+      <c r="W7">
+        <v>1.12</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.18</v>
+      </c>
+      <c r="Z7">
+        <v>4.4</v>
+      </c>
+      <c r="AA7">
+        <v>1.64</v>
+      </c>
+      <c r="AB7">
+        <v>2.13</v>
+      </c>
+      <c r="AC7">
+        <v>2.63</v>
+      </c>
+      <c r="AD7">
         <v>1.44</v>
       </c>
-      <c r="W7">
-        <v>1.06</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>1.25</v>
-      </c>
-      <c r="Z7">
-        <v>3.6</v>
-      </c>
-      <c r="AA7">
-        <v>1.79</v>
-      </c>
-      <c r="AB7">
+      <c r="AE7">
+        <v>1.14</v>
+      </c>
+      <c r="AF7">
+        <v>1.57</v>
+      </c>
+      <c r="AG7">
+        <v>2.25</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.88</v>
       </c>
-      <c r="AC7">
-        <v>3.1</v>
-      </c>
-      <c r="AD7">
-        <v>1.33</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.65</v>
-      </c>
-      <c r="AG7">
-        <v>2.1</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.65</v>
-      </c>
       <c r="AK7">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q24">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R24">
+        <v>2.5</v>
+      </c>
+      <c r="S24">
+        <v>1.22</v>
+      </c>
+      <c r="T24">
+        <v>3.7</v>
+      </c>
+      <c r="U24">
         <v>2.15</v>
       </c>
-      <c r="S24">
-        <v>1.33</v>
-      </c>
-      <c r="T24">
-        <v>3</v>
-      </c>
-      <c r="U24">
-        <v>2.75</v>
-      </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AC24">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AF24">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="O26">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P26">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
+        <v>1.4</v>
+      </c>
+      <c r="W26">
+        <v>1.1</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1.25</v>
+      </c>
+      <c r="Z26">
+        <v>3.8</v>
+      </c>
+      <c r="AA26">
+        <v>1.87</v>
+      </c>
+      <c r="AB26">
+        <v>1.85</v>
+      </c>
+      <c r="AC26">
+        <v>3.1</v>
+      </c>
+      <c r="AD26">
+        <v>1.36</v>
+      </c>
+      <c r="AE26">
+        <v>1.1</v>
+      </c>
+      <c r="AF26">
         <v>1.63</v>
       </c>
-      <c r="W26">
-        <v>1.15</v>
-      </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>1.13</v>
-      </c>
-      <c r="Z26">
-        <v>6</v>
-      </c>
-      <c r="AA26">
-        <v>1.45</v>
-      </c>
-      <c r="AB26">
-        <v>2.54</v>
-      </c>
-      <c r="AC26">
-        <v>2.18</v>
-      </c>
-      <c r="AD26">
-        <v>1.62</v>
-      </c>
-      <c r="AE26">
-        <v>1.29</v>
-      </c>
-      <c r="AF26">
-        <v>1.53</v>
-      </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5866,10 +5866,10 @@
         <v>2.09</v>
       </c>
       <c r="S34">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="U34">
         <v>2.45</v>
@@ -5893,7 +5893,7 @@
         <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC34">
         <v>3.1</v>
@@ -5905,10 +5905,10 @@
         <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG34">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
         <v>1.62</v>
@@ -6020,7 +6020,7 @@
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q35">
         <v>2.47</v>
@@ -6053,16 +6053,16 @@
         <v>3.94</v>
       </c>
       <c r="AA35">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AC35">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="AD35">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE35">
         <v>1.13</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O36">
         <v>3.65</v>
@@ -6186,7 +6186,7 @@
         <v>1.75</v>
       </c>
       <c r="Q36">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="R36">
         <v>2.4</v>
@@ -6216,16 +6216,16 @@
         <v>6</v>
       </c>
       <c r="AA36">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AC36">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD36">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE36">
         <v>1.24</v>
@@ -8139,7 +8139,7 @@
         <v>3.25</v>
       </c>
       <c r="P48">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q48">
         <v>3.31</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="O49">
         <v>3.15</v>
@@ -8305,7 +8305,7 @@
         <v>2.55</v>
       </c>
       <c r="Q49">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R49">
         <v>2.1</v>
@@ -8369,7 +8369,7 @@
         <v>1.33</v>
       </c>
       <c r="AK49">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O57">
         <v>3.25</v>
@@ -10421,10 +10421,10 @@
         <v>3.38</v>
       </c>
       <c r="P62">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="Q62">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R62">
         <v>2.18</v>
@@ -10436,16 +10436,16 @@
         <v>3.22</v>
       </c>
       <c r="U62">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V62">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W62">
         <v>1.08</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
         <v>1.16</v>
@@ -10584,7 +10584,7 @@
         <v>3.2</v>
       </c>
       <c r="P63">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="Q63">
         <v>2.92</v>
@@ -10599,10 +10599,10 @@
         <v>3</v>
       </c>
       <c r="U63">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="V63">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W63">
         <v>1.06</v>
@@ -10611,19 +10611,19 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z63">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AA63">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AB63">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AC63">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="AD63">
         <v>1.32</v>
@@ -10741,16 +10741,16 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O64">
         <v>4.33</v>
       </c>
       <c r="P64">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q64">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R64">
         <v>2.51</v>
@@ -10759,10 +10759,10 @@
         <v>1.15</v>
       </c>
       <c r="T64">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="U64">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V64">
         <v>1.75</v>
@@ -10774,10 +10774,10 @@
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AA64">
         <v>1.32</v>
@@ -10786,19 +10786,19 @@
         <v>3.1</v>
       </c>
       <c r="AC64">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD64">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE64">
         <v>1.31</v>
       </c>
       <c r="AF64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG64">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11423,7 +11423,7 @@
         <v>1.03</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
         <v>1.34</v>
@@ -11444,7 +11444,7 @@
         <v>1.17</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
         <v>1.86</v>
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
         <v>2.7</v>
@@ -11731,7 +11731,7 @@
         <v>2.88</v>
       </c>
       <c r="R70">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="S70">
         <v>1.3</v>
@@ -12048,7 +12048,7 @@
         <v>2.75</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P72">
         <v>2.15</v>
@@ -12087,10 +12087,10 @@
         <v>1.47</v>
       </c>
       <c r="AB72">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AC72">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AD72">
         <v>1.57</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AK73">
         <v>1.38</v>
@@ -12410,7 +12410,7 @@
         <v>5.75</v>
       </c>
       <c r="AA74">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB74">
         <v>2.9</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O79">
         <v>3.4</v>
@@ -13696,7 +13696,7 @@
         <v>3.5</v>
       </c>
       <c r="U82">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="V82">
         <v>1.57</v>
@@ -13714,10 +13714,10 @@
         <v>4.9</v>
       </c>
       <c r="AA82">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AB82">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AC82">
         <v>2.53</v>
@@ -13844,10 +13844,10 @@
         <v>3.75</v>
       </c>
       <c r="P83">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="Q83">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="R83">
         <v>2.38</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O84">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="P84">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q84">
         <v>2.13</v>
@@ -14369,7 +14369,7 @@
         <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC86">
         <v>2.15</v>
@@ -14490,10 +14490,10 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="O87">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P87">
         <v>2.1</v>
@@ -14544,7 +14544,7 @@
         <v>1.1</v>
       </c>
       <c r="AF87">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG87">
         <v>2</v>
@@ -14819,10 +14819,10 @@
         <v>1.73</v>
       </c>
       <c r="O89">
-        <v>3.8</v>
+        <v>3.53</v>
       </c>
       <c r="P89">
-        <v>4.6</v>
+        <v>3.97</v>
       </c>
       <c r="Q89">
         <v>2.32</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="O91">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="P91">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="Q91">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="R91">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S91">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T91">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="U91">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="V91">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X91">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y91">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z91">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC91">
-        <v>2.33</v>
+        <v>2.91</v>
       </c>
       <c r="AD91">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AE91">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF91">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AG91">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AK91">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,65 +15305,65 @@
         </is>
       </c>
       <c r="N92">
+        <v>2.18</v>
+      </c>
+      <c r="O92">
+        <v>3.78</v>
+      </c>
+      <c r="P92">
+        <v>2.88</v>
+      </c>
+      <c r="Q92">
         <v>2.48</v>
       </c>
-      <c r="O92">
-        <v>3.38</v>
-      </c>
-      <c r="P92">
-        <v>2.66</v>
-      </c>
-      <c r="Q92">
-        <v>2.99</v>
-      </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T92">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="U92">
+        <v>2.25</v>
+      </c>
+      <c r="V92">
+        <v>1.58</v>
+      </c>
+      <c r="W92">
+        <v>1.11</v>
+      </c>
+      <c r="X92">
+        <v>1.02</v>
+      </c>
+      <c r="Y92">
+        <v>1.12</v>
+      </c>
+      <c r="Z92">
+        <v>4.75</v>
+      </c>
+      <c r="AA92">
+        <v>1.53</v>
+      </c>
+      <c r="AB92">
+        <v>2.4</v>
+      </c>
+      <c r="AC92">
+        <v>2.33</v>
+      </c>
+      <c r="AD92">
+        <v>1.56</v>
+      </c>
+      <c r="AE92">
+        <v>1.18</v>
+      </c>
+      <c r="AF92">
+        <v>1.45</v>
+      </c>
+      <c r="AG92">
         <v>2.56</v>
       </c>
-      <c r="V92">
-        <v>1.4</v>
-      </c>
-      <c r="W92">
-        <v>1.07</v>
-      </c>
-      <c r="X92">
-        <v>1.04</v>
-      </c>
-      <c r="Y92">
-        <v>1.29</v>
-      </c>
-      <c r="Z92">
-        <v>3.25</v>
-      </c>
-      <c r="AA92">
-        <v>1.88</v>
-      </c>
-      <c r="AB92">
-        <v>1.92</v>
-      </c>
-      <c r="AC92">
-        <v>2.91</v>
-      </c>
-      <c r="AD92">
-        <v>1.33</v>
-      </c>
-      <c r="AE92">
-        <v>1.1</v>
-      </c>
-      <c r="AF92">
-        <v>1.67</v>
-      </c>
-      <c r="AG92">
-        <v>2.1</v>
-      </c>
       <c r="AH92" t="inlineStr">
         <is>
           <t>[]</t>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK92">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O94">
         <v>3.4</v>
@@ -15649,7 +15649,7 @@
         <v>1.36</v>
       </c>
       <c r="T94">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U94">
         <v>2.62</v>
@@ -15839,13 +15839,13 @@
         <v>1.91</v>
       </c>
       <c r="AC95">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="AD95">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE95">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF95">
         <v>1.86</v>
@@ -16624,7 +16624,7 @@
         <v>2.22</v>
       </c>
       <c r="S100">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T100">
         <v>3.3</v>
@@ -16648,7 +16648,7 @@
         <v>4.5</v>
       </c>
       <c r="AA100">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB100">
         <v>2.25</v>
@@ -16663,7 +16663,7 @@
         <v>1.17</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG100">
         <v>2.3</v>
@@ -16682,7 +16682,7 @@
         <v>1.21</v>
       </c>
       <c r="AK100">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16775,10 +16775,10 @@
         <v>2.85</v>
       </c>
       <c r="O101">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P101">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q101">
         <v>3.2</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="O102">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P102">
-        <v>5.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q102">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="R102">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S102">
+        <v>1.22</v>
+      </c>
+      <c r="T102">
+        <v>3.9</v>
+      </c>
+      <c r="U102">
+        <v>2.1</v>
+      </c>
+      <c r="V102">
+        <v>1.58</v>
+      </c>
+      <c r="W102">
+        <v>1.18</v>
+      </c>
+      <c r="X102">
+        <v>1.01</v>
+      </c>
+      <c r="Y102">
         <v>1.17</v>
       </c>
-      <c r="T102">
-        <v>4</v>
-      </c>
-      <c r="U102">
-        <v>2.16</v>
-      </c>
-      <c r="V102">
-        <v>1.67</v>
-      </c>
-      <c r="W102">
-        <v>1.13</v>
-      </c>
-      <c r="X102">
-        <v>1.02</v>
-      </c>
-      <c r="Y102">
-        <v>1.09</v>
-      </c>
       <c r="Z102">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA102">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB102">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AC102">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD102">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE102">
         <v>1.2</v>
       </c>
       <c r="AF102">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AG102">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK102">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P103">
-        <v>2.12</v>
+        <v>5.25</v>
       </c>
       <c r="Q103">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="R103">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S103">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T103">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U103">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V103">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W103">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z103">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA103">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB103">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AC103">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AD103">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE103">
         <v>1.2</v>
       </c>
       <c r="AF103">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AG103">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK103">
-        <v>1.36</v>
+        <v>2.47</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,7 +17261,7 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O104">
         <v>3.4</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O105">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P105">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q105">
         <v>3.41</v>
@@ -17451,7 +17451,7 @@
         <v>1.56</v>
       </c>
       <c r="W105">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
         <v>1.02</v>
@@ -17590,13 +17590,13 @@
         <v>2.5</v>
       </c>
       <c r="O106">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P106">
         <v>2.25</v>
       </c>
       <c r="Q106">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R106">
         <v>2.46</v>
@@ -18085,7 +18085,7 @@
         <v>1.35</v>
       </c>
       <c r="Q109">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="R109">
         <v>2.88</v>
@@ -18408,7 +18408,7 @@
         <v>3.45</v>
       </c>
       <c r="P111">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -19057,7 +19057,7 @@
         <v>7</v>
       </c>
       <c r="O115">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P115">
         <v>1.48</v>
@@ -20035,10 +20035,10 @@
         <v>1.73</v>
       </c>
       <c r="O121">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P121">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q121">
         <v>2.4</v>
@@ -20062,34 +20062,34 @@
         <v>1.03</v>
       </c>
       <c r="X121">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y121">
+        <v>1.5</v>
+      </c>
+      <c r="Z121">
+        <v>2.55</v>
+      </c>
+      <c r="AA121">
+        <v>2.63</v>
+      </c>
+      <c r="AB121">
         <v>1.47</v>
       </c>
-      <c r="Z121">
-        <v>2.44</v>
-      </c>
-      <c r="AA121">
-        <v>2.43</v>
-      </c>
-      <c r="AB121">
-        <v>1.44</v>
-      </c>
       <c r="AC121">
-        <v>4.95</v>
+        <v>5.5</v>
       </c>
       <c r="AD121">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE121">
         <v>1.03</v>
       </c>
       <c r="AF121">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG121">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>3.6</v>
       </c>
       <c r="P129">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="Q129">
         <v>2.57</v>
@@ -21375,10 +21375,10 @@
         <v>6</v>
       </c>
       <c r="AA129">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB129">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC129">
         <v>2.15</v>
@@ -22803,10 +22803,10 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O138">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P138">
         <v>4.4</v>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK138">
         <v>2.1</v>
@@ -22969,7 +22969,7 @@
         <v>2.5</v>
       </c>
       <c r="O139">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P139">
         <v>2.5</v>
@@ -23008,7 +23008,7 @@
         <v>1.91</v>
       </c>
       <c r="AB139">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC139">
         <v>3.52</v>
@@ -23135,10 +23135,10 @@
         <v>3.3</v>
       </c>
       <c r="P140">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q140">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="R140">
         <v>2</v>
@@ -23156,7 +23156,7 @@
         <v>1.33</v>
       </c>
       <c r="W140">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X140">
         <v>1.01</v>
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G143">
@@ -23618,61 +23618,61 @@
         </is>
       </c>
       <c r="N143">
-        <v>4.1</v>
+        <v>2.87</v>
       </c>
       <c r="O143">
+        <v>3.3</v>
+      </c>
+      <c r="P143">
+        <v>2.2</v>
+      </c>
+      <c r="Q143">
+        <v>3.14</v>
+      </c>
+      <c r="R143">
+        <v>2.06</v>
+      </c>
+      <c r="S143">
+        <v>1.31</v>
+      </c>
+      <c r="T143">
+        <v>3.1</v>
+      </c>
+      <c r="U143">
+        <v>2.73</v>
+      </c>
+      <c r="V143">
+        <v>1.47</v>
+      </c>
+      <c r="W143">
+        <v>1.1</v>
+      </c>
+      <c r="X143">
+        <v>1.04</v>
+      </c>
+      <c r="Y143">
+        <v>1.25</v>
+      </c>
+      <c r="Z143">
         <v>3.6</v>
       </c>
-      <c r="P143">
-        <v>1.73</v>
-      </c>
-      <c r="Q143">
-        <v>4</v>
-      </c>
-      <c r="R143">
-        <v>2.18</v>
-      </c>
-      <c r="S143">
-        <v>1.29</v>
-      </c>
-      <c r="T143">
-        <v>3.3</v>
-      </c>
-      <c r="U143">
-        <v>2.5</v>
-      </c>
-      <c r="V143">
-        <v>1.44</v>
-      </c>
-      <c r="W143">
-        <v>1.08</v>
-      </c>
-      <c r="X143">
-        <v>1.03</v>
-      </c>
-      <c r="Y143">
-        <v>1.22</v>
-      </c>
-      <c r="Z143">
-        <v>4.2</v>
-      </c>
       <c r="AA143">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB143">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC143">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD143">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE143">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF143">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG143">
         <v>2.1</v>
@@ -23688,10 +23688,10 @@
         </is>
       </c>
       <c r="AJ143">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK143">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AL143">
         <v>0</v>
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G144">
@@ -23781,61 +23781,61 @@
         </is>
       </c>
       <c r="N144">
-        <v>2.87</v>
+        <v>4.1</v>
       </c>
       <c r="O144">
+        <v>3.6</v>
+      </c>
+      <c r="P144">
+        <v>1.73</v>
+      </c>
+      <c r="Q144">
+        <v>4</v>
+      </c>
+      <c r="R144">
+        <v>2.18</v>
+      </c>
+      <c r="S144">
+        <v>1.29</v>
+      </c>
+      <c r="T144">
         <v>3.3</v>
       </c>
-      <c r="P144">
-        <v>2.2</v>
-      </c>
-      <c r="Q144">
-        <v>3.14</v>
-      </c>
-      <c r="R144">
-        <v>2.06</v>
-      </c>
-      <c r="S144">
-        <v>1.31</v>
-      </c>
-      <c r="T144">
-        <v>3.1</v>
-      </c>
       <c r="U144">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V144">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W144">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X144">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y144">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z144">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA144">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AB144">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AC144">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD144">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE144">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF144">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG144">
         <v>2.1</v>
@@ -23851,10 +23851,10 @@
         </is>
       </c>
       <c r="AJ144">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK144">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AL144">
         <v>0</v>
@@ -24113,7 +24113,7 @@
         <v>3.5</v>
       </c>
       <c r="P146">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q146">
         <v>2.88</v>
@@ -24273,7 +24273,7 @@
         <v>2.3</v>
       </c>
       <c r="O147">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P147">
         <v>2.61</v>
@@ -25737,7 +25737,7 @@
         </is>
       </c>
       <c r="N156">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O156">
         <v>4</v>
@@ -25909,10 +25909,10 @@
         <v>4.9</v>
       </c>
       <c r="Q157">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="R157">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="S157">
         <v>1.33</v>
@@ -25936,7 +25936,7 @@
         <v>1.26</v>
       </c>
       <c r="Z157">
-        <v>3.95</v>
+        <v>4.03</v>
       </c>
       <c r="AA157">
         <v>1.89</v>
@@ -25945,7 +25945,7 @@
         <v>2.06</v>
       </c>
       <c r="AC157">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AD157">
         <v>1.36</v>
@@ -27865,7 +27865,7 @@
         <v>2.25</v>
       </c>
       <c r="Q169">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="R169">
         <v>2.52</v>
@@ -27907,7 +27907,7 @@
         <v>1.84</v>
       </c>
       <c r="AE169">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF169">
         <v>1.35</v>
@@ -28022,10 +28022,10 @@
         <v>3</v>
       </c>
       <c r="O170">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P170">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q170">
         <v>3.08</v>
@@ -28514,7 +28514,7 @@
         <v>4.2</v>
       </c>
       <c r="P173">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="Q173">
         <v>3.31</v>
@@ -28674,7 +28674,7 @@
         <v>2</v>
       </c>
       <c r="O174">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P174">
         <v>3.2</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,25 +29160,25 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O177">
+        <v>3.6</v>
+      </c>
+      <c r="P177">
         <v>3.4</v>
       </c>
-      <c r="P177">
-        <v>2.95</v>
-      </c>
       <c r="Q177">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R177">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S177">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T177">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U177">
         <v>2.5</v>
@@ -29187,37 +29187,37 @@
         <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X177">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y177">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z177">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA177">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AB177">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AC177">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="AD177">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE177">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF177">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG177">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,25 +29323,25 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O178">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P178">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q178">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="R178">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S178">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T178">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U178">
         <v>2.5</v>
@@ -29350,37 +29350,37 @@
         <v>1.44</v>
       </c>
       <c r="W178">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X178">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y178">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z178">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA178">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AB178">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AC178">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="AD178">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE178">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF178">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG178">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29495,10 +29495,10 @@
         <v>2.53</v>
       </c>
       <c r="Q179">
-        <v>2.87</v>
+        <v>3.13</v>
       </c>
       <c r="R179">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S179">
         <v>1.36</v>
@@ -29556,7 +29556,7 @@
         </is>
       </c>
       <c r="AJ179">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK179">
         <v>1.45</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O182">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P182">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="Q182">
+        <v>2.62</v>
+      </c>
+      <c r="R182">
         <v>2.5</v>
       </c>
-      <c r="R182">
-        <v>2.25</v>
-      </c>
       <c r="S182">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T182">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U182">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V182">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W182">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X182">
         <v>1.02</v>
       </c>
       <c r="Y182">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z182">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA182">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AB182">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC182">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="AD182">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AE182">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF182">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AG182">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK182">
         <v>1.67</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O183">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P183">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="Q183">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R183">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S183">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T183">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U183">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V183">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W183">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X183">
         <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z183">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA183">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AB183">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AC183">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AD183">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AE183">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF183">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG183">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK183">
         <v>1.67</v>
@@ -30503,10 +30503,10 @@
         <v>4.15</v>
       </c>
       <c r="AA185">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB185">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC185">
         <v>2.59</v>
@@ -31134,7 +31134,7 @@
         <v>1.36</v>
       </c>
       <c r="T189">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U189">
         <v>2.85</v>
@@ -31279,13 +31279,13 @@
         </is>
       </c>
       <c r="N190">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O190">
         <v>3.4</v>
       </c>
       <c r="P190">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Q190">
         <v>2.25</v>
@@ -31451,16 +31451,16 @@
         <v>1.88</v>
       </c>
       <c r="Q191">
-        <v>4.72</v>
+        <v>4.1</v>
       </c>
       <c r="R191">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S191">
         <v>1.4</v>
       </c>
       <c r="T191">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="U191">
         <v>3</v>
@@ -31940,10 +31940,10 @@
         <v>2.69</v>
       </c>
       <c r="Q194">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="R194">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S194">
         <v>1.3</v>
@@ -32001,7 +32001,7 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AK194">
         <v>1.45</v>
@@ -32097,10 +32097,10 @@
         <v>1.7</v>
       </c>
       <c r="O195">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P195">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="Q195">
         <v>2.14</v>
@@ -32167,7 +32167,7 @@
         <v>1.14</v>
       </c>
       <c r="AK195">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32257,7 +32257,7 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O196">
         <v>3.75</v>
@@ -32423,7 +32423,7 @@
         <v>2.83</v>
       </c>
       <c r="O197">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P197">
         <v>2.2</v>
@@ -33072,10 +33072,10 @@
         </is>
       </c>
       <c r="N201">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O201">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P201">
         <v>2.37</v>
@@ -33733,7 +33733,7 @@
         <v>5.25</v>
       </c>
       <c r="Q205">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="R205">
         <v>2.1</v>
@@ -33778,10 +33778,10 @@
         <v>1.03</v>
       </c>
       <c r="AF205">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AG205">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH205" t="inlineStr">
         <is>
@@ -33794,10 +33794,10 @@
         </is>
       </c>
       <c r="AJ205">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK205">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AL205">
         <v>0</v>
@@ -34089,7 +34089,7 @@
         <v>2.59</v>
       </c>
       <c r="AA207">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AB207">
         <v>1.53</v>
@@ -34213,34 +34213,34 @@
         </is>
       </c>
       <c r="N208">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="O208">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P208">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="Q208">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="R208">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S208">
         <v>1.36</v>
       </c>
       <c r="T208">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U208">
         <v>2.8</v>
       </c>
       <c r="V208">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W208">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X208">
         <v>1.03</v>
@@ -34252,10 +34252,10 @@
         <v>3.08</v>
       </c>
       <c r="AA208">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB208">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC208">
         <v>3.42</v>
@@ -34267,7 +34267,7 @@
         <v>1.08</v>
       </c>
       <c r="AF208">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG208">
         <v>1.95</v>
@@ -34283,10 +34283,10 @@
         </is>
       </c>
       <c r="AJ208">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK208">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL208">
         <v>0</v>
@@ -34433,7 +34433,7 @@
         <v>1.85</v>
       </c>
       <c r="AG209">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O211">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P211">
-        <v>4.79</v>
+        <v>4.1</v>
       </c>
       <c r="Q211">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="R211">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="S211">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T211">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="U211">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="V211">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="W211">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X211">
         <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z211">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA211">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB211">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AC211">
-        <v>2.63</v>
+        <v>2.08</v>
       </c>
       <c r="AD211">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AE211">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF211">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG211">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK211">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="O212">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="P212">
-        <v>4.2</v>
+        <v>9.25</v>
       </c>
       <c r="Q212">
-        <v>2.23</v>
+        <v>1.64</v>
       </c>
       <c r="R212">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="S212">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T212">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="U212">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="V212">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="W212">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X212">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y212">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z212">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="AA212">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB212">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="AC212">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AD212">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AE212">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF212">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AG212">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK212">
-        <v>2.02</v>
+        <v>3.74</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,80 +35028,80 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="O213">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="P213">
-        <v>9.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q213">
-        <v>1.61</v>
+        <v>2.23</v>
       </c>
       <c r="R213">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="S213">
+        <v>1.25</v>
+      </c>
+      <c r="T213">
+        <v>3.7</v>
+      </c>
+      <c r="U213">
+        <v>2.2</v>
+      </c>
+      <c r="V213">
+        <v>1.62</v>
+      </c>
+      <c r="W213">
+        <v>1.15</v>
+      </c>
+      <c r="X213">
+        <v>1.02</v>
+      </c>
+      <c r="Y213">
+        <v>1.17</v>
+      </c>
+      <c r="Z213">
+        <v>5</v>
+      </c>
+      <c r="AA213">
+        <v>1.57</v>
+      </c>
+      <c r="AB213">
+        <v>2.42</v>
+      </c>
+      <c r="AC213">
+        <v>2.25</v>
+      </c>
+      <c r="AD213">
+        <v>1.6</v>
+      </c>
+      <c r="AE213">
         <v>1.2</v>
       </c>
-      <c r="T213">
-        <v>3.85</v>
-      </c>
-      <c r="U213">
-        <v>2.09</v>
-      </c>
-      <c r="V213">
-        <v>1.73</v>
-      </c>
-      <c r="W213">
+      <c r="AF213">
+        <v>1.5</v>
+      </c>
+      <c r="AG213">
+        <v>2.4</v>
+      </c>
+      <c r="AH213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI213" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ213">
         <v>1.17</v>
       </c>
-      <c r="X213">
-        <v>1.01</v>
-      </c>
-      <c r="Y213">
-        <v>1.08</v>
-      </c>
-      <c r="Z213">
-        <v>5.5</v>
-      </c>
-      <c r="AA213">
-        <v>1.44</v>
-      </c>
-      <c r="AB213">
-        <v>2.88</v>
-      </c>
-      <c r="AC213">
-        <v>2.11</v>
-      </c>
-      <c r="AD213">
-        <v>1.72</v>
-      </c>
-      <c r="AE213">
-        <v>1.29</v>
-      </c>
-      <c r="AF213">
-        <v>1.72</v>
-      </c>
-      <c r="AG213">
-        <v>2.01</v>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ213">
-        <v>1.08</v>
-      </c>
       <c r="AK213">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="O214">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="P214">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q214">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="R214">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="S214">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T214">
-        <v>3.74</v>
+        <v>3</v>
       </c>
       <c r="U214">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="V214">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W214">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X214">
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z214">
-        <v>5.5</v>
+        <v>3.76</v>
       </c>
       <c r="AA214">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AB214">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AC214">
-        <v>2.08</v>
+        <v>2.89</v>
       </c>
       <c r="AD214">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AE214">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AF214">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AG214">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK214">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35363,7 +35363,7 @@
         <v>2.3</v>
       </c>
       <c r="Q215">
-        <v>3.02</v>
+        <v>3.46</v>
       </c>
       <c r="R215">
         <v>2.18</v>
@@ -35485,12 +35485,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G216">
@@ -35517,64 +35517,64 @@
         </is>
       </c>
       <c r="N216">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="O216">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P216">
-        <v>4.33</v>
+        <v>4.79</v>
       </c>
       <c r="Q216">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="R216">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S216">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="T216">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U216">
-        <v>2.54</v>
+        <v>2.27</v>
       </c>
       <c r="V216">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W216">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X216">
         <v>1.02</v>
       </c>
       <c r="Y216">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z216">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AA216">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AB216">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AC216">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AD216">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AE216">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF216">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG216">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH216" t="inlineStr">
         <is>
@@ -35587,10 +35587,10 @@
         </is>
       </c>
       <c r="AJ216">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK216">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL216">
         <v>0</v>
@@ -35680,13 +35680,13 @@
         </is>
       </c>
       <c r="N217">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O217">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P217">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="Q217">
         <v>2.5</v>
@@ -35713,7 +35713,7 @@
         <v>1.01</v>
       </c>
       <c r="Y217">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z217">
         <v>3.34</v>
@@ -35725,7 +35725,7 @@
         <v>1.93</v>
       </c>
       <c r="AC217">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AD217">
         <v>1.33</v>
@@ -35753,7 +35753,7 @@
         <v>1.28</v>
       </c>
       <c r="AK217">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AL217">
         <v>0</v>
@@ -37512,7 +37512,7 @@
         <v>3.7</v>
       </c>
       <c r="AA228">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB228">
         <v>2.15</v>
@@ -37546,7 +37546,7 @@
         <v>1.3</v>
       </c>
       <c r="AK228">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL228">
         <v>0</v>
@@ -37983,7 +37983,7 @@
         <v>3.4</v>
       </c>
       <c r="U231">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V231">
         <v>1.51</v>
@@ -38777,13 +38777,13 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O236">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="P236">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q236">
         <v>3</v>
@@ -38955,16 +38955,16 @@
         <v>2.08</v>
       </c>
       <c r="S237">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T237">
         <v>2.9</v>
       </c>
       <c r="U237">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="V237">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W237">
         <v>1.1</v>
@@ -39272,7 +39272,7 @@
         <v>3.1</v>
       </c>
       <c r="P239">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q239">
         <v>3.05</v>
@@ -39281,7 +39281,7 @@
         <v>2.06</v>
       </c>
       <c r="S239">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T239">
         <v>3.2</v>
@@ -39293,7 +39293,7 @@
         <v>1.49</v>
       </c>
       <c r="W239">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X239">
         <v>1.01</v>
@@ -39320,7 +39320,7 @@
         <v>1.09</v>
       </c>
       <c r="AF239">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG239">
         <v>2.21</v>
@@ -39592,19 +39592,19 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O241">
         <v>3.42</v>
       </c>
       <c r="P241">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="Q241">
         <v>2.7</v>
       </c>
       <c r="R241">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S241">
         <v>1.3</v>
@@ -39613,7 +39613,7 @@
         <v>3.25</v>
       </c>
       <c r="U241">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V241">
         <v>1.47</v>
@@ -39755,10 +39755,10 @@
         </is>
       </c>
       <c r="N242">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O242">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="P242">
         <v>3</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O245">
+        <v>2.99</v>
+      </c>
+      <c r="P245">
         <v>3.25</v>
       </c>
-      <c r="P245">
-        <v>3.15</v>
-      </c>
       <c r="Q245">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="R245">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S245">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T245">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="U245">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="V245">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W245">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X245">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y245">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="Z245">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="AA245">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AB245">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AC245">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD245">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AE245">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF245">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AG245">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK245">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O246">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="P246">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q246">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="R246">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S246">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T246">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="U246">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="V246">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W246">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X246">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y246">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="Z246">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA246">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AB246">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AC246">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD246">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AE246">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF246">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AG246">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK246">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -41246,7 +41246,7 @@
         <v>2.45</v>
       </c>
       <c r="V251">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W251">
         <v>1.11</v>
@@ -41711,7 +41711,7 @@
         </is>
       </c>
       <c r="N254">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="O254">
         <v>8</v>
@@ -42873,10 +42873,10 @@
         <v>4.1</v>
       </c>
       <c r="U261">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="V261">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W261">
         <v>1.17</v>
@@ -42888,28 +42888,28 @@
         <v>1.08</v>
       </c>
       <c r="Z261">
-        <v>6.6</v>
+        <v>6.32</v>
       </c>
       <c r="AA261">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB261">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AC261">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="AD261">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE261">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF261">
         <v>2.2</v>
       </c>
       <c r="AG261">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AH261" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="AK261">
         <v>1.04</v>
@@ -43504,13 +43504,13 @@
         </is>
       </c>
       <c r="N265">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="O265">
         <v>2.8</v>
       </c>
       <c r="P265">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q265">
         <v>3.4</v>
@@ -43546,7 +43546,7 @@
         <v>2.75</v>
       </c>
       <c r="AB265">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC265">
         <v>5.5</v>
@@ -44328,7 +44328,7 @@
         <v>2.2</v>
       </c>
       <c r="Q270">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="R270">
         <v>2.38</v>
@@ -44482,13 +44482,13 @@
         </is>
       </c>
       <c r="N271">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="O271">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P271">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="Q271">
         <v>2.88</v>
@@ -44500,7 +44500,7 @@
         <v>1.33</v>
       </c>
       <c r="T271">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="U271">
         <v>2.6</v>
@@ -44518,7 +44518,7 @@
         <v>1.25</v>
       </c>
       <c r="Z271">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="AA271">
         <v>1.8</v>
@@ -44552,10 +44552,10 @@
         </is>
       </c>
       <c r="AJ271">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK271">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AL271">
         <v>0</v>
@@ -44675,7 +44675,7 @@
         <v>1.07</v>
       </c>
       <c r="X272">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y272">
         <v>1.21</v>
@@ -44696,7 +44696,7 @@
         <v>1.31</v>
       </c>
       <c r="AE272">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF272">
         <v>1.62</v>
@@ -44823,10 +44823,10 @@
         <v>2.05</v>
       </c>
       <c r="S273">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T273">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U273">
         <v>2.86</v>
@@ -44850,13 +44850,13 @@
         <v>2.05</v>
       </c>
       <c r="AB273">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC273">
         <v>3.58</v>
       </c>
       <c r="AD273">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE273">
         <v>1.04</v>
@@ -45134,13 +45134,13 @@
         </is>
       </c>
       <c r="N275">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O275">
         <v>3.8</v>
       </c>
       <c r="P275">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="Q275">
         <v>2.1</v>
@@ -45179,13 +45179,13 @@
         <v>2.7</v>
       </c>
       <c r="AC275">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD275">
         <v>1.74</v>
       </c>
       <c r="AE275">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AF275">
         <v>1.44</v>
@@ -45297,13 +45297,13 @@
         </is>
       </c>
       <c r="N276">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O276">
         <v>2.98</v>
       </c>
       <c r="P276">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q276">
         <v>3</v>
@@ -45816,13 +45816,13 @@
         <v>1.08</v>
       </c>
       <c r="X279">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y279">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z279">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA279">
         <v>1.95</v>
@@ -45831,13 +45831,13 @@
         <v>1.85</v>
       </c>
       <c r="AC279">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD279">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE279">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF279">
         <v>1.67</v>
@@ -46607,7 +46607,7 @@
         <v>3.48</v>
       </c>
       <c r="P284">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q284">
         <v>2.74</v>
@@ -46634,19 +46634,19 @@
         <v>1.02</v>
       </c>
       <c r="Y284">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z284">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA284">
         <v>1.47</v>
       </c>
       <c r="AB284">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="AC284">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD284">
         <v>1.57</v>
@@ -46658,7 +46658,7 @@
         <v>1.44</v>
       </c>
       <c r="AG284">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH284" t="inlineStr">
         <is>
@@ -46960,22 +46960,22 @@
         <v>1.02</v>
       </c>
       <c r="Y286">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z286">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA286">
         <v>1.49</v>
       </c>
       <c r="AB286">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="AC286">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AD286">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE286">
         <v>1.22</v>
@@ -46984,7 +46984,7 @@
         <v>1.44</v>
       </c>
       <c r="AG286">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -46997,10 +46997,10 @@
         </is>
       </c>
       <c r="AJ286">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK286">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47093,16 +47093,16 @@
         <v>2.4</v>
       </c>
       <c r="O287">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P287">
         <v>2.37</v>
       </c>
       <c r="Q287">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R287">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S287">
         <v>1.2</v>
@@ -47123,25 +47123,25 @@
         <v>1.01</v>
       </c>
       <c r="Y287">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z287">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA287">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB287">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AC287">
         <v>2</v>
       </c>
       <c r="AD287">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE287">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF287">
         <v>1.36</v>
@@ -47283,13 +47283,13 @@
         <v>1.14</v>
       </c>
       <c r="X288">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y288">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z288">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AA288">
         <v>1.61</v>
@@ -47298,10 +47298,10 @@
         <v>2.25</v>
       </c>
       <c r="AC288">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD288">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE288">
         <v>1.2</v>
@@ -47446,7 +47446,7 @@
         <v>1.11</v>
       </c>
       <c r="X289">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y289">
         <v>1.2</v>
@@ -47473,7 +47473,7 @@
         <v>1.62</v>
       </c>
       <c r="AG289">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH289" t="inlineStr">
         <is>
@@ -47579,13 +47579,13 @@
         </is>
       </c>
       <c r="N290">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="O290">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="P290">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q290">
         <v>1.36</v>
@@ -47938,10 +47938,10 @@
         <v>1.01</v>
       </c>
       <c r="Y292">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z292">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA292">
         <v>1.9</v>
@@ -47956,7 +47956,7 @@
         <v>1.27</v>
       </c>
       <c r="AE292">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF292">
         <v>2.08</v>
@@ -48397,7 +48397,7 @@
         <v>1.87</v>
       </c>
       <c r="O295">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P295">
         <v>3.2</v>
@@ -48427,10 +48427,10 @@
         <v>0</v>
       </c>
       <c r="Y295">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z295">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA295">
         <v>1.25</v>
@@ -48439,13 +48439,13 @@
         <v>3.6</v>
       </c>
       <c r="AC295">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AD295">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE295">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF295">
         <v>1.29</v>
@@ -48557,7 +48557,7 @@
         </is>
       </c>
       <c r="N296">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O296">
         <v>3.25</v>
@@ -48599,7 +48599,7 @@
         <v>2.15</v>
       </c>
       <c r="AB296">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC296">
         <v>3.5</v>
@@ -49046,13 +49046,13 @@
         </is>
       </c>
       <c r="N299">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O299">
         <v>5.25</v>
       </c>
       <c r="P299">
-        <v>7.9</v>
+        <v>7.75</v>
       </c>
       <c r="Q299">
         <v>1.7</v>
@@ -49254,7 +49254,7 @@
         <v>2.38</v>
       </c>
       <c r="AC300">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AD300">
         <v>1.5</v>
@@ -49544,13 +49544,13 @@
         <v>5.25</v>
       </c>
       <c r="Q302">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R302">
         <v>2.29</v>
       </c>
       <c r="S302">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T302">
         <v>3.8</v>
@@ -49707,10 +49707,10 @@
         <v>2</v>
       </c>
       <c r="Q303">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="R303">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="S303">
         <v>1.22</v>
@@ -49728,34 +49728,34 @@
         <v>1.15</v>
       </c>
       <c r="X303">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y303">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z303">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA303">
         <v>1.45</v>
       </c>
       <c r="AB303">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AC303">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AD303">
         <v>1.62</v>
       </c>
       <c r="AE303">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF303">
         <v>1.44</v>
       </c>
       <c r="AG303">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AH303" t="inlineStr">
         <is>
@@ -50024,10 +50024,10 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="O305">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="P305">
         <v>7.5</v>
@@ -50075,7 +50075,7 @@
         <v>1.62</v>
       </c>
       <c r="AE305">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF305">
         <v>1.75</v>
@@ -50217,10 +50217,10 @@
         <v>1.14</v>
       </c>
       <c r="X306">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y306">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z306">
         <v>4.6</v>
@@ -50238,13 +50238,13 @@
         <v>1.49</v>
       </c>
       <c r="AE306">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF306">
         <v>1.62</v>
       </c>
       <c r="AG306">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH306" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>1.76</v>
       </c>
       <c r="V308">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="W308">
         <v>1.3</v>
@@ -50549,7 +50549,7 @@
         <v>1.04</v>
       </c>
       <c r="Z308">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA308">
         <v>1.27</v>
@@ -50676,16 +50676,16 @@
         </is>
       </c>
       <c r="N309">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O309">
         <v>3.5</v>
       </c>
       <c r="P309">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q309">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R309">
         <v>2.3</v>
@@ -50839,10 +50839,10 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O310">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P310">
         <v>2.93</v>
@@ -50912,7 +50912,7 @@
         <v>1.16</v>
       </c>
       <c r="AK310">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -51017,7 +51017,7 @@
         <v>4.25</v>
       </c>
       <c r="S311">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="T311">
         <v>7</v>
@@ -51041,10 +51041,10 @@
         <v>9.699999999999999</v>
       </c>
       <c r="AA311">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB311">
-        <v>6.58</v>
+        <v>6.5</v>
       </c>
       <c r="AC311">
         <v>1.26</v>
@@ -51887,7 +51887,7 @@
         </is>
       </c>
       <c r="AJ316">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AK316">
         <v>1.53</v>
@@ -52019,7 +52019,7 @@
         <v>3.8</v>
       </c>
       <c r="AA317">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB317">
         <v>2</v>
@@ -52143,7 +52143,7 @@
         </is>
       </c>
       <c r="N318">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O318">
         <v>3.8</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G319">
@@ -52306,80 +52306,80 @@
         </is>
       </c>
       <c r="N319">
-        <v>1.61</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O319">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P319">
-        <v>4.6</v>
+        <v>1.34</v>
       </c>
       <c r="Q319">
-        <v>2.17</v>
+        <v>10</v>
       </c>
       <c r="R319">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S319">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="T319">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="U319">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="V319">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W319">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X319">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y319">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Z319">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AA319">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AB319">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AC319">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD319">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AE319">
+        <v>1.05</v>
+      </c>
+      <c r="AF319">
+        <v>2.88</v>
+      </c>
+      <c r="AG319">
+        <v>1.3</v>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ319">
+        <v>3.1</v>
+      </c>
+      <c r="AK319">
         <v>1.04</v>
-      </c>
-      <c r="AF319">
-        <v>2</v>
-      </c>
-      <c r="AG319">
-        <v>1.71</v>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ319">
-        <v>1.29</v>
-      </c>
-      <c r="AK319">
-        <v>2.1</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,64 +52469,64 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O320">
         <v>3.5</v>
       </c>
       <c r="P320">
-        <v>6.25</v>
+        <v>4.6</v>
       </c>
       <c r="Q320">
+        <v>2.17</v>
+      </c>
+      <c r="R320">
+        <v>2.16</v>
+      </c>
+      <c r="S320">
+        <v>1.37</v>
+      </c>
+      <c r="T320">
+        <v>2.8</v>
+      </c>
+      <c r="U320">
+        <v>2.77</v>
+      </c>
+      <c r="V320">
+        <v>1.35</v>
+      </c>
+      <c r="W320">
+        <v>1.06</v>
+      </c>
+      <c r="X320">
+        <v>1.02</v>
+      </c>
+      <c r="Y320">
+        <v>1.31</v>
+      </c>
+      <c r="Z320">
+        <v>2.92</v>
+      </c>
+      <c r="AA320">
         <v>2.05</v>
       </c>
-      <c r="R320">
-        <v>1.91</v>
-      </c>
-      <c r="S320">
-        <v>1.55</v>
-      </c>
-      <c r="T320">
-        <v>2.3</v>
-      </c>
-      <c r="U320">
-        <v>3.52</v>
-      </c>
-      <c r="V320">
-        <v>1.22</v>
-      </c>
-      <c r="W320">
+      <c r="AB320">
+        <v>1.68</v>
+      </c>
+      <c r="AC320">
+        <v>3.5</v>
+      </c>
+      <c r="AD320">
+        <v>1.23</v>
+      </c>
+      <c r="AE320">
         <v>1.04</v>
       </c>
-      <c r="X320">
-        <v>1.06</v>
-      </c>
-      <c r="Y320">
-        <v>1.51</v>
-      </c>
-      <c r="Z320">
-        <v>2.33</v>
-      </c>
-      <c r="AA320">
-        <v>2.56</v>
-      </c>
-      <c r="AB320">
-        <v>1.4</v>
-      </c>
-      <c r="AC320">
-        <v>5.25</v>
-      </c>
-      <c r="AD320">
-        <v>1.09</v>
-      </c>
-      <c r="AE320">
-        <v>1.03</v>
-      </c>
       <c r="AF320">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AG320">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK320">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,80 +52632,80 @@
         </is>
       </c>
       <c r="N321">
-        <v>9.9</v>
+        <v>1.55</v>
       </c>
       <c r="O321">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P321">
-        <v>1.33</v>
+        <v>6.25</v>
       </c>
       <c r="Q321">
-        <v>10</v>
+        <v>2.05</v>
       </c>
       <c r="R321">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="S321">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="T321">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="U321">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="V321">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W321">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X321">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y321">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="Z321">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AA321">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AB321">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AC321">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AD321">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AE321">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF321">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AG321">
+        <v>1.4</v>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ321">
         <v>1.3</v>
       </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ321">
-        <v>3.1</v>
-      </c>
       <c r="AK321">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52961,7 +52961,7 @@
         <v>2.24</v>
       </c>
       <c r="O323">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P323">
         <v>3.41</v>
@@ -53121,7 +53121,7 @@
         </is>
       </c>
       <c r="N324">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O324">
         <v>3.6</v>
@@ -53139,7 +53139,7 @@
         <v>1.4</v>
       </c>
       <c r="T324">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="U324">
         <v>2.81</v>
@@ -53154,22 +53154,22 @@
         <v>1.05</v>
       </c>
       <c r="Y324">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z324">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AA324">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB324">
         <v>1.73</v>
       </c>
       <c r="AC324">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="AD324">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE324">
         <v>1.07</v>
@@ -53290,7 +53290,7 @@
         <v>3.32</v>
       </c>
       <c r="P325">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53447,13 +53447,13 @@
         </is>
       </c>
       <c r="N326">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O326">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="P326">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q326">
         <v>2</v>
@@ -53462,13 +53462,13 @@
         <v>2.1</v>
       </c>
       <c r="S326">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T326">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="U326">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="V326">
         <v>1.29</v>
@@ -53480,10 +53480,10 @@
         <v>1.03</v>
       </c>
       <c r="Y326">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z326">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AA326">
         <v>2.63</v>
@@ -53492,19 +53492,19 @@
         <v>1.5</v>
       </c>
       <c r="AC326">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="AD326">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE326">
         <v>1.02</v>
       </c>
       <c r="AF326">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AG326">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK326">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -53643,22 +53643,22 @@
         <v>1.01</v>
       </c>
       <c r="Y327">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z327">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA327">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB327">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC327">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD327">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE327">
         <v>1.05</v>
@@ -53683,7 +53683,7 @@
         <v>1.2</v>
       </c>
       <c r="AK327">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AL327">
         <v>0</v>
@@ -53773,7 +53773,7 @@
         </is>
       </c>
       <c r="N328">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="O328">
         <v>4.9</v>
@@ -53785,7 +53785,7 @@
         <v>1.83</v>
       </c>
       <c r="R328">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S328">
         <v>1.22</v>
@@ -53794,7 +53794,7 @@
         <v>3.8</v>
       </c>
       <c r="U328">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V328">
         <v>1.61</v>
@@ -53803,25 +53803,25 @@
         <v>1.13</v>
       </c>
       <c r="X328">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y328">
         <v>1.14</v>
       </c>
       <c r="Z328">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="AA328">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB328">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="AC328">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AD328">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE328">
         <v>1.2</v>
@@ -53936,31 +53936,31 @@
         </is>
       </c>
       <c r="N329">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="O329">
-        <v>5.2</v>
+        <v>5.87</v>
       </c>
       <c r="P329">
-        <v>6.45</v>
+        <v>8</v>
       </c>
       <c r="Q329">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="R329">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S329">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T329">
         <v>4</v>
       </c>
       <c r="U329">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="V329">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W329">
         <v>1.18</v>
@@ -53969,31 +53969,31 @@
         <v>0</v>
       </c>
       <c r="Y329">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z329">
-        <v>5.84</v>
+        <v>6.17</v>
       </c>
       <c r="AA329">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB329">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AC329">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="AD329">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AE329">
         <v>1.3</v>
       </c>
       <c r="AF329">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG329">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
@@ -54006,10 +54006,10 @@
         </is>
       </c>
       <c r="AJ329">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK329">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AL329">
         <v>0</v>
@@ -54099,13 +54099,13 @@
         </is>
       </c>
       <c r="N330">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="O330">
-        <v>3.9</v>
+        <v>4.02</v>
       </c>
       <c r="P330">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q330">
         <v>2.8</v>
@@ -54262,7 +54262,7 @@
         </is>
       </c>
       <c r="N331">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O331">
         <v>3.3</v>
@@ -54301,10 +54301,10 @@
         <v>0</v>
       </c>
       <c r="AA331">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AB331">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="AC331">
         <v>0</v>
@@ -54588,13 +54588,13 @@
         </is>
       </c>
       <c r="N333">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O333">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P333">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Q333">
         <v>0</v>
@@ -54751,7 +54751,7 @@
         </is>
       </c>
       <c r="N334">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O334">
         <v>3.1</v>
@@ -54760,10 +54760,10 @@
         <v>3.31</v>
       </c>
       <c r="Q334">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="R334">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S334">
         <v>1.46</v>
@@ -54923,7 +54923,7 @@
         <v>4.33</v>
       </c>
       <c r="Q335">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="R335">
         <v>1.95</v>
@@ -55083,7 +55083,7 @@
         <v>4.8</v>
       </c>
       <c r="P336">
-        <v>6.5</v>
+        <v>7.55</v>
       </c>
       <c r="Q336">
         <v>1.7</v>
@@ -55150,7 +55150,7 @@
         <v>1.07</v>
       </c>
       <c r="AK336">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="AL336">
         <v>0</v>
@@ -55240,13 +55240,13 @@
         </is>
       </c>
       <c r="N337">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O337">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P337">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="Q337">
         <v>2.53</v>
@@ -55267,7 +55267,7 @@
         <v>1.73</v>
       </c>
       <c r="W337">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X337">
         <v>1.02</v>
@@ -55294,7 +55294,7 @@
         <v>1.27</v>
       </c>
       <c r="AF337">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG337">
         <v>2.77</v>
@@ -55566,13 +55566,13 @@
         </is>
       </c>
       <c r="N339">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="O339">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P339">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q339">
         <v>2.99</v>
@@ -55608,7 +55608,7 @@
         <v>1.36</v>
       </c>
       <c r="AB339">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AC339">
         <v>1.83</v>
@@ -55895,7 +55895,7 @@
         <v>3.5</v>
       </c>
       <c r="O341">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P341">
         <v>1.88</v>
@@ -56544,10 +56544,10 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O345">
-        <v>4.34</v>
+        <v>4.43</v>
       </c>
       <c r="P345">
         <v>3.54</v>
@@ -56713,7 +56713,7 @@
         <v>3.5</v>
       </c>
       <c r="P346">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="Q346">
         <v>3.05</v>
@@ -56777,10 +56777,10 @@
         </is>
       </c>
       <c r="AJ346">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="AK346">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL346">
         <v>0</v>
@@ -57685,7 +57685,7 @@
         </is>
       </c>
       <c r="N352">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O352">
         <v>3.5</v>
@@ -57848,7 +57848,7 @@
         </is>
       </c>
       <c r="N353">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O353">
         <v>3.7</v>
@@ -57979,12 +57979,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="G354">
@@ -58011,64 +58011,64 @@
         </is>
       </c>
       <c r="N354">
-        <v>5.5</v>
+        <v>1.57</v>
       </c>
       <c r="O354">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P354">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="Q354">
-        <v>4.51</v>
+        <v>1.9</v>
       </c>
       <c r="R354">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S354">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T354">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U354">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="V354">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W354">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X354">
         <v>1</v>
       </c>
       <c r="Y354">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z354">
-        <v>4.64</v>
+        <v>5.95</v>
       </c>
       <c r="AA354">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AB354">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="AC354">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AD354">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AE354">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AF354">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AG354">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AH354" t="inlineStr">
         <is>
@@ -58081,10 +58081,10 @@
         </is>
       </c>
       <c r="AJ354">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AK354">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="AL354">
         <v>0</v>
@@ -58142,12 +58142,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G355">
@@ -58174,65 +58174,65 @@
         </is>
       </c>
       <c r="N355">
-        <v>1.57</v>
+        <v>5.5</v>
       </c>
       <c r="O355">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P355">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q355">
-        <v>1.9</v>
+        <v>4.51</v>
       </c>
       <c r="R355">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="S355">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T355">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U355">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="V355">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="W355">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X355">
         <v>1</v>
       </c>
       <c r="Y355">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z355">
-        <v>5.95</v>
+        <v>4.64</v>
       </c>
       <c r="AA355">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB355">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="AC355">
+        <v>2.44</v>
+      </c>
+      <c r="AD355">
+        <v>1.53</v>
+      </c>
+      <c r="AE355">
+        <v>1.16</v>
+      </c>
+      <c r="AF355">
+        <v>1.67</v>
+      </c>
+      <c r="AG355">
         <v>2.1</v>
       </c>
-      <c r="AD355">
-        <v>1.71</v>
-      </c>
-      <c r="AE355">
-        <v>1.3</v>
-      </c>
-      <c r="AF355">
-        <v>1.44</v>
-      </c>
-      <c r="AG355">
-        <v>2.47</v>
-      </c>
       <c r="AH355" t="inlineStr">
         <is>
           <t>[]</t>
@@ -58244,10 +58244,10 @@
         </is>
       </c>
       <c r="AJ355">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="AK355">
-        <v>2.3</v>
+        <v>1.13</v>
       </c>
       <c r="AL355">
         <v>0</v>
@@ -58355,7 +58355,7 @@
         <v>1.3</v>
       </c>
       <c r="T356">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U356">
         <v>2.5</v>
@@ -58370,10 +58370,10 @@
         <v>1.01</v>
       </c>
       <c r="Y356">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z356">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA356">
         <v>1.75</v>
@@ -58382,10 +58382,10 @@
         <v>2.2</v>
       </c>
       <c r="AC356">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD356">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE356">
         <v>1.16</v>
@@ -58663,16 +58663,16 @@
         </is>
       </c>
       <c r="N358">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="O358">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P358">
         <v>2.65</v>
       </c>
       <c r="Q358">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="R358">
         <v>2</v>
@@ -58699,7 +58699,7 @@
         <v>1.37</v>
       </c>
       <c r="Z358">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AA358">
         <v>2.25</v>
@@ -58708,7 +58708,7 @@
         <v>1.68</v>
       </c>
       <c r="AC358">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="AD358">
         <v>1.2</v>
@@ -58717,7 +58717,7 @@
         <v>1.04</v>
       </c>
       <c r="AF358">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG358">
         <v>1.85</v>
@@ -58826,7 +58826,7 @@
         </is>
       </c>
       <c r="N359">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O359">
         <v>11</v>
@@ -58859,13 +58859,13 @@
         <v>1</v>
       </c>
       <c r="Y359">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z359">
         <v>8</v>
       </c>
       <c r="AA359">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB359">
         <v>3.88</v>
@@ -58899,7 +58899,7 @@
         <v>1.05</v>
       </c>
       <c r="AK359">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -59152,31 +59152,31 @@
         </is>
       </c>
       <c r="N361">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="O361">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P361">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q361">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="R361">
-        <v>2.54</v>
+        <v>2.81</v>
       </c>
       <c r="S361">
         <v>1.13</v>
       </c>
       <c r="T361">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="U361">
         <v>2</v>
       </c>
       <c r="V361">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W361">
         <v>1.2</v>
@@ -59188,7 +59188,7 @@
         <v>1.11</v>
       </c>
       <c r="Z361">
-        <v>6.62</v>
+        <v>6.55</v>
       </c>
       <c r="AA361">
         <v>1.33</v>
@@ -59197,19 +59197,19 @@
         <v>3.1</v>
       </c>
       <c r="AC361">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AD361">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AE361">
         <v>1.33</v>
       </c>
       <c r="AF361">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AG361">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AH361" t="inlineStr">
         <is>
@@ -59222,10 +59222,10 @@
         </is>
       </c>
       <c r="AJ361">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK361">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AL361">
         <v>0</v>
@@ -59647,7 +59647,7 @@
         <v>6.3</v>
       </c>
       <c r="P364">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Q364">
         <v>1.62</v>
@@ -59711,7 +59711,7 @@
         </is>
       </c>
       <c r="AJ364">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK364">
         <v>3.84</v>
@@ -60293,7 +60293,7 @@
         </is>
       </c>
       <c r="N368">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O368">
         <v>4.78</v>
@@ -60631,7 +60631,7 @@
         <v>2.38</v>
       </c>
       <c r="R370">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S370">
         <v>1.35</v>
@@ -60978,7 +60978,7 @@
         <v>1.02</v>
       </c>
       <c r="Y372">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z372">
         <v>3.15</v>
@@ -60993,7 +60993,7 @@
         <v>3.48</v>
       </c>
       <c r="AD372">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE372">
         <v>1.1</v>
@@ -61111,10 +61111,10 @@
         <v>2.22</v>
       </c>
       <c r="O373">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="P373">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q373">
         <v>2.63</v>
@@ -61147,10 +61147,10 @@
         <v>4.3</v>
       </c>
       <c r="AA373">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB373">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC373">
         <v>2.42</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P2">
         <v>3.3</v>
@@ -668,7 +668,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z2">
         <v>5.5</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="O3">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>2.7</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>2.8</v>
+      </c>
+      <c r="O5">
         <v>3.1</v>
       </c>
-      <c r="O5">
-        <v>3.4</v>
-      </c>
       <c r="P5">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q5">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R5">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="U5">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA5">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AB5">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AK5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P6">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="V6">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AC6">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="AD6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AK6">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O7">
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
         <v>3.52</v>
@@ -1465,7 +1465,7 @@
         <v>2.24</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
         <v>3.3</v>
@@ -1480,34 +1480,34 @@
         <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>4.68</v>
       </c>
       <c r="AA7">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AB7">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AC7">
-        <v>2.63</v>
+        <v>2.36</v>
       </c>
       <c r="AD7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
         <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>2.38</v>
       </c>
       <c r="O8">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -1782,7 +1782,7 @@
         <v>3</v>
       </c>
       <c r="P9">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q9">
         <v>2.63</v>
@@ -1791,10 +1791,10 @@
         <v>2</v>
       </c>
       <c r="S9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T9">
-        <v>2.49</v>
+        <v>2.73</v>
       </c>
       <c r="U9">
         <v>2.89</v>
@@ -1815,7 +1815,7 @@
         <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AB9">
         <v>1.62</v>
@@ -1824,7 +1824,7 @@
         <v>4.2</v>
       </c>
       <c r="AD9">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
         <v>1.04</v>
@@ -1981,13 +1981,13 @@
         <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
@@ -2138,7 +2138,7 @@
         <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.45</v>
+        <v>5.02</v>
       </c>
       <c r="AA11">
         <v>1.53</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
         <v>3.25</v>
@@ -2286,10 +2286,10 @@
         <v>2.8</v>
       </c>
       <c r="U12">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="V12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2310,7 +2310,7 @@
         <v>1.75</v>
       </c>
       <c r="AC12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD12">
         <v>1.29</v>
@@ -2440,7 +2440,7 @@
         <v>3.75</v>
       </c>
       <c r="R13">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2452,7 +2452,7 @@
         <v>2.75</v>
       </c>
       <c r="V13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
         <v>1.06</v>
@@ -2467,13 +2467,13 @@
         <v>3.4</v>
       </c>
       <c r="AA13">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB13">
         <v>1.83</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="AD13">
         <v>1.26</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O14">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P14">
         <v>1.55</v>
       </c>
       <c r="Q14">
-        <v>4.39</v>
+        <v>5.05</v>
       </c>
       <c r="R14">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S14">
         <v>1.3</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="O15">
         <v>3.1</v>
       </c>
       <c r="P15">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q15">
         <v>3.2</v>
@@ -2775,13 +2775,13 @@
         <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="V15">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -2796,7 +2796,7 @@
         <v>1.92</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC15">
         <v>3.5</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O16">
-        <v>4.64</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
         <v>1.46</v>
@@ -2953,13 +2953,13 @@
         <v>1.15</v>
       </c>
       <c r="Z16">
-        <v>4.2</v>
+        <v>4.42</v>
       </c>
       <c r="AA16">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC16">
         <v>2.49</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>2.59</v>
       </c>
       <c r="AK16">
         <v>1.07</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
         <v>3.58</v>
       </c>
       <c r="P17">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q17">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="R17">
         <v>2.13</v>
@@ -3119,10 +3119,10 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB17">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC17">
         <v>3.4</v>
@@ -3131,7 +3131,7 @@
         <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
         <v>1.8</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AK17">
         <v>1.25</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O18">
         <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
         <v>2.63</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
         <v>3.33</v>
@@ -3442,10 +3442,10 @@
         <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="AA19">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB19">
         <v>1.9</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="O20">
         <v>3.6</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q20">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R20">
         <v>2.25</v>
@@ -3608,7 +3608,7 @@
         <v>4.33</v>
       </c>
       <c r="AA20">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB20">
         <v>2.15</v>
@@ -3735,10 +3735,10 @@
         <v>1.72</v>
       </c>
       <c r="O21">
-        <v>4.12</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.9</v>
+        <v>4.32</v>
       </c>
       <c r="Q21">
         <v>2.1</v>
@@ -3750,7 +3750,7 @@
         <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
         <v>2.3</v>
@@ -3904,16 +3904,16 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T22">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U22">
         <v>2.38</v>
@@ -3934,19 +3934,19 @@
         <v>4.5</v>
       </c>
       <c r="AA22">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AB22">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AC22">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="AD22">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
         <v>1.73</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>4.4</v>
+        <v>3.22</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="Q24">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R24">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
+        <v>1.4</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.25</v>
+      </c>
+      <c r="Z24">
+        <v>3.8</v>
+      </c>
+      <c r="AA24">
+        <v>1.87</v>
+      </c>
+      <c r="AB24">
+        <v>1.9</v>
+      </c>
+      <c r="AC24">
+        <v>3.1</v>
+      </c>
+      <c r="AD24">
+        <v>1.36</v>
+      </c>
+      <c r="AE24">
+        <v>1.1</v>
+      </c>
+      <c r="AF24">
         <v>1.63</v>
       </c>
-      <c r="W24">
-        <v>1.15</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.13</v>
-      </c>
-      <c r="Z24">
-        <v>6</v>
-      </c>
-      <c r="AA24">
-        <v>1.45</v>
-      </c>
-      <c r="AB24">
-        <v>2.54</v>
-      </c>
-      <c r="AC24">
-        <v>2.18</v>
-      </c>
-      <c r="AD24">
-        <v>1.62</v>
-      </c>
-      <c r="AE24">
-        <v>1.29</v>
-      </c>
-      <c r="AF24">
-        <v>1.53</v>
-      </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4399,13 +4399,13 @@
         <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
         <v>2.95</v>
       </c>
       <c r="U25">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
         <v>1.42</v>
@@ -4417,16 +4417,16 @@
         <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
         <v>3.1</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.22</v>
+        <v>4.4</v>
       </c>
       <c r="O26">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P26">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q26">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="R26">
+        <v>2.5</v>
+      </c>
+      <c r="S26">
+        <v>1.22</v>
+      </c>
+      <c r="T26">
+        <v>3.75</v>
+      </c>
+      <c r="U26">
+        <v>2.13</v>
+      </c>
+      <c r="V26">
+        <v>1.65</v>
+      </c>
+      <c r="W26">
+        <v>1.17</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.13</v>
+      </c>
+      <c r="Z26">
+        <v>6</v>
+      </c>
+      <c r="AA26">
+        <v>1.44</v>
+      </c>
+      <c r="AB26">
+        <v>2.7</v>
+      </c>
+      <c r="AC26">
         <v>2.15</v>
       </c>
-      <c r="S26">
-        <v>1.33</v>
-      </c>
-      <c r="T26">
-        <v>3</v>
-      </c>
-      <c r="U26">
-        <v>2.75</v>
-      </c>
-      <c r="V26">
-        <v>1.4</v>
-      </c>
-      <c r="W26">
-        <v>1.1</v>
-      </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>1.25</v>
-      </c>
-      <c r="Z26">
-        <v>3.8</v>
-      </c>
-      <c r="AA26">
-        <v>1.87</v>
-      </c>
-      <c r="AB26">
-        <v>1.85</v>
-      </c>
-      <c r="AC26">
-        <v>3.1</v>
-      </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AF26">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG26">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4882,22 +4882,22 @@
         <v>3.5</v>
       </c>
       <c r="Q28">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="R28">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S28">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T28">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="U28">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="V28">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
         <v>1.04</v>
@@ -4906,25 +4906,25 @@
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z28">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="AA28">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AB28">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC28">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AD28">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE28">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
         <v>1.79</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK28">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,52 +5045,52 @@
         <v>2.65</v>
       </c>
       <c r="Q29">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="R29">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T29">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
         <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AB29">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AC29">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AD29">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE29">
         <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG29">
         <v>2</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>1.47</v>
       </c>
       <c r="AE30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF30">
         <v>1.53</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O32">
         <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q32">
         <v>3.1</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
         <v>1.25</v>
@@ -5549,19 +5549,19 @@
         <v>2.3</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA32">
         <v>1.62</v>
@@ -5694,10 +5694,10 @@
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="R33">
         <v>1.98</v>
@@ -5761,7 +5761,7 @@
         <v>1.26</v>
       </c>
       <c r="AK33">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="P37">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="Q37">
         <v>2.84</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="AK37">
         <v>1.41</v>
@@ -6512,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="R38">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="S38">
         <v>1.27</v>
@@ -6542,10 +6542,10 @@
         <v>3.72</v>
       </c>
       <c r="AA38">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC38">
         <v>2.88</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="AK38">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="O39">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P39">
-        <v>2.86</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="R39">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S39">
         <v>1.46</v>
@@ -6687,10 +6687,10 @@
         <v>2.48</v>
       </c>
       <c r="U39">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="V39">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W39">
         <v>1.03</v>
@@ -6699,19 +6699,19 @@
         <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z39">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="AA39">
         <v>2.3</v>
       </c>
       <c r="AB39">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC39">
-        <v>4.64</v>
+        <v>4.28</v>
       </c>
       <c r="AD39">
         <v>1.21</v>
@@ -6720,10 +6720,10 @@
         <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG39">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
+        <v>4.15</v>
+      </c>
+      <c r="O42">
+        <v>3.89</v>
+      </c>
+      <c r="P42">
+        <v>1.76</v>
+      </c>
+      <c r="Q42">
+        <v>4.33</v>
+      </c>
+      <c r="R42">
+        <v>2.3</v>
+      </c>
+      <c r="S42">
+        <v>1.3</v>
+      </c>
+      <c r="T42">
+        <v>3.2</v>
+      </c>
+      <c r="U42">
+        <v>2.63</v>
+      </c>
+      <c r="V42">
+        <v>1.44</v>
+      </c>
+      <c r="W42">
+        <v>1.11</v>
+      </c>
+      <c r="X42">
+        <v>1.03</v>
+      </c>
+      <c r="Y42">
+        <v>1.2</v>
+      </c>
+      <c r="Z42">
         <v>4</v>
       </c>
-      <c r="O42">
-        <v>3.6</v>
-      </c>
-      <c r="P42">
-        <v>1.72</v>
-      </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
-      <c r="V42">
-        <v>0</v>
-      </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
-      <c r="X42">
-        <v>0</v>
-      </c>
-      <c r="Y42">
-        <v>0</v>
-      </c>
-      <c r="Z42">
-        <v>0</v>
-      </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7861,7 +7861,7 @@
         <v>1.17</v>
       </c>
       <c r="AF46">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
         <v>2.18</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O48">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q48">
         <v>3.31</v>
@@ -8157,7 +8157,7 @@
         <v>2.75</v>
       </c>
       <c r="V48">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W48">
         <v>1.08</v>
@@ -8169,16 +8169,16 @@
         <v>1.3</v>
       </c>
       <c r="Z48">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="AA48">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB48">
         <v>1.83</v>
       </c>
       <c r="AC48">
-        <v>3.46</v>
+        <v>3.49</v>
       </c>
       <c r="AD48">
         <v>1.3</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="O49">
         <v>3.15</v>
@@ -8341,7 +8341,7 @@
         <v>1.8</v>
       </c>
       <c r="AC49">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD49">
         <v>1.25</v>
@@ -8498,7 +8498,7 @@
         <v>3.34</v>
       </c>
       <c r="AA50">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB50">
         <v>1.9</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9606,7 +9606,7 @@
         <v>3.25</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -9618,10 +9618,10 @@
         <v>1.45</v>
       </c>
       <c r="T57">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="U57">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="V57">
         <v>1.35</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="O58">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P58">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q58">
         <v>3.52</v>
@@ -9784,7 +9784,7 @@
         <v>2.63</v>
       </c>
       <c r="U58">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="V58">
         <v>1.35</v>
@@ -9808,7 +9808,7 @@
         <v>1.74</v>
       </c>
       <c r="AC58">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="AD58">
         <v>1.24</v>
@@ -10421,7 +10421,7 @@
         <v>3.38</v>
       </c>
       <c r="P62">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="Q62">
         <v>2.63</v>
@@ -10946,7 +10946,7 @@
         <v>1.99</v>
       </c>
       <c r="AB65">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC65">
         <v>3.42</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -12048,7 +12048,7 @@
         <v>2.75</v>
       </c>
       <c r="O72">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
         <v>2.15</v>
@@ -12063,7 +12063,7 @@
         <v>1.22</v>
       </c>
       <c r="T72">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="U72">
         <v>2.15</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.87</v>
+        <v>2.51</v>
       </c>
       <c r="O73">
         <v>3.54</v>
@@ -12250,13 +12250,13 @@
         <v>1.56</v>
       </c>
       <c r="AB73">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC73">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AD73">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE73">
         <v>1.18</v>
@@ -12265,7 +12265,7 @@
         <v>1.5</v>
       </c>
       <c r="AG73">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O74">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
-        <v>4.87</v>
+        <v>4.6</v>
       </c>
       <c r="Q74">
         <v>1.96</v>
@@ -12863,19 +12863,19 @@
         <v>6.5</v>
       </c>
       <c r="O77">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P77">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q77">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="R77">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T77">
         <v>2.62</v>
@@ -12890,25 +12890,25 @@
         <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z77">
         <v>2.92</v>
       </c>
       <c r="AA77">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AB77">
         <v>1.7</v>
       </c>
       <c r="AC77">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AD77">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE77">
         <v>1.03</v>
@@ -12930,7 +12930,7 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK77">
         <v>1.06</v>
@@ -13032,10 +13032,10 @@
         <v>6.65</v>
       </c>
       <c r="Q78">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="R78">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="S78">
         <v>1.31</v>
@@ -13047,7 +13047,7 @@
         <v>2.75</v>
       </c>
       <c r="V78">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W78">
         <v>1.1</v>
@@ -13056,31 +13056,31 @@
         <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AA78">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AB78">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AC78">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AD78">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE78">
         <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK78">
         <v>2.6</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.95</v>
+        <v>4.35</v>
       </c>
       <c r="O80">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P80">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Q80">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R80">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="S80">
         <v>1.24</v>
       </c>
       <c r="T80">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="U80">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="V80">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W80">
         <v>1.14</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
         <v>1.11</v>
       </c>
       <c r="Z80">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA80">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB80">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AC80">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AD80">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE80">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
         <v>1.5</v>
       </c>
       <c r="AG80">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK80">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13545,10 +13545,10 @@
         <v>1.11</v>
       </c>
       <c r="Y81">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z81">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AA81">
         <v>2.45</v>
@@ -13557,7 +13557,7 @@
         <v>1.65</v>
       </c>
       <c r="AC81">
-        <v>4.76</v>
+        <v>4.81</v>
       </c>
       <c r="AD81">
         <v>1.15</v>
@@ -14004,7 +14004,7 @@
         <v>1.66</v>
       </c>
       <c r="O84">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P84">
         <v>4.5</v>
@@ -14203,7 +14203,7 @@
         <v>5.5</v>
       </c>
       <c r="AA85">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB85">
         <v>2.42</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.15</v>
+        <v>1.89</v>
       </c>
       <c r="AK85">
         <v>1.19</v>
@@ -14366,7 +14366,7 @@
         <v>6.5</v>
       </c>
       <c r="AA86">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AB86">
         <v>2.88</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="O88">
-        <v>4.4</v>
+        <v>3.51</v>
       </c>
       <c r="P88">
-        <v>5</v>
+        <v>3.98</v>
       </c>
       <c r="Q88">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="R88">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T88">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="U88">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="V88">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="W88">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X88">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="Z88">
-        <v>5.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA88">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="AB88">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="AC88">
-        <v>2.38</v>
+        <v>3.08</v>
       </c>
       <c r="AD88">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE88">
+        <v>1.12</v>
+      </c>
+      <c r="AF88">
+        <v>1.81</v>
+      </c>
+      <c r="AG88">
+        <v>1.95</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.22</v>
       </c>
-      <c r="AF88">
-        <v>1.57</v>
-      </c>
-      <c r="AG88">
-        <v>2.3</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.16</v>
-      </c>
       <c r="AK88">
-        <v>2.37</v>
+        <v>2.08</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="O89">
-        <v>3.53</v>
+        <v>4.4</v>
       </c>
       <c r="P89">
-        <v>3.97</v>
+        <v>5</v>
       </c>
       <c r="Q89">
+        <v>1.94</v>
+      </c>
+      <c r="R89">
+        <v>2.48</v>
+      </c>
+      <c r="S89">
+        <v>1.25</v>
+      </c>
+      <c r="T89">
+        <v>3.65</v>
+      </c>
+      <c r="U89">
         <v>2.32</v>
       </c>
-      <c r="R89">
-        <v>2.31</v>
-      </c>
-      <c r="S89">
-        <v>1.33</v>
-      </c>
-      <c r="T89">
-        <v>2.88</v>
-      </c>
-      <c r="U89">
-        <v>2.74</v>
-      </c>
       <c r="V89">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="W89">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z89">
-        <v>3.42</v>
+        <v>5.5</v>
       </c>
       <c r="AA89">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="AB89">
-        <v>1.93</v>
+        <v>2.43</v>
       </c>
       <c r="AC89">
-        <v>3.08</v>
+        <v>2.38</v>
       </c>
       <c r="AD89">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE89">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF89">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AG89">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK89">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15480,16 +15480,16 @@
         <v>4.2</v>
       </c>
       <c r="R93">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
         <v>1.36</v>
       </c>
       <c r="T93">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U93">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V93">
         <v>1.45</v>
@@ -15498,34 +15498,34 @@
         <v>1.07</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y93">
         <v>1.22</v>
       </c>
       <c r="Z93">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AA93">
         <v>1.8</v>
       </c>
       <c r="AB93">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC93">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD93">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE93">
         <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK93">
         <v>1.25</v>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="O94">
         <v>3.4</v>
@@ -15972,10 +15972,10 @@
         <v>1.91</v>
       </c>
       <c r="S96">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T96">
-        <v>2.48</v>
+        <v>2.69</v>
       </c>
       <c r="U96">
         <v>3.14</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O100">
         <v>3.4</v>
       </c>
       <c r="P100">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q100">
         <v>3.25</v>
@@ -16633,7 +16633,7 @@
         <v>2.29</v>
       </c>
       <c r="V100">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W100">
         <v>1.1</v>
@@ -16648,7 +16648,7 @@
         <v>4.5</v>
       </c>
       <c r="AA100">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB100">
         <v>2.25</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
         <v>1.35</v>
@@ -16787,7 +16787,7 @@
         <v>2.24</v>
       </c>
       <c r="S101">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T101">
         <v>3.1</v>
@@ -16845,7 +16845,7 @@
         <v>1.29</v>
       </c>
       <c r="AK101">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AK102">
         <v>1.36</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.47</v>
+        <v>2.95</v>
       </c>
       <c r="O103">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P103">
-        <v>5.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q103">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="R103">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S103">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U103">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="V103">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="W103">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="Z103">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA103">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB103">
-        <v>2.56</v>
+        <v>1.97</v>
       </c>
       <c r="AC103">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AD103">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE103">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF103">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG103">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK103">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>2.87</v>
+        <v>1.47</v>
       </c>
       <c r="O104">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="P104">
-        <v>2.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q104">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="R104">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T104">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U104">
-        <v>1.94</v>
+        <v>2.16</v>
       </c>
       <c r="V104">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="W104">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X104">
         <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z104">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA104">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB104">
-        <v>1.97</v>
+        <v>2.56</v>
       </c>
       <c r="AC104">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AD104">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE104">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF104">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG104">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK104">
-        <v>1.36</v>
+        <v>2.47</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17430,7 +17430,7 @@
         <v>3.75</v>
       </c>
       <c r="P105">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q105">
         <v>3.41</v>
@@ -18076,16 +18076,16 @@
         </is>
       </c>
       <c r="N109">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="O109">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P109">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Q109">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="R109">
         <v>2.88</v>
@@ -18097,37 +18097,37 @@
         <v>5</v>
       </c>
       <c r="U109">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V109">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="W109">
         <v>1.25</v>
       </c>
       <c r="X109">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y109">
         <v>1.03</v>
       </c>
       <c r="Z109">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA109">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AB109">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AC109">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AD109">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE109">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AF109">
         <v>1.42</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK109">
         <v>1.06</v>
@@ -18248,7 +18248,7 @@
         <v>1.55</v>
       </c>
       <c r="Q110">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R110">
         <v>2.31</v>
@@ -18408,7 +18408,7 @@
         <v>3.45</v>
       </c>
       <c r="P111">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q111">
         <v>2.4</v>
@@ -20358,13 +20358,13 @@
         </is>
       </c>
       <c r="N123">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O123">
         <v>3.57</v>
       </c>
       <c r="P123">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Q123">
         <v>2.88</v>
@@ -20376,7 +20376,7 @@
         <v>1.33</v>
       </c>
       <c r="T123">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="U123">
         <v>2.62</v>
@@ -20391,7 +20391,7 @@
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z123">
         <v>3.68</v>
@@ -20403,7 +20403,7 @@
         <v>1.91</v>
       </c>
       <c r="AC123">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="AD123">
         <v>1.36</v>
@@ -20533,46 +20533,46 @@
         <v>2.4</v>
       </c>
       <c r="R124">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S124">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T124">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="U124">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="V124">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W124">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X124">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y124">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z124">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA124">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB124">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC124">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AD124">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE124">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF124">
         <v>2.01</v>
@@ -20594,7 +20594,7 @@
         <v>1.25</v>
       </c>
       <c r="AK124">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL124">
         <v>0</v>
@@ -20684,64 +20684,64 @@
         </is>
       </c>
       <c r="N125">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O125">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P125">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q125">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R125">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S125">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="T125">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U125">
         <v>2.73</v>
       </c>
       <c r="V125">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W125">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X125">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y125">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z125">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA125">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB125">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC125">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD125">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE125">
         <v>1.06</v>
       </c>
       <c r="AF125">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG125">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -20754,10 +20754,10 @@
         </is>
       </c>
       <c r="AJ125">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK125">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AL125">
         <v>0</v>
@@ -20847,28 +20847,28 @@
         </is>
       </c>
       <c r="N126">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O126">
         <v>3.25</v>
       </c>
       <c r="P126">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q126">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R126">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S126">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T126">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U126">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V126">
         <v>1.38</v>
@@ -20877,34 +20877,34 @@
         <v>1.06</v>
       </c>
       <c r="X126">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y126">
         <v>1.25</v>
       </c>
       <c r="Z126">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AA126">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB126">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC126">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD126">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE126">
         <v>1.05</v>
       </c>
       <c r="AF126">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG126">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -20917,10 +20917,10 @@
         </is>
       </c>
       <c r="AJ126">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK126">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL126">
         <v>0</v>
@@ -21016,37 +21016,37 @@
         <v>3.4</v>
       </c>
       <c r="P127">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q127">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="R127">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S127">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T127">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U127">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="V127">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W127">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X127">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y127">
         <v>1.25</v>
       </c>
       <c r="Z127">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="AA127">
         <v>1.84</v>
@@ -21055,19 +21055,19 @@
         <v>1.83</v>
       </c>
       <c r="AC127">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD127">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE127">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF127">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG127">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         </is>
       </c>
       <c r="AJ127">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK127">
         <v>1.25</v>
@@ -21345,10 +21345,10 @@
         <v>2.43</v>
       </c>
       <c r="Q129">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="R129">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S129">
         <v>1.22</v>
@@ -21375,16 +21375,16 @@
         <v>6</v>
       </c>
       <c r="AA129">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB129">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC129">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD129">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE129">
         <v>1.25</v>
@@ -21393,7 +21393,7 @@
         <v>1.4</v>
       </c>
       <c r="AG129">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="O130">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P130">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q130">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="R130">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="S130">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T130">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U130">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="V130">
+        <v>1.5</v>
+      </c>
+      <c r="W130">
+        <v>1.11</v>
+      </c>
+      <c r="X130">
+        <v>1</v>
+      </c>
+      <c r="Y130">
+        <v>1.17</v>
+      </c>
+      <c r="Z130">
+        <v>4.24</v>
+      </c>
+      <c r="AA130">
+        <v>1.7</v>
+      </c>
+      <c r="AB130">
+        <v>2.1</v>
+      </c>
+      <c r="AC130">
+        <v>2.56</v>
+      </c>
+      <c r="AD130">
         <v>1.4</v>
       </c>
-      <c r="W130">
-        <v>1.08</v>
-      </c>
-      <c r="X130">
-        <v>1.01</v>
-      </c>
-      <c r="Y130">
-        <v>1.25</v>
-      </c>
-      <c r="Z130">
-        <v>3.28</v>
-      </c>
-      <c r="AA130">
-        <v>1.9</v>
-      </c>
-      <c r="AB130">
-        <v>1.9</v>
-      </c>
-      <c r="AC130">
-        <v>3.14</v>
-      </c>
-      <c r="AD130">
-        <v>1.27</v>
-      </c>
       <c r="AE130">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF130">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG130">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK130">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="O131">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P131">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="Q131">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="R131">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="S131">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T131">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U131">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="V131">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W131">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X131">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y131">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z131">
-        <v>4.24</v>
+        <v>3.5</v>
       </c>
       <c r="AA131">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB131">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC131">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="AD131">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE131">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF131">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG131">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK131">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -21994,7 +21994,7 @@
         <v>3.8</v>
       </c>
       <c r="P133">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="Q133">
         <v>2.08</v>
@@ -22021,7 +22021,7 @@
         <v>1</v>
       </c>
       <c r="Y133">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z133">
         <v>3.34</v>
@@ -22154,10 +22154,10 @@
         <v>1.95</v>
       </c>
       <c r="O134">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P134">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q134">
         <v>2.63</v>
@@ -22507,13 +22507,13 @@
         <v>1.08</v>
       </c>
       <c r="X136">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y136">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z136">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA136">
         <v>1.94</v>
@@ -22522,7 +22522,7 @@
         <v>1.74</v>
       </c>
       <c r="AC136">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AD136">
         <v>1.28</v>
@@ -22646,7 +22646,7 @@
         <v>3.5</v>
       </c>
       <c r="P137">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="Q137">
         <v>2.2</v>
@@ -22713,7 +22713,7 @@
         <v>1.18</v>
       </c>
       <c r="AK137">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AL137">
         <v>0</v>
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="G138">
@@ -22803,64 +22803,64 @@
         </is>
       </c>
       <c r="N138">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="O138">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P138">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q138">
-        <v>2.13</v>
+        <v>3.42</v>
       </c>
       <c r="R138">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="S138">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T138">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="U138">
-        <v>2.4</v>
+        <v>2.99</v>
       </c>
       <c r="V138">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W138">
         <v>1.08</v>
       </c>
       <c r="X138">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z138">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="AA138">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AB138">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AC138">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="AD138">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE138">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF138">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AG138">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AH138" t="inlineStr">
         <is>
@@ -22873,10 +22873,10 @@
         </is>
       </c>
       <c r="AJ138">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK138">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AL138">
         <v>0</v>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G139">
@@ -22966,64 +22966,64 @@
         </is>
       </c>
       <c r="N139">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="O139">
-        <v>3.08</v>
+        <v>3.8</v>
       </c>
       <c r="P139">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q139">
-        <v>3.42</v>
+        <v>2.13</v>
       </c>
       <c r="R139">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="S139">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T139">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="U139">
-        <v>2.99</v>
+        <v>2.4</v>
       </c>
       <c r="V139">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W139">
         <v>1.08</v>
       </c>
       <c r="X139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y139">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z139">
-        <v>3.28</v>
+        <v>4.2</v>
       </c>
       <c r="AA139">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AB139">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="AC139">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD139">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE139">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF139">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG139">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH139" t="inlineStr">
         <is>
@@ -23036,10 +23036,10 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK139">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="AL139">
         <v>0</v>
@@ -23132,7 +23132,7 @@
         <v>2.25</v>
       </c>
       <c r="O140">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P140">
         <v>3.1</v>
@@ -23618,10 +23618,10 @@
         </is>
       </c>
       <c r="N143">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O143">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P143">
         <v>2.2</v>
@@ -23781,13 +23781,13 @@
         </is>
       </c>
       <c r="N144">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="O144">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P144">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q144">
         <v>4</v>
@@ -24270,10 +24270,10 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O147">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P147">
         <v>2.61</v>
@@ -24312,7 +24312,7 @@
         <v>1.55</v>
       </c>
       <c r="AB147">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AC147">
         <v>2.3</v>
@@ -24433,64 +24433,64 @@
         </is>
       </c>
       <c r="N148">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="O148">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P148">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Q148">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R148">
-        <v>2.51</v>
+        <v>2.57</v>
       </c>
       <c r="S148">
         <v>1.22</v>
       </c>
       <c r="T148">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U148">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="V148">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W148">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X148">
         <v>1.02</v>
       </c>
       <c r="Y148">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z148">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="AA148">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB148">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="AC148">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD148">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AE148">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AF148">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG148">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH148" t="inlineStr">
         <is>
@@ -24503,10 +24503,10 @@
         </is>
       </c>
       <c r="AJ148">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK148">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AL148">
         <v>0</v>
@@ -24666,10 +24666,10 @@
         </is>
       </c>
       <c r="AJ149">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK149">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AL149">
         <v>0</v>
@@ -24759,7 +24759,7 @@
         </is>
       </c>
       <c r="N150">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="O150">
         <v>4.8</v>
@@ -25290,7 +25290,7 @@
         <v>2.29</v>
       </c>
       <c r="AB153">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AC153">
         <v>4.5</v>
@@ -25321,7 +25321,7 @@
         <v>1.29</v>
       </c>
       <c r="AK153">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AL153">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         </is>
       </c>
       <c r="N158">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O158">
         <v>3.5</v>
@@ -26431,7 +26431,7 @@
         <v>1.53</v>
       </c>
       <c r="AB160">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC160">
         <v>2.27</v>
@@ -26570,16 +26570,16 @@
         <v>1.2</v>
       </c>
       <c r="T161">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U161">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V161">
         <v>1.7</v>
       </c>
       <c r="W161">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X161">
         <v>1.01</v>
@@ -26715,10 +26715,10 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O162">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P162">
         <v>2.62</v>
@@ -26881,10 +26881,10 @@
         <v>1.79</v>
       </c>
       <c r="O163">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P163">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q163">
         <v>2.25</v>
@@ -27207,7 +27207,7 @@
         <v>1.88</v>
       </c>
       <c r="O165">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P165">
         <v>3.4</v>
@@ -27367,10 +27367,10 @@
         </is>
       </c>
       <c r="N166">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O166">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P166">
         <v>2.2</v>
@@ -27708,7 +27708,7 @@
         <v>2.5</v>
       </c>
       <c r="S168">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T168">
         <v>3.14</v>
@@ -27717,10 +27717,10 @@
         <v>2.4</v>
       </c>
       <c r="V168">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W168">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X168">
         <v>1</v>
@@ -27729,28 +27729,28 @@
         <v>1.19</v>
       </c>
       <c r="Z168">
-        <v>4.19</v>
+        <v>3.89</v>
       </c>
       <c r="AA168">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB168">
         <v>2.02</v>
       </c>
       <c r="AC168">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="AD168">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE168">
         <v>1.11</v>
       </c>
       <c r="AF168">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG168">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH168" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         </is>
       </c>
       <c r="AJ168">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK168">
         <v>1.04</v>
@@ -27987,12 +27987,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G170">
@@ -28019,64 +28019,64 @@
         </is>
       </c>
       <c r="N170">
-        <v>3</v>
+        <v>1.78</v>
       </c>
       <c r="O170">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P170">
-        <v>2.15</v>
+        <v>3.76</v>
       </c>
       <c r="Q170">
-        <v>3.08</v>
+        <v>2.22</v>
       </c>
       <c r="R170">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="S170">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T170">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="U170">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="V170">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="W170">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X170">
         <v>1</v>
       </c>
       <c r="Y170">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z170">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA170">
+        <v>1.28</v>
+      </c>
+      <c r="AB170">
+        <v>3.52</v>
+      </c>
+      <c r="AC170">
+        <v>1.79</v>
+      </c>
+      <c r="AD170">
+        <v>2.05</v>
+      </c>
+      <c r="AE170">
         <v>1.44</v>
       </c>
-      <c r="AB170">
-        <v>2.63</v>
-      </c>
-      <c r="AC170">
-        <v>2.23</v>
-      </c>
-      <c r="AD170">
-        <v>1.67</v>
-      </c>
-      <c r="AE170">
-        <v>1.25</v>
-      </c>
       <c r="AF170">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG170">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AH170" t="inlineStr">
         <is>
@@ -28089,10 +28089,10 @@
         </is>
       </c>
       <c r="AJ170">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="AK170">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="AL170">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>1.78</v>
+        <v>3</v>
       </c>
       <c r="O171">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P171">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="Q171">
-        <v>2.22</v>
+        <v>3.08</v>
       </c>
       <c r="R171">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="S171">
+        <v>1.22</v>
+      </c>
+      <c r="T171">
+        <v>4</v>
+      </c>
+      <c r="U171">
+        <v>2.17</v>
+      </c>
+      <c r="V171">
+        <v>1.71</v>
+      </c>
+      <c r="W171">
         <v>1.18</v>
-      </c>
-      <c r="T171">
-        <v>4.8</v>
-      </c>
-      <c r="U171">
-        <v>1.85</v>
-      </c>
-      <c r="V171">
-        <v>1.91</v>
-      </c>
-      <c r="W171">
-        <v>1.29</v>
       </c>
       <c r="X171">
         <v>1</v>
       </c>
       <c r="Y171">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z171">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA171">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AB171">
-        <v>3.52</v>
+        <v>2.63</v>
       </c>
       <c r="AC171">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="AD171">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AE171">
+        <v>1.25</v>
+      </c>
+      <c r="AF171">
         <v>1.44</v>
       </c>
-      <c r="AF171">
-        <v>1.3</v>
-      </c>
       <c r="AG171">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.22</v>
+        <v>1.72</v>
       </c>
       <c r="AK171">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -29036,7 +29036,7 @@
         <v>7</v>
       </c>
       <c r="AA176">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB176">
         <v>3</v>
@@ -29160,10 +29160,10 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O177">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P177">
         <v>3.4</v>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="N180">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="O180">
         <v>3.35</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G182">
@@ -29975,64 +29975,64 @@
         </is>
       </c>
       <c r="N182">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O182">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P182">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="Q182">
         <v>2.62</v>
       </c>
       <c r="R182">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S182">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T182">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U182">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V182">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W182">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X182">
         <v>1.02</v>
       </c>
       <c r="Y182">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z182">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA182">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AB182">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC182">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AD182">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AE182">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF182">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG182">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK182">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O183">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P183">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="Q183">
+        <v>2.62</v>
+      </c>
+      <c r="R183">
         <v>2.5</v>
       </c>
-      <c r="R183">
-        <v>2.25</v>
-      </c>
       <c r="S183">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T183">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U183">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="V183">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W183">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X183">
         <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z183">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA183">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AB183">
-        <v>2.17</v>
+        <v>2.5</v>
       </c>
       <c r="AC183">
-        <v>2.46</v>
+        <v>2.27</v>
       </c>
       <c r="AD183">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AE183">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AF183">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AG183">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK183">
         <v>1.67</v>
@@ -30627,13 +30627,13 @@
         </is>
       </c>
       <c r="N186">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O186">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q186">
         <v>0</v>
@@ -30666,10 +30666,10 @@
         <v>0</v>
       </c>
       <c r="AA186">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB186">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC186">
         <v>0</v>
@@ -30953,13 +30953,13 @@
         </is>
       </c>
       <c r="N188">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="O188">
+        <v>2.58</v>
+      </c>
+      <c r="P188">
         <v>2.6</v>
-      </c>
-      <c r="P188">
-        <v>2.57</v>
       </c>
       <c r="Q188">
         <v>3.75</v>
@@ -31306,7 +31306,7 @@
         <v>1.33</v>
       </c>
       <c r="W190">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X190">
         <v>1.03</v>
@@ -31445,10 +31445,10 @@
         <v>3.7</v>
       </c>
       <c r="O191">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P191">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q191">
         <v>4.1</v>
@@ -31475,16 +31475,16 @@
         <v>1.03</v>
       </c>
       <c r="Y191">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z191">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA191">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB191">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC191">
         <v>4.05</v>
@@ -31493,7 +31493,7 @@
         <v>1.19</v>
       </c>
       <c r="AE191">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF191">
         <v>1.95</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,65 +31768,65 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O193">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P193">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q193">
-        <v>2.61</v>
+        <v>2.28</v>
       </c>
       <c r="R193">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S193">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="T193">
-        <v>2.51</v>
+        <v>2.89</v>
       </c>
       <c r="U193">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="V193">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="W193">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X193">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y193">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="Z193">
-        <v>2.79</v>
+        <v>3.84</v>
       </c>
       <c r="AA193">
+        <v>1.73</v>
+      </c>
+      <c r="AB193">
+        <v>2.1</v>
+      </c>
+      <c r="AC193">
+        <v>2.7</v>
+      </c>
+      <c r="AD193">
+        <v>1.41</v>
+      </c>
+      <c r="AE193">
+        <v>1.13</v>
+      </c>
+      <c r="AF193">
+        <v>1.62</v>
+      </c>
+      <c r="AG193">
         <v>2.15</v>
       </c>
-      <c r="AB193">
-        <v>1.67</v>
-      </c>
-      <c r="AC193">
-        <v>3.82</v>
-      </c>
-      <c r="AD193">
-        <v>1.22</v>
-      </c>
-      <c r="AE193">
-        <v>1.07</v>
-      </c>
-      <c r="AF193">
-        <v>1.83</v>
-      </c>
-      <c r="AG193">
-        <v>1.85</v>
-      </c>
       <c r="AH193" t="inlineStr">
         <is>
           <t>[]</t>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AK193">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,65 +31931,65 @@
         </is>
       </c>
       <c r="N194">
+        <v>1.7</v>
+      </c>
+      <c r="O194">
+        <v>3.7</v>
+      </c>
+      <c r="P194">
+        <v>3.95</v>
+      </c>
+      <c r="Q194">
+        <v>2.14</v>
+      </c>
+      <c r="R194">
+        <v>2.5</v>
+      </c>
+      <c r="S194">
+        <v>1.25</v>
+      </c>
+      <c r="T194">
+        <v>3.6</v>
+      </c>
+      <c r="U194">
+        <v>2.19</v>
+      </c>
+      <c r="V194">
+        <v>1.55</v>
+      </c>
+      <c r="W194">
+        <v>1.13</v>
+      </c>
+      <c r="X194">
+        <v>1.01</v>
+      </c>
+      <c r="Y194">
+        <v>1.14</v>
+      </c>
+      <c r="Z194">
+        <v>4.45</v>
+      </c>
+      <c r="AA194">
+        <v>1.57</v>
+      </c>
+      <c r="AB194">
+        <v>2.38</v>
+      </c>
+      <c r="AC194">
+        <v>2.52</v>
+      </c>
+      <c r="AD194">
+        <v>1.51</v>
+      </c>
+      <c r="AE194">
+        <v>1.19</v>
+      </c>
+      <c r="AF194">
+        <v>1.53</v>
+      </c>
+      <c r="AG194">
         <v>2.3</v>
       </c>
-      <c r="O194">
-        <v>3.4</v>
-      </c>
-      <c r="P194">
-        <v>2.69</v>
-      </c>
-      <c r="Q194">
-        <v>2.9</v>
-      </c>
-      <c r="R194">
-        <v>2.2</v>
-      </c>
-      <c r="S194">
-        <v>1.3</v>
-      </c>
-      <c r="T194">
-        <v>3.3</v>
-      </c>
-      <c r="U194">
-        <v>2.3</v>
-      </c>
-      <c r="V194">
-        <v>1.47</v>
-      </c>
-      <c r="W194">
-        <v>1.12</v>
-      </c>
-      <c r="X194">
-        <v>1.03</v>
-      </c>
-      <c r="Y194">
-        <v>1.2</v>
-      </c>
-      <c r="Z194">
-        <v>4.1</v>
-      </c>
-      <c r="AA194">
-        <v>1.73</v>
-      </c>
-      <c r="AB194">
-        <v>2.1</v>
-      </c>
-      <c r="AC194">
-        <v>2.7</v>
-      </c>
-      <c r="AD194">
-        <v>1.36</v>
-      </c>
-      <c r="AE194">
-        <v>1.13</v>
-      </c>
-      <c r="AF194">
-        <v>1.55</v>
-      </c>
-      <c r="AG194">
-        <v>2.25</v>
-      </c>
       <c r="AH194" t="inlineStr">
         <is>
           <t>[]</t>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="AK194">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="O195">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P195">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q195">
-        <v>2.14</v>
+        <v>2.76</v>
       </c>
       <c r="R195">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="S195">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T195">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="U195">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="V195">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W195">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X195">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y195">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z195">
-        <v>4.45</v>
+        <v>2.79</v>
       </c>
       <c r="AA195">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB195">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC195">
-        <v>2.52</v>
+        <v>3.82</v>
       </c>
       <c r="AD195">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AE195">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF195">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AG195">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AK195">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,43 +32257,43 @@
         </is>
       </c>
       <c r="N196">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O196">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P196">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="Q196">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="R196">
         <v>2.2</v>
       </c>
       <c r="S196">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T196">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="U196">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V196">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W196">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X196">
         <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z196">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA196">
         <v>1.73</v>
@@ -32305,16 +32305,16 @@
         <v>2.7</v>
       </c>
       <c r="AD196">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE196">
         <v>1.13</v>
       </c>
       <c r="AF196">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG196">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AK196">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="N197">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="O197">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P197">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q197">
         <v>3.3</v>
@@ -32592,7 +32592,7 @@
         <v>4.4</v>
       </c>
       <c r="Q198">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="R198">
         <v>2.41</v>
@@ -32616,7 +32616,7 @@
         <v>1.02</v>
       </c>
       <c r="Y198">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z198">
         <v>3.8</v>
@@ -32628,7 +32628,7 @@
         <v>2.1</v>
       </c>
       <c r="AC198">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="AD198">
         <v>1.4</v>
@@ -32746,16 +32746,16 @@
         </is>
       </c>
       <c r="N199">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O199">
         <v>3.3</v>
       </c>
       <c r="P199">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q199">
-        <v>3.26</v>
+        <v>3.06</v>
       </c>
       <c r="R199">
         <v>2.2</v>
@@ -32764,13 +32764,13 @@
         <v>1.33</v>
       </c>
       <c r="T199">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U199">
         <v>2.53</v>
       </c>
       <c r="V199">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W199">
         <v>1.06</v>
@@ -32782,7 +32782,7 @@
         <v>1.22</v>
       </c>
       <c r="Z199">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="AA199">
         <v>1.8</v>
@@ -32816,10 +32816,10 @@
         </is>
       </c>
       <c r="AJ199">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AK199">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL199">
         <v>0</v>
@@ -33407,7 +33407,7 @@
         <v>2.75</v>
       </c>
       <c r="Q203">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R203">
         <v>2.05</v>
@@ -33579,10 +33579,10 @@
         <v>1.36</v>
       </c>
       <c r="T204">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U204">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V204">
         <v>1.39</v>
@@ -33724,13 +33724,13 @@
         </is>
       </c>
       <c r="N205">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O205">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P205">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q205">
         <v>2.11</v>
@@ -33766,7 +33766,7 @@
         <v>2.2</v>
       </c>
       <c r="AB205">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC205">
         <v>3.8</v>
@@ -34089,7 +34089,7 @@
         <v>2.59</v>
       </c>
       <c r="AA207">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AB207">
         <v>1.53</v>
@@ -34104,7 +34104,7 @@
         <v>1.05</v>
       </c>
       <c r="AF207">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG207">
         <v>1.7</v>
@@ -34225,7 +34225,7 @@
         <v>2.93</v>
       </c>
       <c r="R208">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="S208">
         <v>1.36</v>
@@ -34270,7 +34270,7 @@
         <v>1.74</v>
       </c>
       <c r="AG208">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>2.02</v>
       </c>
       <c r="AB209">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC209">
         <v>3.28</v>
@@ -34539,7 +34539,7 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="O210">
         <v>3.15</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="O211">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="P211">
-        <v>4.1</v>
+        <v>9.25</v>
       </c>
       <c r="Q211">
-        <v>2.01</v>
+        <v>1.64</v>
       </c>
       <c r="R211">
-        <v>2.51</v>
+        <v>2.84</v>
       </c>
       <c r="S211">
         <v>1.2</v>
       </c>
       <c r="T211">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="U211">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V211">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W211">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X211">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y211">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z211">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA211">
         <v>1.44</v>
       </c>
       <c r="AB211">
-        <v>2.51</v>
+        <v>2.88</v>
       </c>
       <c r="AC211">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AD211">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AE211">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF211">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AG211">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK211">
-        <v>2.08</v>
+        <v>3.74</v>
       </c>
       <c r="AL211">
         <v>0</v>
@@ -34833,12 +34833,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G212">
@@ -34865,64 +34865,64 @@
         </is>
       </c>
       <c r="N212">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="O212">
-        <v>5.75</v>
+        <v>3.7</v>
       </c>
       <c r="P212">
-        <v>9.25</v>
+        <v>4.33</v>
       </c>
       <c r="Q212">
-        <v>1.64</v>
+        <v>2.23</v>
       </c>
       <c r="R212">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="S212">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T212">
-        <v>3.92</v>
+        <v>3</v>
       </c>
       <c r="U212">
-        <v>2.02</v>
+        <v>2.57</v>
       </c>
       <c r="V212">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="W212">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="X212">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y212">
+        <v>1.22</v>
+      </c>
+      <c r="Z212">
+        <v>3.71</v>
+      </c>
+      <c r="AA212">
+        <v>1.89</v>
+      </c>
+      <c r="AB212">
+        <v>1.93</v>
+      </c>
+      <c r="AC212">
+        <v>2.91</v>
+      </c>
+      <c r="AD212">
+        <v>1.34</v>
+      </c>
+      <c r="AE212">
         <v>1.08</v>
-      </c>
-      <c r="Z212">
-        <v>5.65</v>
-      </c>
-      <c r="AA212">
-        <v>1.44</v>
-      </c>
-      <c r="AB212">
-        <v>2.88</v>
-      </c>
-      <c r="AC212">
-        <v>2.11</v>
-      </c>
-      <c r="AD212">
-        <v>1.72</v>
-      </c>
-      <c r="AE212">
-        <v>1.3</v>
       </c>
       <c r="AF212">
         <v>1.74</v>
       </c>
       <c r="AG212">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
@@ -34935,10 +34935,10 @@
         </is>
       </c>
       <c r="AJ212">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK212">
-        <v>3.74</v>
+        <v>1.99</v>
       </c>
       <c r="AL212">
         <v>0</v>
@@ -34996,12 +34996,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G213">
@@ -35028,64 +35028,64 @@
         </is>
       </c>
       <c r="N213">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="O213">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P213">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q213">
-        <v>2.23</v>
+        <v>3.02</v>
       </c>
       <c r="R213">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="S213">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T213">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="U213">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="V213">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="W213">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X213">
         <v>1.02</v>
       </c>
       <c r="Y213">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z213">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AA213">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AB213">
-        <v>2.42</v>
+        <v>2.04</v>
       </c>
       <c r="AC213">
-        <v>2.25</v>
+        <v>3.02</v>
       </c>
       <c r="AD213">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AE213">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AF213">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AG213">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AH213" t="inlineStr">
         <is>
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="AJ213">
-        <v>1.17</v>
+        <v>1.51</v>
       </c>
       <c r="AK213">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL213">
         <v>0</v>
@@ -35159,12 +35159,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G214">
@@ -35191,64 +35191,64 @@
         </is>
       </c>
       <c r="N214">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="O214">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="P214">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="Q214">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="R214">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="S214">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T214">
-        <v>3</v>
+        <v>3.74</v>
       </c>
       <c r="U214">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="V214">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W214">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X214">
         <v>1.02</v>
       </c>
       <c r="Y214">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z214">
-        <v>3.76</v>
+        <v>5.5</v>
       </c>
       <c r="AA214">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AB214">
-        <v>1.93</v>
+        <v>2.51</v>
       </c>
       <c r="AC214">
-        <v>2.89</v>
+        <v>2.08</v>
       </c>
       <c r="AD214">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="AE214">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AF214">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AG214">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AH214" t="inlineStr">
         <is>
@@ -35261,10 +35261,10 @@
         </is>
       </c>
       <c r="AJ214">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK214">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL214">
         <v>0</v>
@@ -35322,12 +35322,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G215">
@@ -35354,64 +35354,64 @@
         </is>
       </c>
       <c r="N215">
-        <v>2.87</v>
+        <v>1.8</v>
       </c>
       <c r="O215">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P215">
+        <v>4</v>
+      </c>
+      <c r="Q215">
+        <v>2.33</v>
+      </c>
+      <c r="R215">
+        <v>2.34</v>
+      </c>
+      <c r="S215">
+        <v>1.25</v>
+      </c>
+      <c r="T215">
+        <v>3.6</v>
+      </c>
+      <c r="U215">
+        <v>2.25</v>
+      </c>
+      <c r="V215">
+        <v>1.6</v>
+      </c>
+      <c r="W215">
+        <v>1.15</v>
+      </c>
+      <c r="X215">
+        <v>1.01</v>
+      </c>
+      <c r="Y215">
+        <v>1.17</v>
+      </c>
+      <c r="Z215">
+        <v>5</v>
+      </c>
+      <c r="AA215">
+        <v>1.59</v>
+      </c>
+      <c r="AB215">
         <v>2.3</v>
       </c>
-      <c r="Q215">
-        <v>3.46</v>
-      </c>
-      <c r="R215">
-        <v>2.18</v>
-      </c>
-      <c r="S215">
-        <v>1.35</v>
-      </c>
-      <c r="T215">
-        <v>3.2</v>
-      </c>
-      <c r="U215">
-        <v>2.47</v>
-      </c>
-      <c r="V215">
-        <v>1.46</v>
-      </c>
-      <c r="W215">
-        <v>1.07</v>
-      </c>
-      <c r="X215">
-        <v>1.02</v>
-      </c>
-      <c r="Y215">
-        <v>1.2</v>
-      </c>
-      <c r="Z215">
-        <v>3.7</v>
-      </c>
-      <c r="AA215">
-        <v>1.78</v>
-      </c>
-      <c r="AB215">
-        <v>2.04</v>
-      </c>
       <c r="AC215">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="AD215">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AE215">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF215">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="AG215">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AH215" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         </is>
       </c>
       <c r="AJ215">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="AK215">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="AL215">
         <v>0</v>
@@ -35692,7 +35692,7 @@
         <v>2.5</v>
       </c>
       <c r="R217">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="S217">
         <v>1.35</v>
@@ -36332,13 +36332,13 @@
         </is>
       </c>
       <c r="N221">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O221">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="P221">
-        <v>2.81</v>
+        <v>2.53</v>
       </c>
       <c r="Q221">
         <v>2.9</v>
@@ -38684,7 +38684,7 @@
         </is>
       </c>
       <c r="AJ235">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK235">
         <v>2.12</v>
@@ -38777,10 +38777,10 @@
         </is>
       </c>
       <c r="N236">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O236">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="P236">
         <v>2.6</v>
@@ -39429,13 +39429,13 @@
         </is>
       </c>
       <c r="N240">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="O240">
         <v>3.7</v>
       </c>
       <c r="P240">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q240">
         <v>3.75</v>
@@ -39592,16 +39592,16 @@
         </is>
       </c>
       <c r="N241">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="O241">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="P241">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="Q241">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R241">
         <v>2.2</v>
@@ -39613,10 +39613,10 @@
         <v>3.25</v>
       </c>
       <c r="U241">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="V241">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W241">
         <v>1.11</v>
@@ -39625,25 +39625,25 @@
         <v>1.01</v>
       </c>
       <c r="Y241">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z241">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA241">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB241">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC241">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AD241">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE241">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF241">
         <v>1.62</v>
@@ -39662,10 +39662,10 @@
         </is>
       </c>
       <c r="AJ241">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK241">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AL241">
         <v>0</v>
@@ -39761,13 +39761,13 @@
         <v>3.33</v>
       </c>
       <c r="P242">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q242">
         <v>2.77</v>
       </c>
       <c r="R242">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S242">
         <v>1.36</v>
@@ -40212,12 +40212,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G245">
@@ -40244,64 +40244,64 @@
         </is>
       </c>
       <c r="N245">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O245">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="P245">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q245">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="R245">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="S245">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T245">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="U245">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="V245">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W245">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X245">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y245">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="Z245">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA245">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AB245">
-        <v>1.44</v>
+        <v>1.87</v>
       </c>
       <c r="AC245">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD245">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AE245">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AF245">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AG245">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AH245" t="inlineStr">
         <is>
@@ -40314,10 +40314,10 @@
         </is>
       </c>
       <c r="AJ245">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AK245">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AL245">
         <v>0</v>
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G246">
@@ -40407,64 +40407,64 @@
         </is>
       </c>
       <c r="N246">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="O246">
+        <v>3</v>
+      </c>
+      <c r="P246">
         <v>3.25</v>
       </c>
-      <c r="P246">
-        <v>3.15</v>
-      </c>
       <c r="Q246">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="R246">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S246">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T246">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="U246">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="V246">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="W246">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X246">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y246">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="Z246">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="AA246">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AB246">
-        <v>1.87</v>
+        <v>1.44</v>
       </c>
       <c r="AC246">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD246">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AE246">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF246">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AG246">
-        <v>1.95</v>
+        <v>1.64</v>
       </c>
       <c r="AH246" t="inlineStr">
         <is>
@@ -40477,10 +40477,10 @@
         </is>
       </c>
       <c r="AJ246">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AK246">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AL246">
         <v>0</v>
@@ -40733,13 +40733,13 @@
         </is>
       </c>
       <c r="N248">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O248">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P248">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q248">
         <v>2.59</v>
@@ -40929,31 +40929,31 @@
         <v>1</v>
       </c>
       <c r="Y249">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z249">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="AA249">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB249">
         <v>2.15</v>
       </c>
       <c r="AC249">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AD249">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE249">
         <v>1.1</v>
       </c>
       <c r="AF249">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG249">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH249" t="inlineStr">
         <is>
@@ -41228,10 +41228,10 @@
         <v>3.4</v>
       </c>
       <c r="P251">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q251">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="R251">
         <v>2.12</v>
@@ -41391,7 +41391,7 @@
         <v>3.5</v>
       </c>
       <c r="P252">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q252">
         <v>2.25</v>
@@ -41548,7 +41548,7 @@
         </is>
       </c>
       <c r="N253">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O253">
         <v>3.4</v>
@@ -41593,7 +41593,7 @@
         <v>1.87</v>
       </c>
       <c r="AC253">
-        <v>3.14</v>
+        <v>3.47</v>
       </c>
       <c r="AD253">
         <v>1.27</v>
@@ -41877,10 +41877,10 @@
         <v>3</v>
       </c>
       <c r="O255">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P255">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q255">
         <v>3.7</v>
@@ -41922,13 +41922,13 @@
         <v>2.01</v>
       </c>
       <c r="AD255">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AE255">
         <v>1.25</v>
       </c>
       <c r="AF255">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG255">
         <v>2.8</v>
@@ -42052,7 +42052,7 @@
         <v>2.56</v>
       </c>
       <c r="S256">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T256">
         <v>3.9</v>
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="N261">
-        <v>8.699999999999999</v>
+        <v>17</v>
       </c>
       <c r="O261">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="P261">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Q261">
         <v>8.5</v>
@@ -42867,7 +42867,7 @@
         <v>2.88</v>
       </c>
       <c r="S261">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T261">
         <v>4.1</v>
@@ -42888,7 +42888,7 @@
         <v>1.08</v>
       </c>
       <c r="Z261">
-        <v>6.32</v>
+        <v>6.03</v>
       </c>
       <c r="AA261">
         <v>1.5</v>
@@ -42922,7 +42922,7 @@
         </is>
       </c>
       <c r="AJ261">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AK261">
         <v>1.04</v>
@@ -43217,10 +43217,10 @@
         <v>2.92</v>
       </c>
       <c r="AA263">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB263">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC263">
         <v>3.5</v>
@@ -44684,7 +44684,7 @@
         <v>3.58</v>
       </c>
       <c r="AA272">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB272">
         <v>1.88</v>
@@ -44998,10 +44998,10 @@
         <v>1.5</v>
       </c>
       <c r="W274">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X274">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y274">
         <v>1.18</v>
@@ -45025,10 +45025,10 @@
         <v>1.12</v>
       </c>
       <c r="AF274">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG274">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH274" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>2.15</v>
       </c>
       <c r="O276">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P276">
         <v>3.1</v>
@@ -45463,13 +45463,13 @@
         <v>1.95</v>
       </c>
       <c r="O277">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P277">
         <v>3.6</v>
       </c>
       <c r="Q277">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R277">
         <v>2.05</v>
@@ -45478,19 +45478,19 @@
         <v>1.38</v>
       </c>
       <c r="T277">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U277">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V277">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W277">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X277">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y277">
         <v>1.31</v>
@@ -45502,16 +45502,16 @@
         <v>2.07</v>
       </c>
       <c r="AB277">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC277">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD277">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE277">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF277">
         <v>1.85</v>
@@ -45638,10 +45638,10 @@
         <v>1.87</v>
       </c>
       <c r="S278">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T278">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="U278">
         <v>3.06</v>
@@ -45662,10 +45662,10 @@
         <v>2.62</v>
       </c>
       <c r="AA278">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AB278">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC278">
         <v>4.1</v>
@@ -46169,7 +46169,7 @@
         <v>1.33</v>
       </c>
       <c r="AG281">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AH281" t="inlineStr">
         <is>
@@ -46895,12 +46895,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="G286">
@@ -46927,64 +46927,64 @@
         </is>
       </c>
       <c r="N286">
+        <v>2.4</v>
+      </c>
+      <c r="O286">
+        <v>3.8</v>
+      </c>
+      <c r="P286">
+        <v>2.37</v>
+      </c>
+      <c r="Q286">
+        <v>2.9</v>
+      </c>
+      <c r="R286">
+        <v>2.5</v>
+      </c>
+      <c r="S286">
+        <v>1.2</v>
+      </c>
+      <c r="T286">
+        <v>4.2</v>
+      </c>
+      <c r="U286">
+        <v>1.95</v>
+      </c>
+      <c r="V286">
         <v>1.75</v>
       </c>
-      <c r="O286">
-        <v>3.7</v>
-      </c>
-      <c r="P286">
-        <v>3.6</v>
-      </c>
-      <c r="Q286">
-        <v>2.17</v>
-      </c>
-      <c r="R286">
-        <v>2.36</v>
-      </c>
-      <c r="S286">
+      <c r="W286">
         <v>1.22</v>
       </c>
-      <c r="T286">
-        <v>3.8</v>
-      </c>
-      <c r="U286">
-        <v>2.07</v>
-      </c>
-      <c r="V286">
-        <v>1.64</v>
-      </c>
-      <c r="W286">
-        <v>1.18</v>
-      </c>
       <c r="X286">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y286">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z286">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA286">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AB286">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AC286">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD286">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE286">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF286">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG286">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AH286" t="inlineStr">
         <is>
@@ -47000,7 +47000,7 @@
         <v>1.22</v>
       </c>
       <c r="AK286">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AL286">
         <v>0</v>
@@ -47058,12 +47058,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G287">
@@ -47090,64 +47090,64 @@
         </is>
       </c>
       <c r="N287">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="O287">
+        <v>3.7</v>
+      </c>
+      <c r="P287">
+        <v>3.6</v>
+      </c>
+      <c r="Q287">
+        <v>2.17</v>
+      </c>
+      <c r="R287">
+        <v>2.36</v>
+      </c>
+      <c r="S287">
+        <v>1.22</v>
+      </c>
+      <c r="T287">
         <v>3.8</v>
       </c>
-      <c r="P287">
-        <v>2.37</v>
-      </c>
-      <c r="Q287">
-        <v>2.9</v>
-      </c>
-      <c r="R287">
-        <v>2.5</v>
-      </c>
-      <c r="S287">
-        <v>1.2</v>
-      </c>
-      <c r="T287">
-        <v>4.2</v>
-      </c>
       <c r="U287">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="V287">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="W287">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X287">
         <v>1.01</v>
       </c>
       <c r="Y287">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z287">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA287">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AB287">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AC287">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD287">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE287">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF287">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG287">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AH287" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>1.22</v>
       </c>
       <c r="AK287">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="AL287">
         <v>0</v>
@@ -47253,16 +47253,16 @@
         </is>
       </c>
       <c r="N288">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O288">
         <v>3.6</v>
       </c>
       <c r="P288">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q288">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R288">
         <v>2.3</v>
@@ -47588,22 +47588,22 @@
         <v>17</v>
       </c>
       <c r="Q290">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="R290">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="S290">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T290">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="U290">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="V290">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="W290">
         <v>1.29</v>
@@ -47621,7 +47621,7 @@
         <v>1.23</v>
       </c>
       <c r="AB290">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC290">
         <v>1.62</v>
@@ -47784,7 +47784,7 @@
         <v>1.44</v>
       </c>
       <c r="AB291">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AC291">
         <v>2.15</v>
@@ -48467,7 +48467,7 @@
         <v>1.29</v>
       </c>
       <c r="AK295">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL295">
         <v>0</v>
@@ -48720,13 +48720,13 @@
         </is>
       </c>
       <c r="N297">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="O297">
         <v>3.1</v>
       </c>
       <c r="P297">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="Q297">
         <v>2.89</v>
@@ -48922,7 +48922,7 @@
         <v>4.33</v>
       </c>
       <c r="AA298">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB298">
         <v>2.2</v>
@@ -49538,7 +49538,7 @@
         <v>1.43</v>
       </c>
       <c r="O302">
-        <v>4.33</v>
+        <v>4.44</v>
       </c>
       <c r="P302">
         <v>5.25</v>
@@ -49698,10 +49698,10 @@
         </is>
       </c>
       <c r="N303">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O303">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P303">
         <v>2</v>
@@ -49903,7 +49903,7 @@
         <v>1.76</v>
       </c>
       <c r="AB304">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC304">
         <v>2.88</v>
@@ -50024,10 +50024,10 @@
         </is>
       </c>
       <c r="N305">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O305">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="P305">
         <v>7.5</v>
@@ -50097,7 +50097,7 @@
         <v>1.08</v>
       </c>
       <c r="AK305">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="AL305">
         <v>0</v>
@@ -50359,10 +50359,10 @@
         <v>10</v>
       </c>
       <c r="Q307">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R307">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="S307">
         <v>1.25</v>
@@ -50377,7 +50377,7 @@
         <v>1.62</v>
       </c>
       <c r="W307">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X307">
         <v>1.01</v>
@@ -50389,25 +50389,25 @@
         <v>5</v>
       </c>
       <c r="AA307">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB307">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AC307">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD307">
         <v>1.53</v>
       </c>
       <c r="AE307">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF307">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG307">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AH307" t="inlineStr">
         <is>
@@ -50706,13 +50706,13 @@
         <v>1.11</v>
       </c>
       <c r="X309">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y309">
         <v>1.14</v>
       </c>
       <c r="Z309">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA309">
         <v>1.59</v>
@@ -50721,13 +50721,13 @@
         <v>2.17</v>
       </c>
       <c r="AC309">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="AD309">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE309">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF309">
         <v>1.5</v>
@@ -50807,12 +50807,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G310">
@@ -50839,64 +50839,64 @@
         </is>
       </c>
       <c r="N310">
-        <v>2.1</v>
+        <v>1.09</v>
       </c>
       <c r="O310">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="P310">
-        <v>2.93</v>
+        <v>23</v>
       </c>
       <c r="Q310">
+        <v>1.24</v>
+      </c>
+      <c r="R310">
+        <v>4.25</v>
+      </c>
+      <c r="S310">
+        <v>1.07</v>
+      </c>
+      <c r="T310">
+        <v>7</v>
+      </c>
+      <c r="U310">
+        <v>1.45</v>
+      </c>
+      <c r="V310">
         <v>2.5</v>
       </c>
-      <c r="R310">
-        <v>2.52</v>
-      </c>
-      <c r="S310">
-        <v>1.18</v>
-      </c>
-      <c r="T310">
-        <v>4.4</v>
-      </c>
-      <c r="U310">
-        <v>1.9</v>
-      </c>
-      <c r="V310">
-        <v>1.81</v>
-      </c>
       <c r="W310">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="X310">
         <v>1</v>
       </c>
       <c r="Y310">
+        <v>1.02</v>
+      </c>
+      <c r="Z310">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AA310">
         <v>1.08</v>
       </c>
-      <c r="Z310">
-        <v>6.85</v>
-      </c>
-      <c r="AA310">
-        <v>1.36</v>
-      </c>
       <c r="AB310">
-        <v>2.98</v>
+        <v>6.5</v>
       </c>
       <c r="AC310">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="AD310">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE310">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AF310">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AG310">
-        <v>3.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH310" t="inlineStr">
         <is>
@@ -50909,10 +50909,10 @@
         </is>
       </c>
       <c r="AJ310">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK310">
-        <v>1.77</v>
+        <v>9</v>
       </c>
       <c r="AL310">
         <v>0</v>
@@ -50970,12 +50970,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G311">
@@ -51002,64 +51002,64 @@
         </is>
       </c>
       <c r="N311">
-        <v>1.09</v>
+        <v>2.1</v>
       </c>
       <c r="O311">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="P311">
-        <v>23</v>
+        <v>2.93</v>
       </c>
       <c r="Q311">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="R311">
-        <v>4.25</v>
+        <v>2.52</v>
       </c>
       <c r="S311">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="T311">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="U311">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="V311">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="W311">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="X311">
         <v>1</v>
       </c>
       <c r="Y311">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z311">
-        <v>9.699999999999999</v>
+        <v>6.85</v>
       </c>
       <c r="AA311">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AB311">
-        <v>6.5</v>
+        <v>2.98</v>
       </c>
       <c r="AC311">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="AD311">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="AE311">
-        <v>2.13</v>
+        <v>1.38</v>
       </c>
       <c r="AF311">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AG311">
-        <v>2.1</v>
+        <v>3.04</v>
       </c>
       <c r="AH311" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         </is>
       </c>
       <c r="AJ311">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AK311">
-        <v>9</v>
+        <v>1.77</v>
       </c>
       <c r="AL311">
         <v>0</v>
@@ -51654,13 +51654,13 @@
         </is>
       </c>
       <c r="N315">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O315">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P315">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q315">
         <v>3.5</v>
@@ -51705,7 +51705,7 @@
         <v>1.13</v>
       </c>
       <c r="AE315">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF315">
         <v>2.1</v>
@@ -51835,7 +51835,7 @@
         <v>1.3</v>
       </c>
       <c r="T316">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U316">
         <v>2.5</v>
@@ -52019,7 +52019,7 @@
         <v>3.8</v>
       </c>
       <c r="AA317">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB317">
         <v>2</v>
@@ -52274,12 +52274,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G319">
@@ -52306,80 +52306,80 @@
         </is>
       </c>
       <c r="N319">
-        <v>9.199999999999999</v>
+        <v>1.61</v>
       </c>
       <c r="O319">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P319">
-        <v>1.34</v>
+        <v>4.6</v>
       </c>
       <c r="Q319">
-        <v>10</v>
+        <v>2.17</v>
       </c>
       <c r="R319">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S319">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T319">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="U319">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="V319">
+        <v>1.36</v>
+      </c>
+      <c r="W319">
+        <v>1.06</v>
+      </c>
+      <c r="X319">
+        <v>1.02</v>
+      </c>
+      <c r="Y319">
+        <v>1.31</v>
+      </c>
+      <c r="Z319">
+        <v>2.92</v>
+      </c>
+      <c r="AA319">
+        <v>2.05</v>
+      </c>
+      <c r="AB319">
+        <v>1.68</v>
+      </c>
+      <c r="AC319">
+        <v>3.5</v>
+      </c>
+      <c r="AD319">
+        <v>1.23</v>
+      </c>
+      <c r="AE319">
+        <v>1.04</v>
+      </c>
+      <c r="AF319">
+        <v>2</v>
+      </c>
+      <c r="AG319">
+        <v>1.71</v>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ319">
         <v>1.29</v>
       </c>
-      <c r="W319">
-        <v>1.04</v>
-      </c>
-      <c r="X319">
-        <v>1.07</v>
-      </c>
-      <c r="Y319">
-        <v>1.44</v>
-      </c>
-      <c r="Z319">
-        <v>2.7</v>
-      </c>
-      <c r="AA319">
-        <v>2.36</v>
-      </c>
-      <c r="AB319">
-        <v>1.5</v>
-      </c>
-      <c r="AC319">
-        <v>4.5</v>
-      </c>
-      <c r="AD319">
-        <v>1.16</v>
-      </c>
-      <c r="AE319">
-        <v>1.05</v>
-      </c>
-      <c r="AF319">
-        <v>2.88</v>
-      </c>
-      <c r="AG319">
-        <v>1.3</v>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ319">
-        <v>3.1</v>
-      </c>
       <c r="AK319">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="AL319">
         <v>0</v>
@@ -52437,12 +52437,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G320">
@@ -52469,34 +52469,34 @@
         </is>
       </c>
       <c r="N320">
-        <v>1.61</v>
+        <v>7.5</v>
       </c>
       <c r="O320">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P320">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="Q320">
-        <v>2.17</v>
+        <v>7.51</v>
       </c>
       <c r="R320">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="S320">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T320">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U320">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="V320">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W320">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X320">
         <v>1.02</v>
@@ -52508,25 +52508,25 @@
         <v>2.92</v>
       </c>
       <c r="AA320">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB320">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC320">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AD320">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE320">
         <v>1.04</v>
       </c>
       <c r="AF320">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="AG320">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
@@ -52539,10 +52539,10 @@
         </is>
       </c>
       <c r="AJ320">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK320">
-        <v>2.1</v>
+        <v>1.06</v>
       </c>
       <c r="AL320">
         <v>0</v>
@@ -52600,12 +52600,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G321">
@@ -52632,64 +52632,64 @@
         </is>
       </c>
       <c r="N321">
-        <v>1.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O321">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P321">
-        <v>6.25</v>
+        <v>1.35</v>
       </c>
       <c r="Q321">
-        <v>2.05</v>
+        <v>10</v>
       </c>
       <c r="R321">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="S321">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="T321">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="U321">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="V321">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="W321">
+        <v>1.04</v>
+      </c>
+      <c r="X321">
+        <v>1.07</v>
+      </c>
+      <c r="Y321">
+        <v>1.44</v>
+      </c>
+      <c r="Z321">
+        <v>2.7</v>
+      </c>
+      <c r="AA321">
+        <v>2.36</v>
+      </c>
+      <c r="AB321">
+        <v>1.5</v>
+      </c>
+      <c r="AC321">
+        <v>4.5</v>
+      </c>
+      <c r="AD321">
+        <v>1.16</v>
+      </c>
+      <c r="AE321">
         <v>1.05</v>
       </c>
-      <c r="X321">
-        <v>1.06</v>
-      </c>
-      <c r="Y321">
-        <v>1.51</v>
-      </c>
-      <c r="Z321">
-        <v>2.33</v>
-      </c>
-      <c r="AA321">
-        <v>2.56</v>
-      </c>
-      <c r="AB321">
-        <v>1.4</v>
-      </c>
-      <c r="AC321">
-        <v>5.25</v>
-      </c>
-      <c r="AD321">
-        <v>1.09</v>
-      </c>
-      <c r="AE321">
-        <v>1.03</v>
-      </c>
       <c r="AF321">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="AG321">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
@@ -52702,10 +52702,10 @@
         </is>
       </c>
       <c r="AJ321">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="AK321">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="AL321">
         <v>0</v>
@@ -52763,12 +52763,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G322">
@@ -52795,80 +52795,80 @@
         </is>
       </c>
       <c r="N322">
-        <v>7.5</v>
+        <v>1.55</v>
       </c>
       <c r="O322">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P322">
-        <v>1.38</v>
+        <v>6.25</v>
       </c>
       <c r="Q322">
-        <v>7.51</v>
+        <v>2.05</v>
       </c>
       <c r="R322">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="S322">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="T322">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U322">
-        <v>2.96</v>
+        <v>3.52</v>
       </c>
       <c r="V322">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W322">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X322">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y322">
+        <v>1.51</v>
+      </c>
+      <c r="Z322">
+        <v>2.33</v>
+      </c>
+      <c r="AA322">
+        <v>2.56</v>
+      </c>
+      <c r="AB322">
+        <v>1.4</v>
+      </c>
+      <c r="AC322">
+        <v>5.25</v>
+      </c>
+      <c r="AD322">
+        <v>1.09</v>
+      </c>
+      <c r="AE322">
+        <v>1.03</v>
+      </c>
+      <c r="AF322">
+        <v>2.62</v>
+      </c>
+      <c r="AG322">
+        <v>1.4</v>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ322">
         <v>1.3</v>
       </c>
-      <c r="Z322">
-        <v>2.97</v>
-      </c>
-      <c r="AA322">
-        <v>2.1</v>
-      </c>
-      <c r="AB322">
-        <v>1.69</v>
-      </c>
-      <c r="AC322">
-        <v>3.38</v>
-      </c>
-      <c r="AD322">
-        <v>1.22</v>
-      </c>
-      <c r="AE322">
-        <v>1.04</v>
-      </c>
-      <c r="AF322">
-        <v>2.34</v>
-      </c>
-      <c r="AG322">
-        <v>1.55</v>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ322">
-        <v>1.22</v>
-      </c>
       <c r="AK322">
-        <v>1.06</v>
+        <v>2.38</v>
       </c>
       <c r="AL322">
         <v>0</v>
@@ -52958,7 +52958,7 @@
         </is>
       </c>
       <c r="N323">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="O323">
         <v>2.75</v>
@@ -53284,13 +53284,13 @@
         </is>
       </c>
       <c r="N325">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O325">
         <v>3.32</v>
       </c>
       <c r="P325">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q325">
         <v>0</v>
@@ -53450,10 +53450,10 @@
         <v>1.43</v>
       </c>
       <c r="O326">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P326">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="Q326">
         <v>2</v>
@@ -53517,10 +53517,10 @@
         </is>
       </c>
       <c r="AJ326">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AK326">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="AL326">
         <v>0</v>
@@ -54099,22 +54099,22 @@
         </is>
       </c>
       <c r="N330">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="O330">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="P330">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q330">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R330">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S330">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T330">
         <v>4.5</v>
@@ -54123,40 +54123,40 @@
         <v>1.86</v>
       </c>
       <c r="V330">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="W330">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X330">
         <v>0</v>
       </c>
       <c r="Y330">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z330">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA330">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB330">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AC330">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD330">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AE330">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AF330">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AG330">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH330" t="inlineStr">
         <is>
@@ -54172,7 +54172,7 @@
         <v>1.25</v>
       </c>
       <c r="AK330">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL330">
         <v>0</v>
@@ -54757,7 +54757,7 @@
         <v>3.1</v>
       </c>
       <c r="P334">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="Q334">
         <v>2.97</v>
@@ -54805,10 +54805,10 @@
         <v>1.03</v>
       </c>
       <c r="AF334">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG334">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH334" t="inlineStr">
         <is>
@@ -54956,7 +54956,7 @@
         <v>2.6</v>
       </c>
       <c r="AB335">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC335">
         <v>4.55</v>
@@ -55098,7 +55098,7 @@
         <v>4.4</v>
       </c>
       <c r="U336">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="V336">
         <v>1.8</v>
@@ -55243,7 +55243,7 @@
         <v>2.05</v>
       </c>
       <c r="O337">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="P337">
         <v>2.95</v>
@@ -55732,10 +55732,10 @@
         <v>1.73</v>
       </c>
       <c r="O340">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P340">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Q340">
         <v>2.3</v>
@@ -55780,7 +55780,7 @@
         <v>1.13</v>
       </c>
       <c r="AE340">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF340">
         <v>2.3</v>
@@ -55895,7 +55895,7 @@
         <v>3.5</v>
       </c>
       <c r="O341">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P341">
         <v>1.88</v>
@@ -56055,13 +56055,13 @@
         </is>
       </c>
       <c r="N342">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="O342">
         <v>3.2</v>
       </c>
       <c r="P342">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q342">
         <v>2.48</v>
@@ -56094,10 +56094,10 @@
         <v>2.7</v>
       </c>
       <c r="AA342">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AB342">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC342">
         <v>4.2</v>
@@ -56218,13 +56218,13 @@
         </is>
       </c>
       <c r="N343">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O343">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P343">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q343">
         <v>2.9</v>
@@ -56257,7 +56257,7 @@
         <v>2.56</v>
       </c>
       <c r="AA343">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AB343">
         <v>1.5</v>
@@ -56423,7 +56423,7 @@
         <v>1.44</v>
       </c>
       <c r="AB344">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC344">
         <v>2</v>
@@ -56544,13 +56544,13 @@
         </is>
       </c>
       <c r="N345">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O345">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="P345">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="Q345">
         <v>2.3</v>
@@ -56707,13 +56707,13 @@
         </is>
       </c>
       <c r="N346">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="O346">
         <v>3.5</v>
       </c>
       <c r="P346">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q346">
         <v>3.05</v>
@@ -56740,25 +56740,25 @@
         <v>1.02</v>
       </c>
       <c r="Y346">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z346">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA346">
         <v>1.53</v>
       </c>
       <c r="AB346">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AC346">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD346">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE346">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF346">
         <v>1.44</v>
@@ -56876,7 +56876,7 @@
         <v>3.2</v>
       </c>
       <c r="P347">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q347">
         <v>2.95</v>
@@ -56909,10 +56909,10 @@
         <v>3.1</v>
       </c>
       <c r="AA347">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB347">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC347">
         <v>3.9</v>
@@ -56940,10 +56940,10 @@
         </is>
       </c>
       <c r="AJ347">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK347">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL347">
         <v>0</v>
@@ -57036,7 +57036,7 @@
         <v>2.09</v>
       </c>
       <c r="O348">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="P348">
         <v>2.96</v>
@@ -57090,7 +57090,7 @@
         <v>1.53</v>
       </c>
       <c r="AG348">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH348" t="inlineStr">
         <is>
@@ -57208,7 +57208,7 @@
         <v>3</v>
       </c>
       <c r="R349">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="S349">
         <v>1.18</v>
@@ -57398,7 +57398,7 @@
         <v>5.5</v>
       </c>
       <c r="AA350">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB350">
         <v>2.68</v>
@@ -57552,34 +57552,34 @@
         <v>1.06</v>
       </c>
       <c r="X351">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y351">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z351">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA351">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AB351">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC351">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD351">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE351">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF351">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG351">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AH351" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         </is>
       </c>
       <c r="N352">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O352">
         <v>3.5</v>
@@ -58065,7 +58065,7 @@
         <v>1.3</v>
       </c>
       <c r="AF354">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG354">
         <v>2.47</v>
@@ -58180,7 +58180,7 @@
         <v>4.5</v>
       </c>
       <c r="P355">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q355">
         <v>4.51</v>
@@ -58533,10 +58533,10 @@
         <v>1.04</v>
       </c>
       <c r="Y357">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z357">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AA357">
         <v>2.4</v>
@@ -58545,7 +58545,7 @@
         <v>1.53</v>
       </c>
       <c r="AC357">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="AD357">
         <v>1.17</v>
@@ -58669,10 +58669,10 @@
         <v>3.18</v>
       </c>
       <c r="P358">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q358">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="R358">
         <v>2</v>
@@ -58835,10 +58835,10 @@
         <v>20</v>
       </c>
       <c r="Q359">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R359">
-        <v>3.72</v>
+        <v>3.66</v>
       </c>
       <c r="S359">
         <v>1.12</v>
@@ -58874,10 +58874,10 @@
         <v>1.59</v>
       </c>
       <c r="AD359">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AE359">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF359">
         <v>1.91</v>
@@ -58899,7 +58899,7 @@
         <v>1.05</v>
       </c>
       <c r="AK359">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AL359">
         <v>0</v>
@@ -59641,7 +59641,7 @@
         </is>
       </c>
       <c r="N364">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="O364">
         <v>6.3</v>
@@ -59674,7 +59674,7 @@
         <v>1</v>
       </c>
       <c r="Y364">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z364">
         <v>4.1</v>
@@ -59686,16 +59686,16 @@
         <v>2.17</v>
       </c>
       <c r="AC364">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD364">
         <v>1.42</v>
       </c>
       <c r="AE364">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF364">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="AG364">
         <v>1.45</v>
@@ -59711,10 +59711,10 @@
         </is>
       </c>
       <c r="AJ364">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AK364">
-        <v>3.84</v>
+        <v>3.93</v>
       </c>
       <c r="AL364">
         <v>0</v>
@@ -59807,10 +59807,10 @@
         <v>2.3</v>
       </c>
       <c r="O365">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P365">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q365">
         <v>2.9</v>
@@ -60136,7 +60136,7 @@
         <v>3.75</v>
       </c>
       <c r="P367">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="Q367">
         <v>2.7</v>
@@ -60160,7 +60160,7 @@
         <v>1.18</v>
       </c>
       <c r="X367">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y367">
         <v>1.1</v>
@@ -60326,10 +60326,10 @@
         <v>0</v>
       </c>
       <c r="Y368">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z368">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="AA368">
         <v>1.4</v>
@@ -60338,10 +60338,10 @@
         <v>2.87</v>
       </c>
       <c r="AC368">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD368">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE368">
         <v>1.29</v>
@@ -60670,7 +60670,7 @@
         <v>1.25</v>
       </c>
       <c r="AE370">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF370">
         <v>1.83</v>
@@ -60788,7 +60788,7 @@
         <v>3.25</v>
       </c>
       <c r="P371">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q371">
         <v>2.5</v>
@@ -60984,16 +60984,16 @@
         <v>3.15</v>
       </c>
       <c r="AA372">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB372">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC372">
         <v>3.48</v>
       </c>
       <c r="AD372">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE372">
         <v>1.1</v>
@@ -61108,7 +61108,7 @@
         </is>
       </c>
       <c r="N373">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O373">
         <v>3.6</v>
@@ -61117,10 +61117,10 @@
         <v>2.87</v>
       </c>
       <c r="Q373">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R373">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S373">
         <v>1.29</v>
@@ -61181,7 +61181,7 @@
         <v>1.36</v>
       </c>
       <c r="AK373">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL373">
         <v>0</v>

--- a/jogos_2026-10-31.xlsx
+++ b/jogos_2026-10-31.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O4">
         <v>3.4</v>
       </c>
       <c r="P4">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Q4">
         <v>2.9</v>
@@ -1000,10 +1000,10 @@
         <v>3.86</v>
       </c>
       <c r="AA4">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC4">
         <v>2.62</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Kataller Toyama</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O6">
+        <v>3.5</v>
+      </c>
+      <c r="P6">
+        <v>1.91</v>
+      </c>
+      <c r="Q6">
+        <v>3.52</v>
+      </c>
+      <c r="R6">
+        <v>2.24</v>
+      </c>
+      <c r="S6">
+        <v>1.29</v>
+      </c>
+      <c r="T6">
         <v>3.3</v>
       </c>
-      <c r="P6">
-        <v>2.05</v>
-      </c>
-      <c r="Q6">
-        <v>3.5</v>
-      </c>
-      <c r="R6">
-        <v>2.15</v>
-      </c>
-      <c r="S6">
-        <v>1.37</v>
-      </c>
-      <c r="T6">
-        <v>3.07</v>
-      </c>
       <c r="U6">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>3.6</v>
+        <v>4.68</v>
       </c>
       <c r="AA6">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AB6">
-        <v>1.94</v>
+        <v>2.27</v>
       </c>
       <c r="AC6">
-        <v>3.21</v>
+        <v>2.36</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="AK6">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kataller Toyama</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
+        <v>3.1</v>
+      </c>
+      <c r="O7">
         <v>3.3</v>
       </c>
-      <c r="O7">
+      <c r="P7">
+        <v>2.05</v>
+      </c>
+      <c r="Q7">
         <v>3.5</v>
       </c>
-      <c r="P7">
-        <v>1.91</v>
-      </c>
-      <c r="Q7">
-        <v>3.52</v>
-      </c>
       <c r="R7">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>3.07</v>
       </c>
       <c r="U7">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>4.68</v>
+        <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AB7">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>2.36</v>
+        <v>3.21</v>
       </c>
       <c r="AD7">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AK7">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>4.4</v>
+        <v>2.06</v>
       </c>
       <c r="O26">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P26">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>4.6</v>
+        <v>2.63</v>
       </c>
       <c r="R26">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>3.75</v>
+        <v>2.69</v>
       </c>
       <c r="U26">
-        <v>2.13</v>
+        <v>2.77</v>
       </c>
       <c r="V26">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="W26">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X26">
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>3.08</v>
       </c>
       <c r="AA26">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="AB26">
-        <v>2.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC26">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="AD26">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AK26">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O31">
         <v>3.3</v>
@@ -5374,19 +5374,19 @@
         <v>3.5</v>
       </c>
       <c r="R31">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
         <v>1.1</v>
@@ -5398,16 +5398,16 @@
         <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB31">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AC31">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AD31">
         <v>1.35</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK31">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="O39">
         <v>2.98</v>
@@ -7336,13 +7336,13 @@
         <v>1.3</v>
       </c>
       <c r="T43">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U43">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V43">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W43">
         <v>1.09</v>
@@ -7360,7 +7360,7 @@
         <v>1.67</v>
       </c>
       <c r="AB43">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AC43">
         <v>2.88</v>
@@ -7369,7 +7369,7 @@
         <v>1.4</v>
       </c>
       <c r="AE43">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
         <v>1.6</v>
@@ -7499,7 +7499,7 @@
         <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
         <v>2.6</v>
@@ -8139,7 +8139,7 @@
         <v>3.3</v>
       </c>
       <c r="P48">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="Q48">
         <v>3.31</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
         <v>3.15</v>
@@ -9446,55 +9446,55 @@
         <v>3.99</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X56">
         <v>0</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9603,10 +9603,10 @@
         <v>2.05</v>
       </c>
       <c r="O57">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P57">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q57">
         <v>2.5</v>
@@ -9769,7 +9769,7 @@
         <v>3.25</v>
       </c>
       <c r="P58">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q58">
         <v>3.52</v>
@@ -9793,13 +9793,13 @@
         <v>1.02</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z58">
-        <v>3.06</v>
+        <v>2.97</v>
       </c>
       <c r="AA58">
         <v>2.11</v>
@@ -9811,10 +9811,10 @@
         <v>3.69</v>
       </c>
       <c r="AD58">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF58">
         <v>1.81</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB59">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="O62">
         <v>3.38</v>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK63">
         <v>1.4</v>
@@ -10943,7 +10943,7 @@
         <v>3.04</v>
       </c>
       <c r="AA65">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB65">
         <v>1.7</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Q70">
         <v>2.88</v>
@@ -11770,7 +11770,7 @@
         <v>1.32</v>
       </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF70">
         <v>1.62</v>
@@ -11792,7 +11792,7 @@
         <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12048,7 +12048,7 @@
         <v>2.75</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P72">
         <v>2.15</v>
@@ -12090,7 +12090,7 @@
         <v>2.34</v>
       </c>
       <c r="AC72">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AD72">
         <v>1.57</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,65 +12208,65 @@
         </is>
       </c>
       <c r="N73">
+        <v>1.53</v>
+      </c>
+      <c r="O73">
+        <v>4.2</v>
+      </c>
+      <c r="P73">
+        <v>4.6</v>
+      </c>
+      <c r="Q73">
+        <v>1.96</v>
+      </c>
+      <c r="R73">
+        <v>2.63</v>
+      </c>
+      <c r="S73">
+        <v>1.18</v>
+      </c>
+      <c r="T73">
+        <v>4.33</v>
+      </c>
+      <c r="U73">
+        <v>1.98</v>
+      </c>
+      <c r="V73">
+        <v>1.84</v>
+      </c>
+      <c r="W73">
+        <v>1.2</v>
+      </c>
+      <c r="X73">
+        <v>1.01</v>
+      </c>
+      <c r="Y73">
+        <v>1.07</v>
+      </c>
+      <c r="Z73">
+        <v>5.75</v>
+      </c>
+      <c r="AA73">
+        <v>1.36</v>
+      </c>
+      <c r="AB73">
+        <v>2.9</v>
+      </c>
+      <c r="AC73">
+        <v>1.97</v>
+      </c>
+      <c r="AD73">
+        <v>1.85</v>
+      </c>
+      <c r="AE73">
+        <v>1.3</v>
+      </c>
+      <c r="AF73">
+        <v>1.44</v>
+      </c>
+      <c r="AG73">
         <v>2.51</v>
       </c>
-      <c r="O73">
-        <v>3.54</v>
-      </c>
-      <c r="P73">
-        <v>2.26</v>
-      </c>
-      <c r="Q73">
-        <v>3.2</v>
-      </c>
-      <c r="R73">
-        <v>2.25</v>
-      </c>
-      <c r="S73">
-        <v>1.25</v>
-      </c>
-      <c r="T73">
-        <v>3.5</v>
-      </c>
-      <c r="U73">
-        <v>2.18</v>
-      </c>
-      <c r="V73">
-        <v>1.57</v>
-      </c>
-      <c r="W73">
-        <v>1.15</v>
-      </c>
-      <c r="X73">
-        <v>1.03</v>
-      </c>
-      <c r="Y73">
-        <v>1.17</v>
-      </c>
-      <c r="Z73">
-        <v>5</v>
-      </c>
-      <c r="AA73">
-        <v>1.56</v>
-      </c>
-      <c r="AB73">
-        <v>2.38</v>
-      </c>
-      <c r="AC73">
-        <v>2.34</v>
-      </c>
-      <c r="AD73">
-        <v>1.51</v>
-      </c>
-      <c r="AE73">
-        <v>1.18</v>
-      </c>
-      <c r="AF73">
-        <v>1.5</v>
-      </c>
-      <c r="AG73">
-        <v>2.4</v>
-      </c>
       <c r="AH73" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AK73">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.53</v>
+        <v>2.51</v>
       </c>
       <c r="O74">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="P74">
-        <v>4.6</v>
+        <v>2.26</v>
       </c>
       <c r="Q74">
-        <v>1.96</v>
+        <v>3.2</v>
       </c>
       <c r="R74">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
+        <v>1.25</v>
+      </c>
+      <c r="T74">
+        <v>3.5</v>
+      </c>
+      <c r="U74">
+        <v>2.18</v>
+      </c>
+      <c r="V74">
+        <v>1.57</v>
+      </c>
+      <c r="W74">
+        <v>1.15</v>
+      </c>
+      <c r="X74">
+        <v>1.03</v>
+      </c>
+      <c r="Y74">
+        <v>1.17</v>
+      </c>
+      <c r="Z74">
+        <v>5</v>
+      </c>
+      <c r="AA74">
+        <v>1.56</v>
+      </c>
+      <c r="AB74">
+        <v>2.38</v>
+      </c>
+      <c r="AC74">
+        <v>2.34</v>
+      </c>
+      <c r="AD74">
+        <v>1.51</v>
+      </c>
+      <c r="AE74">
         <v>1.18</v>
       </c>
-      <c r="T74">
-        <v>4.33</v>
-      </c>
-      <c r="U74">
-        <v>1.98</v>
-      </c>
-      <c r="V74">
-        <v>1.84</v>
-      </c>
-      <c r="W74">
-        <v>1.2</v>
-      </c>
-      <c r="X74">
-        <v>1.01</v>
-      </c>
-      <c r="Y74">
-        <v>1.07</v>
-      </c>
-      <c r="Z74">
-        <v>5.75</v>
-      </c>
-      <c r="AA74">
-        <v>1.36</v>
-      </c>
-      <c r="AB74">
-        <v>2.9</v>
-      </c>
-      <c r="AC74">
-        <v>1.97</v>
-      </c>
-      <c r="AD74">
-        <v>1.85</v>
-      </c>
-      <c r="AE74">
-        <v>1.3</v>
-      </c>
       <c r="AF74">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG74">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK74">
-        <v>2.35</v>
+        <v>1.38</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O77">
         <v>4</v>
@@ -13032,10 +13032,10 @@
         <v>6.65</v>
       </c>
       <c r="Q78">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="R78">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="S78">
         <v>1.31</v>
@@ -13047,7 +13047,7 @@
         <v>2.75</v>
       </c>
       <c r="V78">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
         <v>1.1</v>
@@ -13056,31 +13056,31 @@
         <v>1</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z78">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA78">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AB78">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC78">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD78">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE78">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF78">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG78">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK78">
         <v>2.6</v>
@@ -13512,7 +13512,7 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="O81">
         <v>3.26</v>
@@ -13521,7 +13521,7 @@
         <v>3.43</v>
       </c>
       <c r="Q81">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="R81">
         <v>2.05</v>
@@ -13545,7 +13545,7 @@
         <v>1.11</v>
       </c>
       <c r="Y81">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z81">
         <v>2.74</v>
@@ -13557,7 +13557,7 @@
         <v>1.65</v>
       </c>
       <c r="AC81">
-        <v>4.81</v>
+        <v>4.8</v>
       </c>
       <c r="AD81">
         <v>1.15</v>
@@ -13714,7 +13714,7 @@
         <v>4.9</v>
       </c>
       <c r="AA82">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
         <v>2.25</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O83">
         <v>3.75</v>
       </c>
       <c r="P83">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="Q83">
         <v>2.8</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.22</v>
@@ -14004,7 +14004,7 @@
         <v>1.66</v>
       </c>
       <c r="O84">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="P84">
         <v>4.5</v>
@@ -14203,10 +14203,10 @@
         <v>5.5</v>
       </c>
       <c r="AA85">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB85">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AC85">
         <v>2.3</v>
@@ -14366,10 +14366,10 @@
         <v>6.5</v>
       </c>
       <c r="AA86">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AB86">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AC86">
         <v>2.15</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="O87">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="P87">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q87">
-        <v>3.75</v>
+        <v>2.36</v>
       </c>
       <c r="R87">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U87">
-        <v>2.61</v>
+        <v>2.74</v>
       </c>
       <c r="V87">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W87">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z87">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA87">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AB87">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC87">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="AD87">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF87">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AK87">
-        <v>1.33</v>
+        <v>2.08</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.73</v>
+        <v>3.3</v>
       </c>
       <c r="O88">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="P88">
-        <v>3.98</v>
+        <v>2.15</v>
       </c>
       <c r="Q88">
-        <v>2.36</v>
+        <v>3.75</v>
       </c>
       <c r="R88">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T88">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U88">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="V88">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W88">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
         <v>1.29</v>
       </c>
       <c r="Z88">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA88">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB88">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC88">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AD88">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE88">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF88">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AG88">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AK88">
-        <v>2.08</v>
+        <v>1.33</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14837,7 +14837,7 @@
         <v>3.65</v>
       </c>
       <c r="U89">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V89">
         <v>1.59</v>
@@ -14855,10 +14855,10 @@
         <v>5.5</v>
       </c>
       <c r="AA89">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB89">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AC89">
         <v>2.38</v>
@@ -14889,7 +14889,7 @@
         <v>1.16</v>
       </c>
       <c r="AK89">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15021,7 +15021,7 @@
         <v>1.81</v>
       </c>
       <c r="AB90">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC90">
         <v>3.1</v>
@@ -15163,7 +15163,7 @@
         <v>2.73</v>
       </c>
       <c r="U91">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="V91">
         <v>1.4</v>
@@ -15181,7 +15181,7 @@
         <v>3.25</v>
       </c>
       <c r="AA91">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB91">
         <v>1.92</v>
@@ -15317,7 +15317,7 @@
         <v>2.48</v>
       </c>
       <c r="R92">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S92">
         <v>1.22</v>
@@ -15634,7 +15634,7 @@
         <v>2.54</v>
       </c>
       <c r="O94">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P94">
         <v>2.59</v>
@@ -15646,10 +15646,10 @@
         <v>2.05</v>
       </c>
       <c r="S94">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T94">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="U94">
         <v>2.62</v>
@@ -15676,7 +15676,7 @@
         <v>1.88</v>
       </c>
       <c r="AC94">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="AD94">
         <v>1.33</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FC Tekstilshchik Ivanovo</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.61</v>
+        <v>2.6</v>
       </c>
       <c r="O95">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="P95">
-        <v>4.45</v>
+        <v>2.33</v>
       </c>
       <c r="Q95">
-        <v>2.14</v>
+        <v>3.52</v>
       </c>
       <c r="R95">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="S95">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T95">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="U95">
-        <v>2.7</v>
+        <v>3.14</v>
       </c>
       <c r="V95">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W95">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X95">
+        <v>1.04</v>
+      </c>
+      <c r="Y95">
+        <v>1.4</v>
+      </c>
+      <c r="Z95">
+        <v>2.74</v>
+      </c>
+      <c r="AA95">
+        <v>2.33</v>
+      </c>
+      <c r="AB95">
+        <v>1.55</v>
+      </c>
+      <c r="AC95">
+        <v>4.33</v>
+      </c>
+      <c r="AD95">
+        <v>1.14</v>
+      </c>
+      <c r="AE95">
         <v>1.03</v>
       </c>
-      <c r="Y95">
-        <v>1.28</v>
-      </c>
-      <c r="Z95">
-        <v>3.44</v>
-      </c>
-      <c r="AA95">
-        <v>1.91</v>
-      </c>
-      <c r="AB95">
-        <v>1.91</v>
-      </c>
-      <c r="AC95">
-        <v>3.19</v>
-      </c>
-      <c r="AD95">
-        <v>1.33</v>
-      </c>
-      <c r="AE95">
-        <v>1.1</v>
-      </c>
       <c r="AF95">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG95">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AK95">
-        <v>2.28</v>
+        <v>1.44</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>FC Tekstilshchik Ivanovo</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="O96">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="P96">
-        <v>2.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q96">
-        <v>3.52</v>
+        <v>2.14</v>
       </c>
       <c r="R96">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="S96">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="T96">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="U96">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="V96">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W96">
+        <v>1.05</v>
+      </c>
+      <c r="X96">
         <v>1.03</v>
       </c>
-      <c r="X96">
-        <v>1.04</v>
-      </c>
       <c r="Y96">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z96">
-        <v>2.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA96">
-        <v>2.33</v>
+        <v>1.87</v>
       </c>
       <c r="AB96">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC96">
-        <v>4.33</v>
+        <v>3.19</v>
       </c>
       <c r="AD96">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AE96">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF96">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG96">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK96">
-        <v>1.44</v>
+        <v>2.28</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O100">
         <v>3.4</v>
@@ -16811,13 +16811,13 @@
         <v>3.78</v>
       </c>
       <c r="AA101">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB101">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC101">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AD101">
         <v>1.33</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="O102">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P102">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="Q102">
-        <v>3</v>
+        <v>1.96</v>
       </c>
       <c r="R102">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="S102">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T102">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U102">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V102">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W102">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z102">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA102">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AB102">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AC102">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="AD102">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE102">
         <v>1.2</v>
       </c>
       <c r="AF102">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AG102">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK102">
-        <v>1.36</v>
+        <v>2.47</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17101,10 +17101,10 @@
         <v>2.95</v>
       </c>
       <c r="O103">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="O104">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>5.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q104">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="R104">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
+        <v>1.22</v>
+      </c>
+      <c r="T104">
+        <v>3.9</v>
+      </c>
+      <c r="U104">
+        <v>2.1</v>
+      </c>
+      <c r="V104">
+        <v>1.58</v>
+      </c>
+      <c r="W104">
+        <v>1.18</v>
+      </c>
+      <c r="X104">
+        <v>1.01</v>
+      </c>
+      <c r="Y104">
         <v>1.17</v>
       </c>
-      <c r="T104">
-        <v>4</v>
-      </c>
-      <c r="U104">
-        <v>2.16</v>
-      </c>
-      <c r="V104">
-        <v>1.67</v>
-      </c>
-      <c r="W104">
-        <v>1.13</v>
-      </c>
-      <c r="X104">
-        <v>1.02</v>
-      </c>
-      <c r="Y104">
-        <v>1.09</v>
-      </c>
       <c r="Z104">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA104">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AB104">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AC104">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD104">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE104">
         <v>1.2</v>
       </c>
       <c r="AF104">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AG104">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK104">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17590,7 +17590,7 @@
         <v>2.5</v>
       </c>
       <c r="O106">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P106">
         <v>2.25</v>
@@ -18085,7 +18085,7 @@
         <v>1.4</v>
       </c>
       <c r="Q109">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="R109">
         <v>2.88</v>
@@ -18106,7 +18106,7 @@
         <v>1.25</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y109">
         <v>1.03</v>
@@ -18121,10 +18121,10 @@
         <v>3.34</v>
       </c>
       <c r="AC109">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AD109">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AE109">
         <v>1.42</v>
@@ -18402,7 +18402,7 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="O111">
         <v>3.45</v>
@@ -18411,7 +18411,7 @@
         <v>3.7</v>
       </c>
       <c r="Q111">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R111">
         <v>2.2</v>
@@ -18429,7 +18429,7 @@
         <v>1.4</v>
       </c>
       <c r="W111">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X111">
         <v>1.04</v>
@@ -18447,16 +18447,16 @@
         <v>1.93</v>
       </c>
       <c r="AC111">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG111">
         <v>2</v>
@@ -18475,7 +18475,7 @@
         <v>1.22</v>
       </c>
       <c r="AK111">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18586,7 +18586,7 @@
         <v>3.24</v>
       </c>
       <c r="U112">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V112">
         <v>1.48</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O115">
         <v>3.5</v>
       </c>
       <c r="P115">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q115">
         <v>8.300000000000001</v>
@@ -19942,7 +19942,7 @@
         <v>1.12</v>
       </c>
       <c r="AK120">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20364,7 +20364,7 @@
         <v>3.57</v>
       </c>
       <c r="P123">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="Q123">
         <v>2.88</v>
@@ -20391,10 +20391,10 @@
         <v>1.04</v>
       </c>
       <c r="Y123">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z123">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="AA123">
         <v>1.83</v>
@@ -20403,13 +20403,13 @@
         <v>1.91</v>
       </c>
       <c r="AC123">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD123">
         <v>1.36</v>
       </c>
       <c r="AE123">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF123">
         <v>1.65</v>
@@ -21336,19 +21336,19 @@
         </is>
       </c>
       <c r="N129">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O129">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P129">
-        <v>2.43</v>
+        <v>2.78</v>
       </c>
       <c r="Q129">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="R129">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S129">
         <v>1.22</v>
@@ -21381,7 +21381,7 @@
         <v>2.63</v>
       </c>
       <c r="AC129">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AD129">
         <v>1.63</v>
@@ -21409,7 +21409,7 @@
         <v>1.36</v>
       </c>
       <c r="AK129">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL129">
         <v>0</v>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,64 +21499,64 @@
         </is>
       </c>
       <c r="N130">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="O130">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P130">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="Q130">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="R130">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="S130">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T130">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U130">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="V130">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W130">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X130">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y130">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z130">
-        <v>4.24</v>
+        <v>3.5</v>
       </c>
       <c r="AA130">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AB130">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AC130">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="AD130">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE130">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF130">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG130">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -21569,10 +21569,10 @@
         </is>
       </c>
       <c r="AJ130">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK130">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL130">
         <v>0</v>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G131">
@@ -21662,64 +21662,64 @@
         </is>
       </c>
       <c r="N131">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="O131">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P131">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q131">
-        <v>2.32</v>
+        <v>2.96</v>
       </c>
       <c r="R131">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="S131">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T131">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U131">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="V131">
+        <v>1.5</v>
+      </c>
+      <c r="W131">
+        <v>1.11</v>
+      </c>
+      <c r="X131">
+        <v>1</v>
+      </c>
+      <c r="Y131">
+        <v>1.17</v>
+      </c>
+      <c r="Z131">
+        <v>4.24</v>
+      </c>
+      <c r="AA131">
+        <v>1.7</v>
+      </c>
+      <c r="AB131">
+        <v>2.1</v>
+      </c>
+      <c r="AC131">
+        <v>2.56</v>
+      </c>
+      <c r="AD131">
         <v>1.4</v>
       </c>
-      <c r="W131">
-        <v>1.08</v>
-      </c>
-      <c r="X131">
-        <v>1.01</v>
-      </c>
-      <c r="Y131">
-        <v>1.25</v>
-      </c>
-      <c r="Z131">
-        <v>3.5</v>
-      </c>
-      <c r="AA131">
-        <v>1.9</v>
-      </c>
-      <c r="AB131">
-        <v>1.9</v>
-      </c>
-      <c r="AC131">
-        <v>3.14</v>
-      </c>
-      <c r="AD131">
-        <v>1.27</v>
-      </c>
       <c r="AE131">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF131">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG131">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="AJ131">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK131">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL131">
         <v>0</v>
@@ -22806,7 +22806,7 @@
         <v>2.5</v>
       </c>
       <c r="O138">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="P138">
         <v>2.5</v>
@@ -22824,7 +22824,7 @@
         <v>2.88</v>
       </c>
       <c r="U138">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V138">
         <v>1.36</v>
@@ -22836,7 +22836,7 @@
         <v>1.01</v>
       </c>
       <c r="Y138">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z138">
         <v>3.28</v>
@@ -22845,10 +22845,10 @@
         <v>1.91</v>
       </c>
       <c r="AB138">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC138">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="AD138">
         <v>1.3</v>
@@ -22969,7 +22969,7 @@
         <v>1.67</v>
       </c>
       <c r="O139">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P139">
         <v>4.4</v>
@@ -23036,7 +23036,7 @@
         </is>
       </c>
       <c r="AJ139">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK139">
         <v>2.1</v>
@@ -23132,10 +23132,10 @@
         <v>2.25</v>
       </c>
       <c r="O140">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="P140">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="Q140">
         <v>2.88</v>
@@ -23165,16 +23165,16 @@
         <v>1.35</v>
       </c>
       <c r="Z140">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="AA140">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AB140">
         <v>1.74</v>
       </c>
       <c r="AC140">
-        <v>3.76</v>
+        <v>3.79</v>
       </c>
       <c r="AD140">
         <v>1.24</v>
@@ -23470,10 +23470,10 @@
         <v>2.05</v>
       </c>
       <c r="S142">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T142">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="U142">
         <v>3.05</v>
@@ -23494,7 +23494,7 @@
         <v>3.25</v>
       </c>
       <c r="AA142">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB142">
         <v>1.75</v>
@@ -23621,7 +23621,7 @@
         <v>2.75</v>
       </c>
       <c r="O143">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P143">
         <v>2.2</v>
@@ -23639,7 +23639,7 @@
         <v>3.1</v>
       </c>
       <c r="U143">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V143">
         <v>1.47</v>
@@ -23784,7 +23784,7 @@
         <v>4.05</v>
       </c>
       <c r="O144">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P144">
         <v>1.74</v>
@@ -23835,7 +23835,7 @@
         <v>1.14</v>
       </c>
       <c r="AF144">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG144">
         <v>2.1</v>
@@ -23944,10 +23944,10 @@
         </is>
       </c>
       <c r="N145">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O145">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P145">
         <v>3.6</v>
@@ -23965,10 +23965,10 @@
         <v>2.97</v>
       </c>
       <c r="U145">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="V145">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W145">
         <v>1.07</v>
@@ -24270,13 +24270,13 @@
         </is>
       </c>
       <c r="N147">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O147">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P147">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="Q147">
         <v>2.81</v>
@@ -24300,7 +24300,7 @@
         <v>1.15</v>
       </c>
       <c r="X147">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y147">
         <v>1.12</v>
@@ -24451,10 +24451,10 @@
         <v>1.22</v>
       </c>
       <c r="T148">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U148">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="V148">
         <v>1.7</v>
@@ -24780,7 +24780,7 @@
         <v>3.3</v>
       </c>
       <c r="U150">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V150">
         <v>1.5</v>
@@ -25287,7 +25287,7 @@
         <v>2.75</v>
       </c>
       <c r="AA153">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AB153">
         <v>1.59</v>
@@ -25420,22 +25420,22 @@
         <v>0</v>
       </c>
       <c r="Q154">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="R154">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S154">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T154">
-        <v>3</v>
+        <v>2.37</v>
       </c>
       <c r="U154">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="V154">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W154">
         <v>1.09</v>
@@ -25444,31 +25444,31 @@
         <v>1.01</v>
       </c>
       <c r="Y154">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z154">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA154">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB154">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AC154">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="AD154">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE154">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF154">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AG154">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AH154" t="inlineStr">
         <is>
@@ -25481,10 +25481,10 @@
         </is>
       </c>
       <c r="AJ154">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK154">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL154">
         <v>0</v>
@@ -25604,7 +25604,7 @@
         <v>1.07</v>
       </c>
       <c r="X155">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y155">
         <v>1.22</v>
@@ -25613,19 +25613,19 @@
         <v>3.5</v>
       </c>
       <c r="AA155">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB155">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC155">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AD155">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE155">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF155">
         <v>1.63</v>
@@ -25912,7 +25912,7 @@
         <v>2.3</v>
       </c>
       <c r="R157">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="S157">
         <v>1.33</v>
@@ -26069,7 +26069,7 @@
         <v>3.5</v>
       </c>
       <c r="P158">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q158">
         <v>3.6</v>
@@ -26084,7 +26084,7 @@
         <v>3.24</v>
       </c>
       <c r="U158">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V158">
         <v>1.54</v>
@@ -26099,13 +26099,13 @@
         <v>1.19</v>
       </c>
       <c r="Z158">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA158">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB158">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AC158">
         <v>2.6</v>
@@ -26226,13 +26226,13 @@
         </is>
       </c>
       <c r="N159">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="O159">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P159">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q159">
         <v>2.8</v>
@@ -26271,10 +26271,10 @@
         <v>2.25</v>
       </c>
       <c r="AC159">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AD159">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE159">
         <v>1.19</v>
@@ -26422,25 +26422,25 @@
         <v>1.01</v>
       </c>
       <c r="Y160">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z160">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="AA160">
         <v>1.53</v>
       </c>
       <c r="AB160">
+        <v>2.44</v>
+      </c>
+      <c r="AC160">
         <v>2.35</v>
       </c>
-      <c r="AC160">
-        <v>2.27</v>
-      </c>
       <c r="AD160">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AE160">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF160">
         <v>1.44</v>
@@ -26603,7 +26603,7 @@
         <v>1.85</v>
       </c>
       <c r="AE161">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF161">
         <v>1.38</v>
@@ -26715,13 +26715,13 @@
         </is>
       </c>
       <c r="N162">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O162">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P162">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q162">
         <v>2.67</v>
@@ -26748,10 +26748,10 @@
         <v>1.02</v>
       </c>
       <c r="Y162">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z162">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AA162">
         <v>1.7</v>
@@ -26890,7 +26890,7 @@
         <v>2.25</v>
       </c>
       <c r="R163">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="S163">
         <v>1.25</v>
@@ -26914,7 +26914,7 @@
         <v>1.14</v>
       </c>
       <c r="Z163">
-        <v>4.52</v>
+        <v>4.57</v>
       </c>
       <c r="AA163">
         <v>1.59</v>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="AJ163">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK163">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL163">
         <v>0</v>
@@ -27065,7 +27065,7 @@
         <v>1.99</v>
       </c>
       <c r="V164">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="W164">
         <v>1.2</v>
@@ -27077,7 +27077,7 @@
         <v>1.11</v>
       </c>
       <c r="Z164">
-        <v>6.14</v>
+        <v>6.23</v>
       </c>
       <c r="AA164">
         <v>1.4</v>
@@ -27089,10 +27089,10 @@
         <v>1.95</v>
       </c>
       <c r="AD164">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AE164">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AF164">
         <v>1.35</v>
@@ -27207,7 +27207,7 @@
         <v>1.88</v>
       </c>
       <c r="O165">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="P165">
         <v>3.4</v>
@@ -27370,7 +27370,7 @@
         <v>2.55</v>
       </c>
       <c r="O166">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P166">
         <v>2.2</v>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="N167">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="O167">
         <v>4.38</v>
@@ -27563,16 +27563,16 @@
         <v>1</v>
       </c>
       <c r="Y167">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z167">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="AA167">
         <v>1.75</v>
       </c>
       <c r="AB167">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AC167">
         <v>2.71</v>
@@ -27699,7 +27699,7 @@
         <v>5.5</v>
       </c>
       <c r="P168">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Q168">
         <v>9.9</v>
@@ -27729,16 +27729,16 @@
         <v>1.19</v>
       </c>
       <c r="Z168">
-        <v>3.89</v>
+        <v>3.93</v>
       </c>
       <c r="AA168">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB168">
         <v>2.02</v>
       </c>
       <c r="AC168">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD168">
         <v>1.38</v>
@@ -27824,12 +27824,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G169">
@@ -27856,64 +27856,64 @@
         </is>
       </c>
       <c r="N169">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="O169">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P169">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q169">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="R169">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="S169">
+        <v>1.22</v>
+      </c>
+      <c r="T169">
+        <v>4</v>
+      </c>
+      <c r="U169">
+        <v>2.17</v>
+      </c>
+      <c r="V169">
+        <v>1.71</v>
+      </c>
+      <c r="W169">
         <v>1.18</v>
-      </c>
-      <c r="T169">
-        <v>4.5</v>
-      </c>
-      <c r="U169">
-        <v>2.08</v>
-      </c>
-      <c r="V169">
-        <v>1.75</v>
-      </c>
-      <c r="W169">
-        <v>1.22</v>
       </c>
       <c r="X169">
         <v>1</v>
       </c>
       <c r="Y169">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z169">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA169">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB169">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="AC169">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AD169">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AE169">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF169">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AG169">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AH169" t="inlineStr">
         <is>
@@ -27926,10 +27926,10 @@
         </is>
       </c>
       <c r="AJ169">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK169">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AL169">
         <v>0</v>
@@ -28150,12 +28150,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G171">
@@ -28182,64 +28182,64 @@
         </is>
       </c>
       <c r="N171">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="O171">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P171">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q171">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="R171">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="S171">
+        <v>1.2</v>
+      </c>
+      <c r="T171">
+        <v>4.5</v>
+      </c>
+      <c r="U171">
+        <v>2.08</v>
+      </c>
+      <c r="V171">
+        <v>1.75</v>
+      </c>
+      <c r="W171">
         <v>1.22</v>
-      </c>
-      <c r="T171">
-        <v>4</v>
-      </c>
-      <c r="U171">
-        <v>2.17</v>
-      </c>
-      <c r="V171">
-        <v>1.71</v>
-      </c>
-      <c r="W171">
-        <v>1.18</v>
       </c>
       <c r="X171">
         <v>1</v>
       </c>
       <c r="Y171">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z171">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA171">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB171">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="AC171">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AD171">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="AE171">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF171">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AG171">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="AH171" t="inlineStr">
         <is>
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="AJ171">
-        <v>1.72</v>
+        <v>1.27</v>
       </c>
       <c r="AK171">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AL171">
         <v>0</v>
@@ -28313,12 +28313,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G172">
@@ -28345,64 +28345,64 @@
         </is>
       </c>
       <c r="N172">
-        <v>1.95</v>
+        <v>3.08</v>
       </c>
       <c r="O172">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="P172">
-        <v>3.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q172">
-        <v>2.52</v>
+        <v>3.31</v>
       </c>
       <c r="R172">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S172">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T172">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U172">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V172">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="W172">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X172">
         <v>1</v>
       </c>
       <c r="Y172">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z172">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA172">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB172">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="AC172">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AD172">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AE172">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF172">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG172">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="AJ172">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK172">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="AL172">
         <v>0</v>
@@ -28476,12 +28476,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G173">
@@ -28508,64 +28508,64 @@
         </is>
       </c>
       <c r="N173">
-        <v>3.08</v>
+        <v>1.95</v>
       </c>
       <c r="O173">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P173">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q173">
-        <v>3.31</v>
+        <v>2.52</v>
       </c>
       <c r="R173">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S173">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T173">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U173">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V173">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="W173">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X173">
         <v>1</v>
       </c>
       <c r="Y173">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z173">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA173">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AB173">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="AC173">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AD173">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AE173">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF173">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG173">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="AH173" t="inlineStr">
         <is>
@@ -28578,10 +28578,10 @@
         </is>
       </c>
       <c r="AJ173">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AK173">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AL173">
         <v>0</v>
@@ -28689,10 +28689,10 @@
         <v>1.3</v>
       </c>
       <c r="T174">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="U174">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V174">
         <v>1.43</v>
@@ -28710,7 +28710,7 @@
         <v>3.74</v>
       </c>
       <c r="AA174">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB174">
         <v>2.05</v>
@@ -29128,12 +29128,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G177">
@@ -29160,25 +29160,25 @@
         </is>
       </c>
       <c r="N177">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O177">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P177">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="Q177">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="R177">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="S177">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T177">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U177">
         <v>2.5</v>
@@ -29187,37 +29187,37 @@
         <v>1.44</v>
       </c>
       <c r="W177">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X177">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y177">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z177">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA177">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AB177">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="AC177">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="AD177">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE177">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF177">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG177">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>1.25</v>
       </c>
       <c r="AK177">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL177">
         <v>0</v>
@@ -29291,12 +29291,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G178">
@@ -29323,25 +29323,25 @@
         </is>
       </c>
       <c r="N178">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O178">
+        <v>3.7</v>
+      </c>
+      <c r="P178">
         <v>3.4</v>
       </c>
-      <c r="P178">
-        <v>2.95</v>
-      </c>
       <c r="Q178">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R178">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S178">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T178">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="U178">
         <v>2.5</v>
@@ -29350,37 +29350,37 @@
         <v>1.44</v>
       </c>
       <c r="W178">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X178">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y178">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z178">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA178">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AB178">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AC178">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="AD178">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE178">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF178">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG178">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH178" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>1.25</v>
       </c>
       <c r="AK178">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL178">
         <v>0</v>
@@ -29486,13 +29486,13 @@
         </is>
       </c>
       <c r="N179">
-        <v>2.37</v>
+        <v>2.56</v>
       </c>
       <c r="O179">
         <v>3.5</v>
       </c>
       <c r="P179">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q179">
         <v>3.13</v>
@@ -29537,7 +29537,7 @@
         <v>1.33</v>
       </c>
       <c r="AE179">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF179">
         <v>1.6</v>
@@ -29649,7 +29649,7 @@
         </is>
       </c>
       <c r="N180">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="O180">
         <v>3.35</v>
@@ -29943,12 +29943,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Limavady United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G182">
@@ -29978,61 +29978,61 @@
         <v>2.05</v>
       </c>
       <c r="O182">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P182">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="Q182">
         <v>2.62</v>
       </c>
       <c r="R182">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S182">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T182">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U182">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V182">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="W182">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X182">
         <v>1.02</v>
       </c>
       <c r="Y182">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z182">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA182">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AB182">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC182">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="AD182">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AE182">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AF182">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AG182">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
@@ -30045,10 +30045,10 @@
         </is>
       </c>
       <c r="AJ182">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK182">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL182">
         <v>0</v>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Limavady United</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G183">
@@ -30138,64 +30138,64 @@
         </is>
       </c>
       <c r="N183">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O183">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P183">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="Q183">
         <v>2.62</v>
       </c>
       <c r="R183">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S183">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T183">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="U183">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="V183">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W183">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X183">
         <v>1.02</v>
       </c>
       <c r="Y183">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z183">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA183">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AB183">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AC183">
-        <v>2.27</v>
+        <v>2.46</v>
       </c>
       <c r="AD183">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AE183">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AF183">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AG183">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH183" t="inlineStr">
         <is>
@@ -30208,10 +30208,10 @@
         </is>
       </c>
       <c r="AJ183">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK183">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL183">
         <v>0</v>
@@ -30307,7 +30307,7 @@
         <v>4.1</v>
       </c>
       <c r="P184">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="Q184">
         <v>1.98</v>
@@ -30337,7 +30337,7 @@
         <v>1.13</v>
       </c>
       <c r="Z184">
-        <v>4.13</v>
+        <v>3.13</v>
       </c>
       <c r="AA184">
         <v>1.66</v>
@@ -30349,7 +30349,7 @@
         <v>2.52</v>
       </c>
       <c r="AD184">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE184">
         <v>1.12</v>
@@ -30464,7 +30464,7 @@
         </is>
       </c>
       <c r="N185">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O185">
         <v>4</v>
@@ -30503,7 +30503,7 @@
         <v>4.15</v>
       </c>
       <c r="AA185">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB185">
         <v>2.15</v>
@@ -30636,55 +30636,55 @@
         <v>3.02</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R186">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S186">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T186">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U186">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V186">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W186">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y186">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z186">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA186">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB186">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC186">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD186">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE186">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF186">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG186">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH186" t="inlineStr">
         <is>
@@ -30697,10 +30697,10 @@
         </is>
       </c>
       <c r="AJ186">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK186">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL186">
         <v>0</v>
@@ -31122,7 +31122,7 @@
         <v>3.25</v>
       </c>
       <c r="P189">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q189">
         <v>2.47</v>
@@ -31140,7 +31140,7 @@
         <v>2.85</v>
       </c>
       <c r="V189">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W189">
         <v>1.08</v>
@@ -31173,7 +31173,7 @@
         <v>1.77</v>
       </c>
       <c r="AG189">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>2.9</v>
       </c>
       <c r="U190">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="V190">
         <v>1.33</v>
@@ -31318,10 +31318,10 @@
         <v>3.2</v>
       </c>
       <c r="AA190">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB190">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC190">
         <v>3.6</v>
@@ -31442,7 +31442,7 @@
         </is>
       </c>
       <c r="N191">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="O191">
         <v>3.25</v>
@@ -31487,7 +31487,7 @@
         <v>1.65</v>
       </c>
       <c r="AC191">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="AD191">
         <v>1.19</v>
@@ -31736,12 +31736,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="G193">
@@ -31768,43 +31768,43 @@
         </is>
       </c>
       <c r="N193">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O193">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P193">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="Q193">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="R193">
         <v>2.2</v>
       </c>
       <c r="S193">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T193">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="U193">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="V193">
         <v>1.47</v>
       </c>
       <c r="W193">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X193">
         <v>1.03</v>
       </c>
       <c r="Y193">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z193">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA193">
         <v>1.73</v>
@@ -31816,16 +31816,16 @@
         <v>2.7</v>
       </c>
       <c r="AD193">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE193">
         <v>1.13</v>
       </c>
       <c r="AF193">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG193">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH193" t="inlineStr">
         <is>
@@ -31838,10 +31838,10 @@
         </is>
       </c>
       <c r="AJ193">
-        <v>1.16</v>
+        <v>1.37</v>
       </c>
       <c r="AK193">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AL193">
         <v>0</v>
@@ -31899,12 +31899,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G194">
@@ -31931,64 +31931,64 @@
         </is>
       </c>
       <c r="N194">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="O194">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P194">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="Q194">
-        <v>2.14</v>
+        <v>2.76</v>
       </c>
       <c r="R194">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="S194">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T194">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="U194">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="V194">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W194">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X194">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y194">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="Z194">
-        <v>4.45</v>
+        <v>2.79</v>
       </c>
       <c r="AA194">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AB194">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC194">
-        <v>2.52</v>
+        <v>3.85</v>
       </c>
       <c r="AD194">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AE194">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AF194">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AG194">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
@@ -32001,10 +32001,10 @@
         </is>
       </c>
       <c r="AJ194">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AK194">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AL194">
         <v>0</v>
@@ -32062,12 +32062,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G195">
@@ -32094,64 +32094,64 @@
         </is>
       </c>
       <c r="N195">
-        <v>1.99</v>
+        <v>1.7</v>
       </c>
       <c r="O195">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="P195">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="Q195">
-        <v>2.76</v>
+        <v>2.14</v>
       </c>
       <c r="R195">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="S195">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="T195">
-        <v>2.51</v>
+        <v>3.6</v>
       </c>
       <c r="U195">
-        <v>3.2</v>
+        <v>2.19</v>
       </c>
       <c r="V195">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="W195">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X195">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y195">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z195">
-        <v>2.79</v>
+        <v>4.45</v>
       </c>
       <c r="AA195">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AB195">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AC195">
-        <v>3.82</v>
+        <v>2.53</v>
       </c>
       <c r="AD195">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AE195">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="AF195">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG195">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH195" t="inlineStr">
         <is>
@@ -32164,10 +32164,10 @@
         </is>
       </c>
       <c r="AJ195">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AK195">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AL195">
         <v>0</v>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G196">
@@ -32257,43 +32257,43 @@
         </is>
       </c>
       <c r="N196">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O196">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P196">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
       <c r="Q196">
-        <v>2.9</v>
+        <v>2.28</v>
       </c>
       <c r="R196">
         <v>2.2</v>
       </c>
       <c r="S196">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T196">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U196">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="V196">
         <v>1.47</v>
       </c>
       <c r="W196">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X196">
         <v>1.03</v>
       </c>
       <c r="Y196">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z196">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA196">
         <v>1.73</v>
@@ -32305,16 +32305,16 @@
         <v>2.7</v>
       </c>
       <c r="AD196">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE196">
         <v>1.13</v>
       </c>
       <c r="AF196">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG196">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH196" t="inlineStr">
         <is>
@@ -32327,10 +32327,10 @@
         </is>
       </c>
       <c r="AJ196">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="AK196">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="AL196">
         <v>0</v>
@@ -32456,7 +32456,7 @@
         <v>1.15</v>
       </c>
       <c r="Z197">
-        <v>4.67</v>
+        <v>4.75</v>
       </c>
       <c r="AA197">
         <v>1.55</v>
@@ -32628,7 +32628,7 @@
         <v>2.1</v>
       </c>
       <c r="AC198">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AD198">
         <v>1.4</v>
@@ -32752,7 +32752,7 @@
         <v>3.3</v>
       </c>
       <c r="P199">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="Q199">
         <v>3.06</v>
@@ -32764,7 +32764,7 @@
         <v>1.33</v>
       </c>
       <c r="T199">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="U199">
         <v>2.53</v>
@@ -32782,7 +32782,7 @@
         <v>1.22</v>
       </c>
       <c r="Z199">
-        <v>3.98</v>
+        <v>4.02</v>
       </c>
       <c r="AA199">
         <v>1.8</v>
@@ -32927,10 +32927,10 @@
         <v>1.36</v>
       </c>
       <c r="T200">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="U200">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="V200">
         <v>1.35</v>
@@ -32963,7 +32963,7 @@
         <v>1.05</v>
       </c>
       <c r="AF200">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG200">
         <v>1.91</v>
@@ -33084,7 +33084,7 @@
         <v>2.99</v>
       </c>
       <c r="R201">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="S201">
         <v>1.3</v>
@@ -33401,7 +33401,7 @@
         <v>2.25</v>
       </c>
       <c r="O203">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P203">
         <v>2.75</v>
@@ -33887,13 +33887,13 @@
         </is>
       </c>
       <c r="N206">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="O206">
         <v>3.5</v>
       </c>
       <c r="P206">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q206">
         <v>3.6</v>
@@ -33908,7 +33908,7 @@
         <v>3.4</v>
       </c>
       <c r="U206">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="V206">
         <v>1.53</v>
@@ -33932,7 +33932,7 @@
         <v>2.3</v>
       </c>
       <c r="AC206">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="AD206">
         <v>1.45</v>
@@ -34225,7 +34225,7 @@
         <v>2.93</v>
       </c>
       <c r="R208">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S208">
         <v>1.36</v>
@@ -34270,7 +34270,7 @@
         <v>1.74</v>
       </c>
       <c r="AG208">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH208" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>2.02</v>
       </c>
       <c r="AB209">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC209">
         <v>3.28</v>
@@ -34539,10 +34539,10 @@
         </is>
       </c>
       <c r="N210">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="O210">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P210">
         <v>3.6</v>
@@ -34670,12 +34670,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G211">
@@ -34702,64 +34702,64 @@
         </is>
       </c>
       <c r="N211">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="O211">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="P211">
-        <v>9.25</v>
+        <v>4.1</v>
       </c>
       <c r="Q211">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="R211">
-        <v>2.84</v>
+        <v>2.51</v>
       </c>
       <c r="S211">
         <v>1.2</v>
       </c>
       <c r="T211">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="U211">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V211">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W211">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X211">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y211">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z211">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AA211">
         <v>1.44</v>
       </c>
       <c r="AB211">
-        <v>2.88</v>
+        <v>2.51</v>
       </c>
       <c r="AC211">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AD211">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AE211">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF211">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AG211">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="AH211" t="inlineStr">
         <is>
@@ -34772,10 +34772,10 @@
         </is>
       </c>
       <c r="AJ211">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
  